--- a/pesm-pantanal-norte/dados/Matriz_SWOT_PESM_Pantanal_Norte.xlsx
+++ b/pesm-pantanal-norte/dados/Matriz_SWOT_PESM_Pantanal_Norte.xlsx
@@ -74,6 +74,18 @@
         </r>
       </text>
     </comment>
+    <comment ref="G8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Variação 2019–2024 (efetivo em 31/12). Fonte: d1_agropecuaria.csv (IBGE/PPM).</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="G11" authorId="0">
       <text>
         <r>
@@ -122,12 +134,36 @@
         </r>
       </text>
     </comment>
+    <comment ref="I7" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">MT = Σ valor da produção das lavouras ÷ Σ área colhida dos 141 municípios, 2024 (IBGE/PAM via d1_agropecuaria.csv).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">MT: 31.654.882 cab. (2019) → 32.853.368 cab. (2024) = +3,79%.</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="319">
   <si>
     <t xml:space="preserve">MATRIZ SWOT DO PERFIL ECONÔMICO-PRODUTIVO SETORIAL MUNICIPAL (PESM) — PANTANAL NORTE</t>
   </si>
@@ -576,61 +612,118 @@
     <t xml:space="preserve">O VAB setorial de 2022–2023 já foi divulgado pelo IBGE (dez/2025), mas não estava acessível no ambiente em que esta planilha foi preenchida. Os QLs e o EST-02 usam 2021 e devem ser atualizados pela Tabela 5938 do SIDRA (variáveis de VAB, anos 2022–2023). O PIB per capita (EST-01) já está em 2023.</t>
   </si>
   <si>
-    <t xml:space="preserve">PENDENTES (11 indicadores)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGR-02, AGR-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IBGE – PAM, SIDRA Tabela 5457 (valor da produção e área colhida por produto)</t>
+    <t xml:space="preserve">PENDENTES (9 indicadores)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGR-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBGE – PAM, SIDRA Tabela 5457 (valor da produção por produto). A base tratada d1_agropecuaria.csv traz só a diversificação do VBP entre lavoura, pecuária, extrativismo e pesca, que não mede a mesma coisa; por isso o indicador segue em branco.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGR-02, AGR-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preenchidos em 25/09/2026 (ver bloco "BASES TRATADAS" abaixo).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGR-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBGE – Censo Agropecuário 2017 (orientação técnica recebida)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IND-02, IND-03, CS-02, EST-03, EST-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAIS/MTE – vínculos e remuneração por seção CNAE (PDET ou Base dos Dados)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBGE – CEMPRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EST-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siconfi/STN – DCA Anexo I-C (receitas próprias e receita corrente)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RODADA DE 25/09/2026 — FATORES EXTERNOS (O-A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OP-01 a AM-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notas 0–3 atribuídas a partir de pesquisa web-based (evidências registradas na coluna E da aba 'Fatores Externos (O-A)'). Principais fontes: IBGE/PPM 2023 (rebanho de MT e Cáceres); Embrapa Pantanal, Comunicado Técnico 122; Corpo de Bombeiros-MT e INPE (área queimada 2024); Rumo/BNDES (Ferrovia Estadual); Portos e Navios e Gov. MT (Porto de Cáceres); NovaCana (Cooperb); EC 132/2023, LC 214/2025; IBGE/REGIC 2018.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notas preliminares de uma única rodada. Seguir o PASSO 3: revisar por consenso de dois pesquisadores e confrontar com a pesquisa de campo antes do Relatório Parcial.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicadores internos pendentes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Os 9 indicadores pendentes (linhas 11–16 acima) continuam em branco. Parte deles está em bases tratadas do catálogo que ainda não foram enviadas: d1_emprego_rais.csv (IND-02, IND-03, CS-02, EST-04), d1_pib_vab.csv (EST-03, via vinculos_31dez), d1_empresas.csv (CS-03) e d6_financas.csv (EST-05). AGR-04 (Censo Agro 2017) não consta do catálogo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RODADA DE 25/09/2026 — BASES TRATADAS (CATALOGO_BASES_TRATADAS, dimensão D1_PESM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGR-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d1_agropecuaria.csv (IBGE – PAM): pam_valor_producao_brl (R$ mil) e pam_area_colhida_ha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor da produção das lavouras × 1.000 ÷ área colhida (R$/ha). Ref. MT = soma dos 141 municípios = R$ 5.602,90/ha.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Critério Razão MT (±10%). Nota: municípios pequenos com pouca área colhida (ex.: Barão de Melgaço, 354 ha) têm valor/ha alto e instável; conferir a composição das lavouras.</t>
   </si>
   <si>
     <t xml:space="preserve">AGR-03</t>
   </si>
   <si>
-    <t xml:space="preserve">IBGE – PPM, SIDRA Tabela 3939 (efetivo bovino)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGR-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IBGE – Censo Agropecuário 2017 (orientação técnica recebida)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IND-02, IND-03, CS-02, EST-03, EST-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAIS/MTE – vínculos e remuneração por seção CNAE (PDET ou Base dos Dados)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IBGE – CEMPRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EST-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siconfi/STN – DCA Anexo I-C (receitas próprias e receita corrente)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RODADA DE 25/09/2026 — FATORES EXTERNOS (O-A)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OP-01 a AM-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notas 0–3 atribuídas a partir de pesquisa web-based (evidências registradas na coluna E da aba 'Fatores Externos (O-A)'). Principais fontes: IBGE/PPM 2023 (rebanho de MT e Cáceres); Embrapa Pantanal, Comunicado Técnico 122; Corpo de Bombeiros-MT e INPE (área queimada 2024); Rumo/BNDES (Ferrovia Estadual); Portos e Navios e Gov. MT (Porto de Cáceres); NovaCana (Cooperb); EC 132/2023, LC 214/2025; IBGE/REGIC 2018.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notas preliminares de uma única rodada. Seguir o PASSO 3: revisar por consenso de dois pesquisadores e confrontar com a pesquisa de campo antes do Relatório Parcial.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indicadores internos pendentes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Os 11 indicadores pendentes (linhas 11–16 acima) continuam em branco: as bases oficiais (API SIDRA/IBGE, IBGE Cidades, Tesouro/Siconfi) não estavam acessíveis no ambiente desta rodada e a busca web não trouxe valores municipais confiáveis. Pela regra 'DADO AUSENTE', ficam fora dos quadrantes até serem baixados das fontes indicadas.</t>
+    <t xml:space="preserve">2019–2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d1_agropecuaria.csv (IBGE – PPM): rebanho_bovino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Efetivo 2024 ÷ efetivo 2019 − 1) × 100. Ref. MT = +3,79% (31,65 → 32,85 milhões de cabeças).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total MT 2024 confere com o divulgado pelo IBGE (32,9 milhões). Critério Dif. MT (±2 p.p.).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">painel_pantanal_norte.csv: pib ÷ populacao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conferência da planilha: pib (R$ mil) ÷ população reproduz os 13 valores já preenchidos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sem alteração.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Séries históricas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2000–2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">painel_pantanal_norte.csv, painel_municipios_mt.csv, d1_agropecuaria.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usadas nos gráficos de evolução da página (PIB per capita relativo a MT, composição do VAB, rebanho, valor/ha das lavouras, crédito rural, desmatamento).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O VAB setorial das bases vai até 2021 e não inclui a administração pública; o PIB vai até 2023.</t>
   </si>
   <si>
     <t xml:space="preserve">PARÂMETROS</t>
@@ -714,9 +807,6 @@
     <t xml:space="preserve">Absoluto</t>
   </si>
   <si>
-    <t xml:space="preserve">AGR-02</t>
-  </si>
-  <si>
     <t xml:space="preserve">Valor da produção das lavouras por área colhida</t>
   </si>
   <si>
@@ -745,9 +835,6 @@
   </si>
   <si>
     <t xml:space="preserve">IBGE – Censo Agropecuário 2017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGR-05</t>
   </si>
   <si>
     <t xml:space="preserve">Diversificação agrícola (1 − HHI do valor da produção das lavouras)</t>
@@ -1382,7 +1469,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="93">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1633,6 +1720,10 @@
     </xf>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="173" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -2233,7 +2324,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="B2" s="1" t="n">
         <f aca="false">IFERROR(MATCH($B$1,'Indicadores (F-W)'!$A$4:$AM$4,0),"")</f>
@@ -2242,7 +2333,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="B3" s="1" t="n">
         <f aca="false">IFERROR(MATCH($B$1,'Fatores Externos (O-A)'!$A$4:$R$4,0),"")</f>
@@ -2254,7 +2345,7 @@
         <v>59</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>102</v>
@@ -2263,16 +2354,16 @@
         <v>31</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>59</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>67</v>
@@ -2281,16 +2372,16 @@
         <v>33</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2306,7 +2397,7 @@
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A6:$AM6,1,$B$2+1))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="D6" s="86" t="n">
+      <c r="D6" s="87" t="n">
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A6:$AM6,1,$B$2))</f>
         <v>0.3713</v>
       </c>
@@ -2362,11 +2453,11 @@
       </c>
       <c r="C7" s="1" t="str">
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A7:$AM7,1,$B$2+1))</f>
-        <v/>
-      </c>
-      <c r="D7" s="87" t="n">
+        <v>Neutro</v>
+      </c>
+      <c r="D7" s="88" t="n">
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A7:$AM7,1,$B$2))</f>
-        <v>0</v>
+        <v>5729.32</v>
       </c>
       <c r="E7" s="1" t="str">
         <f aca="false">IF(C7="Força",COUNTIF(C$6:C7,"Força"),"")</f>
@@ -2420,15 +2511,15 @@
       </c>
       <c r="C8" s="1" t="str">
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A8:$AM8,1,$B$2+1))</f>
-        <v/>
-      </c>
-      <c r="D8" s="87" t="n">
+        <v>Força</v>
+      </c>
+      <c r="D8" s="88" t="n">
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A8:$AM8,1,$B$2))</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="1" t="str">
+        <v>22.65</v>
+      </c>
+      <c r="E8" s="1" t="n">
         <f aca="false">IF(C8="Força",COUNTIF(C$6:C8,"Força"),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F8" s="1" t="str">
         <f aca="false">IF(C8="Fraqueza",COUNTIF(C$6:C8,"Fraqueza"),"")</f>
@@ -2480,7 +2571,7 @@
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A9:$AM9,1,$B$2+1))</f>
         <v/>
       </c>
-      <c r="D9" s="87" t="n">
+      <c r="D9" s="88" t="n">
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A9:$AM9,1,$B$2))</f>
         <v>0</v>
       </c>
@@ -2538,7 +2629,7 @@
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A10:$AM10,1,$B$2+1))</f>
         <v/>
       </c>
-      <c r="D10" s="87" t="n">
+      <c r="D10" s="88" t="n">
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A10:$AM10,1,$B$2))</f>
         <v>0</v>
       </c>
@@ -2596,7 +2687,7 @@
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A11:$AM11,1,$B$2+1))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="D11" s="86" t="n">
+      <c r="D11" s="87" t="n">
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A11:$AM11,1,$B$2))</f>
         <v>0.6374</v>
       </c>
@@ -2654,7 +2745,7 @@
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A12:$AM12,1,$B$2+1))</f>
         <v/>
       </c>
-      <c r="D12" s="87" t="n">
+      <c r="D12" s="88" t="n">
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A12:$AM12,1,$B$2))</f>
         <v>0</v>
       </c>
@@ -2712,7 +2803,7 @@
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A13:$AM13,1,$B$2+1))</f>
         <v/>
       </c>
-      <c r="D13" s="87" t="n">
+      <c r="D13" s="88" t="n">
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A13:$AM13,1,$B$2))</f>
         <v>0</v>
       </c>
@@ -2770,13 +2861,13 @@
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A14:$AM14,1,$B$2+1))</f>
         <v>Força</v>
       </c>
-      <c r="D14" s="86" t="n">
+      <c r="D14" s="87" t="n">
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A14:$AM14,1,$B$2))</f>
         <v>1.3013</v>
       </c>
       <c r="E14" s="1" t="n">
         <f aca="false">IF(C14="Força",COUNTIF(C$6:C14,"Força"),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="1" t="str">
         <f aca="false">IF(C14="Fraqueza",COUNTIF(C$6:C14,"Fraqueza"),"")</f>
@@ -2828,7 +2919,7 @@
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A15:$AM15,1,$B$2+1))</f>
         <v/>
       </c>
-      <c r="D15" s="87" t="n">
+      <c r="D15" s="88" t="n">
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A15:$AM15,1,$B$2))</f>
         <v>0</v>
       </c>
@@ -2886,7 +2977,7 @@
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A16:$AM16,1,$B$2+1))</f>
         <v/>
       </c>
-      <c r="D16" s="87" t="n">
+      <c r="D16" s="88" t="n">
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A16:$AM16,1,$B$2))</f>
         <v>0</v>
       </c>
@@ -2944,7 +3035,7 @@
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A17:$AM17,1,$B$2+1))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="D17" s="88" t="n">
+      <c r="D17" s="89" t="n">
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A17:$AM17,1,$B$2))</f>
         <v>31174.15</v>
       </c>
@@ -2970,7 +3061,7 @@
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A18:$AM18,1,$B$2+1))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="D18" s="89" t="n">
+      <c r="D18" s="90" t="n">
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A18:$AM18,1,$B$2))</f>
         <v>30.82</v>
       </c>
@@ -2996,7 +3087,7 @@
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A19:$AM19,1,$B$2+1))</f>
         <v/>
       </c>
-      <c r="D19" s="87" t="n">
+      <c r="D19" s="88" t="n">
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A19:$AM19,1,$B$2))</f>
         <v>0</v>
       </c>
@@ -3022,7 +3113,7 @@
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A20:$AM20,1,$B$2+1))</f>
         <v/>
       </c>
-      <c r="D20" s="87" t="n">
+      <c r="D20" s="88" t="n">
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A20:$AM20,1,$B$2))</f>
         <v>0</v>
       </c>
@@ -3048,7 +3139,7 @@
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A21:$AM21,1,$B$2+1))</f>
         <v/>
       </c>
-      <c r="D21" s="87" t="n">
+      <c r="D21" s="88" t="n">
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A21:$AM21,1,$B$2))</f>
         <v>0</v>
       </c>
@@ -3093,19 +3184,19 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="90" t="s">
-        <v>287</v>
+      <c r="B1" s="91" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="91" t="str">
+      <c r="B3" s="92" t="str">
         <f aca="false">"Indicadores internos com dado: "&amp;(COUNTA(L6:L21)-COUNTBLANK(L6:L21))&amp;" de 16  |  Neutros: "&amp;COUNTIF(L6:L21,"Neutro")&amp;"  |  Fatores externos pontuados: "&amp;COUNT(S6:S16)&amp;" de 11"</f>
-        <v>Indicadores internos com dado: 5 de 16  |  Neutros: 1  |  Fatores externos pontuados: 11 de 11</v>
+        <v>Indicadores internos com dado: 7 de 16  |  Neutros: 1  |  Fatores externos pontuados: 11 de 11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3123,7 +3214,7 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="11" t="str">
         <f aca="false">"FORÇAS (S) — "&amp;COUNTIF($L$6:$L$21,"Força")&amp;" item(ns)"</f>
-        <v>FORÇAS (S) — 0 item(ns)</v>
+        <v>FORÇAS (S) — 2 item(ns)</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
@@ -3141,7 +3232,7 @@
         <f aca="false">'Indicadores (F-W)'!O6</f>
         <v>Neutro</v>
       </c>
-      <c r="M6" s="86" t="n">
+      <c r="M6" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!N6="","",'Indicadores (F-W)'!N6)</f>
         <v>0.9631</v>
       </c>
@@ -3207,15 +3298,15 @@
       </c>
       <c r="L7" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!O7</f>
-        <v/>
-      </c>
-      <c r="M7" s="1" t="str">
+        <v>Força</v>
+      </c>
+      <c r="M7" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!N7="","",'Indicadores (F-W)'!N7)</f>
-        <v/>
-      </c>
-      <c r="N7" s="1" t="str">
+        <v>19926.55</v>
+      </c>
+      <c r="N7" s="1" t="n">
         <f aca="false">IF(L7="Força",COUNTIF(L$6:L7,"Força"),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="O7" s="1" t="str">
         <f aca="false">IF(L7="Fraqueza",COUNTIF(L$6:L7,"Fraqueza"),"")</f>
@@ -3254,17 +3345,17 @@
       <c r="A8" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="16" t="str">
+      <c r="B8" s="16" t="n">
         <f aca="false">IF(C8="","",1)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="C8" s="17" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(1,$N$6:$N$21,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D8" s="18" t="str">
+        <v>[Agropecuária] AGR-02 – Valor da produção das lavouras por área colhida (R$/ha)</v>
+      </c>
+      <c r="D8" s="18" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(1,$N$6:$N$21,0)),"")</f>
-        <v/>
+        <v>19926.55</v>
       </c>
       <c r="F8" s="19" t="n">
         <f aca="false">IF(G8="","",1)</f>
@@ -3284,15 +3375,15 @@
       </c>
       <c r="L8" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!O8</f>
-        <v/>
-      </c>
-      <c r="M8" s="1" t="str">
+        <v>Força</v>
+      </c>
+      <c r="M8" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!N8="","",'Indicadores (F-W)'!N8)</f>
-        <v/>
-      </c>
-      <c r="N8" s="1" t="str">
+        <v>16.6</v>
+      </c>
+      <c r="N8" s="1" t="n">
         <f aca="false">IF(L8="Força",COUNTIF(L$6:L8,"Força"),"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O8" s="1" t="str">
         <f aca="false">IF(L8="Fraqueza",COUNTIF(L$6:L8,"Fraqueza"),"")</f>
@@ -3329,17 +3420,17 @@
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15"/>
-      <c r="B9" s="16" t="str">
+      <c r="B9" s="16" t="n">
         <f aca="false">IF(C9="","",2)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C9" s="17" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(2,$N$6:$N$21,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D9" s="18" t="str">
+        <v>[Agropecuária] AGR-03 – Variação do efetivo bovino em 5 anos (%)</v>
+      </c>
+      <c r="D9" s="18" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(2,$N$6:$N$21,0)),"")</f>
-        <v/>
+        <v>16.6</v>
       </c>
       <c r="F9" s="19" t="n">
         <f aca="false">IF(G9="","",2)</f>
@@ -3511,7 +3602,7 @@
         <f aca="false">'Indicadores (F-W)'!O11</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M11" s="86" t="n">
+      <c r="M11" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!N11="","",'Indicadores (F-W)'!N11)</f>
         <v>0.169</v>
       </c>
@@ -3736,7 +3827,7 @@
         <f aca="false">'Indicadores (F-W)'!O14</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M14" s="86" t="n">
+      <c r="M14" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!N14="","",'Indicadores (F-W)'!N14)</f>
         <v>0.4274</v>
       </c>
@@ -3961,7 +4052,7 @@
         <f aca="false">'Indicadores (F-W)'!O17</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M17" s="88" t="n">
+      <c r="M17" s="89" t="n">
         <f aca="false">IF('Indicadores (F-W)'!N17="","",'Indicadores (F-W)'!N17)</f>
         <v>19806.58</v>
       </c>
@@ -4008,7 +4099,7 @@
         <f aca="false">'Indicadores (F-W)'!O18</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M18" s="89" t="n">
+      <c r="M18" s="90" t="n">
         <f aca="false">IF('Indicadores (F-W)'!N18="","",'Indicadores (F-W)'!N18)</f>
         <v>45.95</v>
       </c>
@@ -4492,7 +4583,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -4537,19 +4628,19 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="90" t="s">
-        <v>290</v>
+      <c r="B1" s="91" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="91" t="str">
+      <c r="B3" s="92" t="str">
         <f aca="false">"Indicadores internos com dado: "&amp;(COUNTA(L6:L21)-COUNTBLANK(L6:L21))&amp;" de 16  |  Neutros: "&amp;COUNTIF(L6:L21,"Neutro")&amp;"  |  Fatores externos pontuados: "&amp;COUNT(S6:S16)&amp;" de 11"</f>
-        <v>Indicadores internos com dado: 5 de 16  |  Neutros: 0  |  Fatores externos pontuados: 11 de 11</v>
+        <v>Indicadores internos com dado: 7 de 16  |  Neutros: 1  |  Fatores externos pontuados: 11 de 11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4567,7 +4658,7 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="11" t="str">
         <f aca="false">"FORÇAS (S) — "&amp;COUNTIF($L$6:$L$21,"Força")&amp;" item(ns)"</f>
-        <v>FORÇAS (S) — 1 item(ns)</v>
+        <v>FORÇAS (S) — 2 item(ns)</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
@@ -4585,7 +4676,7 @@
         <f aca="false">'Indicadores (F-W)'!Q6</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M6" s="86" t="n">
+      <c r="M6" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!P6="","",'Indicadores (F-W)'!P6)</f>
         <v>0.3713</v>
       </c>
@@ -4651,11 +4742,11 @@
       </c>
       <c r="L7" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!Q7</f>
-        <v/>
-      </c>
-      <c r="M7" s="1" t="str">
+        <v>Neutro</v>
+      </c>
+      <c r="M7" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!P7="","",'Indicadores (F-W)'!P7)</f>
-        <v/>
+        <v>5729.32</v>
       </c>
       <c r="N7" s="1" t="str">
         <f aca="false">IF(L7="Força",COUNTIF(L$6:L7,"Força"),"")</f>
@@ -4704,11 +4795,11 @@
       </c>
       <c r="C8" s="17" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(1,$N$6:$N$21,0)),"")</f>
-        <v>[Comércio e Serviços] CS-01 – Quociente locacional do VAB de serviços, exceto adm. pública (base MT) (índice)</v>
+        <v>[Agropecuária] AGR-03 – Variação do efetivo bovino em 5 anos (%)</v>
       </c>
       <c r="D8" s="18" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(1,$N$6:$N$21,0)),"")</f>
-        <v>1.3013</v>
+        <v>22.65</v>
       </c>
       <c r="F8" s="19" t="n">
         <f aca="false">IF(G8="","",1)</f>
@@ -4728,15 +4819,15 @@
       </c>
       <c r="L8" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!Q8</f>
-        <v/>
-      </c>
-      <c r="M8" s="1" t="str">
+        <v>Força</v>
+      </c>
+      <c r="M8" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!P8="","",'Indicadores (F-W)'!P8)</f>
-        <v/>
-      </c>
-      <c r="N8" s="1" t="str">
+        <v>22.65</v>
+      </c>
+      <c r="N8" s="1" t="n">
         <f aca="false">IF(L8="Força",COUNTIF(L$6:L8,"Força"),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="O8" s="1" t="str">
         <f aca="false">IF(L8="Fraqueza",COUNTIF(L$6:L8,"Fraqueza"),"")</f>
@@ -4773,17 +4864,17 @@
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15"/>
-      <c r="B9" s="16" t="str">
+      <c r="B9" s="16" t="n">
         <f aca="false">IF(C9="","",2)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C9" s="17" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(2,$N$6:$N$21,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D9" s="18" t="str">
+        <v>[Comércio e Serviços] CS-01 – Quociente locacional do VAB de serviços, exceto adm. pública (base MT) (índice)</v>
+      </c>
+      <c r="D9" s="18" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(2,$N$6:$N$21,0)),"")</f>
-        <v/>
+        <v>1.3013</v>
       </c>
       <c r="F9" s="19" t="n">
         <f aca="false">IF(G9="","",2)</f>
@@ -4955,7 +5046,7 @@
         <f aca="false">'Indicadores (F-W)'!Q11</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M11" s="86" t="n">
+      <c r="M11" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!P11="","",'Indicadores (F-W)'!P11)</f>
         <v>0.6374</v>
       </c>
@@ -5180,13 +5271,13 @@
         <f aca="false">'Indicadores (F-W)'!Q14</f>
         <v>Força</v>
       </c>
-      <c r="M14" s="86" t="n">
+      <c r="M14" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!P14="","",'Indicadores (F-W)'!P14)</f>
         <v>1.3013</v>
       </c>
       <c r="N14" s="1" t="n">
         <f aca="false">IF(L14="Força",COUNTIF(L$6:L14,"Força"),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O14" s="1" t="str">
         <f aca="false">IF(L14="Fraqueza",COUNTIF(L$6:L14,"Fraqueza"),"")</f>
@@ -5405,7 +5496,7 @@
         <f aca="false">'Indicadores (F-W)'!Q17</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M17" s="88" t="n">
+      <c r="M17" s="89" t="n">
         <f aca="false">IF('Indicadores (F-W)'!P17="","",'Indicadores (F-W)'!P17)</f>
         <v>31174.15</v>
       </c>
@@ -5452,7 +5543,7 @@
         <f aca="false">'Indicadores (F-W)'!Q18</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M18" s="89" t="n">
+      <c r="M18" s="90" t="n">
         <f aca="false">IF('Indicadores (F-W)'!P18="","",'Indicadores (F-W)'!P18)</f>
         <v>30.82</v>
       </c>
@@ -5936,7 +6027,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -5981,19 +6072,19 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="90" t="s">
-        <v>291</v>
+      <c r="B1" s="91" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="91" t="str">
+      <c r="B3" s="92" t="str">
         <f aca="false">"Indicadores internos com dado: "&amp;(COUNTA(L6:L21)-COUNTBLANK(L6:L21))&amp;" de 16  |  Neutros: "&amp;COUNTIF(L6:L21,"Neutro")&amp;"  |  Fatores externos pontuados: "&amp;COUNT(S6:S16)&amp;" de 11"</f>
-        <v>Indicadores internos com dado: 5 de 16  |  Neutros: 0  |  Fatores externos pontuados: 11 de 11</v>
+        <v>Indicadores internos com dado: 7 de 16  |  Neutros: 1  |  Fatores externos pontuados: 11 de 11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6011,7 +6102,7 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="11" t="str">
         <f aca="false">"FORÇAS (S) — "&amp;COUNTIF($L$6:$L$21,"Força")&amp;" item(ns)"</f>
-        <v>FORÇAS (S) — 1 item(ns)</v>
+        <v>FORÇAS (S) — 2 item(ns)</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
@@ -6029,7 +6120,7 @@
         <f aca="false">'Indicadores (F-W)'!S6</f>
         <v>Força</v>
       </c>
-      <c r="M6" s="86" t="n">
+      <c r="M6" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!R6="","",'Indicadores (F-W)'!R6)</f>
         <v>1.2022</v>
       </c>
@@ -6095,15 +6186,15 @@
       </c>
       <c r="L7" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!S7</f>
-        <v/>
-      </c>
-      <c r="M7" s="1" t="str">
+        <v>Força</v>
+      </c>
+      <c r="M7" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!R7="","",'Indicadores (F-W)'!R7)</f>
-        <v/>
-      </c>
-      <c r="N7" s="1" t="str">
+        <v>10834.24</v>
+      </c>
+      <c r="N7" s="1" t="n">
         <f aca="false">IF(L7="Força",COUNTIF(L$6:L7,"Força"),"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O7" s="1" t="str">
         <f aca="false">IF(L7="Fraqueza",COUNTIF(L$6:L7,"Fraqueza"),"")</f>
@@ -6172,11 +6263,11 @@
       </c>
       <c r="L8" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!S8</f>
-        <v/>
-      </c>
-      <c r="M8" s="1" t="str">
+        <v>Neutro</v>
+      </c>
+      <c r="M8" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!R8="","",'Indicadores (F-W)'!R8)</f>
-        <v/>
+        <v>2.73</v>
       </c>
       <c r="N8" s="1" t="str">
         <f aca="false">IF(L8="Força",COUNTIF(L$6:L8,"Força"),"")</f>
@@ -6217,17 +6308,17 @@
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15"/>
-      <c r="B9" s="16" t="str">
+      <c r="B9" s="16" t="n">
         <f aca="false">IF(C9="","",2)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C9" s="17" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(2,$N$6:$N$21,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D9" s="18" t="str">
+        <v>[Agropecuária] AGR-02 – Valor da produção das lavouras por área colhida (R$/ha)</v>
+      </c>
+      <c r="D9" s="18" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(2,$N$6:$N$21,0)),"")</f>
-        <v/>
+        <v>10834.24</v>
       </c>
       <c r="F9" s="19" t="n">
         <f aca="false">IF(G9="","",2)</f>
@@ -6399,7 +6490,7 @@
         <f aca="false">'Indicadores (F-W)'!S11</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M11" s="86" t="n">
+      <c r="M11" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!R11="","",'Indicadores (F-W)'!R11)</f>
         <v>0.4717</v>
       </c>
@@ -6624,7 +6715,7 @@
         <f aca="false">'Indicadores (F-W)'!S14</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M14" s="86" t="n">
+      <c r="M14" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!R14="","",'Indicadores (F-W)'!R14)</f>
         <v>0.5029</v>
       </c>
@@ -6849,7 +6940,7 @@
         <f aca="false">'Indicadores (F-W)'!S17</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M17" s="88" t="n">
+      <c r="M17" s="89" t="n">
         <f aca="false">IF('Indicadores (F-W)'!R17="","",'Indicadores (F-W)'!R17)</f>
         <v>27693.14</v>
       </c>
@@ -6896,7 +6987,7 @@
         <f aca="false">'Indicadores (F-W)'!S18</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M18" s="89" t="n">
+      <c r="M18" s="90" t="n">
         <f aca="false">IF('Indicadores (F-W)'!R18="","",'Indicadores (F-W)'!R18)</f>
         <v>29.61</v>
       </c>
@@ -7380,7 +7471,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -7425,19 +7516,19 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="90" t="s">
-        <v>292</v>
+      <c r="B1" s="91" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="91" t="str">
+      <c r="B3" s="92" t="str">
         <f aca="false">"Indicadores internos com dado: "&amp;(COUNTA(L6:L21)-COUNTBLANK(L6:L21))&amp;" de 16  |  Neutros: "&amp;COUNTIF(L6:L21,"Neutro")&amp;"  |  Fatores externos pontuados: "&amp;COUNT(S6:S16)&amp;" de 11"</f>
-        <v>Indicadores internos com dado: 5 de 16  |  Neutros: 0  |  Fatores externos pontuados: 11 de 11</v>
+        <v>Indicadores internos com dado: 7 de 16  |  Neutros: 1  |  Fatores externos pontuados: 11 de 11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7455,7 +7546,7 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="11" t="str">
         <f aca="false">"FORÇAS (S) — "&amp;COUNTIF($L$6:$L$21,"Força")&amp;" item(ns)"</f>
-        <v>FORÇAS (S) — 1 item(ns)</v>
+        <v>FORÇAS (S) — 2 item(ns)</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
@@ -7473,7 +7564,7 @@
         <f aca="false">'Indicadores (F-W)'!U6</f>
         <v>Força</v>
       </c>
-      <c r="M6" s="86" t="n">
+      <c r="M6" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!T6="","",'Indicadores (F-W)'!T6)</f>
         <v>1.3866</v>
       </c>
@@ -7539,15 +7630,15 @@
       </c>
       <c r="L7" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!U7</f>
-        <v/>
-      </c>
-      <c r="M7" s="1" t="str">
+        <v>Força</v>
+      </c>
+      <c r="M7" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!T7="","",'Indicadores (F-W)'!T7)</f>
-        <v/>
-      </c>
-      <c r="N7" s="1" t="str">
+        <v>10020.12</v>
+      </c>
+      <c r="N7" s="1" t="n">
         <f aca="false">IF(L7="Força",COUNTIF(L$6:L7,"Força"),"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O7" s="1" t="str">
         <f aca="false">IF(L7="Fraqueza",COUNTIF(L$6:L7,"Fraqueza"),"")</f>
@@ -7616,11 +7707,11 @@
       </c>
       <c r="L8" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!U8</f>
-        <v/>
-      </c>
-      <c r="M8" s="1" t="str">
+        <v>Neutro</v>
+      </c>
+      <c r="M8" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!T8="","",'Indicadores (F-W)'!T8)</f>
-        <v/>
+        <v>2.27</v>
       </c>
       <c r="N8" s="1" t="str">
         <f aca="false">IF(L8="Força",COUNTIF(L$6:L8,"Força"),"")</f>
@@ -7661,17 +7752,17 @@
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15"/>
-      <c r="B9" s="16" t="str">
+      <c r="B9" s="16" t="n">
         <f aca="false">IF(C9="","",2)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C9" s="17" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(2,$N$6:$N$21,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D9" s="18" t="str">
+        <v>[Agropecuária] AGR-02 – Valor da produção das lavouras por área colhida (R$/ha)</v>
+      </c>
+      <c r="D9" s="18" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(2,$N$6:$N$21,0)),"")</f>
-        <v/>
+        <v>10020.12</v>
       </c>
       <c r="F9" s="19" t="n">
         <f aca="false">IF(G9="","",2)</f>
@@ -7843,7 +7934,7 @@
         <f aca="false">'Indicadores (F-W)'!U11</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M11" s="86" t="n">
+      <c r="M11" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!T11="","",'Indicadores (F-W)'!T11)</f>
         <v>0.2854</v>
       </c>
@@ -8068,7 +8159,7 @@
         <f aca="false">'Indicadores (F-W)'!U14</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M14" s="86" t="n">
+      <c r="M14" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!T14="","",'Indicadores (F-W)'!T14)</f>
         <v>0.4636</v>
       </c>
@@ -8293,7 +8384,7 @@
         <f aca="false">'Indicadores (F-W)'!U17</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M17" s="88" t="n">
+      <c r="M17" s="89" t="n">
         <f aca="false">IF('Indicadores (F-W)'!T17="","",'Indicadores (F-W)'!T17)</f>
         <v>39644.82</v>
       </c>
@@ -8340,7 +8431,7 @@
         <f aca="false">'Indicadores (F-W)'!U18</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M18" s="89" t="n">
+      <c r="M18" s="90" t="n">
         <f aca="false">IF('Indicadores (F-W)'!T18="","",'Indicadores (F-W)'!T18)</f>
         <v>26.83</v>
       </c>
@@ -8824,7 +8915,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -8869,19 +8960,19 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="90" t="s">
-        <v>293</v>
+      <c r="B1" s="91" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="91" t="str">
+      <c r="B3" s="92" t="str">
         <f aca="false">"Indicadores internos com dado: "&amp;(COUNTA(L6:L21)-COUNTBLANK(L6:L21))&amp;" de 16  |  Neutros: "&amp;COUNTIF(L6:L21,"Neutro")&amp;"  |  Fatores externos pontuados: "&amp;COUNT(S6:S16)&amp;" de 11"</f>
-        <v>Indicadores internos com dado: 5 de 16  |  Neutros: 0  |  Fatores externos pontuados: 11 de 11</v>
+        <v>Indicadores internos com dado: 7 de 16  |  Neutros: 1  |  Fatores externos pontuados: 11 de 11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8899,7 +8990,7 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="11" t="str">
         <f aca="false">"FORÇAS (S) — "&amp;COUNTIF($L$6:$L$21,"Força")&amp;" item(ns)"</f>
-        <v>FORÇAS (S) — 4 item(ns)</v>
+        <v>FORÇAS (S) — 5 item(ns)</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
@@ -8917,7 +9008,7 @@
         <f aca="false">'Indicadores (F-W)'!W6</f>
         <v>Força</v>
       </c>
-      <c r="M6" s="86" t="n">
+      <c r="M6" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!V6="","",'Indicadores (F-W)'!V6)</f>
         <v>1.6266</v>
       </c>
@@ -8983,11 +9074,11 @@
       </c>
       <c r="L7" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!W7</f>
-        <v/>
-      </c>
-      <c r="M7" s="1" t="str">
+        <v>Neutro</v>
+      </c>
+      <c r="M7" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!V7="","",'Indicadores (F-W)'!V7)</f>
-        <v/>
+        <v>5402.93</v>
       </c>
       <c r="N7" s="1" t="str">
         <f aca="false">IF(L7="Força",COUNTIF(L$6:L7,"Força"),"")</f>
@@ -9060,15 +9151,15 @@
       </c>
       <c r="L8" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!W8</f>
-        <v/>
-      </c>
-      <c r="M8" s="1" t="str">
+        <v>Força</v>
+      </c>
+      <c r="M8" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!V8="","",'Indicadores (F-W)'!V8)</f>
-        <v/>
-      </c>
-      <c r="N8" s="1" t="str">
+        <v>26.4</v>
+      </c>
+      <c r="N8" s="1" t="n">
         <f aca="false">IF(L8="Força",COUNTIF(L$6:L8,"Força"),"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O8" s="1" t="str">
         <f aca="false">IF(L8="Fraqueza",COUNTIF(L$6:L8,"Fraqueza"),"")</f>
@@ -9111,11 +9202,11 @@
       </c>
       <c r="C9" s="17" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(2,$N$6:$N$21,0)),"")</f>
-        <v>[Indústria] IND-01 – Quociente locacional do VAB industrial (base MT) (índice)</v>
+        <v>[Agropecuária] AGR-03 – Variação do efetivo bovino em 5 anos (%)</v>
       </c>
       <c r="D9" s="18" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(2,$N$6:$N$21,0)),"")</f>
-        <v>1.2891</v>
+        <v>26.4</v>
       </c>
       <c r="F9" s="19" t="str">
         <f aca="false">IF(G9="","",2)</f>
@@ -9186,11 +9277,11 @@
       </c>
       <c r="C10" s="17" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(3,$N$6:$N$21,0)),"")</f>
-        <v>[Estrutura Econômica e Fiscal] EST-01 – PIB per capita (R$)</v>
+        <v>[Indústria] IND-01 – Quociente locacional do VAB industrial (base MT) (índice)</v>
       </c>
       <c r="D10" s="18" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(3,$N$6:$N$21,0)),"")</f>
-        <v>167482.75</v>
+        <v>1.2891</v>
       </c>
       <c r="F10" s="19" t="str">
         <f aca="false">IF(G10="","",3)</f>
@@ -9261,11 +9352,11 @@
       </c>
       <c r="C11" s="17" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(4,$N$6:$N$21,0)),"")</f>
-        <v>[Estrutura Econômica e Fiscal] EST-02 – Participação da administração pública no VAB total (%)</v>
+        <v>[Estrutura Econômica e Fiscal] EST-01 – PIB per capita (R$)</v>
       </c>
       <c r="D11" s="18" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(4,$N$6:$N$21,0)),"")</f>
-        <v>5.88</v>
+        <v>167482.75</v>
       </c>
       <c r="F11" s="19" t="str">
         <f aca="false">IF(G11="","",4)</f>
@@ -9287,13 +9378,13 @@
         <f aca="false">'Indicadores (F-W)'!W11</f>
         <v>Força</v>
       </c>
-      <c r="M11" s="86" t="n">
+      <c r="M11" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!V11="","",'Indicadores (F-W)'!V11)</f>
         <v>1.2891</v>
       </c>
       <c r="N11" s="1" t="n">
         <f aca="false">IF(L11="Força",COUNTIF(L$6:L11,"Força"),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O11" s="1" t="str">
         <f aca="false">IF(L11="Fraqueza",COUNTIF(L$6:L11,"Fraqueza"),"")</f>
@@ -9330,17 +9421,17 @@
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15"/>
-      <c r="B12" s="16" t="str">
+      <c r="B12" s="16" t="n">
         <f aca="false">IF(C12="","",5)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="C12" s="17" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(5,$N$6:$N$21,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D12" s="18" t="str">
+        <v>[Estrutura Econômica e Fiscal] EST-02 – Participação da administração pública no VAB total (%)</v>
+      </c>
+      <c r="D12" s="18" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(5,$N$6:$N$21,0)),"")</f>
-        <v/>
+        <v>5.88</v>
       </c>
       <c r="F12" s="19" t="str">
         <f aca="false">IF(G12="","",5)</f>
@@ -9512,7 +9603,7 @@
         <f aca="false">'Indicadores (F-W)'!W14</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M14" s="86" t="n">
+      <c r="M14" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!V14="","",'Indicadores (F-W)'!V14)</f>
         <v>0.3623</v>
       </c>
@@ -9737,13 +9828,13 @@
         <f aca="false">'Indicadores (F-W)'!W17</f>
         <v>Força</v>
       </c>
-      <c r="M17" s="88" t="n">
+      <c r="M17" s="89" t="n">
         <f aca="false">IF('Indicadores (F-W)'!V17="","",'Indicadores (F-W)'!V17)</f>
         <v>167482.75</v>
       </c>
       <c r="N17" s="1" t="n">
         <f aca="false">IF(L17="Força",COUNTIF(L$6:L17,"Força"),"")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O17" s="1" t="str">
         <f aca="false">IF(L17="Fraqueza",COUNTIF(L$6:L17,"Fraqueza"),"")</f>
@@ -9784,13 +9875,13 @@
         <f aca="false">'Indicadores (F-W)'!W18</f>
         <v>Força</v>
       </c>
-      <c r="M18" s="89" t="n">
+      <c r="M18" s="90" t="n">
         <f aca="false">IF('Indicadores (F-W)'!V18="","",'Indicadores (F-W)'!V18)</f>
         <v>5.88</v>
       </c>
       <c r="N18" s="1" t="n">
         <f aca="false">IF(L18="Força",COUNTIF(L$6:L18,"Força"),"")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O18" s="1" t="str">
         <f aca="false">IF(L18="Fraqueza",COUNTIF(L$6:L18,"Fraqueza"),"")</f>
@@ -10268,7 +10359,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -10313,19 +10404,19 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="90" t="s">
-        <v>294</v>
+      <c r="B1" s="91" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="91" t="str">
+      <c r="B3" s="92" t="str">
         <f aca="false">"Indicadores internos com dado: "&amp;(COUNTA(L6:L21)-COUNTBLANK(L6:L21))&amp;" de 16  |  Neutros: "&amp;COUNTIF(L6:L21,"Neutro")&amp;"  |  Fatores externos pontuados: "&amp;COUNT(S6:S16)&amp;" de 11"</f>
-        <v>Indicadores internos com dado: 5 de 16  |  Neutros: 1  |  Fatores externos pontuados: 11 de 11</v>
+        <v>Indicadores internos com dado: 7 de 16  |  Neutros: 3  |  Fatores externos pontuados: 11 de 11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10361,7 +10452,7 @@
         <f aca="false">'Indicadores (F-W)'!Y6</f>
         <v>Força</v>
       </c>
-      <c r="M6" s="86" t="n">
+      <c r="M6" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!X6="","",'Indicadores (F-W)'!X6)</f>
         <v>1.319</v>
       </c>
@@ -10427,11 +10518,11 @@
       </c>
       <c r="L7" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!Y7</f>
-        <v/>
-      </c>
-      <c r="M7" s="1" t="str">
+        <v>Neutro</v>
+      </c>
+      <c r="M7" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!X7="","",'Indicadores (F-W)'!X7)</f>
-        <v/>
+        <v>5889.67</v>
       </c>
       <c r="N7" s="1" t="str">
         <f aca="false">IF(L7="Força",COUNTIF(L$6:L7,"Força"),"")</f>
@@ -10504,11 +10595,11 @@
       </c>
       <c r="L8" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!Y8</f>
-        <v/>
-      </c>
-      <c r="M8" s="1" t="str">
+        <v>Neutro</v>
+      </c>
+      <c r="M8" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!X8="","",'Indicadores (F-W)'!X8)</f>
-        <v/>
+        <v>1.8</v>
       </c>
       <c r="N8" s="1" t="str">
         <f aca="false">IF(L8="Força",COUNTIF(L$6:L8,"Força"),"")</f>
@@ -10731,7 +10822,7 @@
         <f aca="false">'Indicadores (F-W)'!Y11</f>
         <v>Neutro</v>
       </c>
-      <c r="M11" s="86" t="n">
+      <c r="M11" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!X11="","",'Indicadores (F-W)'!X11)</f>
         <v>1.1671</v>
       </c>
@@ -10956,7 +11047,7 @@
         <f aca="false">'Indicadores (F-W)'!Y14</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M14" s="86" t="n">
+      <c r="M14" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!X14="","",'Indicadores (F-W)'!X14)</f>
         <v>0.4388</v>
       </c>
@@ -11181,7 +11272,7 @@
         <f aca="false">'Indicadores (F-W)'!Y17</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M17" s="88" t="n">
+      <c r="M17" s="89" t="n">
         <f aca="false">IF('Indicadores (F-W)'!X17="","",'Indicadores (F-W)'!X17)</f>
         <v>48349.24</v>
       </c>
@@ -11228,7 +11319,7 @@
         <f aca="false">'Indicadores (F-W)'!Y18</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M18" s="89" t="n">
+      <c r="M18" s="90" t="n">
         <f aca="false">IF('Indicadores (F-W)'!X18="","",'Indicadores (F-W)'!X18)</f>
         <v>16.77</v>
       </c>
@@ -11712,7 +11803,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -11757,19 +11848,19 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="90" t="s">
-        <v>295</v>
+      <c r="B1" s="91" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="91" t="str">
+      <c r="B3" s="92" t="str">
         <f aca="false">"Indicadores internos com dado: "&amp;(COUNTA(L6:L21)-COUNTBLANK(L6:L21))&amp;" de 16  |  Neutros: "&amp;COUNTIF(L6:L21,"Neutro")&amp;"  |  Fatores externos pontuados: "&amp;COUNT(S6:S16)&amp;" de 11"</f>
-        <v>Indicadores internos com dado: 5 de 16  |  Neutros: 1  |  Fatores externos pontuados: 11 de 11</v>
+        <v>Indicadores internos com dado: 7 de 16  |  Neutros: 1  |  Fatores externos pontuados: 11 de 11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11787,13 +11878,13 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="11" t="str">
         <f aca="false">"FORÇAS (S) — "&amp;COUNTIF($L$6:$L$21,"Força")&amp;" item(ns)"</f>
-        <v>FORÇAS (S) — 1 item(ns)</v>
+        <v>FORÇAS (S) — 2 item(ns)</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
       <c r="F6" s="12" t="str">
         <f aca="false">"FRAQUEZAS (W) — "&amp;COUNTIF($L$6:$L$21,"Fraqueza")&amp;" item(ns)"</f>
-        <v>FRAQUEZAS (W) — 3 item(ns)</v>
+        <v>FRAQUEZAS (W) — 4 item(ns)</v>
       </c>
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
@@ -11805,7 +11896,7 @@
         <f aca="false">'Indicadores (F-W)'!AA6</f>
         <v>Força</v>
       </c>
-      <c r="M6" s="86" t="n">
+      <c r="M6" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!Z6="","",'Indicadores (F-W)'!Z6)</f>
         <v>1.364</v>
       </c>
@@ -11871,15 +11962,15 @@
       </c>
       <c r="L7" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!AA7</f>
-        <v/>
-      </c>
-      <c r="M7" s="1" t="str">
+        <v>Força</v>
+      </c>
+      <c r="M7" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!Z7="","",'Indicadores (F-W)'!Z7)</f>
-        <v/>
-      </c>
-      <c r="N7" s="1" t="str">
+        <v>9903.13</v>
+      </c>
+      <c r="N7" s="1" t="n">
         <f aca="false">IF(L7="Força",COUNTIF(L$6:L7,"Força"),"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O7" s="1" t="str">
         <f aca="false">IF(L7="Fraqueza",COUNTIF(L$6:L7,"Fraqueza"),"")</f>
@@ -11936,11 +12027,11 @@
       </c>
       <c r="G8" s="20" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(1,$O$6:$O$21,0)),"")</f>
-        <v>[Comércio e Serviços] CS-01 – Quociente locacional do VAB de serviços, exceto adm. pública (base MT) (índice)</v>
+        <v>[Agropecuária] AGR-03 – Variação do efetivo bovino em 5 anos (%)</v>
       </c>
       <c r="H8" s="21" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(1,$O$6:$O$21,0)),"")</f>
-        <v>0.3227</v>
+        <v>-2.74</v>
       </c>
       <c r="K8" s="1" t="str">
         <f aca="false">Aux!B8</f>
@@ -11948,19 +12039,19 @@
       </c>
       <c r="L8" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!AA8</f>
-        <v/>
-      </c>
-      <c r="M8" s="1" t="str">
+        <v>Fraqueza</v>
+      </c>
+      <c r="M8" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!Z8="","",'Indicadores (F-W)'!Z8)</f>
-        <v/>
+        <v>-2.74</v>
       </c>
       <c r="N8" s="1" t="str">
         <f aca="false">IF(L8="Força",COUNTIF(L$6:L8,"Força"),"")</f>
         <v/>
       </c>
-      <c r="O8" s="1" t="str">
+      <c r="O8" s="1" t="n">
         <f aca="false">IF(L8="Fraqueza",COUNTIF(L$6:L8,"Fraqueza"),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Q8" s="1" t="str">
         <f aca="false">Aux!I8</f>
@@ -11993,17 +12084,17 @@
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15"/>
-      <c r="B9" s="16" t="str">
+      <c r="B9" s="16" t="n">
         <f aca="false">IF(C9="","",2)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C9" s="17" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(2,$N$6:$N$21,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D9" s="18" t="str">
+        <v>[Agropecuária] AGR-02 – Valor da produção das lavouras por área colhida (R$/ha)</v>
+      </c>
+      <c r="D9" s="18" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(2,$N$6:$N$21,0)),"")</f>
-        <v/>
+        <v>9903.13</v>
       </c>
       <c r="F9" s="19" t="n">
         <f aca="false">IF(G9="","",2)</f>
@@ -12011,11 +12102,11 @@
       </c>
       <c r="G9" s="20" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(2,$O$6:$O$21,0)),"")</f>
-        <v>[Estrutura Econômica e Fiscal] EST-01 – PIB per capita (R$)</v>
+        <v>[Comércio e Serviços] CS-01 – Quociente locacional do VAB de serviços, exceto adm. pública (base MT) (índice)</v>
       </c>
       <c r="H9" s="21" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(2,$O$6:$O$21,0)),"")</f>
-        <v>59335.82</v>
+        <v>0.3227</v>
       </c>
       <c r="K9" s="1" t="str">
         <f aca="false">Aux!B9</f>
@@ -12086,11 +12177,11 @@
       </c>
       <c r="G10" s="20" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(3,$O$6:$O$21,0)),"")</f>
-        <v>[Estrutura Econômica e Fiscal] EST-02 – Participação da administração pública no VAB total (%)</v>
+        <v>[Estrutura Econômica e Fiscal] EST-01 – PIB per capita (R$)</v>
       </c>
       <c r="H10" s="21" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(3,$O$6:$O$21,0)),"")</f>
-        <v>18.67</v>
+        <v>59335.82</v>
       </c>
       <c r="K10" s="1" t="str">
         <f aca="false">Aux!B10</f>
@@ -12155,17 +12246,17 @@
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(4,$N$6:$N$21,0)),"")</f>
         <v/>
       </c>
-      <c r="F11" s="19" t="str">
+      <c r="F11" s="19" t="n">
         <f aca="false">IF(G11="","",4)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="G11" s="20" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(4,$O$6:$O$21,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H11" s="21" t="str">
+        <v>[Estrutura Econômica e Fiscal] EST-02 – Participação da administração pública no VAB total (%)</v>
+      </c>
+      <c r="H11" s="21" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(4,$O$6:$O$21,0)),"")</f>
-        <v/>
+        <v>18.67</v>
       </c>
       <c r="K11" s="1" t="str">
         <f aca="false">Aux!B11</f>
@@ -12175,7 +12266,7 @@
         <f aca="false">'Indicadores (F-W)'!AA11</f>
         <v>Neutro</v>
       </c>
-      <c r="M11" s="86" t="n">
+      <c r="M11" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!Z11="","",'Indicadores (F-W)'!Z11)</f>
         <v>1.1956</v>
       </c>
@@ -12400,7 +12491,7 @@
         <f aca="false">'Indicadores (F-W)'!AA14</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M14" s="86" t="n">
+      <c r="M14" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!Z14="","",'Indicadores (F-W)'!Z14)</f>
         <v>0.3227</v>
       </c>
@@ -12410,7 +12501,7 @@
       </c>
       <c r="O14" s="1" t="n">
         <f aca="false">IF(L14="Fraqueza",COUNTIF(L$6:L14,"Fraqueza"),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q14" s="1" t="str">
         <f aca="false">Aux!I14</f>
@@ -12625,7 +12716,7 @@
         <f aca="false">'Indicadores (F-W)'!AA17</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M17" s="88" t="n">
+      <c r="M17" s="89" t="n">
         <f aca="false">IF('Indicadores (F-W)'!Z17="","",'Indicadores (F-W)'!Z17)</f>
         <v>59335.82</v>
       </c>
@@ -12635,7 +12726,7 @@
       </c>
       <c r="O17" s="1" t="n">
         <f aca="false">IF(L17="Fraqueza",COUNTIF(L$6:L17,"Fraqueza"),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12672,7 +12763,7 @@
         <f aca="false">'Indicadores (F-W)'!AA18</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M18" s="89" t="n">
+      <c r="M18" s="90" t="n">
         <f aca="false">IF('Indicadores (F-W)'!Z18="","",'Indicadores (F-W)'!Z18)</f>
         <v>18.67</v>
       </c>
@@ -12682,7 +12773,7 @@
       </c>
       <c r="O18" s="1" t="n">
         <f aca="false">IF(L18="Fraqueza",COUNTIF(L$6:L18,"Fraqueza"),"")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13156,7 +13247,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -13201,19 +13292,19 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="90" t="s">
-        <v>296</v>
+      <c r="B1" s="91" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="91" t="str">
+      <c r="B3" s="92" t="str">
         <f aca="false">"Indicadores internos com dado: "&amp;(COUNTA(L6:L21)-COUNTBLANK(L6:L21))&amp;" de 16  |  Neutros: "&amp;COUNTIF(L6:L21,"Neutro")&amp;"  |  Fatores externos pontuados: "&amp;COUNT(S6:S16)&amp;" de 11"</f>
-        <v>Indicadores internos com dado: 5 de 16  |  Neutros: 1  |  Fatores externos pontuados: 11 de 11</v>
+        <v>Indicadores internos com dado: 7 de 16  |  Neutros: 1  |  Fatores externos pontuados: 11 de 11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13231,13 +13322,13 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="11" t="str">
         <f aca="false">"FORÇAS (S) — "&amp;COUNTIF($L$6:$L$21,"Força")&amp;" item(ns)"</f>
-        <v>FORÇAS (S) — 1 item(ns)</v>
+        <v>FORÇAS (S) — 2 item(ns)</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
       <c r="F6" s="12" t="str">
         <f aca="false">"FRAQUEZAS (W) — "&amp;COUNTIF($L$6:$L$21,"Fraqueza")&amp;" item(ns)"</f>
-        <v>FRAQUEZAS (W) — 3 item(ns)</v>
+        <v>FRAQUEZAS (W) — 4 item(ns)</v>
       </c>
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
@@ -13249,7 +13340,7 @@
         <f aca="false">'Indicadores (F-W)'!AC6</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M6" s="86" t="n">
+      <c r="M6" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AB6="","",'Indicadores (F-W)'!AB6)</f>
         <v>0.416</v>
       </c>
@@ -13315,15 +13406,15 @@
       </c>
       <c r="L7" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!AC7</f>
-        <v/>
-      </c>
-      <c r="M7" s="1" t="str">
+        <v>Força</v>
+      </c>
+      <c r="M7" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AB7="","",'Indicadores (F-W)'!AB7)</f>
-        <v/>
-      </c>
-      <c r="N7" s="1" t="str">
+        <v>10166.09</v>
+      </c>
+      <c r="N7" s="1" t="n">
         <f aca="false">IF(L7="Força",COUNTIF(L$6:L7,"Força"),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="O7" s="1" t="str">
         <f aca="false">IF(L7="Fraqueza",COUNTIF(L$6:L7,"Fraqueza"),"")</f>
@@ -13368,11 +13459,11 @@
       </c>
       <c r="C8" s="17" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(1,$N$6:$N$21,0)),"")</f>
-        <v>[Indústria] IND-01 – Quociente locacional do VAB industrial (base MT) (índice)</v>
+        <v>[Agropecuária] AGR-02 – Valor da produção das lavouras por área colhida (R$/ha)</v>
       </c>
       <c r="D8" s="18" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(1,$N$6:$N$21,0)),"")</f>
-        <v>1.2112</v>
+        <v>10166.09</v>
       </c>
       <c r="F8" s="19" t="n">
         <f aca="false">IF(G8="","",1)</f>
@@ -13392,19 +13483,19 @@
       </c>
       <c r="L8" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!AC8</f>
-        <v/>
-      </c>
-      <c r="M8" s="1" t="str">
+        <v>Fraqueza</v>
+      </c>
+      <c r="M8" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AB8="","",'Indicadores (F-W)'!AB8)</f>
-        <v/>
+        <v>-2.58</v>
       </c>
       <c r="N8" s="1" t="str">
         <f aca="false">IF(L8="Força",COUNTIF(L$6:L8,"Força"),"")</f>
         <v/>
       </c>
-      <c r="O8" s="1" t="str">
+      <c r="O8" s="1" t="n">
         <f aca="false">IF(L8="Fraqueza",COUNTIF(L$6:L8,"Fraqueza"),"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Q8" s="1" t="str">
         <f aca="false">Aux!I8</f>
@@ -13437,17 +13528,17 @@
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15"/>
-      <c r="B9" s="16" t="str">
+      <c r="B9" s="16" t="n">
         <f aca="false">IF(C9="","",2)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C9" s="17" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(2,$N$6:$N$21,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D9" s="18" t="str">
+        <v>[Indústria] IND-01 – Quociente locacional do VAB industrial (base MT) (índice)</v>
+      </c>
+      <c r="D9" s="18" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(2,$N$6:$N$21,0)),"")</f>
-        <v/>
+        <v>1.2112</v>
       </c>
       <c r="F9" s="19" t="n">
         <f aca="false">IF(G9="","",2)</f>
@@ -13455,11 +13546,11 @@
       </c>
       <c r="G9" s="20" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(2,$O$6:$O$21,0)),"")</f>
-        <v>[Estrutura Econômica e Fiscal] EST-01 – PIB per capita (R$)</v>
+        <v>[Agropecuária] AGR-03 – Variação do efetivo bovino em 5 anos (%)</v>
       </c>
       <c r="H9" s="21" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(2,$O$6:$O$21,0)),"")</f>
-        <v>43433.97</v>
+        <v>-2.58</v>
       </c>
       <c r="K9" s="1" t="str">
         <f aca="false">Aux!B9</f>
@@ -13530,11 +13621,11 @@
       </c>
       <c r="G10" s="20" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(3,$O$6:$O$21,0)),"")</f>
-        <v>[Estrutura Econômica e Fiscal] EST-02 – Participação da administração pública no VAB total (%)</v>
+        <v>[Estrutura Econômica e Fiscal] EST-01 – PIB per capita (R$)</v>
       </c>
       <c r="H10" s="21" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(3,$O$6:$O$21,0)),"")</f>
-        <v>25.62</v>
+        <v>43433.97</v>
       </c>
       <c r="K10" s="1" t="str">
         <f aca="false">Aux!B10</f>
@@ -13599,17 +13690,17 @@
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(4,$N$6:$N$21,0)),"")</f>
         <v/>
       </c>
-      <c r="F11" s="19" t="str">
+      <c r="F11" s="19" t="n">
         <f aca="false">IF(G11="","",4)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="G11" s="20" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(4,$O$6:$O$21,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H11" s="21" t="str">
+        <v>[Estrutura Econômica e Fiscal] EST-02 – Participação da administração pública no VAB total (%)</v>
+      </c>
+      <c r="H11" s="21" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(4,$O$6:$O$21,0)),"")</f>
-        <v/>
+        <v>25.62</v>
       </c>
       <c r="K11" s="1" t="str">
         <f aca="false">Aux!B11</f>
@@ -13619,13 +13710,13 @@
         <f aca="false">'Indicadores (F-W)'!AC11</f>
         <v>Força</v>
       </c>
-      <c r="M11" s="86" t="n">
+      <c r="M11" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AB11="","",'Indicadores (F-W)'!AB11)</f>
         <v>1.2112</v>
       </c>
       <c r="N11" s="1" t="n">
         <f aca="false">IF(L11="Força",COUNTIF(L$6:L11,"Força"),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O11" s="1" t="str">
         <f aca="false">IF(L11="Fraqueza",COUNTIF(L$6:L11,"Fraqueza"),"")</f>
@@ -13844,7 +13935,7 @@
         <f aca="false">'Indicadores (F-W)'!AC14</f>
         <v>Neutro</v>
       </c>
-      <c r="M14" s="86" t="n">
+      <c r="M14" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AB14="","",'Indicadores (F-W)'!AB14)</f>
         <v>1.1498</v>
       </c>
@@ -14069,7 +14160,7 @@
         <f aca="false">'Indicadores (F-W)'!AC17</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M17" s="88" t="n">
+      <c r="M17" s="89" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AB17="","",'Indicadores (F-W)'!AB17)</f>
         <v>43433.97</v>
       </c>
@@ -14079,7 +14170,7 @@
       </c>
       <c r="O17" s="1" t="n">
         <f aca="false">IF(L17="Fraqueza",COUNTIF(L$6:L17,"Fraqueza"),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14116,7 +14207,7 @@
         <f aca="false">'Indicadores (F-W)'!AC18</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M18" s="89" t="n">
+      <c r="M18" s="90" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AB18="","",'Indicadores (F-W)'!AB18)</f>
         <v>25.62</v>
       </c>
@@ -14126,7 +14217,7 @@
       </c>
       <c r="O18" s="1" t="n">
         <f aca="false">IF(L18="Fraqueza",COUNTIF(L$6:L18,"Fraqueza"),"")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14600,7 +14691,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -14645,19 +14736,19 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="90" t="s">
-        <v>297</v>
+      <c r="B1" s="91" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="91" t="str">
+      <c r="B3" s="92" t="str">
         <f aca="false">"Indicadores internos com dado: "&amp;(COUNTA(L6:L21)-COUNTBLANK(L6:L21))&amp;" de 16  |  Neutros: "&amp;COUNTIF(L6:L21,"Neutro")&amp;"  |  Fatores externos pontuados: "&amp;COUNT(S6:S16)&amp;" de 11"</f>
-        <v>Indicadores internos com dado: 5 de 16  |  Neutros: 0  |  Fatores externos pontuados: 11 de 11</v>
+        <v>Indicadores internos com dado: 7 de 16  |  Neutros: 1  |  Fatores externos pontuados: 11 de 11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14675,7 +14766,7 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="11" t="str">
         <f aca="false">"FORÇAS (S) — "&amp;COUNTIF($L$6:$L$21,"Força")&amp;" item(ns)"</f>
-        <v>FORÇAS (S) — 1 item(ns)</v>
+        <v>FORÇAS (S) — 2 item(ns)</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
@@ -14693,7 +14784,7 @@
         <f aca="false">'Indicadores (F-W)'!AE6</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M6" s="86" t="n">
+      <c r="M6" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AD6="","",'Indicadores (F-W)'!AD6)</f>
         <v>0.5183</v>
       </c>
@@ -14759,11 +14850,11 @@
       </c>
       <c r="L7" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!AE7</f>
-        <v/>
-      </c>
-      <c r="M7" s="1" t="str">
+        <v>Neutro</v>
+      </c>
+      <c r="M7" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AD7="","",'Indicadores (F-W)'!AD7)</f>
-        <v/>
+        <v>5734.66</v>
       </c>
       <c r="N7" s="1" t="str">
         <f aca="false">IF(L7="Força",COUNTIF(L$6:L7,"Força"),"")</f>
@@ -14812,11 +14903,11 @@
       </c>
       <c r="C8" s="17" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(1,$N$6:$N$21,0)),"")</f>
-        <v>[Indústria] IND-01 – Quociente locacional do VAB industrial (base MT) (índice)</v>
+        <v>[Agropecuária] AGR-03 – Variação do efetivo bovino em 5 anos (%)</v>
       </c>
       <c r="D8" s="18" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(1,$N$6:$N$21,0)),"")</f>
-        <v>2.0033</v>
+        <v>23.81</v>
       </c>
       <c r="F8" s="19" t="n">
         <f aca="false">IF(G8="","",1)</f>
@@ -14836,15 +14927,15 @@
       </c>
       <c r="L8" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!AE8</f>
-        <v/>
-      </c>
-      <c r="M8" s="1" t="str">
+        <v>Força</v>
+      </c>
+      <c r="M8" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AD8="","",'Indicadores (F-W)'!AD8)</f>
-        <v/>
-      </c>
-      <c r="N8" s="1" t="str">
+        <v>23.81</v>
+      </c>
+      <c r="N8" s="1" t="n">
         <f aca="false">IF(L8="Força",COUNTIF(L$6:L8,"Força"),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="O8" s="1" t="str">
         <f aca="false">IF(L8="Fraqueza",COUNTIF(L$6:L8,"Fraqueza"),"")</f>
@@ -14881,17 +14972,17 @@
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15"/>
-      <c r="B9" s="16" t="str">
+      <c r="B9" s="16" t="n">
         <f aca="false">IF(C9="","",2)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C9" s="17" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(2,$N$6:$N$21,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D9" s="18" t="str">
+        <v>[Indústria] IND-01 – Quociente locacional do VAB industrial (base MT) (índice)</v>
+      </c>
+      <c r="D9" s="18" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(2,$N$6:$N$21,0)),"")</f>
-        <v/>
+        <v>2.0033</v>
       </c>
       <c r="F9" s="19" t="n">
         <f aca="false">IF(G9="","",2)</f>
@@ -15063,13 +15154,13 @@
         <f aca="false">'Indicadores (F-W)'!AE11</f>
         <v>Força</v>
       </c>
-      <c r="M11" s="86" t="n">
+      <c r="M11" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AD11="","",'Indicadores (F-W)'!AD11)</f>
         <v>2.0033</v>
       </c>
       <c r="N11" s="1" t="n">
         <f aca="false">IF(L11="Força",COUNTIF(L$6:L11,"Força"),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O11" s="1" t="str">
         <f aca="false">IF(L11="Fraqueza",COUNTIF(L$6:L11,"Fraqueza"),"")</f>
@@ -15288,7 +15379,7 @@
         <f aca="false">'Indicadores (F-W)'!AE14</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M14" s="86" t="n">
+      <c r="M14" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AD14="","",'Indicadores (F-W)'!AD14)</f>
         <v>0.7089</v>
       </c>
@@ -15513,7 +15604,7 @@
         <f aca="false">'Indicadores (F-W)'!AE17</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M17" s="88" t="n">
+      <c r="M17" s="89" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AD17="","",'Indicadores (F-W)'!AD17)</f>
         <v>33510.51</v>
       </c>
@@ -15560,7 +15651,7 @@
         <f aca="false">'Indicadores (F-W)'!AE18</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M18" s="89" t="n">
+      <c r="M18" s="90" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AD18="","",'Indicadores (F-W)'!AD18)</f>
         <v>24.97</v>
       </c>
@@ -16044,7 +16135,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -16101,7 +16192,7 @@
       <c r="D3" s="8"/>
       <c r="F3" s="9" t="str">
         <f aca="false">"Indicadores: "&amp;COUNTIF(Aux!$C$6:$C$21,"Neutro")&amp;" neutros | "&amp;(COUNTA(Aux!$A$6:$A$21)-COUNTIF(Aux!$C$6:$C$21,"Força")-COUNTIF(Aux!$C$6:$C$21,"Fraqueza")-COUNTIF(Aux!$C$6:$C$21,"Neutro"))&amp;" sem dado"</f>
-        <v>Indicadores: 0 neutros | 11 sem dado</v>
+        <v>Indicadores: 1 neutros | 9 sem dado</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16119,7 +16210,7 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="11" t="str">
         <f aca="false">"FORÇAS (S) — "&amp;COUNTIF(Aux!$C$6:$C$21,"Força")&amp;" item(ns)"</f>
-        <v>FORÇAS (S) — 1 item(ns)</v>
+        <v>FORÇAS (S) — 2 item(ns)</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
@@ -16160,11 +16251,11 @@
       </c>
       <c r="C8" s="17" t="str">
         <f aca="false">IFERROR(INDEX(Aux!$B$6:$B$21,MATCH(1,Aux!$E$6:$E$21,0)),"")</f>
-        <v>[Comércio e Serviços] CS-01 – Quociente locacional do VAB de serviços, exceto adm. pública (base MT) (índice)</v>
+        <v>[Agropecuária] AGR-03 – Variação do efetivo bovino em 5 anos (%)</v>
       </c>
       <c r="D8" s="18" t="n">
         <f aca="false">IFERROR(INDEX(Aux!$D$6:$D$21,MATCH(1,Aux!$E$6:$E$21,0)),"")</f>
-        <v>1.3013</v>
+        <v>22.65</v>
       </c>
       <c r="F8" s="19" t="n">
         <f aca="false">IF(G8="","",1)</f>
@@ -16181,17 +16272,17 @@
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15"/>
-      <c r="B9" s="16" t="str">
+      <c r="B9" s="16" t="n">
         <f aca="false">IF(C9="","",2)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C9" s="17" t="str">
         <f aca="false">IFERROR(INDEX(Aux!$B$6:$B$21,MATCH(2,Aux!$E$6:$E$21,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D9" s="18" t="str">
+        <v>[Comércio e Serviços] CS-01 – Quociente locacional do VAB de serviços, exceto adm. pública (base MT) (índice)</v>
+      </c>
+      <c r="D9" s="18" t="n">
         <f aca="false">IFERROR(INDEX(Aux!$D$6:$D$21,MATCH(2,Aux!$E$6:$E$21,0)),"")</f>
-        <v/>
+        <v>1.3013</v>
       </c>
       <c r="F9" s="19" t="n">
         <f aca="false">IF(G9="","",2)</f>
@@ -16910,19 +17001,19 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="90" t="s">
-        <v>298</v>
+      <c r="B1" s="91" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="91" t="str">
+      <c r="B3" s="92" t="str">
         <f aca="false">"Indicadores internos com dado: "&amp;(COUNTA(L6:L21)-COUNTBLANK(L6:L21))&amp;" de 16  |  Neutros: "&amp;COUNTIF(L6:L21,"Neutro")&amp;"  |  Fatores externos pontuados: "&amp;COUNT(S6:S16)&amp;" de 11"</f>
-        <v>Indicadores internos com dado: 5 de 16  |  Neutros: 1  |  Fatores externos pontuados: 11 de 11</v>
+        <v>Indicadores internos com dado: 7 de 16  |  Neutros: 2  |  Fatores externos pontuados: 11 de 11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16940,7 +17031,7 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="11" t="str">
         <f aca="false">"FORÇAS (S) — "&amp;COUNTIF($L$6:$L$21,"Força")&amp;" item(ns)"</f>
-        <v>FORÇAS (S) — 0 item(ns)</v>
+        <v>FORÇAS (S) — 1 item(ns)</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
@@ -16958,7 +17049,7 @@
         <f aca="false">'Indicadores (F-W)'!AG6</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M6" s="86" t="n">
+      <c r="M6" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AF6="","",'Indicadores (F-W)'!AF6)</f>
         <v>0.5066</v>
       </c>
@@ -17024,11 +17115,11 @@
       </c>
       <c r="L7" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!AG7</f>
-        <v/>
-      </c>
-      <c r="M7" s="1" t="str">
+        <v>Neutro</v>
+      </c>
+      <c r="M7" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AF7="","",'Indicadores (F-W)'!AF7)</f>
-        <v/>
+        <v>5045</v>
       </c>
       <c r="N7" s="1" t="str">
         <f aca="false">IF(L7="Força",COUNTIF(L$6:L7,"Força"),"")</f>
@@ -17071,17 +17162,17 @@
       <c r="A8" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="16" t="str">
+      <c r="B8" s="16" t="n">
         <f aca="false">IF(C8="","",1)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="C8" s="17" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(1,$N$6:$N$21,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D8" s="18" t="str">
+        <v>[Agropecuária] AGR-03 – Variação do efetivo bovino em 5 anos (%)</v>
+      </c>
+      <c r="D8" s="18" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(1,$N$6:$N$21,0)),"")</f>
-        <v/>
+        <v>16.79</v>
       </c>
       <c r="F8" s="19" t="n">
         <f aca="false">IF(G8="","",1)</f>
@@ -17101,15 +17192,15 @@
       </c>
       <c r="L8" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!AG8</f>
-        <v/>
-      </c>
-      <c r="M8" s="1" t="str">
+        <v>Força</v>
+      </c>
+      <c r="M8" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AF8="","",'Indicadores (F-W)'!AF8)</f>
-        <v/>
-      </c>
-      <c r="N8" s="1" t="str">
+        <v>16.79</v>
+      </c>
+      <c r="N8" s="1" t="n">
         <f aca="false">IF(L8="Força",COUNTIF(L$6:L8,"Força"),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="O8" s="1" t="str">
         <f aca="false">IF(L8="Fraqueza",COUNTIF(L$6:L8,"Fraqueza"),"")</f>
@@ -17328,7 +17419,7 @@
         <f aca="false">'Indicadores (F-W)'!AG11</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M11" s="86" t="n">
+      <c r="M11" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AF11="","",'Indicadores (F-W)'!AF11)</f>
         <v>0.5947</v>
       </c>
@@ -17553,7 +17644,7 @@
         <f aca="false">'Indicadores (F-W)'!AG14</f>
         <v>Neutro</v>
       </c>
-      <c r="M14" s="86" t="n">
+      <c r="M14" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AF14="","",'Indicadores (F-W)'!AF14)</f>
         <v>1.1034</v>
       </c>
@@ -17778,7 +17869,7 @@
         <f aca="false">'Indicadores (F-W)'!AG17</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M17" s="88" t="n">
+      <c r="M17" s="89" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AF17="","",'Indicadores (F-W)'!AF17)</f>
         <v>27609.14</v>
       </c>
@@ -17825,7 +17916,7 @@
         <f aca="false">'Indicadores (F-W)'!AG18</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M18" s="89" t="n">
+      <c r="M18" s="90" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AF18="","",'Indicadores (F-W)'!AF18)</f>
         <v>33.23</v>
       </c>
@@ -18309,7 +18400,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -18354,19 +18445,19 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="90" t="s">
-        <v>299</v>
+      <c r="B1" s="91" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="91" t="str">
+      <c r="B3" s="92" t="str">
         <f aca="false">"Indicadores internos com dado: "&amp;(COUNTA(L6:L21)-COUNTBLANK(L6:L21))&amp;" de 16  |  Neutros: "&amp;COUNTIF(L6:L21,"Neutro")&amp;"  |  Fatores externos pontuados: "&amp;COUNT(S6:S16)&amp;" de 11"</f>
-        <v>Indicadores internos com dado: 5 de 16  |  Neutros: 2  |  Fatores externos pontuados: 11 de 11</v>
+        <v>Indicadores internos com dado: 7 de 16  |  Neutros: 2  |  Fatores externos pontuados: 11 de 11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18384,7 +18475,7 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="11" t="str">
         <f aca="false">"FORÇAS (S) — "&amp;COUNTIF($L$6:$L$21,"Força")&amp;" item(ns)"</f>
-        <v>FORÇAS (S) — 0 item(ns)</v>
+        <v>FORÇAS (S) — 2 item(ns)</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
@@ -18402,7 +18493,7 @@
         <f aca="false">'Indicadores (F-W)'!AI6</f>
         <v>Neutro</v>
       </c>
-      <c r="M6" s="86" t="n">
+      <c r="M6" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AH6="","",'Indicadores (F-W)'!AH6)</f>
         <v>1.0048</v>
       </c>
@@ -18468,15 +18559,15 @@
       </c>
       <c r="L7" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!AI7</f>
-        <v/>
-      </c>
-      <c r="M7" s="1" t="str">
+        <v>Força</v>
+      </c>
+      <c r="M7" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AH7="","",'Indicadores (F-W)'!AH7)</f>
-        <v/>
-      </c>
-      <c r="N7" s="1" t="str">
+        <v>6552.04</v>
+      </c>
+      <c r="N7" s="1" t="n">
         <f aca="false">IF(L7="Força",COUNTIF(L$6:L7,"Força"),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="O7" s="1" t="str">
         <f aca="false">IF(L7="Fraqueza",COUNTIF(L$6:L7,"Fraqueza"),"")</f>
@@ -18515,17 +18606,17 @@
       <c r="A8" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="16" t="str">
+      <c r="B8" s="16" t="n">
         <f aca="false">IF(C8="","",1)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="C8" s="17" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(1,$N$6:$N$21,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D8" s="18" t="str">
+        <v>[Agropecuária] AGR-02 – Valor da produção das lavouras por área colhida (R$/ha)</v>
+      </c>
+      <c r="D8" s="18" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(1,$N$6:$N$21,0)),"")</f>
-        <v/>
+        <v>6552.04</v>
       </c>
       <c r="F8" s="19" t="n">
         <f aca="false">IF(G8="","",1)</f>
@@ -18545,15 +18636,15 @@
       </c>
       <c r="L8" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!AI8</f>
-        <v/>
-      </c>
-      <c r="M8" s="1" t="str">
+        <v>Força</v>
+      </c>
+      <c r="M8" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AH8="","",'Indicadores (F-W)'!AH8)</f>
-        <v/>
-      </c>
-      <c r="N8" s="1" t="str">
+        <v>8.4</v>
+      </c>
+      <c r="N8" s="1" t="n">
         <f aca="false">IF(L8="Força",COUNTIF(L$6:L8,"Força"),"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O8" s="1" t="str">
         <f aca="false">IF(L8="Fraqueza",COUNTIF(L$6:L8,"Fraqueza"),"")</f>
@@ -18590,17 +18681,17 @@
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15"/>
-      <c r="B9" s="16" t="str">
+      <c r="B9" s="16" t="n">
         <f aca="false">IF(C9="","",2)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C9" s="17" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(2,$N$6:$N$21,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D9" s="18" t="str">
+        <v>[Agropecuária] AGR-03 – Variação do efetivo bovino em 5 anos (%)</v>
+      </c>
+      <c r="D9" s="18" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(2,$N$6:$N$21,0)),"")</f>
-        <v/>
+        <v>8.4</v>
       </c>
       <c r="F9" s="19" t="n">
         <f aca="false">IF(G9="","",2)</f>
@@ -18772,7 +18863,7 @@
         <f aca="false">'Indicadores (F-W)'!AI11</f>
         <v>Neutro</v>
       </c>
-      <c r="M11" s="86" t="n">
+      <c r="M11" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AH11="","",'Indicadores (F-W)'!AH11)</f>
         <v>1.0107</v>
       </c>
@@ -18997,7 +19088,7 @@
         <f aca="false">'Indicadores (F-W)'!AI14</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M14" s="86" t="n">
+      <c r="M14" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AH14="","",'Indicadores (F-W)'!AH14)</f>
         <v>0.505</v>
       </c>
@@ -19222,7 +19313,7 @@
         <f aca="false">'Indicadores (F-W)'!AI17</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M17" s="88" t="n">
+      <c r="M17" s="89" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AH17="","",'Indicadores (F-W)'!AH17)</f>
         <v>31726.19</v>
       </c>
@@ -19269,7 +19360,7 @@
         <f aca="false">'Indicadores (F-W)'!AI18</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M18" s="89" t="n">
+      <c r="M18" s="90" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AH18="","",'Indicadores (F-W)'!AH18)</f>
         <v>28.79</v>
       </c>
@@ -19753,7 +19844,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -19798,19 +19889,19 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="90" t="s">
-        <v>300</v>
+      <c r="B1" s="91" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="91" t="str">
+      <c r="B3" s="92" t="str">
         <f aca="false">"Indicadores internos com dado: "&amp;(COUNTA(L6:L21)-COUNTBLANK(L6:L21))&amp;" de 16  |  Neutros: "&amp;COUNTIF(L6:L21,"Neutro")&amp;"  |  Fatores externos pontuados: "&amp;COUNT(S6:S16)&amp;" de 11"</f>
-        <v>Indicadores internos com dado: 5 de 16  |  Neutros: 2  |  Fatores externos pontuados: 11 de 11</v>
+        <v>Indicadores internos com dado: 7 de 16  |  Neutros: 3  |  Fatores externos pontuados: 11 de 11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19834,7 +19925,7 @@
       <c r="D6" s="11"/>
       <c r="F6" s="12" t="str">
         <f aca="false">"FRAQUEZAS (W) — "&amp;COUNTIF($L$6:$L$21,"Fraqueza")&amp;" item(ns)"</f>
-        <v>FRAQUEZAS (W) — 1 item(ns)</v>
+        <v>FRAQUEZAS (W) — 2 item(ns)</v>
       </c>
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
@@ -19846,7 +19937,7 @@
         <f aca="false">'Indicadores (F-W)'!AK6</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M6" s="86" t="n">
+      <c r="M6" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AJ6="","",'Indicadores (F-W)'!AJ6)</f>
         <v>0.1067</v>
       </c>
@@ -19912,11 +20003,11 @@
       </c>
       <c r="L7" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!AK7</f>
-        <v/>
-      </c>
-      <c r="M7" s="1" t="str">
+        <v>Neutro</v>
+      </c>
+      <c r="M7" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AJ7="","",'Indicadores (F-W)'!AJ7)</f>
-        <v/>
+        <v>5354.94</v>
       </c>
       <c r="N7" s="1" t="str">
         <f aca="false">IF(L7="Força",COUNTIF(L$6:L7,"Força"),"")</f>
@@ -19989,19 +20080,19 @@
       </c>
       <c r="L8" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!AK8</f>
-        <v/>
-      </c>
-      <c r="M8" s="1" t="str">
+        <v>Fraqueza</v>
+      </c>
+      <c r="M8" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AJ8="","",'Indicadores (F-W)'!AJ8)</f>
-        <v/>
+        <v>0.39</v>
       </c>
       <c r="N8" s="1" t="str">
         <f aca="false">IF(L8="Força",COUNTIF(L$6:L8,"Força"),"")</f>
         <v/>
       </c>
-      <c r="O8" s="1" t="str">
+      <c r="O8" s="1" t="n">
         <f aca="false">IF(L8="Fraqueza",COUNTIF(L$6:L8,"Fraqueza"),"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Q8" s="1" t="str">
         <f aca="false">Aux!I8</f>
@@ -20046,17 +20137,17 @@
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(2,$N$6:$N$21,0)),"")</f>
         <v>1.5988</v>
       </c>
-      <c r="F9" s="19" t="str">
+      <c r="F9" s="19" t="n">
         <f aca="false">IF(G9="","",2)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G9" s="20" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(2,$O$6:$O$21,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H9" s="21" t="str">
+        <v>[Agropecuária] AGR-03 – Variação do efetivo bovino em 5 anos (%)</v>
+      </c>
+      <c r="H9" s="21" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(2,$O$6:$O$21,0)),"")</f>
-        <v/>
+        <v>0.39</v>
       </c>
       <c r="K9" s="1" t="str">
         <f aca="false">Aux!B9</f>
@@ -20216,7 +20307,7 @@
         <f aca="false">'Indicadores (F-W)'!AK11</f>
         <v>Força</v>
       </c>
-      <c r="M11" s="86" t="n">
+      <c r="M11" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AJ11="","",'Indicadores (F-W)'!AJ11)</f>
         <v>1.8691</v>
       </c>
@@ -20441,7 +20532,7 @@
         <f aca="false">'Indicadores (F-W)'!AK14</f>
         <v>Força</v>
       </c>
-      <c r="M14" s="86" t="n">
+      <c r="M14" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AJ14="","",'Indicadores (F-W)'!AJ14)</f>
         <v>1.5988</v>
       </c>
@@ -20666,7 +20757,7 @@
         <f aca="false">'Indicadores (F-W)'!AK17</f>
         <v>Neutro</v>
       </c>
-      <c r="M17" s="88" t="n">
+      <c r="M17" s="89" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AJ17="","",'Indicadores (F-W)'!AJ17)</f>
         <v>67650.09</v>
       </c>
@@ -20713,7 +20804,7 @@
         <f aca="false">'Indicadores (F-W)'!AK18</f>
         <v>Neutro</v>
       </c>
-      <c r="M18" s="89" t="n">
+      <c r="M18" s="90" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AJ18="","",'Indicadores (F-W)'!AJ18)</f>
         <v>11.66</v>
       </c>
@@ -21197,7 +21288,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -21242,19 +21333,19 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="90" t="s">
-        <v>301</v>
+      <c r="B1" s="91" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="91" t="str">
+      <c r="B3" s="92" t="str">
         <f aca="false">"Indicadores internos com dado: "&amp;(COUNTA(L6:L21)-COUNTBLANK(L6:L21))&amp;" de 16  |  Neutros: "&amp;COUNTIF(L6:L21,"Neutro")&amp;"  |  Fatores externos pontuados: "&amp;COUNT(S6:S16)&amp;" de 11"</f>
-        <v>Indicadores internos com dado: 5 de 16  |  Neutros: 0  |  Fatores externos pontuados: 11 de 11</v>
+        <v>Indicadores internos com dado: 7 de 16  |  Neutros: 1  |  Fatores externos pontuados: 11 de 11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21278,7 +21369,7 @@
       <c r="D6" s="11"/>
       <c r="F6" s="12" t="str">
         <f aca="false">"FRAQUEZAS (W) — "&amp;COUNTIF($L$6:$L$21,"Fraqueza")&amp;" item(ns)"</f>
-        <v>FRAQUEZAS (W) — 4 item(ns)</v>
+        <v>FRAQUEZAS (W) — 5 item(ns)</v>
       </c>
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
@@ -21290,7 +21381,7 @@
         <f aca="false">'Indicadores (F-W)'!AM6</f>
         <v>Força</v>
       </c>
-      <c r="M6" s="86" t="n">
+      <c r="M6" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AL6="","",'Indicadores (F-W)'!AL6)</f>
         <v>1.714</v>
       </c>
@@ -21356,19 +21447,19 @@
       </c>
       <c r="L7" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!AM7</f>
-        <v/>
-      </c>
-      <c r="M7" s="1" t="str">
+        <v>Fraqueza</v>
+      </c>
+      <c r="M7" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AL7="","",'Indicadores (F-W)'!AL7)</f>
-        <v/>
+        <v>4958.82</v>
       </c>
       <c r="N7" s="1" t="str">
         <f aca="false">IF(L7="Força",COUNTIF(L$6:L7,"Força"),"")</f>
         <v/>
       </c>
-      <c r="O7" s="1" t="str">
+      <c r="O7" s="1" t="n">
         <f aca="false">IF(L7="Fraqueza",COUNTIF(L$6:L7,"Fraqueza"),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Q7" s="1" t="str">
         <f aca="false">Aux!I7</f>
@@ -21421,11 +21512,11 @@
       </c>
       <c r="G8" s="20" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(1,$O$6:$O$21,0)),"")</f>
-        <v>[Indústria] IND-01 – Quociente locacional do VAB industrial (base MT) (índice)</v>
+        <v>[Agropecuária] AGR-02 – Valor da produção das lavouras por área colhida (R$/ha)</v>
       </c>
       <c r="H8" s="21" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(1,$O$6:$O$21,0)),"")</f>
-        <v>0.4719</v>
+        <v>4958.82</v>
       </c>
       <c r="K8" s="1" t="str">
         <f aca="false">Aux!B8</f>
@@ -21433,11 +21524,11 @@
       </c>
       <c r="L8" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!AM8</f>
-        <v/>
-      </c>
-      <c r="M8" s="1" t="str">
+        <v>Neutro</v>
+      </c>
+      <c r="M8" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AL8="","",'Indicadores (F-W)'!AL8)</f>
-        <v/>
+        <v>4.74</v>
       </c>
       <c r="N8" s="1" t="str">
         <f aca="false">IF(L8="Força",COUNTIF(L$6:L8,"Força"),"")</f>
@@ -21496,11 +21587,11 @@
       </c>
       <c r="G9" s="20" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(2,$O$6:$O$21,0)),"")</f>
-        <v>[Comércio e Serviços] CS-01 – Quociente locacional do VAB de serviços, exceto adm. pública (base MT) (índice)</v>
+        <v>[Indústria] IND-01 – Quociente locacional do VAB industrial (base MT) (índice)</v>
       </c>
       <c r="H9" s="21" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(2,$O$6:$O$21,0)),"")</f>
-        <v>0.3417</v>
+        <v>0.4719</v>
       </c>
       <c r="K9" s="1" t="str">
         <f aca="false">Aux!B9</f>
@@ -21571,11 +21662,11 @@
       </c>
       <c r="G10" s="20" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(3,$O$6:$O$21,0)),"")</f>
-        <v>[Estrutura Econômica e Fiscal] EST-01 – PIB per capita (R$)</v>
+        <v>[Comércio e Serviços] CS-01 – Quociente locacional do VAB de serviços, exceto adm. pública (base MT) (índice)</v>
       </c>
       <c r="H10" s="21" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(3,$O$6:$O$21,0)),"")</f>
-        <v>48781.11</v>
+        <v>0.3417</v>
       </c>
       <c r="K10" s="1" t="str">
         <f aca="false">Aux!B10</f>
@@ -21646,11 +21737,11 @@
       </c>
       <c r="G11" s="20" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(4,$O$6:$O$21,0)),"")</f>
-        <v>[Estrutura Econômica e Fiscal] EST-02 – Participação da administração pública no VAB total (%)</v>
+        <v>[Estrutura Econômica e Fiscal] EST-01 – PIB per capita (R$)</v>
       </c>
       <c r="H11" s="21" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(4,$O$6:$O$21,0)),"")</f>
-        <v>15.78</v>
+        <v>48781.11</v>
       </c>
       <c r="K11" s="1" t="str">
         <f aca="false">Aux!B11</f>
@@ -21660,7 +21751,7 @@
         <f aca="false">'Indicadores (F-W)'!AM11</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M11" s="86" t="n">
+      <c r="M11" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AL11="","",'Indicadores (F-W)'!AL11)</f>
         <v>0.4719</v>
       </c>
@@ -21670,7 +21761,7 @@
       </c>
       <c r="O11" s="1" t="n">
         <f aca="false">IF(L11="Fraqueza",COUNTIF(L$6:L11,"Fraqueza"),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q11" s="1" t="str">
         <f aca="false">Aux!I11</f>
@@ -21715,17 +21806,17 @@
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(5,$N$6:$N$21,0)),"")</f>
         <v/>
       </c>
-      <c r="F12" s="19" t="str">
+      <c r="F12" s="19" t="n">
         <f aca="false">IF(G12="","",5)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="G12" s="20" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(5,$O$6:$O$21,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H12" s="21" t="str">
+        <v>[Estrutura Econômica e Fiscal] EST-02 – Participação da administração pública no VAB total (%)</v>
+      </c>
+      <c r="H12" s="21" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(5,$O$6:$O$21,0)),"")</f>
-        <v/>
+        <v>15.78</v>
       </c>
       <c r="K12" s="1" t="str">
         <f aca="false">Aux!B12</f>
@@ -21885,7 +21976,7 @@
         <f aca="false">'Indicadores (F-W)'!AM14</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M14" s="86" t="n">
+      <c r="M14" s="87" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AL14="","",'Indicadores (F-W)'!AL14)</f>
         <v>0.3417</v>
       </c>
@@ -21895,7 +21986,7 @@
       </c>
       <c r="O14" s="1" t="n">
         <f aca="false">IF(L14="Fraqueza",COUNTIF(L$6:L14,"Fraqueza"),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q14" s="1" t="str">
         <f aca="false">Aux!I14</f>
@@ -22110,7 +22201,7 @@
         <f aca="false">'Indicadores (F-W)'!AM17</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M17" s="88" t="n">
+      <c r="M17" s="89" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AL17="","",'Indicadores (F-W)'!AL17)</f>
         <v>48781.11</v>
       </c>
@@ -22120,7 +22211,7 @@
       </c>
       <c r="O17" s="1" t="n">
         <f aca="false">IF(L17="Fraqueza",COUNTIF(L$6:L17,"Fraqueza"),"")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22157,7 +22248,7 @@
         <f aca="false">'Indicadores (F-W)'!AM18</f>
         <v>Fraqueza</v>
       </c>
-      <c r="M18" s="89" t="n">
+      <c r="M18" s="90" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AL18="","",'Indicadores (F-W)'!AL18)</f>
         <v>15.78</v>
       </c>
@@ -22167,7 +22258,7 @@
       </c>
       <c r="O18" s="1" t="n">
         <f aca="false">IF(L18="Fraqueza",COUNTIF(L$6:L18,"Fraqueza"),"")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22641,7 +22732,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -22723,7 +22814,7 @@
       </c>
       <c r="B4" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!O$6:O$21,"Força")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C4" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!O$6:O$21,"Fraqueza")</f>
@@ -22735,11 +22826,11 @@
       </c>
       <c r="E4" s="36" t="n">
         <f aca="false">COUNTBLANK('Indicadores (F-W)'!N$6:N$21)</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F4" s="36" t="n">
         <f aca="false">B4-C4</f>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="G4" s="36" t="n">
         <f aca="false">COUNTIFS('Fatores Externos (O-A)'!$B$6:$B$16,"Oportunidade",'Fatores Externos (O-A)'!F$6:F$16,"&gt;="&amp;Parâmetros!$B$5)</f>
@@ -22760,7 +22851,7 @@
       </c>
       <c r="B5" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!Q$6:Q$21,"Força")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!Q$6:Q$21,"Fraqueza")</f>
@@ -22768,15 +22859,15 @@
       </c>
       <c r="D5" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!Q$6:Q$21,"Neutro")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="36" t="n">
         <f aca="false">COUNTBLANK('Indicadores (F-W)'!P$6:P$21)</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F5" s="36" t="n">
         <f aca="false">B5-C5</f>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="G5" s="36" t="n">
         <f aca="false">COUNTIFS('Fatores Externos (O-A)'!$B$6:$B$16,"Oportunidade",'Fatores Externos (O-A)'!G$6:G$16,"&gt;="&amp;Parâmetros!$B$5)</f>
@@ -22797,7 +22888,7 @@
       </c>
       <c r="B6" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!S$6:S$21,"Força")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!S$6:S$21,"Fraqueza")</f>
@@ -22805,15 +22896,15 @@
       </c>
       <c r="D6" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!S$6:S$21,"Neutro")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="36" t="n">
         <f aca="false">COUNTBLANK('Indicadores (F-W)'!R$6:R$21)</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F6" s="36" t="n">
         <f aca="false">B6-C6</f>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="G6" s="36" t="n">
         <f aca="false">COUNTIFS('Fatores Externos (O-A)'!$B$6:$B$16,"Oportunidade",'Fatores Externos (O-A)'!H$6:H$16,"&gt;="&amp;Parâmetros!$B$5)</f>
@@ -22834,7 +22925,7 @@
       </c>
       <c r="B7" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!U$6:U$21,"Força")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!U$6:U$21,"Fraqueza")</f>
@@ -22842,15 +22933,15 @@
       </c>
       <c r="D7" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!U$6:U$21,"Neutro")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="36" t="n">
         <f aca="false">COUNTBLANK('Indicadores (F-W)'!T$6:T$21)</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">B7-C7</f>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="G7" s="36" t="n">
         <f aca="false">COUNTIFS('Fatores Externos (O-A)'!$B$6:$B$16,"Oportunidade",'Fatores Externos (O-A)'!I$6:I$16,"&gt;="&amp;Parâmetros!$B$5)</f>
@@ -22871,7 +22962,7 @@
       </c>
       <c r="B8" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!W$6:W$21,"Força")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!W$6:W$21,"Fraqueza")</f>
@@ -22879,15 +22970,15 @@
       </c>
       <c r="D8" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!W$6:W$21,"Neutro")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="36" t="n">
         <f aca="false">COUNTBLANK('Indicadores (F-W)'!V$6:V$21)</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F8" s="36" t="n">
         <f aca="false">B8-C8</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8" s="36" t="n">
         <f aca="false">COUNTIFS('Fatores Externos (O-A)'!$B$6:$B$16,"Oportunidade",'Fatores Externos (O-A)'!J$6:J$16,"&gt;="&amp;Parâmetros!$B$5)</f>
@@ -22916,11 +23007,11 @@
       </c>
       <c r="D9" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!Y$6:Y$21,"Neutro")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9" s="36" t="n">
         <f aca="false">COUNTBLANK('Indicadores (F-W)'!X$6:X$21)</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F9" s="36" t="n">
         <f aca="false">B9-C9</f>
@@ -22945,11 +23036,11 @@
       </c>
       <c r="B10" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AA$6:AA$21,"Força")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AA$6:AA$21,"Fraqueza")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AA$6:AA$21,"Neutro")</f>
@@ -22957,7 +23048,7 @@
       </c>
       <c r="E10" s="36" t="n">
         <f aca="false">COUNTBLANK('Indicadores (F-W)'!Z$6:Z$21)</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F10" s="36" t="n">
         <f aca="false">B10-C10</f>
@@ -22982,11 +23073,11 @@
       </c>
       <c r="B11" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AC$6:AC$21,"Força")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AC$6:AC$21,"Fraqueza")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AC$6:AC$21,"Neutro")</f>
@@ -22994,7 +23085,7 @@
       </c>
       <c r="E11" s="36" t="n">
         <f aca="false">COUNTBLANK('Indicadores (F-W)'!AB$6:AB$21)</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F11" s="36" t="n">
         <f aca="false">B11-C11</f>
@@ -23019,7 +23110,7 @@
       </c>
       <c r="B12" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AE$6:AE$21,"Força")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AE$6:AE$21,"Fraqueza")</f>
@@ -23027,15 +23118,15 @@
       </c>
       <c r="D12" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AE$6:AE$21,"Neutro")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="36" t="n">
         <f aca="false">COUNTBLANK('Indicadores (F-W)'!AD$6:AD$21)</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F12" s="36" t="n">
         <f aca="false">B12-C12</f>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="G12" s="36" t="n">
         <f aca="false">COUNTIFS('Fatores Externos (O-A)'!$B$6:$B$16,"Oportunidade",'Fatores Externos (O-A)'!N$6:N$16,"&gt;="&amp;Parâmetros!$B$5)</f>
@@ -23056,7 +23147,7 @@
       </c>
       <c r="B13" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AG$6:AG$21,"Força")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AG$6:AG$21,"Fraqueza")</f>
@@ -23064,15 +23155,15 @@
       </c>
       <c r="D13" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AG$6:AG$21,"Neutro")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" s="36" t="n">
         <f aca="false">COUNTBLANK('Indicadores (F-W)'!AF$6:AF$21)</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F13" s="36" t="n">
         <f aca="false">B13-C13</f>
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="G13" s="36" t="n">
         <f aca="false">COUNTIFS('Fatores Externos (O-A)'!$B$6:$B$16,"Oportunidade",'Fatores Externos (O-A)'!O$6:O$16,"&gt;="&amp;Parâmetros!$B$5)</f>
@@ -23093,7 +23184,7 @@
       </c>
       <c r="B14" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AI$6:AI$21,"Força")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C14" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AI$6:AI$21,"Fraqueza")</f>
@@ -23105,11 +23196,11 @@
       </c>
       <c r="E14" s="36" t="n">
         <f aca="false">COUNTBLANK('Indicadores (F-W)'!AH$6:AH$21)</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F14" s="36" t="n">
         <f aca="false">B14-C14</f>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="G14" s="36" t="n">
         <f aca="false">COUNTIFS('Fatores Externos (O-A)'!$B$6:$B$16,"Oportunidade",'Fatores Externos (O-A)'!P$6:P$16,"&gt;="&amp;Parâmetros!$B$5)</f>
@@ -23134,19 +23225,19 @@
       </c>
       <c r="C15" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AK$6:AK$21,"Fraqueza")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AK$6:AK$21,"Neutro")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="36" t="n">
         <f aca="false">COUNTBLANK('Indicadores (F-W)'!AJ$6:AJ$21)</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F15" s="36" t="n">
         <f aca="false">B15-C15</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="36" t="n">
         <f aca="false">COUNTIFS('Fatores Externos (O-A)'!$B$6:$B$16,"Oportunidade",'Fatores Externos (O-A)'!Q$6:Q$16,"&gt;="&amp;Parâmetros!$B$5)</f>
@@ -23171,19 +23262,19 @@
       </c>
       <c r="C16" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AM$6:AM$21,"Fraqueza")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AM$6:AM$21,"Neutro")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="36" t="n">
         <f aca="false">COUNTBLANK('Indicadores (F-W)'!AL$6:AL$21)</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F16" s="36" t="n">
         <f aca="false">B16-C16</f>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G16" s="36" t="n">
         <f aca="false">COUNTIFS('Fatores Externos (O-A)'!$B$6:$B$16,"Oportunidade",'Fatores Externos (O-A)'!R$6:R$16,"&gt;="&amp;Parâmetros!$B$5)</f>
@@ -23267,23 +23358,23 @@
       </c>
       <c r="C22" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!$N7:$AM7,"Força")</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D22" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!$N7:$AM7,"Neutro")</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E22" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!$N7:$AM7,"Fraqueza")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="36" t="n">
         <f aca="false">13-C22-D22-E22</f>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G22" s="36" t="str">
         <f aca="false">IF(C22+D22+E22=0,"sem dados",IF(C22&gt;=13/2,"Força regional",IF(E22&gt;=13/2,"Fraqueza regional","Heterogêneo")))</f>
-        <v>sem dados</v>
+        <v>Heterogêneo</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23297,23 +23388,23 @@
       </c>
       <c r="C23" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!$N8:$AM8,"Força")</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D23" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!$N8:$AM8,"Neutro")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E23" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!$N8:$AM8,"Fraqueza")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F23" s="36" t="n">
         <f aca="false">13-C23-D23-E23</f>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G23" s="36" t="str">
         <f aca="false">IF(C23+D23+E23=0,"sem dados",IF(C23&gt;=13/2,"Força regional",IF(E23&gt;=13/2,"Fraqueza regional","Heterogêneo")))</f>
-        <v>sem dados</v>
+        <v>Heterogêneo</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26834,7 +26925,7 @@
       </c>
       <c r="B5" s="53" t="n">
         <f aca="false">Painel!B4</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C5" s="53" t="n">
         <f aca="false">Painel!C4</f>
@@ -26842,15 +26933,15 @@
       </c>
       <c r="D5" s="53" t="n">
         <f aca="false">16-Painel!E4</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E5" s="54" t="n">
         <f aca="false">D5/16</f>
-        <v>0.3125</v>
+        <v>0.4375</v>
       </c>
       <c r="F5" s="55" t="n">
         <f aca="false">IF(D5=0,"",(B5-C5)/D5)</f>
-        <v>-0.8</v>
+        <v>-0.285714285714286</v>
       </c>
       <c r="G5" s="53" t="n">
         <f aca="false">Painel!G4</f>
@@ -26874,11 +26965,11 @@
       </c>
       <c r="L5" s="56" t="n">
         <f aca="false">IF(F5="","",IF(K5="",F5,(F5+K5)/2))</f>
-        <v>-0.445454545454546</v>
+        <v>-0.188311688311688</v>
       </c>
       <c r="M5" s="46" t="n">
         <f aca="false">IF(L5="","",RANK(L5,$L$5:$L$17,0))</f>
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="N5" s="49" t="str">
         <f aca="false">IF(AND(E5&gt;=0.75,J5&gt;=0.75),"Consolidado","PROVISÓRIO")</f>
@@ -26886,7 +26977,7 @@
       </c>
       <c r="T5" s="1" t="n">
         <f aca="false">IF(L5="",-9,L5)-ROW()*0.000000001</f>
-        <v>-0.445454550454546</v>
+        <v>-0.188311693311688</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26895,7 +26986,7 @@
       </c>
       <c r="B6" s="53" t="n">
         <f aca="false">Painel!B5</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="53" t="n">
         <f aca="false">Painel!C5</f>
@@ -26903,15 +26994,15 @@
       </c>
       <c r="D6" s="53" t="n">
         <f aca="false">16-Painel!E5</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E6" s="54" t="n">
         <f aca="false">D6/16</f>
-        <v>0.3125</v>
+        <v>0.4375</v>
       </c>
       <c r="F6" s="55" t="n">
         <f aca="false">IF(D6=0,"",(B6-C6)/D6)</f>
-        <v>-0.6</v>
+        <v>-0.285714285714286</v>
       </c>
       <c r="G6" s="53" t="n">
         <f aca="false">Painel!G5</f>
@@ -26935,11 +27026,11 @@
       </c>
       <c r="L6" s="56" t="n">
         <f aca="false">IF(F6="","",IF(K6="",F6,(F6+K6)/2))</f>
-        <v>-0.209090909090909</v>
+        <v>-0.0519480519480519</v>
       </c>
       <c r="M6" s="46" t="n">
         <f aca="false">IF(L6="","",RANK(L6,$L$5:$L$17,0))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N6" s="49" t="str">
         <f aca="false">IF(AND(E6&gt;=0.75,J6&gt;=0.75),"Consolidado","PROVISÓRIO")</f>
@@ -26947,7 +27038,7 @@
       </c>
       <c r="T6" s="1" t="n">
         <f aca="false">IF(L6="",-9,L6)-ROW()*0.000000001</f>
-        <v>-0.209090915090909</v>
+        <v>-0.0519480579480519</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26956,7 +27047,7 @@
       </c>
       <c r="B7" s="53" t="n">
         <f aca="false">Painel!B6</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="53" t="n">
         <f aca="false">Painel!C6</f>
@@ -26964,15 +27055,15 @@
       </c>
       <c r="D7" s="53" t="n">
         <f aca="false">16-Painel!E6</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E7" s="54" t="n">
         <f aca="false">D7/16</f>
-        <v>0.3125</v>
+        <v>0.4375</v>
       </c>
       <c r="F7" s="55" t="n">
         <f aca="false">IF(D7=0,"",(B7-C7)/D7)</f>
-        <v>-0.6</v>
+        <v>-0.285714285714286</v>
       </c>
       <c r="G7" s="53" t="n">
         <f aca="false">Painel!G6</f>
@@ -26996,11 +27087,11 @@
       </c>
       <c r="L7" s="56" t="n">
         <f aca="false">IF(F7="","",IF(K7="",F7,(F7+K7)/2))</f>
-        <v>-0.345454545454545</v>
+        <v>-0.188311688311688</v>
       </c>
       <c r="M7" s="46" t="n">
         <f aca="false">IF(L7="","",RANK(L7,$L$5:$L$17,0))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N7" s="49" t="str">
         <f aca="false">IF(AND(E7&gt;=0.75,J7&gt;=0.75),"Consolidado","PROVISÓRIO")</f>
@@ -27008,7 +27099,7 @@
       </c>
       <c r="T7" s="1" t="n">
         <f aca="false">IF(L7="",-9,L7)-ROW()*0.000000001</f>
-        <v>-0.345454552454546</v>
+        <v>-0.188311695311688</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27017,7 +27108,7 @@
       </c>
       <c r="B8" s="53" t="n">
         <f aca="false">Painel!B7</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="53" t="n">
         <f aca="false">Painel!C7</f>
@@ -27025,15 +27116,15 @@
       </c>
       <c r="D8" s="53" t="n">
         <f aca="false">16-Painel!E7</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E8" s="54" t="n">
         <f aca="false">D8/16</f>
-        <v>0.3125</v>
+        <v>0.4375</v>
       </c>
       <c r="F8" s="55" t="n">
         <f aca="false">IF(D8=0,"",(B8-C8)/D8)</f>
-        <v>-0.6</v>
+        <v>-0.285714285714286</v>
       </c>
       <c r="G8" s="53" t="n">
         <f aca="false">Painel!G7</f>
@@ -27057,11 +27148,11 @@
       </c>
       <c r="L8" s="56" t="n">
         <f aca="false">IF(F8="","",IF(K8="",F8,(F8+K8)/2))</f>
-        <v>-0.345454545454545</v>
+        <v>-0.188311688311688</v>
       </c>
       <c r="M8" s="46" t="n">
         <f aca="false">IF(L8="","",RANK(L8,$L$5:$L$17,0))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N8" s="49" t="str">
         <f aca="false">IF(AND(E8&gt;=0.75,J8&gt;=0.75),"Consolidado","PROVISÓRIO")</f>
@@ -27069,7 +27160,7 @@
       </c>
       <c r="T8" s="1" t="n">
         <f aca="false">IF(L8="",-9,L8)-ROW()*0.000000001</f>
-        <v>-0.345454553454545</v>
+        <v>-0.188311696311688</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27078,7 +27169,7 @@
       </c>
       <c r="B9" s="53" t="n">
         <f aca="false">Painel!B8</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" s="53" t="n">
         <f aca="false">Painel!C8</f>
@@ -27086,15 +27177,15 @@
       </c>
       <c r="D9" s="53" t="n">
         <f aca="false">16-Painel!E8</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E9" s="54" t="n">
         <f aca="false">D9/16</f>
-        <v>0.3125</v>
+        <v>0.4375</v>
       </c>
       <c r="F9" s="55" t="n">
         <f aca="false">IF(D9=0,"",(B9-C9)/D9)</f>
-        <v>0.6</v>
+        <v>0.571428571428571</v>
       </c>
       <c r="G9" s="53" t="n">
         <f aca="false">Painel!G8</f>
@@ -27118,7 +27209,7 @@
       </c>
       <c r="L9" s="56" t="n">
         <f aca="false">IF(F9="","",IF(K9="",F9,(F9+K9)/2))</f>
-        <v>0.3</v>
+        <v>0.285714285714286</v>
       </c>
       <c r="M9" s="46" t="n">
         <f aca="false">IF(L9="","",RANK(L9,$L$5:$L$17,0))</f>
@@ -27130,7 +27221,7 @@
       </c>
       <c r="T9" s="1" t="n">
         <f aca="false">IF(L9="",-9,L9)-ROW()*0.000000001</f>
-        <v>0.299999991</v>
+        <v>0.285714276714286</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27147,15 +27238,15 @@
       </c>
       <c r="D10" s="53" t="n">
         <f aca="false">16-Painel!E9</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E10" s="54" t="n">
         <f aca="false">D10/16</f>
-        <v>0.3125</v>
+        <v>0.4375</v>
       </c>
       <c r="F10" s="55" t="n">
         <f aca="false">IF(D10=0,"",(B10-C10)/D10)</f>
-        <v>-0.4</v>
+        <v>-0.285714285714286</v>
       </c>
       <c r="G10" s="53" t="n">
         <f aca="false">Painel!G9</f>
@@ -27179,11 +27270,11 @@
       </c>
       <c r="L10" s="56" t="n">
         <f aca="false">IF(F10="","",IF(K10="",F10,(F10+K10)/2))</f>
-        <v>-0.154545454545455</v>
+        <v>-0.0974025974025974</v>
       </c>
       <c r="M10" s="46" t="n">
         <f aca="false">IF(L10="","",RANK(L10,$L$5:$L$17,0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N10" s="49" t="str">
         <f aca="false">IF(AND(E10&gt;=0.75,J10&gt;=0.75),"Consolidado","PROVISÓRIO")</f>
@@ -27191,7 +27282,7 @@
       </c>
       <c r="T10" s="1" t="n">
         <f aca="false">IF(L10="",-9,L10)-ROW()*0.000000001</f>
-        <v>-0.154545464545455</v>
+        <v>-0.0974026074025974</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27200,23 +27291,23 @@
       </c>
       <c r="B11" s="53" t="n">
         <f aca="false">Painel!B10</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="53" t="n">
         <f aca="false">Painel!C10</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" s="53" t="n">
         <f aca="false">16-Painel!E10</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E11" s="54" t="n">
         <f aca="false">D11/16</f>
-        <v>0.3125</v>
+        <v>0.4375</v>
       </c>
       <c r="F11" s="55" t="n">
         <f aca="false">IF(D11=0,"",(B11-C11)/D11)</f>
-        <v>-0.4</v>
+        <v>-0.285714285714286</v>
       </c>
       <c r="G11" s="53" t="n">
         <f aca="false">Painel!G10</f>
@@ -27240,11 +27331,11 @@
       </c>
       <c r="L11" s="56" t="n">
         <f aca="false">IF(F11="","",IF(K11="",F11,(F11+K11)/2))</f>
-        <v>-0.245454545454545</v>
+        <v>-0.188311688311688</v>
       </c>
       <c r="M11" s="46" t="n">
         <f aca="false">IF(L11="","",RANK(L11,$L$5:$L$17,0))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N11" s="49" t="str">
         <f aca="false">IF(AND(E11&gt;=0.75,J11&gt;=0.75),"Consolidado","PROVISÓRIO")</f>
@@ -27252,7 +27343,7 @@
       </c>
       <c r="T11" s="1" t="n">
         <f aca="false">IF(L11="",-9,L11)-ROW()*0.000000001</f>
-        <v>-0.245454556454545</v>
+        <v>-0.188311699311688</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27261,23 +27352,23 @@
       </c>
       <c r="B12" s="53" t="n">
         <f aca="false">Painel!B11</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="53" t="n">
         <f aca="false">Painel!C11</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="53" t="n">
         <f aca="false">16-Painel!E11</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E12" s="54" t="n">
         <f aca="false">D12/16</f>
-        <v>0.3125</v>
+        <v>0.4375</v>
       </c>
       <c r="F12" s="55" t="n">
         <f aca="false">IF(D12=0,"",(B12-C12)/D12)</f>
-        <v>-0.4</v>
+        <v>-0.285714285714286</v>
       </c>
       <c r="G12" s="53" t="n">
         <f aca="false">Painel!G11</f>
@@ -27301,7 +27392,7 @@
       </c>
       <c r="L12" s="56" t="n">
         <f aca="false">IF(F12="","",IF(K12="",F12,(F12+K12)/2))</f>
-        <v>-0.0636363636363637</v>
+        <v>-0.0064935064935065</v>
       </c>
       <c r="M12" s="46" t="n">
         <f aca="false">IF(L12="","",RANK(L12,$L$5:$L$17,0))</f>
@@ -27313,7 +27404,7 @@
       </c>
       <c r="T12" s="1" t="n">
         <f aca="false">IF(L12="",-9,L12)-ROW()*0.000000001</f>
-        <v>-0.0636363756363637</v>
+        <v>-0.0064935184935065</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27322,7 +27413,7 @@
       </c>
       <c r="B13" s="53" t="n">
         <f aca="false">Painel!B12</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="53" t="n">
         <f aca="false">Painel!C12</f>
@@ -27330,15 +27421,15 @@
       </c>
       <c r="D13" s="53" t="n">
         <f aca="false">16-Painel!E12</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E13" s="54" t="n">
         <f aca="false">D13/16</f>
-        <v>0.3125</v>
+        <v>0.4375</v>
       </c>
       <c r="F13" s="55" t="n">
         <f aca="false">IF(D13=0,"",(B13-C13)/D13)</f>
-        <v>-0.6</v>
+        <v>-0.285714285714286</v>
       </c>
       <c r="G13" s="53" t="n">
         <f aca="false">Painel!G12</f>
@@ -27362,11 +27453,11 @@
       </c>
       <c r="L13" s="56" t="n">
         <f aca="false">IF(F13="","",IF(K13="",F13,(F13+K13)/2))</f>
-        <v>-0.254545454545455</v>
+        <v>-0.0974025974025974</v>
       </c>
       <c r="M13" s="46" t="n">
         <f aca="false">IF(L13="","",RANK(L13,$L$5:$L$17,0))</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N13" s="49" t="str">
         <f aca="false">IF(AND(E13&gt;=0.75,J13&gt;=0.75),"Consolidado","PROVISÓRIO")</f>
@@ -27374,7 +27465,7 @@
       </c>
       <c r="T13" s="1" t="n">
         <f aca="false">IF(L13="",-9,L13)-ROW()*0.000000001</f>
-        <v>-0.254545467545455</v>
+        <v>-0.0974026104025974</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27383,7 +27474,7 @@
       </c>
       <c r="B14" s="53" t="n">
         <f aca="false">Painel!B13</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" s="53" t="n">
         <f aca="false">Painel!C13</f>
@@ -27391,15 +27482,15 @@
       </c>
       <c r="D14" s="53" t="n">
         <f aca="false">16-Painel!E13</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E14" s="54" t="n">
         <f aca="false">D14/16</f>
-        <v>0.3125</v>
+        <v>0.4375</v>
       </c>
       <c r="F14" s="55" t="n">
         <f aca="false">IF(D14=0,"",(B14-C14)/D14)</f>
-        <v>-0.8</v>
+        <v>-0.428571428571429</v>
       </c>
       <c r="G14" s="53" t="n">
         <f aca="false">Painel!G13</f>
@@ -27423,7 +27514,7 @@
       </c>
       <c r="L14" s="56" t="n">
         <f aca="false">IF(F14="","",IF(K14="",F14,(F14+K14)/2))</f>
-        <v>-0.4</v>
+        <v>-0.214285714285714</v>
       </c>
       <c r="M14" s="46" t="n">
         <f aca="false">IF(L14="","",RANK(L14,$L$5:$L$17,0))</f>
@@ -27435,7 +27526,7 @@
       </c>
       <c r="T14" s="1" t="n">
         <f aca="false">IF(L14="",-9,L14)-ROW()*0.000000001</f>
-        <v>-0.400000014</v>
+        <v>-0.214285728285714</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27444,7 +27535,7 @@
       </c>
       <c r="B15" s="53" t="n">
         <f aca="false">Painel!B14</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C15" s="53" t="n">
         <f aca="false">Painel!C14</f>
@@ -27452,15 +27543,15 @@
       </c>
       <c r="D15" s="53" t="n">
         <f aca="false">16-Painel!E14</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E15" s="54" t="n">
         <f aca="false">D15/16</f>
-        <v>0.3125</v>
+        <v>0.4375</v>
       </c>
       <c r="F15" s="55" t="n">
         <f aca="false">IF(D15=0,"",(B15-C15)/D15)</f>
-        <v>-0.6</v>
+        <v>-0.142857142857143</v>
       </c>
       <c r="G15" s="53" t="n">
         <f aca="false">Painel!G14</f>
@@ -27484,11 +27575,11 @@
       </c>
       <c r="L15" s="56" t="n">
         <f aca="false">IF(F15="","",IF(K15="",F15,(F15+K15)/2))</f>
-        <v>-0.345454545454545</v>
+        <v>-0.116883116883117</v>
       </c>
       <c r="M15" s="46" t="n">
         <f aca="false">IF(L15="","",RANK(L15,$L$5:$L$17,0))</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N15" s="49" t="str">
         <f aca="false">IF(AND(E15&gt;=0.75,J15&gt;=0.75),"Consolidado","PROVISÓRIO")</f>
@@ -27496,7 +27587,7 @@
       </c>
       <c r="T15" s="1" t="n">
         <f aca="false">IF(L15="",-9,L15)-ROW()*0.000000001</f>
-        <v>-0.345454560454546</v>
+        <v>-0.116883131883117</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27509,19 +27600,19 @@
       </c>
       <c r="C16" s="53" t="n">
         <f aca="false">Painel!C15</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="53" t="n">
         <f aca="false">16-Painel!E15</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E16" s="54" t="n">
         <f aca="false">D16/16</f>
-        <v>0.3125</v>
+        <v>0.4375</v>
       </c>
       <c r="F16" s="55" t="n">
         <f aca="false">IF(D16=0,"",(B16-C16)/D16)</f>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G16" s="53" t="n">
         <f aca="false">Painel!G15</f>
@@ -27545,7 +27636,7 @@
       </c>
       <c r="L16" s="56" t="n">
         <f aca="false">IF(F16="","",IF(K16="",F16,(F16+K16)/2))</f>
-        <v>0.190909090909091</v>
+        <v>0.0909090909090909</v>
       </c>
       <c r="M16" s="46" t="n">
         <f aca="false">IF(L16="","",RANK(L16,$L$5:$L$17,0))</f>
@@ -27557,7 +27648,7 @@
       </c>
       <c r="T16" s="1" t="n">
         <f aca="false">IF(L16="",-9,L16)-ROW()*0.000000001</f>
-        <v>0.190909074909091</v>
+        <v>0.0909090749090909</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27570,19 +27661,19 @@
       </c>
       <c r="C17" s="53" t="n">
         <f aca="false">Painel!C16</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" s="53" t="n">
         <f aca="false">16-Painel!E16</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E17" s="54" t="n">
         <f aca="false">D17/16</f>
-        <v>0.3125</v>
+        <v>0.4375</v>
       </c>
       <c r="F17" s="55" t="n">
         <f aca="false">IF(D17=0,"",(B17-C17)/D17)</f>
-        <v>-0.6</v>
+        <v>-0.571428571428571</v>
       </c>
       <c r="G17" s="53" t="n">
         <f aca="false">Painel!G16</f>
@@ -27606,11 +27697,11 @@
       </c>
       <c r="L17" s="56" t="n">
         <f aca="false">IF(F17="","",IF(K17="",F17,(F17+K17)/2))</f>
-        <v>-0.3</v>
+        <v>-0.285714285714286</v>
       </c>
       <c r="M17" s="46" t="n">
         <f aca="false">IF(L17="","",RANK(L17,$L$5:$L$17,0))</f>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="N17" s="49" t="str">
         <f aca="false">IF(AND(E17&gt;=0.75,J17&gt;=0.75),"Consolidado","PROVISÓRIO")</f>
@@ -27618,7 +27709,7 @@
       </c>
       <c r="T17" s="1" t="n">
         <f aca="false">IF(L17="",-9,L17)-ROW()*0.000000001</f>
-        <v>-0.300000017</v>
+        <v>-0.285714302714286</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27657,11 +27748,11 @@
       </c>
       <c r="C22" s="55" t="n">
         <f aca="false">INDEX($L$5:$L$17,MATCH(LARGE($T$5:$T$17,1),$T$5:$T$17,0))</f>
-        <v>0.3</v>
+        <v>0.285714285714286</v>
       </c>
       <c r="D22" s="54" t="n">
         <f aca="false">INDEX($E$5:$E$17,MATCH(LARGE($T$5:$T$17,1),$T$5:$T$17,0))</f>
-        <v>0.3125</v>
+        <v>0.4375</v>
       </c>
       <c r="E22" s="54" t="n">
         <f aca="false">INDEX($J$5:$J$17,MATCH(LARGE($T$5:$T$17,1),$T$5:$T$17,0))</f>
@@ -27683,11 +27774,11 @@
       </c>
       <c r="C23" s="55" t="n">
         <f aca="false">INDEX($L$5:$L$17,MATCH(LARGE($T$5:$T$17,2),$T$5:$T$17,0))</f>
-        <v>0.190909090909091</v>
+        <v>0.0909090909090909</v>
       </c>
       <c r="D23" s="54" t="n">
         <f aca="false">INDEX($E$5:$E$17,MATCH(LARGE($T$5:$T$17,2),$T$5:$T$17,0))</f>
-        <v>0.3125</v>
+        <v>0.4375</v>
       </c>
       <c r="E23" s="54" t="n">
         <f aca="false">INDEX($J$5:$J$17,MATCH(LARGE($T$5:$T$17,2),$T$5:$T$17,0))</f>
@@ -27709,11 +27800,11 @@
       </c>
       <c r="C24" s="55" t="n">
         <f aca="false">INDEX($L$5:$L$17,MATCH(LARGE($T$5:$T$17,3),$T$5:$T$17,0))</f>
-        <v>-0.0636363636363637</v>
+        <v>-0.0064935064935065</v>
       </c>
       <c r="D24" s="54" t="n">
         <f aca="false">INDEX($E$5:$E$17,MATCH(LARGE($T$5:$T$17,3),$T$5:$T$17,0))</f>
-        <v>0.3125</v>
+        <v>0.4375</v>
       </c>
       <c r="E24" s="54" t="n">
         <f aca="false">INDEX($J$5:$J$17,MATCH(LARGE($T$5:$T$17,3),$T$5:$T$17,0))</f>
@@ -27731,15 +27822,15 @@
       </c>
       <c r="B25" s="38" t="str">
         <f aca="false">INDEX($A$5:$A$17,MATCH(LARGE($T$5:$T$17,4),$T$5:$T$17,0))</f>
-        <v>Juscimeira</v>
+        <v>Cáceres</v>
       </c>
       <c r="C25" s="55" t="n">
         <f aca="false">INDEX($L$5:$L$17,MATCH(LARGE($T$5:$T$17,4),$T$5:$T$17,0))</f>
-        <v>-0.154545454545455</v>
+        <v>-0.0519480519480519</v>
       </c>
       <c r="D25" s="54" t="n">
         <f aca="false">INDEX($E$5:$E$17,MATCH(LARGE($T$5:$T$17,4),$T$5:$T$17,0))</f>
-        <v>0.3125</v>
+        <v>0.4375</v>
       </c>
       <c r="E25" s="54" t="n">
         <f aca="false">INDEX($J$5:$J$17,MATCH(LARGE($T$5:$T$17,4),$T$5:$T$17,0))</f>
@@ -27757,15 +27848,15 @@
       </c>
       <c r="B26" s="38" t="str">
         <f aca="false">INDEX($A$5:$A$17,MATCH(LARGE($T$5:$T$17,5),$T$5:$T$17,0))</f>
-        <v>Cáceres</v>
+        <v>Juscimeira</v>
       </c>
       <c r="C26" s="55" t="n">
         <f aca="false">INDEX($L$5:$L$17,MATCH(LARGE($T$5:$T$17,5),$T$5:$T$17,0))</f>
-        <v>-0.209090909090909</v>
+        <v>-0.0974025974025974</v>
       </c>
       <c r="D26" s="54" t="n">
         <f aca="false">INDEX($E$5:$E$17,MATCH(LARGE($T$5:$T$17,5),$T$5:$T$17,0))</f>
-        <v>0.3125</v>
+        <v>0.4375</v>
       </c>
       <c r="E26" s="54" t="n">
         <f aca="false">INDEX($J$5:$J$17,MATCH(LARGE($T$5:$T$17,5),$T$5:$T$17,0))</f>
@@ -27779,19 +27870,19 @@
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="46" t="n">
         <f aca="false">INDEX($M$5:$M$17,MATCH(LARGE($T$5:$T$17,6),$T$5:$T$17,0))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B27" s="38" t="str">
         <f aca="false">INDEX($A$5:$A$17,MATCH(LARGE($T$5:$T$17,6),$T$5:$T$17,0))</f>
-        <v>Lambari D'Oeste</v>
+        <v>Nossa Senhora do Livramento</v>
       </c>
       <c r="C27" s="55" t="n">
         <f aca="false">INDEX($L$5:$L$17,MATCH(LARGE($T$5:$T$17,6),$T$5:$T$17,0))</f>
-        <v>-0.245454545454545</v>
+        <v>-0.0974025974025974</v>
       </c>
       <c r="D27" s="54" t="n">
         <f aca="false">INDEX($E$5:$E$17,MATCH(LARGE($T$5:$T$17,6),$T$5:$T$17,0))</f>
-        <v>0.3125</v>
+        <v>0.4375</v>
       </c>
       <c r="E27" s="54" t="n">
         <f aca="false">INDEX($J$5:$J$17,MATCH(LARGE($T$5:$T$17,6),$T$5:$T$17,0))</f>
@@ -27809,15 +27900,15 @@
       </c>
       <c r="B28" s="38" t="str">
         <f aca="false">INDEX($A$5:$A$17,MATCH(LARGE($T$5:$T$17,7),$T$5:$T$17,0))</f>
-        <v>Nossa Senhora do Livramento</v>
+        <v>Porto Esperidião</v>
       </c>
       <c r="C28" s="55" t="n">
         <f aca="false">INDEX($L$5:$L$17,MATCH(LARGE($T$5:$T$17,7),$T$5:$T$17,0))</f>
-        <v>-0.254545454545455</v>
+        <v>-0.116883116883117</v>
       </c>
       <c r="D28" s="54" t="n">
         <f aca="false">INDEX($E$5:$E$17,MATCH(LARGE($T$5:$T$17,7),$T$5:$T$17,0))</f>
-        <v>0.3125</v>
+        <v>0.4375</v>
       </c>
       <c r="E28" s="54" t="n">
         <f aca="false">INDEX($J$5:$J$17,MATCH(LARGE($T$5:$T$17,7),$T$5:$T$17,0))</f>
@@ -27835,15 +27926,15 @@
       </c>
       <c r="B29" s="38" t="str">
         <f aca="false">INDEX($A$5:$A$17,MATCH(LARGE($T$5:$T$17,8),$T$5:$T$17,0))</f>
-        <v>Santo Antônio do Leverger</v>
+        <v>Barão de Melgaço</v>
       </c>
       <c r="C29" s="55" t="n">
         <f aca="false">INDEX($L$5:$L$17,MATCH(LARGE($T$5:$T$17,8),$T$5:$T$17,0))</f>
-        <v>-0.3</v>
+        <v>-0.188311688311688</v>
       </c>
       <c r="D29" s="54" t="n">
         <f aca="false">INDEX($E$5:$E$17,MATCH(LARGE($T$5:$T$17,8),$T$5:$T$17,0))</f>
-        <v>0.3125</v>
+        <v>0.4375</v>
       </c>
       <c r="E29" s="54" t="n">
         <f aca="false">INDEX($J$5:$J$17,MATCH(LARGE($T$5:$T$17,8),$T$5:$T$17,0))</f>
@@ -27857,7 +27948,7 @@
     <row r="30" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="46" t="n">
         <f aca="false">INDEX($M$5:$M$17,MATCH(LARGE($T$5:$T$17,9),$T$5:$T$17,0))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B30" s="38" t="str">
         <f aca="false">INDEX($A$5:$A$17,MATCH(LARGE($T$5:$T$17,9),$T$5:$T$17,0))</f>
@@ -27865,11 +27956,11 @@
       </c>
       <c r="C30" s="55" t="n">
         <f aca="false">INDEX($L$5:$L$17,MATCH(LARGE($T$5:$T$17,9),$T$5:$T$17,0))</f>
-        <v>-0.345454545454545</v>
+        <v>-0.188311688311688</v>
       </c>
       <c r="D30" s="54" t="n">
         <f aca="false">INDEX($E$5:$E$17,MATCH(LARGE($T$5:$T$17,9),$T$5:$T$17,0))</f>
-        <v>0.3125</v>
+        <v>0.4375</v>
       </c>
       <c r="E30" s="54" t="n">
         <f aca="false">INDEX($J$5:$J$17,MATCH(LARGE($T$5:$T$17,9),$T$5:$T$17,0))</f>
@@ -27883,7 +27974,7 @@
     <row r="31" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="46" t="n">
         <f aca="false">INDEX($M$5:$M$17,MATCH(LARGE($T$5:$T$17,10),$T$5:$T$17,0))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B31" s="38" t="str">
         <f aca="false">INDEX($A$5:$A$17,MATCH(LARGE($T$5:$T$17,10),$T$5:$T$17,0))</f>
@@ -27891,11 +27982,11 @@
       </c>
       <c r="C31" s="55" t="n">
         <f aca="false">INDEX($L$5:$L$17,MATCH(LARGE($T$5:$T$17,10),$T$5:$T$17,0))</f>
-        <v>-0.345454545454545</v>
+        <v>-0.188311688311688</v>
       </c>
       <c r="D31" s="54" t="n">
         <f aca="false">INDEX($E$5:$E$17,MATCH(LARGE($T$5:$T$17,10),$T$5:$T$17,0))</f>
-        <v>0.3125</v>
+        <v>0.4375</v>
       </c>
       <c r="E31" s="54" t="n">
         <f aca="false">INDEX($J$5:$J$17,MATCH(LARGE($T$5:$T$17,10),$T$5:$T$17,0))</f>
@@ -27909,19 +28000,19 @@
     <row r="32" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="46" t="n">
         <f aca="false">INDEX($M$5:$M$17,MATCH(LARGE($T$5:$T$17,11),$T$5:$T$17,0))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B32" s="38" t="str">
         <f aca="false">INDEX($A$5:$A$17,MATCH(LARGE($T$5:$T$17,11),$T$5:$T$17,0))</f>
-        <v>Porto Esperidião</v>
+        <v>Lambari D'Oeste</v>
       </c>
       <c r="C32" s="55" t="n">
         <f aca="false">INDEX($L$5:$L$17,MATCH(LARGE($T$5:$T$17,11),$T$5:$T$17,0))</f>
-        <v>-0.345454545454545</v>
+        <v>-0.188311688311688</v>
       </c>
       <c r="D32" s="54" t="n">
         <f aca="false">INDEX($E$5:$E$17,MATCH(LARGE($T$5:$T$17,11),$T$5:$T$17,0))</f>
-        <v>0.3125</v>
+        <v>0.4375</v>
       </c>
       <c r="E32" s="54" t="n">
         <f aca="false">INDEX($J$5:$J$17,MATCH(LARGE($T$5:$T$17,11),$T$5:$T$17,0))</f>
@@ -27943,11 +28034,11 @@
       </c>
       <c r="C33" s="55" t="n">
         <f aca="false">INDEX($L$5:$L$17,MATCH(LARGE($T$5:$T$17,12),$T$5:$T$17,0))</f>
-        <v>-0.4</v>
+        <v>-0.214285714285714</v>
       </c>
       <c r="D33" s="54" t="n">
         <f aca="false">INDEX($E$5:$E$17,MATCH(LARGE($T$5:$T$17,12),$T$5:$T$17,0))</f>
-        <v>0.3125</v>
+        <v>0.4375</v>
       </c>
       <c r="E33" s="54" t="n">
         <f aca="false">INDEX($J$5:$J$17,MATCH(LARGE($T$5:$T$17,12),$T$5:$T$17,0))</f>
@@ -27965,15 +28056,15 @@
       </c>
       <c r="B34" s="38" t="str">
         <f aca="false">INDEX($A$5:$A$17,MATCH(LARGE($T$5:$T$17,13),$T$5:$T$17,0))</f>
-        <v>Barão de Melgaço</v>
+        <v>Santo Antônio do Leverger</v>
       </c>
       <c r="C34" s="55" t="n">
         <f aca="false">INDEX($L$5:$L$17,MATCH(LARGE($T$5:$T$17,13),$T$5:$T$17,0))</f>
-        <v>-0.445454545454546</v>
+        <v>-0.285714285714286</v>
       </c>
       <c r="D34" s="54" t="n">
         <f aca="false">INDEX($E$5:$E$17,MATCH(LARGE($T$5:$T$17,13),$T$5:$T$17,0))</f>
-        <v>0.3125</v>
+        <v>0.4375</v>
       </c>
       <c r="E34" s="54" t="n">
         <f aca="false">INDEX($J$5:$J$17,MATCH(LARGE($T$5:$T$17,13),$T$5:$T$17,0))</f>
@@ -28083,7 +28174,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
@@ -28230,7 +28321,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="62" t="s">
         <v>162</v>
       </c>
@@ -28267,6 +28358,96 @@
       <c r="C21" s="60"/>
       <c r="D21" s="60"/>
       <c r="E21" s="60"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="63" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="57" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="57" t="s">
+        <v>129</v>
+      </c>
+      <c r="C24" s="57" t="s">
+        <v>130</v>
+      </c>
+      <c r="D24" s="57" t="s">
+        <v>131</v>
+      </c>
+      <c r="E24" s="57" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="58" t="s">
+        <v>169</v>
+      </c>
+      <c r="B25" s="58" t="s">
+        <v>170</v>
+      </c>
+      <c r="C25" s="58" t="s">
+        <v>171</v>
+      </c>
+      <c r="D25" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="E25" s="58" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="58" t="s">
+        <v>174</v>
+      </c>
+      <c r="B26" s="58" t="s">
+        <v>175</v>
+      </c>
+      <c r="C26" s="58" t="s">
+        <v>176</v>
+      </c>
+      <c r="D26" s="58" t="s">
+        <v>177</v>
+      </c>
+      <c r="E26" s="58" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="58" t="s">
+        <v>142</v>
+      </c>
+      <c r="B27" s="58" t="s">
+        <v>143</v>
+      </c>
+      <c r="C27" s="58" t="s">
+        <v>179</v>
+      </c>
+      <c r="D27" s="58" t="s">
+        <v>180</v>
+      </c>
+      <c r="E27" s="58" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="58" t="s">
+        <v>182</v>
+      </c>
+      <c r="B28" s="58" t="s">
+        <v>183</v>
+      </c>
+      <c r="C28" s="58" t="s">
+        <v>184</v>
+      </c>
+      <c r="D28" s="58" t="s">
+        <v>185</v>
+      </c>
+      <c r="E28" s="58" t="s">
+        <v>186</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -28300,42 +28481,42 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="47" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="40" t="s">
-        <v>169</v>
-      </c>
-      <c r="B3" s="63" t="n">
+        <v>188</v>
+      </c>
+      <c r="B3" s="64" t="n">
         <v>0.1</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="40" t="s">
-        <v>171</v>
-      </c>
-      <c r="B4" s="64" t="n">
+        <v>190</v>
+      </c>
+      <c r="B4" s="65" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="B5" s="65" t="n">
+        <v>191</v>
+      </c>
+      <c r="B5" s="66" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28462,1965 +28643,2025 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="66" t="s">
+      <c r="A4" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="66" t="s">
-        <v>177</v>
-      </c>
-      <c r="C4" s="66" t="s">
+      <c r="B4" s="67" t="s">
+        <v>196</v>
+      </c>
+      <c r="C4" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="66" t="s">
-        <v>178</v>
-      </c>
-      <c r="E4" s="66" t="s">
-        <v>179</v>
-      </c>
-      <c r="F4" s="66" t="s">
-        <v>180</v>
-      </c>
-      <c r="G4" s="66" t="s">
-        <v>181</v>
-      </c>
-      <c r="H4" s="66" t="s">
-        <v>182</v>
-      </c>
-      <c r="I4" s="66" t="s">
-        <v>183</v>
-      </c>
-      <c r="J4" s="66" t="s">
-        <v>184</v>
-      </c>
-      <c r="K4" s="66" t="s">
-        <v>185</v>
-      </c>
-      <c r="L4" s="66" t="s">
-        <v>186</v>
-      </c>
-      <c r="M4" s="66" t="s">
-        <v>187</v>
-      </c>
-      <c r="N4" s="66" t="s">
+      <c r="D4" s="67" t="s">
+        <v>197</v>
+      </c>
+      <c r="E4" s="67" t="s">
+        <v>198</v>
+      </c>
+      <c r="F4" s="67" t="s">
+        <v>199</v>
+      </c>
+      <c r="G4" s="67" t="s">
+        <v>200</v>
+      </c>
+      <c r="H4" s="67" t="s">
+        <v>201</v>
+      </c>
+      <c r="I4" s="67" t="s">
+        <v>202</v>
+      </c>
+      <c r="J4" s="67" t="s">
+        <v>203</v>
+      </c>
+      <c r="K4" s="67" t="s">
+        <v>204</v>
+      </c>
+      <c r="L4" s="67" t="s">
+        <v>205</v>
+      </c>
+      <c r="M4" s="67" t="s">
+        <v>206</v>
+      </c>
+      <c r="N4" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="O4" s="66"/>
-      <c r="P4" s="66" t="s">
+      <c r="O4" s="67"/>
+      <c r="P4" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="Q4" s="66"/>
-      <c r="R4" s="66" t="s">
+      <c r="Q4" s="67"/>
+      <c r="R4" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="S4" s="66"/>
-      <c r="T4" s="66" t="s">
+      <c r="S4" s="67"/>
+      <c r="T4" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="U4" s="66"/>
-      <c r="V4" s="66" t="s">
+      <c r="U4" s="67"/>
+      <c r="V4" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="W4" s="66"/>
-      <c r="X4" s="66" t="s">
+      <c r="W4" s="67"/>
+      <c r="X4" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="Y4" s="66"/>
-      <c r="Z4" s="66" t="s">
+      <c r="Y4" s="67"/>
+      <c r="Z4" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="AA4" s="66"/>
-      <c r="AB4" s="66" t="s">
+      <c r="AA4" s="67"/>
+      <c r="AB4" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="AC4" s="66"/>
-      <c r="AD4" s="66" t="s">
+      <c r="AC4" s="67"/>
+      <c r="AD4" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="AE4" s="66"/>
-      <c r="AF4" s="66" t="s">
+      <c r="AE4" s="67"/>
+      <c r="AF4" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="AG4" s="66"/>
-      <c r="AH4" s="66" t="s">
+      <c r="AG4" s="67"/>
+      <c r="AH4" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="AI4" s="66"/>
-      <c r="AJ4" s="66" t="s">
+      <c r="AI4" s="67"/>
+      <c r="AJ4" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="AK4" s="66"/>
-      <c r="AL4" s="66" t="s">
+      <c r="AK4" s="67"/>
+      <c r="AL4" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="AM4" s="66"/>
+      <c r="AM4" s="67"/>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="66"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="66"/>
-      <c r="K5" s="66"/>
-      <c r="L5" s="66"/>
-      <c r="M5" s="66"/>
-      <c r="N5" s="67" t="s">
-        <v>188</v>
-      </c>
-      <c r="O5" s="67" t="s">
+      <c r="A5" s="67"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="67"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="68" t="s">
+        <v>207</v>
+      </c>
+      <c r="O5" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="P5" s="67" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q5" s="67" t="s">
+      <c r="P5" s="68" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q5" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="R5" s="67" t="s">
-        <v>188</v>
-      </c>
-      <c r="S5" s="67" t="s">
+      <c r="R5" s="68" t="s">
+        <v>207</v>
+      </c>
+      <c r="S5" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="T5" s="67" t="s">
-        <v>188</v>
-      </c>
-      <c r="U5" s="67" t="s">
+      <c r="T5" s="68" t="s">
+        <v>207</v>
+      </c>
+      <c r="U5" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="V5" s="67" t="s">
-        <v>188</v>
-      </c>
-      <c r="W5" s="67" t="s">
+      <c r="V5" s="68" t="s">
+        <v>207</v>
+      </c>
+      <c r="W5" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="X5" s="67" t="s">
-        <v>188</v>
-      </c>
-      <c r="Y5" s="67" t="s">
+      <c r="X5" s="68" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y5" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="Z5" s="67" t="s">
-        <v>188</v>
-      </c>
-      <c r="AA5" s="67" t="s">
+      <c r="Z5" s="68" t="s">
+        <v>207</v>
+      </c>
+      <c r="AA5" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="AB5" s="67" t="s">
-        <v>188</v>
-      </c>
-      <c r="AC5" s="67" t="s">
+      <c r="AB5" s="68" t="s">
+        <v>207</v>
+      </c>
+      <c r="AC5" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="AD5" s="67" t="s">
-        <v>188</v>
-      </c>
-      <c r="AE5" s="67" t="s">
+      <c r="AD5" s="68" t="s">
+        <v>207</v>
+      </c>
+      <c r="AE5" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="AF5" s="67" t="s">
-        <v>188</v>
-      </c>
-      <c r="AG5" s="67" t="s">
+      <c r="AF5" s="68" t="s">
+        <v>207</v>
+      </c>
+      <c r="AG5" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="AH5" s="67" t="s">
-        <v>188</v>
-      </c>
-      <c r="AI5" s="67" t="s">
+      <c r="AH5" s="68" t="s">
+        <v>207</v>
+      </c>
+      <c r="AI5" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="AJ5" s="67" t="s">
-        <v>188</v>
-      </c>
-      <c r="AK5" s="67" t="s">
+      <c r="AJ5" s="68" t="s">
+        <v>207</v>
+      </c>
+      <c r="AK5" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="AL5" s="67" t="s">
-        <v>188</v>
-      </c>
-      <c r="AM5" s="67" t="s">
+      <c r="AL5" s="68" t="s">
+        <v>207</v>
+      </c>
+      <c r="AM5" s="68" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="68" t="s">
-        <v>189</v>
-      </c>
-      <c r="B6" s="69" t="s">
+      <c r="A6" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="B6" s="70" t="s">
         <v>74</v>
       </c>
-      <c r="C6" s="69" t="s">
-        <v>190</v>
-      </c>
-      <c r="D6" s="68" t="s">
-        <v>191</v>
-      </c>
-      <c r="E6" s="70" t="s">
-        <v>192</v>
-      </c>
-      <c r="F6" s="69" t="s">
-        <v>193</v>
-      </c>
-      <c r="G6" s="70" t="n">
+      <c r="C6" s="70" t="s">
+        <v>209</v>
+      </c>
+      <c r="D6" s="69" t="s">
+        <v>210</v>
+      </c>
+      <c r="E6" s="71" t="s">
+        <v>211</v>
+      </c>
+      <c r="F6" s="70" t="s">
+        <v>212</v>
+      </c>
+      <c r="G6" s="71" t="n">
         <v>2021</v>
       </c>
-      <c r="H6" s="70" t="s">
-        <v>194</v>
-      </c>
-      <c r="I6" s="71" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="71" t="n">
+      <c r="H6" s="71" t="s">
+        <v>213</v>
+      </c>
+      <c r="I6" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="72" t="n">
         <v>0.8</v>
       </c>
-      <c r="K6" s="71" t="n">
+      <c r="K6" s="72" t="n">
         <v>1.2</v>
       </c>
-      <c r="L6" s="72" t="n">
+      <c r="L6" s="73" t="n">
         <f aca="false">IF($H6="Absoluto",IF($J6="","",$J6),IF($I6="","",IF($H6="Razão MT",MIN($I6*(1-Parâmetros!$B$3),$I6*(1+Parâmetros!$B$3)),$I6-Parâmetros!$B$4)))</f>
         <v>0.8</v>
       </c>
-      <c r="M6" s="72" t="n">
+      <c r="M6" s="73" t="n">
         <f aca="false">IF($H6="Absoluto",IF($K6="","",$K6),IF($I6="","",IF($H6="Razão MT",MAX($I6*(1-Parâmetros!$B$3),$I6*(1+Parâmetros!$B$3)),$I6+Parâmetros!$B$4)))</f>
         <v>1.2</v>
       </c>
-      <c r="N6" s="73" t="n">
+      <c r="N6" s="74" t="n">
         <v>0.9631</v>
       </c>
-      <c r="O6" s="74" t="str">
+      <c r="O6" s="75" t="str">
         <f aca="false">IF(OR(N6="",$L6="",$M6=""),"",IF($E6="+",IF(N6&gt;$M6,"Força",IF(N6&lt;$L6,"Fraqueza","Neutro")),IF(N6&lt;$L6,"Força",IF(N6&gt;$M6,"Fraqueza","Neutro"))))</f>
         <v>Neutro</v>
       </c>
-      <c r="P6" s="73" t="n">
+      <c r="P6" s="74" t="n">
         <v>0.3713</v>
       </c>
-      <c r="Q6" s="74" t="str">
+      <c r="Q6" s="75" t="str">
         <f aca="false">IF(OR(P6="",$L6="",$M6=""),"",IF($E6="+",IF(P6&gt;$M6,"Força",IF(P6&lt;$L6,"Fraqueza","Neutro")),IF(P6&lt;$L6,"Força",IF(P6&gt;$M6,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="R6" s="73" t="n">
+      <c r="R6" s="74" t="n">
         <v>1.2022</v>
       </c>
-      <c r="S6" s="74" t="str">
+      <c r="S6" s="75" t="str">
         <f aca="false">IF(OR(R6="",$L6="",$M6=""),"",IF($E6="+",IF(R6&gt;$M6,"Força",IF(R6&lt;$L6,"Fraqueza","Neutro")),IF(R6&lt;$L6,"Força",IF(R6&gt;$M6,"Fraqueza","Neutro"))))</f>
         <v>Força</v>
       </c>
-      <c r="T6" s="73" t="n">
+      <c r="T6" s="74" t="n">
         <v>1.3866</v>
       </c>
-      <c r="U6" s="74" t="str">
+      <c r="U6" s="75" t="str">
         <f aca="false">IF(OR(T6="",$L6="",$M6=""),"",IF($E6="+",IF(T6&gt;$M6,"Força",IF(T6&lt;$L6,"Fraqueza","Neutro")),IF(T6&lt;$L6,"Força",IF(T6&gt;$M6,"Fraqueza","Neutro"))))</f>
         <v>Força</v>
       </c>
-      <c r="V6" s="73" t="n">
+      <c r="V6" s="74" t="n">
         <v>1.6266</v>
       </c>
-      <c r="W6" s="74" t="str">
+      <c r="W6" s="75" t="str">
         <f aca="false">IF(OR(V6="",$L6="",$M6=""),"",IF($E6="+",IF(V6&gt;$M6,"Força",IF(V6&lt;$L6,"Fraqueza","Neutro")),IF(V6&lt;$L6,"Força",IF(V6&gt;$M6,"Fraqueza","Neutro"))))</f>
         <v>Força</v>
       </c>
-      <c r="X6" s="73" t="n">
+      <c r="X6" s="74" t="n">
         <v>1.319</v>
       </c>
-      <c r="Y6" s="74" t="str">
+      <c r="Y6" s="75" t="str">
         <f aca="false">IF(OR(X6="",$L6="",$M6=""),"",IF($E6="+",IF(X6&gt;$M6,"Força",IF(X6&lt;$L6,"Fraqueza","Neutro")),IF(X6&lt;$L6,"Força",IF(X6&gt;$M6,"Fraqueza","Neutro"))))</f>
         <v>Força</v>
       </c>
-      <c r="Z6" s="73" t="n">
+      <c r="Z6" s="74" t="n">
         <v>1.364</v>
       </c>
-      <c r="AA6" s="74" t="str">
+      <c r="AA6" s="75" t="str">
         <f aca="false">IF(OR(Z6="",$L6="",$M6=""),"",IF($E6="+",IF(Z6&gt;$M6,"Força",IF(Z6&lt;$L6,"Fraqueza","Neutro")),IF(Z6&lt;$L6,"Força",IF(Z6&gt;$M6,"Fraqueza","Neutro"))))</f>
         <v>Força</v>
       </c>
-      <c r="AB6" s="73" t="n">
+      <c r="AB6" s="74" t="n">
         <v>0.416</v>
       </c>
-      <c r="AC6" s="74" t="str">
+      <c r="AC6" s="75" t="str">
         <f aca="false">IF(OR(AB6="",$L6="",$M6=""),"",IF($E6="+",IF(AB6&gt;$M6,"Força",IF(AB6&lt;$L6,"Fraqueza","Neutro")),IF(AB6&lt;$L6,"Força",IF(AB6&gt;$M6,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="AD6" s="73" t="n">
+      <c r="AD6" s="74" t="n">
         <v>0.5183</v>
       </c>
-      <c r="AE6" s="74" t="str">
+      <c r="AE6" s="75" t="str">
         <f aca="false">IF(OR(AD6="",$L6="",$M6=""),"",IF($E6="+",IF(AD6&gt;$M6,"Força",IF(AD6&lt;$L6,"Fraqueza","Neutro")),IF(AD6&lt;$L6,"Força",IF(AD6&gt;$M6,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="AF6" s="73" t="n">
+      <c r="AF6" s="74" t="n">
         <v>0.5066</v>
       </c>
-      <c r="AG6" s="74" t="str">
+      <c r="AG6" s="75" t="str">
         <f aca="false">IF(OR(AF6="",$L6="",$M6=""),"",IF($E6="+",IF(AF6&gt;$M6,"Força",IF(AF6&lt;$L6,"Fraqueza","Neutro")),IF(AF6&lt;$L6,"Força",IF(AF6&gt;$M6,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="AH6" s="73" t="n">
+      <c r="AH6" s="74" t="n">
         <v>1.0048</v>
       </c>
-      <c r="AI6" s="74" t="str">
+      <c r="AI6" s="75" t="str">
         <f aca="false">IF(OR(AH6="",$L6="",$M6=""),"",IF($E6="+",IF(AH6&gt;$M6,"Força",IF(AH6&lt;$L6,"Fraqueza","Neutro")),IF(AH6&lt;$L6,"Força",IF(AH6&gt;$M6,"Fraqueza","Neutro"))))</f>
         <v>Neutro</v>
       </c>
-      <c r="AJ6" s="73" t="n">
+      <c r="AJ6" s="74" t="n">
         <v>0.1067</v>
       </c>
-      <c r="AK6" s="74" t="str">
+      <c r="AK6" s="75" t="str">
         <f aca="false">IF(OR(AJ6="",$L6="",$M6=""),"",IF($E6="+",IF(AJ6&gt;$M6,"Força",IF(AJ6&lt;$L6,"Fraqueza","Neutro")),IF(AJ6&lt;$L6,"Força",IF(AJ6&gt;$M6,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="AL6" s="73" t="n">
+      <c r="AL6" s="74" t="n">
         <v>1.714</v>
       </c>
-      <c r="AM6" s="74" t="str">
+      <c r="AM6" s="75" t="str">
         <f aca="false">IF(OR(AL6="",$L6="",$M6=""),"",IF($E6="+",IF(AL6&gt;$M6,"Força",IF(AL6&lt;$L6,"Fraqueza","Neutro")),IF(AL6&lt;$L6,"Força",IF(AL6&gt;$M6,"Fraqueza","Neutro"))))</f>
         <v>Força</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="68" t="s">
-        <v>195</v>
-      </c>
-      <c r="B7" s="69" t="s">
+      <c r="A7" s="69" t="s">
+        <v>169</v>
+      </c>
+      <c r="B7" s="70" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="69" t="s">
-        <v>196</v>
-      </c>
-      <c r="D7" s="68" t="s">
-        <v>197</v>
-      </c>
-      <c r="E7" s="70" t="s">
-        <v>192</v>
-      </c>
-      <c r="F7" s="69" t="s">
-        <v>198</v>
-      </c>
-      <c r="G7" s="70"/>
-      <c r="H7" s="70" t="s">
-        <v>199</v>
-      </c>
-      <c r="I7" s="71"/>
-      <c r="J7" s="71"/>
-      <c r="K7" s="71"/>
-      <c r="L7" s="72" t="str">
+      <c r="C7" s="70" t="s">
+        <v>214</v>
+      </c>
+      <c r="D7" s="69" t="s">
+        <v>215</v>
+      </c>
+      <c r="E7" s="71" t="s">
+        <v>211</v>
+      </c>
+      <c r="F7" s="70" t="s">
+        <v>216</v>
+      </c>
+      <c r="G7" s="71" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H7" s="71" t="s">
+        <v>217</v>
+      </c>
+      <c r="I7" s="72" t="n">
+        <v>5602.9</v>
+      </c>
+      <c r="J7" s="72"/>
+      <c r="K7" s="72"/>
+      <c r="L7" s="73" t="n">
         <f aca="false">IF($H7="Absoluto",IF($J7="","",$J7),IF($I7="","",IF($H7="Razão MT",MIN($I7*(1-Parâmetros!$B$3),$I7*(1+Parâmetros!$B$3)),$I7-Parâmetros!$B$4)))</f>
-        <v/>
-      </c>
-      <c r="M7" s="72" t="str">
+        <v>5042.61</v>
+      </c>
+      <c r="M7" s="73" t="n">
         <f aca="false">IF($H7="Absoluto",IF($K7="","",$K7),IF($I7="","",IF($H7="Razão MT",MAX($I7*(1-Parâmetros!$B$3),$I7*(1+Parâmetros!$B$3)),$I7+Parâmetros!$B$4)))</f>
-        <v/>
-      </c>
-      <c r="N7" s="71"/>
-      <c r="O7" s="74" t="str">
+        <v>6163.19</v>
+      </c>
+      <c r="N7" s="72" t="n">
+        <v>19926.55</v>
+      </c>
+      <c r="O7" s="75" t="str">
         <f aca="false">IF(OR(N7="",$L7="",$M7=""),"",IF($E7="+",IF(N7&gt;$M7,"Força",IF(N7&lt;$L7,"Fraqueza","Neutro")),IF(N7&lt;$L7,"Força",IF(N7&gt;$M7,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="P7" s="71"/>
-      <c r="Q7" s="74" t="str">
+        <v>Força</v>
+      </c>
+      <c r="P7" s="72" t="n">
+        <v>5729.32</v>
+      </c>
+      <c r="Q7" s="75" t="str">
         <f aca="false">IF(OR(P7="",$L7="",$M7=""),"",IF($E7="+",IF(P7&gt;$M7,"Força",IF(P7&lt;$L7,"Fraqueza","Neutro")),IF(P7&lt;$L7,"Força",IF(P7&gt;$M7,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="R7" s="71"/>
-      <c r="S7" s="74" t="str">
+        <v>Neutro</v>
+      </c>
+      <c r="R7" s="72" t="n">
+        <v>10834.24</v>
+      </c>
+      <c r="S7" s="75" t="str">
         <f aca="false">IF(OR(R7="",$L7="",$M7=""),"",IF($E7="+",IF(R7&gt;$M7,"Força",IF(R7&lt;$L7,"Fraqueza","Neutro")),IF(R7&lt;$L7,"Força",IF(R7&gt;$M7,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="T7" s="71"/>
-      <c r="U7" s="74" t="str">
+        <v>Força</v>
+      </c>
+      <c r="T7" s="72" t="n">
+        <v>10020.12</v>
+      </c>
+      <c r="U7" s="75" t="str">
         <f aca="false">IF(OR(T7="",$L7="",$M7=""),"",IF($E7="+",IF(T7&gt;$M7,"Força",IF(T7&lt;$L7,"Fraqueza","Neutro")),IF(T7&lt;$L7,"Força",IF(T7&gt;$M7,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="V7" s="71"/>
-      <c r="W7" s="74" t="str">
+        <v>Força</v>
+      </c>
+      <c r="V7" s="72" t="n">
+        <v>5402.93</v>
+      </c>
+      <c r="W7" s="75" t="str">
         <f aca="false">IF(OR(V7="",$L7="",$M7=""),"",IF($E7="+",IF(V7&gt;$M7,"Força",IF(V7&lt;$L7,"Fraqueza","Neutro")),IF(V7&lt;$L7,"Força",IF(V7&gt;$M7,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="X7" s="71"/>
-      <c r="Y7" s="74" t="str">
+        <v>Neutro</v>
+      </c>
+      <c r="X7" s="72" t="n">
+        <v>5889.67</v>
+      </c>
+      <c r="Y7" s="75" t="str">
         <f aca="false">IF(OR(X7="",$L7="",$M7=""),"",IF($E7="+",IF(X7&gt;$M7,"Força",IF(X7&lt;$L7,"Fraqueza","Neutro")),IF(X7&lt;$L7,"Força",IF(X7&gt;$M7,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="Z7" s="71"/>
-      <c r="AA7" s="74" t="str">
+        <v>Neutro</v>
+      </c>
+      <c r="Z7" s="72" t="n">
+        <v>9903.13</v>
+      </c>
+      <c r="AA7" s="75" t="str">
         <f aca="false">IF(OR(Z7="",$L7="",$M7=""),"",IF($E7="+",IF(Z7&gt;$M7,"Força",IF(Z7&lt;$L7,"Fraqueza","Neutro")),IF(Z7&lt;$L7,"Força",IF(Z7&gt;$M7,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AB7" s="71"/>
-      <c r="AC7" s="74" t="str">
+        <v>Força</v>
+      </c>
+      <c r="AB7" s="72" t="n">
+        <v>10166.09</v>
+      </c>
+      <c r="AC7" s="75" t="str">
         <f aca="false">IF(OR(AB7="",$L7="",$M7=""),"",IF($E7="+",IF(AB7&gt;$M7,"Força",IF(AB7&lt;$L7,"Fraqueza","Neutro")),IF(AB7&lt;$L7,"Força",IF(AB7&gt;$M7,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AD7" s="71"/>
-      <c r="AE7" s="74" t="str">
+        <v>Força</v>
+      </c>
+      <c r="AD7" s="72" t="n">
+        <v>5734.66</v>
+      </c>
+      <c r="AE7" s="75" t="str">
         <f aca="false">IF(OR(AD7="",$L7="",$M7=""),"",IF($E7="+",IF(AD7&gt;$M7,"Força",IF(AD7&lt;$L7,"Fraqueza","Neutro")),IF(AD7&lt;$L7,"Força",IF(AD7&gt;$M7,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AF7" s="71"/>
-      <c r="AG7" s="74" t="str">
+        <v>Neutro</v>
+      </c>
+      <c r="AF7" s="72" t="n">
+        <v>5045</v>
+      </c>
+      <c r="AG7" s="75" t="str">
         <f aca="false">IF(OR(AF7="",$L7="",$M7=""),"",IF($E7="+",IF(AF7&gt;$M7,"Força",IF(AF7&lt;$L7,"Fraqueza","Neutro")),IF(AF7&lt;$L7,"Força",IF(AF7&gt;$M7,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AH7" s="71"/>
-      <c r="AI7" s="74" t="str">
+        <v>Neutro</v>
+      </c>
+      <c r="AH7" s="72" t="n">
+        <v>6552.04</v>
+      </c>
+      <c r="AI7" s="75" t="str">
         <f aca="false">IF(OR(AH7="",$L7="",$M7=""),"",IF($E7="+",IF(AH7&gt;$M7,"Força",IF(AH7&lt;$L7,"Fraqueza","Neutro")),IF(AH7&lt;$L7,"Força",IF(AH7&gt;$M7,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AJ7" s="71"/>
-      <c r="AK7" s="74" t="str">
+        <v>Força</v>
+      </c>
+      <c r="AJ7" s="72" t="n">
+        <v>5354.94</v>
+      </c>
+      <c r="AK7" s="75" t="str">
         <f aca="false">IF(OR(AJ7="",$L7="",$M7=""),"",IF($E7="+",IF(AJ7&gt;$M7,"Força",IF(AJ7&lt;$L7,"Fraqueza","Neutro")),IF(AJ7&lt;$L7,"Força",IF(AJ7&gt;$M7,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AL7" s="71"/>
-      <c r="AM7" s="74" t="str">
+        <v>Neutro</v>
+      </c>
+      <c r="AL7" s="72" t="n">
+        <v>4958.82</v>
+      </c>
+      <c r="AM7" s="75" t="str">
         <f aca="false">IF(OR(AL7="",$L7="",$M7=""),"",IF($E7="+",IF(AL7&gt;$M7,"Força",IF(AL7&lt;$L7,"Fraqueza","Neutro")),IF(AL7&lt;$L7,"Força",IF(AL7&gt;$M7,"Fraqueza","Neutro"))))</f>
-        <v/>
+        <v>Fraqueza</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="68" t="s">
-        <v>152</v>
-      </c>
-      <c r="B8" s="69" t="s">
+      <c r="A8" s="69" t="s">
+        <v>174</v>
+      </c>
+      <c r="B8" s="70" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="69" t="s">
-        <v>200</v>
-      </c>
-      <c r="D8" s="68" t="s">
-        <v>201</v>
-      </c>
-      <c r="E8" s="70" t="s">
-        <v>192</v>
-      </c>
-      <c r="F8" s="69" t="s">
-        <v>202</v>
-      </c>
-      <c r="G8" s="70"/>
-      <c r="H8" s="70" t="s">
-        <v>203</v>
-      </c>
-      <c r="I8" s="71"/>
-      <c r="J8" s="71"/>
-      <c r="K8" s="71"/>
-      <c r="L8" s="72" t="str">
+      <c r="C8" s="70" t="s">
+        <v>218</v>
+      </c>
+      <c r="D8" s="69" t="s">
+        <v>219</v>
+      </c>
+      <c r="E8" s="71" t="s">
+        <v>211</v>
+      </c>
+      <c r="F8" s="70" t="s">
+        <v>220</v>
+      </c>
+      <c r="G8" s="71" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H8" s="71" t="s">
+        <v>221</v>
+      </c>
+      <c r="I8" s="72" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="J8" s="72"/>
+      <c r="K8" s="72"/>
+      <c r="L8" s="73" t="n">
         <f aca="false">IF($H8="Absoluto",IF($J8="","",$J8),IF($I8="","",IF($H8="Razão MT",MIN($I8*(1-Parâmetros!$B$3),$I8*(1+Parâmetros!$B$3)),$I8-Parâmetros!$B$4)))</f>
-        <v/>
-      </c>
-      <c r="M8" s="72" t="str">
+        <v>1.79</v>
+      </c>
+      <c r="M8" s="73" t="n">
         <f aca="false">IF($H8="Absoluto",IF($K8="","",$K8),IF($I8="","",IF($H8="Razão MT",MAX($I8*(1-Parâmetros!$B$3),$I8*(1+Parâmetros!$B$3)),$I8+Parâmetros!$B$4)))</f>
-        <v/>
-      </c>
-      <c r="N8" s="71"/>
-      <c r="O8" s="74" t="str">
+        <v>5.79</v>
+      </c>
+      <c r="N8" s="72" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="O8" s="75" t="str">
         <f aca="false">IF(OR(N8="",$L8="",$M8=""),"",IF($E8="+",IF(N8&gt;$M8,"Força",IF(N8&lt;$L8,"Fraqueza","Neutro")),IF(N8&lt;$L8,"Força",IF(N8&gt;$M8,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="P8" s="71"/>
-      <c r="Q8" s="74" t="str">
+        <v>Força</v>
+      </c>
+      <c r="P8" s="72" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="Q8" s="75" t="str">
         <f aca="false">IF(OR(P8="",$L8="",$M8=""),"",IF($E8="+",IF(P8&gt;$M8,"Força",IF(P8&lt;$L8,"Fraqueza","Neutro")),IF(P8&lt;$L8,"Força",IF(P8&gt;$M8,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="R8" s="71"/>
-      <c r="S8" s="74" t="str">
+        <v>Força</v>
+      </c>
+      <c r="R8" s="72" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="S8" s="75" t="str">
         <f aca="false">IF(OR(R8="",$L8="",$M8=""),"",IF($E8="+",IF(R8&gt;$M8,"Força",IF(R8&lt;$L8,"Fraqueza","Neutro")),IF(R8&lt;$L8,"Força",IF(R8&gt;$M8,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="T8" s="71"/>
-      <c r="U8" s="74" t="str">
+        <v>Neutro</v>
+      </c>
+      <c r="T8" s="72" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U8" s="75" t="str">
         <f aca="false">IF(OR(T8="",$L8="",$M8=""),"",IF($E8="+",IF(T8&gt;$M8,"Força",IF(T8&lt;$L8,"Fraqueza","Neutro")),IF(T8&lt;$L8,"Força",IF(T8&gt;$M8,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="V8" s="71"/>
-      <c r="W8" s="74" t="str">
+        <v>Neutro</v>
+      </c>
+      <c r="V8" s="72" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="W8" s="75" t="str">
         <f aca="false">IF(OR(V8="",$L8="",$M8=""),"",IF($E8="+",IF(V8&gt;$M8,"Força",IF(V8&lt;$L8,"Fraqueza","Neutro")),IF(V8&lt;$L8,"Força",IF(V8&gt;$M8,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="X8" s="71"/>
-      <c r="Y8" s="74" t="str">
+        <v>Força</v>
+      </c>
+      <c r="X8" s="72" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y8" s="75" t="str">
         <f aca="false">IF(OR(X8="",$L8="",$M8=""),"",IF($E8="+",IF(X8&gt;$M8,"Força",IF(X8&lt;$L8,"Fraqueza","Neutro")),IF(X8&lt;$L8,"Força",IF(X8&gt;$M8,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="Z8" s="71"/>
-      <c r="AA8" s="74" t="str">
+        <v>Neutro</v>
+      </c>
+      <c r="Z8" s="72" t="n">
+        <v>-2.74</v>
+      </c>
+      <c r="AA8" s="75" t="str">
         <f aca="false">IF(OR(Z8="",$L8="",$M8=""),"",IF($E8="+",IF(Z8&gt;$M8,"Força",IF(Z8&lt;$L8,"Fraqueza","Neutro")),IF(Z8&lt;$L8,"Força",IF(Z8&gt;$M8,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AB8" s="71"/>
-      <c r="AC8" s="74" t="str">
+        <v>Fraqueza</v>
+      </c>
+      <c r="AB8" s="72" t="n">
+        <v>-2.58</v>
+      </c>
+      <c r="AC8" s="75" t="str">
         <f aca="false">IF(OR(AB8="",$L8="",$M8=""),"",IF($E8="+",IF(AB8&gt;$M8,"Força",IF(AB8&lt;$L8,"Fraqueza","Neutro")),IF(AB8&lt;$L8,"Força",IF(AB8&gt;$M8,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AD8" s="71"/>
-      <c r="AE8" s="74" t="str">
+        <v>Fraqueza</v>
+      </c>
+      <c r="AD8" s="72" t="n">
+        <v>23.81</v>
+      </c>
+      <c r="AE8" s="75" t="str">
         <f aca="false">IF(OR(AD8="",$L8="",$M8=""),"",IF($E8="+",IF(AD8&gt;$M8,"Força",IF(AD8&lt;$L8,"Fraqueza","Neutro")),IF(AD8&lt;$L8,"Força",IF(AD8&gt;$M8,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AF8" s="71"/>
-      <c r="AG8" s="74" t="str">
+        <v>Força</v>
+      </c>
+      <c r="AF8" s="72" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="AG8" s="75" t="str">
         <f aca="false">IF(OR(AF8="",$L8="",$M8=""),"",IF($E8="+",IF(AF8&gt;$M8,"Força",IF(AF8&lt;$L8,"Fraqueza","Neutro")),IF(AF8&lt;$L8,"Força",IF(AF8&gt;$M8,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AH8" s="71"/>
-      <c r="AI8" s="74" t="str">
+        <v>Força</v>
+      </c>
+      <c r="AH8" s="72" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AI8" s="75" t="str">
         <f aca="false">IF(OR(AH8="",$L8="",$M8=""),"",IF($E8="+",IF(AH8&gt;$M8,"Força",IF(AH8&lt;$L8,"Fraqueza","Neutro")),IF(AH8&lt;$L8,"Força",IF(AH8&gt;$M8,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AJ8" s="71"/>
-      <c r="AK8" s="74" t="str">
+        <v>Força</v>
+      </c>
+      <c r="AJ8" s="72" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AK8" s="75" t="str">
         <f aca="false">IF(OR(AJ8="",$L8="",$M8=""),"",IF($E8="+",IF(AJ8&gt;$M8,"Força",IF(AJ8&lt;$L8,"Fraqueza","Neutro")),IF(AJ8&lt;$L8,"Força",IF(AJ8&gt;$M8,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AL8" s="71"/>
-      <c r="AM8" s="74" t="str">
+        <v>Fraqueza</v>
+      </c>
+      <c r="AL8" s="72" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="AM8" s="75" t="str">
         <f aca="false">IF(OR(AL8="",$L8="",$M8=""),"",IF($E8="+",IF(AL8&gt;$M8,"Força",IF(AL8&lt;$L8,"Fraqueza","Neutro")),IF(AL8&lt;$L8,"Força",IF(AL8&gt;$M8,"Fraqueza","Neutro"))))</f>
-        <v/>
+        <v>Neutro</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="68" t="s">
+      <c r="A9" s="69" t="s">
         <v>154</v>
       </c>
-      <c r="B9" s="69" t="s">
+      <c r="B9" s="70" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="69" t="s">
-        <v>204</v>
-      </c>
-      <c r="D9" s="68" t="s">
-        <v>201</v>
-      </c>
-      <c r="E9" s="70" t="s">
-        <v>192</v>
-      </c>
-      <c r="F9" s="69" t="s">
-        <v>205</v>
-      </c>
-      <c r="G9" s="70"/>
-      <c r="H9" s="70" t="s">
-        <v>203</v>
-      </c>
-      <c r="I9" s="71"/>
-      <c r="J9" s="71"/>
-      <c r="K9" s="71"/>
-      <c r="L9" s="72" t="str">
+      <c r="C9" s="70" t="s">
+        <v>222</v>
+      </c>
+      <c r="D9" s="69" t="s">
+        <v>219</v>
+      </c>
+      <c r="E9" s="71" t="s">
+        <v>211</v>
+      </c>
+      <c r="F9" s="70" t="s">
+        <v>223</v>
+      </c>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71" t="s">
+        <v>221</v>
+      </c>
+      <c r="I9" s="72"/>
+      <c r="J9" s="72"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="73" t="str">
         <f aca="false">IF($H9="Absoluto",IF($J9="","",$J9),IF($I9="","",IF($H9="Razão MT",MIN($I9*(1-Parâmetros!$B$3),$I9*(1+Parâmetros!$B$3)),$I9-Parâmetros!$B$4)))</f>
         <v/>
       </c>
-      <c r="M9" s="72" t="str">
+      <c r="M9" s="73" t="str">
         <f aca="false">IF($H9="Absoluto",IF($K9="","",$K9),IF($I9="","",IF($H9="Razão MT",MAX($I9*(1-Parâmetros!$B$3),$I9*(1+Parâmetros!$B$3)),$I9+Parâmetros!$B$4)))</f>
         <v/>
       </c>
-      <c r="N9" s="71"/>
-      <c r="O9" s="74" t="str">
+      <c r="N9" s="72"/>
+      <c r="O9" s="75" t="str">
         <f aca="false">IF(OR(N9="",$L9="",$M9=""),"",IF($E9="+",IF(N9&gt;$M9,"Força",IF(N9&lt;$L9,"Fraqueza","Neutro")),IF(N9&lt;$L9,"Força",IF(N9&gt;$M9,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="P9" s="71"/>
-      <c r="Q9" s="74" t="str">
+      <c r="P9" s="72"/>
+      <c r="Q9" s="75" t="str">
         <f aca="false">IF(OR(P9="",$L9="",$M9=""),"",IF($E9="+",IF(P9&gt;$M9,"Força",IF(P9&lt;$L9,"Fraqueza","Neutro")),IF(P9&lt;$L9,"Força",IF(P9&gt;$M9,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="R9" s="71"/>
-      <c r="S9" s="74" t="str">
+      <c r="R9" s="72"/>
+      <c r="S9" s="75" t="str">
         <f aca="false">IF(OR(R9="",$L9="",$M9=""),"",IF($E9="+",IF(R9&gt;$M9,"Força",IF(R9&lt;$L9,"Fraqueza","Neutro")),IF(R9&lt;$L9,"Força",IF(R9&gt;$M9,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="T9" s="71"/>
-      <c r="U9" s="74" t="str">
+      <c r="T9" s="72"/>
+      <c r="U9" s="75" t="str">
         <f aca="false">IF(OR(T9="",$L9="",$M9=""),"",IF($E9="+",IF(T9&gt;$M9,"Força",IF(T9&lt;$L9,"Fraqueza","Neutro")),IF(T9&lt;$L9,"Força",IF(T9&gt;$M9,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="V9" s="71"/>
-      <c r="W9" s="74" t="str">
+      <c r="V9" s="72"/>
+      <c r="W9" s="75" t="str">
         <f aca="false">IF(OR(V9="",$L9="",$M9=""),"",IF($E9="+",IF(V9&gt;$M9,"Força",IF(V9&lt;$L9,"Fraqueza","Neutro")),IF(V9&lt;$L9,"Força",IF(V9&gt;$M9,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="X9" s="71"/>
-      <c r="Y9" s="74" t="str">
+      <c r="X9" s="72"/>
+      <c r="Y9" s="75" t="str">
         <f aca="false">IF(OR(X9="",$L9="",$M9=""),"",IF($E9="+",IF(X9&gt;$M9,"Força",IF(X9&lt;$L9,"Fraqueza","Neutro")),IF(X9&lt;$L9,"Força",IF(X9&gt;$M9,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="Z9" s="71"/>
-      <c r="AA9" s="74" t="str">
+      <c r="Z9" s="72"/>
+      <c r="AA9" s="75" t="str">
         <f aca="false">IF(OR(Z9="",$L9="",$M9=""),"",IF($E9="+",IF(Z9&gt;$M9,"Força",IF(Z9&lt;$L9,"Fraqueza","Neutro")),IF(Z9&lt;$L9,"Força",IF(Z9&gt;$M9,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AB9" s="71"/>
-      <c r="AC9" s="74" t="str">
+      <c r="AB9" s="72"/>
+      <c r="AC9" s="75" t="str">
         <f aca="false">IF(OR(AB9="",$L9="",$M9=""),"",IF($E9="+",IF(AB9&gt;$M9,"Força",IF(AB9&lt;$L9,"Fraqueza","Neutro")),IF(AB9&lt;$L9,"Força",IF(AB9&gt;$M9,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AD9" s="71"/>
-      <c r="AE9" s="74" t="str">
+      <c r="AD9" s="72"/>
+      <c r="AE9" s="75" t="str">
         <f aca="false">IF(OR(AD9="",$L9="",$M9=""),"",IF($E9="+",IF(AD9&gt;$M9,"Força",IF(AD9&lt;$L9,"Fraqueza","Neutro")),IF(AD9&lt;$L9,"Força",IF(AD9&gt;$M9,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AF9" s="71"/>
-      <c r="AG9" s="74" t="str">
+      <c r="AF9" s="72"/>
+      <c r="AG9" s="75" t="str">
         <f aca="false">IF(OR(AF9="",$L9="",$M9=""),"",IF($E9="+",IF(AF9&gt;$M9,"Força",IF(AF9&lt;$L9,"Fraqueza","Neutro")),IF(AF9&lt;$L9,"Força",IF(AF9&gt;$M9,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AH9" s="71"/>
-      <c r="AI9" s="74" t="str">
+      <c r="AH9" s="72"/>
+      <c r="AI9" s="75" t="str">
         <f aca="false">IF(OR(AH9="",$L9="",$M9=""),"",IF($E9="+",IF(AH9&gt;$M9,"Força",IF(AH9&lt;$L9,"Fraqueza","Neutro")),IF(AH9&lt;$L9,"Força",IF(AH9&gt;$M9,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AJ9" s="71"/>
-      <c r="AK9" s="74" t="str">
+      <c r="AJ9" s="72"/>
+      <c r="AK9" s="75" t="str">
         <f aca="false">IF(OR(AJ9="",$L9="",$M9=""),"",IF($E9="+",IF(AJ9&gt;$M9,"Força",IF(AJ9&lt;$L9,"Fraqueza","Neutro")),IF(AJ9&lt;$L9,"Força",IF(AJ9&gt;$M9,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AL9" s="71"/>
-      <c r="AM9" s="74" t="str">
+      <c r="AL9" s="72"/>
+      <c r="AM9" s="75" t="str">
         <f aca="false">IF(OR(AL9="",$L9="",$M9=""),"",IF($E9="+",IF(AL9&gt;$M9,"Força",IF(AL9&lt;$L9,"Fraqueza","Neutro")),IF(AL9&lt;$L9,"Força",IF(AL9&gt;$M9,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="68" t="s">
-        <v>206</v>
-      </c>
-      <c r="B10" s="69" t="s">
+      <c r="A10" s="69" t="s">
+        <v>150</v>
+      </c>
+      <c r="B10" s="70" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="69" t="s">
-        <v>207</v>
-      </c>
-      <c r="D10" s="68" t="s">
-        <v>208</v>
-      </c>
-      <c r="E10" s="70" t="s">
-        <v>192</v>
-      </c>
-      <c r="F10" s="69" t="s">
-        <v>209</v>
-      </c>
-      <c r="G10" s="70"/>
-      <c r="H10" s="70" t="s">
-        <v>199</v>
-      </c>
-      <c r="I10" s="71"/>
-      <c r="J10" s="71"/>
-      <c r="K10" s="71"/>
-      <c r="L10" s="72" t="str">
+      <c r="C10" s="70" t="s">
+        <v>224</v>
+      </c>
+      <c r="D10" s="69" t="s">
+        <v>225</v>
+      </c>
+      <c r="E10" s="71" t="s">
+        <v>211</v>
+      </c>
+      <c r="F10" s="70" t="s">
+        <v>226</v>
+      </c>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71" t="s">
+        <v>217</v>
+      </c>
+      <c r="I10" s="72"/>
+      <c r="J10" s="72"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="73" t="str">
         <f aca="false">IF($H10="Absoluto",IF($J10="","",$J10),IF($I10="","",IF($H10="Razão MT",MIN($I10*(1-Parâmetros!$B$3),$I10*(1+Parâmetros!$B$3)),$I10-Parâmetros!$B$4)))</f>
         <v/>
       </c>
-      <c r="M10" s="72" t="str">
+      <c r="M10" s="73" t="str">
         <f aca="false">IF($H10="Absoluto",IF($K10="","",$K10),IF($I10="","",IF($H10="Razão MT",MAX($I10*(1-Parâmetros!$B$3),$I10*(1+Parâmetros!$B$3)),$I10+Parâmetros!$B$4)))</f>
         <v/>
       </c>
-      <c r="N10" s="71"/>
-      <c r="O10" s="74" t="str">
+      <c r="N10" s="72"/>
+      <c r="O10" s="75" t="str">
         <f aca="false">IF(OR(N10="",$L10="",$M10=""),"",IF($E10="+",IF(N10&gt;$M10,"Força",IF(N10&lt;$L10,"Fraqueza","Neutro")),IF(N10&lt;$L10,"Força",IF(N10&gt;$M10,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="P10" s="71"/>
-      <c r="Q10" s="74" t="str">
+      <c r="P10" s="72"/>
+      <c r="Q10" s="75" t="str">
         <f aca="false">IF(OR(P10="",$L10="",$M10=""),"",IF($E10="+",IF(P10&gt;$M10,"Força",IF(P10&lt;$L10,"Fraqueza","Neutro")),IF(P10&lt;$L10,"Força",IF(P10&gt;$M10,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="R10" s="71"/>
-      <c r="S10" s="74" t="str">
+      <c r="R10" s="72"/>
+      <c r="S10" s="75" t="str">
         <f aca="false">IF(OR(R10="",$L10="",$M10=""),"",IF($E10="+",IF(R10&gt;$M10,"Força",IF(R10&lt;$L10,"Fraqueza","Neutro")),IF(R10&lt;$L10,"Força",IF(R10&gt;$M10,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="T10" s="71"/>
-      <c r="U10" s="74" t="str">
+      <c r="T10" s="72"/>
+      <c r="U10" s="75" t="str">
         <f aca="false">IF(OR(T10="",$L10="",$M10=""),"",IF($E10="+",IF(T10&gt;$M10,"Força",IF(T10&lt;$L10,"Fraqueza","Neutro")),IF(T10&lt;$L10,"Força",IF(T10&gt;$M10,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="V10" s="71"/>
-      <c r="W10" s="74" t="str">
+      <c r="V10" s="72"/>
+      <c r="W10" s="75" t="str">
         <f aca="false">IF(OR(V10="",$L10="",$M10=""),"",IF($E10="+",IF(V10&gt;$M10,"Força",IF(V10&lt;$L10,"Fraqueza","Neutro")),IF(V10&lt;$L10,"Força",IF(V10&gt;$M10,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="X10" s="71"/>
-      <c r="Y10" s="74" t="str">
+      <c r="X10" s="72"/>
+      <c r="Y10" s="75" t="str">
         <f aca="false">IF(OR(X10="",$L10="",$M10=""),"",IF($E10="+",IF(X10&gt;$M10,"Força",IF(X10&lt;$L10,"Fraqueza","Neutro")),IF(X10&lt;$L10,"Força",IF(X10&gt;$M10,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="Z10" s="71"/>
-      <c r="AA10" s="74" t="str">
+      <c r="Z10" s="72"/>
+      <c r="AA10" s="75" t="str">
         <f aca="false">IF(OR(Z10="",$L10="",$M10=""),"",IF($E10="+",IF(Z10&gt;$M10,"Força",IF(Z10&lt;$L10,"Fraqueza","Neutro")),IF(Z10&lt;$L10,"Força",IF(Z10&gt;$M10,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AB10" s="71"/>
-      <c r="AC10" s="74" t="str">
+      <c r="AB10" s="72"/>
+      <c r="AC10" s="75" t="str">
         <f aca="false">IF(OR(AB10="",$L10="",$M10=""),"",IF($E10="+",IF(AB10&gt;$M10,"Força",IF(AB10&lt;$L10,"Fraqueza","Neutro")),IF(AB10&lt;$L10,"Força",IF(AB10&gt;$M10,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AD10" s="71"/>
-      <c r="AE10" s="74" t="str">
+      <c r="AD10" s="72"/>
+      <c r="AE10" s="75" t="str">
         <f aca="false">IF(OR(AD10="",$L10="",$M10=""),"",IF($E10="+",IF(AD10&gt;$M10,"Força",IF(AD10&lt;$L10,"Fraqueza","Neutro")),IF(AD10&lt;$L10,"Força",IF(AD10&gt;$M10,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AF10" s="71"/>
-      <c r="AG10" s="74" t="str">
+      <c r="AF10" s="72"/>
+      <c r="AG10" s="75" t="str">
         <f aca="false">IF(OR(AF10="",$L10="",$M10=""),"",IF($E10="+",IF(AF10&gt;$M10,"Força",IF(AF10&lt;$L10,"Fraqueza","Neutro")),IF(AF10&lt;$L10,"Força",IF(AF10&gt;$M10,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AH10" s="71"/>
-      <c r="AI10" s="74" t="str">
+      <c r="AH10" s="72"/>
+      <c r="AI10" s="75" t="str">
         <f aca="false">IF(OR(AH10="",$L10="",$M10=""),"",IF($E10="+",IF(AH10&gt;$M10,"Força",IF(AH10&lt;$L10,"Fraqueza","Neutro")),IF(AH10&lt;$L10,"Força",IF(AH10&gt;$M10,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AJ10" s="71"/>
-      <c r="AK10" s="74" t="str">
+      <c r="AJ10" s="72"/>
+      <c r="AK10" s="75" t="str">
         <f aca="false">IF(OR(AJ10="",$L10="",$M10=""),"",IF($E10="+",IF(AJ10&gt;$M10,"Força",IF(AJ10&lt;$L10,"Fraqueza","Neutro")),IF(AJ10&lt;$L10,"Força",IF(AJ10&gt;$M10,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AL10" s="71"/>
-      <c r="AM10" s="74" t="str">
+      <c r="AL10" s="72"/>
+      <c r="AM10" s="75" t="str">
         <f aca="false">IF(OR(AL10="",$L10="",$M10=""),"",IF($E10="+",IF(AL10&gt;$M10,"Força",IF(AL10&lt;$L10,"Fraqueza","Neutro")),IF(AL10&lt;$L10,"Força",IF(AL10&gt;$M10,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="75" t="s">
+      <c r="A11" s="76" t="s">
+        <v>227</v>
+      </c>
+      <c r="B11" s="77" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" s="77" t="s">
+        <v>228</v>
+      </c>
+      <c r="D11" s="76" t="s">
         <v>210</v>
       </c>
-      <c r="B11" s="76" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" s="76" t="s">
+      <c r="E11" s="71" t="s">
         <v>211</v>
       </c>
-      <c r="D11" s="75" t="s">
-        <v>191</v>
-      </c>
-      <c r="E11" s="70" t="s">
-        <v>192</v>
-      </c>
-      <c r="F11" s="76" t="s">
-        <v>193</v>
-      </c>
-      <c r="G11" s="70" t="n">
+      <c r="F11" s="77" t="s">
+        <v>212</v>
+      </c>
+      <c r="G11" s="71" t="n">
         <v>2021</v>
       </c>
-      <c r="H11" s="70" t="s">
-        <v>194</v>
-      </c>
-      <c r="I11" s="71" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="71" t="n">
+      <c r="H11" s="71" t="s">
+        <v>213</v>
+      </c>
+      <c r="I11" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="72" t="n">
         <v>0.8</v>
       </c>
-      <c r="K11" s="71" t="n">
+      <c r="K11" s="72" t="n">
         <v>1.2</v>
       </c>
-      <c r="L11" s="72" t="n">
+      <c r="L11" s="73" t="n">
         <f aca="false">IF($H11="Absoluto",IF($J11="","",$J11),IF($I11="","",IF($H11="Razão MT",MIN($I11*(1-Parâmetros!$B$3),$I11*(1+Parâmetros!$B$3)),$I11-Parâmetros!$B$4)))</f>
         <v>0.8</v>
       </c>
-      <c r="M11" s="72" t="n">
+      <c r="M11" s="73" t="n">
         <f aca="false">IF($H11="Absoluto",IF($K11="","",$K11),IF($I11="","",IF($H11="Razão MT",MAX($I11*(1-Parâmetros!$B$3),$I11*(1+Parâmetros!$B$3)),$I11+Parâmetros!$B$4)))</f>
         <v>1.2</v>
       </c>
-      <c r="N11" s="73" t="n">
+      <c r="N11" s="74" t="n">
         <v>0.169</v>
       </c>
-      <c r="O11" s="74" t="str">
+      <c r="O11" s="75" t="str">
         <f aca="false">IF(OR(N11="",$L11="",$M11=""),"",IF($E11="+",IF(N11&gt;$M11,"Força",IF(N11&lt;$L11,"Fraqueza","Neutro")),IF(N11&lt;$L11,"Força",IF(N11&gt;$M11,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="P11" s="73" t="n">
+      <c r="P11" s="74" t="n">
         <v>0.6374</v>
       </c>
-      <c r="Q11" s="74" t="str">
+      <c r="Q11" s="75" t="str">
         <f aca="false">IF(OR(P11="",$L11="",$M11=""),"",IF($E11="+",IF(P11&gt;$M11,"Força",IF(P11&lt;$L11,"Fraqueza","Neutro")),IF(P11&lt;$L11,"Força",IF(P11&gt;$M11,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="R11" s="73" t="n">
+      <c r="R11" s="74" t="n">
         <v>0.4717</v>
       </c>
-      <c r="S11" s="74" t="str">
+      <c r="S11" s="75" t="str">
         <f aca="false">IF(OR(R11="",$L11="",$M11=""),"",IF($E11="+",IF(R11&gt;$M11,"Força",IF(R11&lt;$L11,"Fraqueza","Neutro")),IF(R11&lt;$L11,"Força",IF(R11&gt;$M11,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="T11" s="73" t="n">
+      <c r="T11" s="74" t="n">
         <v>0.2854</v>
       </c>
-      <c r="U11" s="74" t="str">
+      <c r="U11" s="75" t="str">
         <f aca="false">IF(OR(T11="",$L11="",$M11=""),"",IF($E11="+",IF(T11&gt;$M11,"Força",IF(T11&lt;$L11,"Fraqueza","Neutro")),IF(T11&lt;$L11,"Força",IF(T11&gt;$M11,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="V11" s="73" t="n">
+      <c r="V11" s="74" t="n">
         <v>1.2891</v>
       </c>
-      <c r="W11" s="74" t="str">
+      <c r="W11" s="75" t="str">
         <f aca="false">IF(OR(V11="",$L11="",$M11=""),"",IF($E11="+",IF(V11&gt;$M11,"Força",IF(V11&lt;$L11,"Fraqueza","Neutro")),IF(V11&lt;$L11,"Força",IF(V11&gt;$M11,"Fraqueza","Neutro"))))</f>
         <v>Força</v>
       </c>
-      <c r="X11" s="73" t="n">
+      <c r="X11" s="74" t="n">
         <v>1.1671</v>
       </c>
-      <c r="Y11" s="74" t="str">
+      <c r="Y11" s="75" t="str">
         <f aca="false">IF(OR(X11="",$L11="",$M11=""),"",IF($E11="+",IF(X11&gt;$M11,"Força",IF(X11&lt;$L11,"Fraqueza","Neutro")),IF(X11&lt;$L11,"Força",IF(X11&gt;$M11,"Fraqueza","Neutro"))))</f>
         <v>Neutro</v>
       </c>
-      <c r="Z11" s="73" t="n">
+      <c r="Z11" s="74" t="n">
         <v>1.1956</v>
       </c>
-      <c r="AA11" s="74" t="str">
+      <c r="AA11" s="75" t="str">
         <f aca="false">IF(OR(Z11="",$L11="",$M11=""),"",IF($E11="+",IF(Z11&gt;$M11,"Força",IF(Z11&lt;$L11,"Fraqueza","Neutro")),IF(Z11&lt;$L11,"Força",IF(Z11&gt;$M11,"Fraqueza","Neutro"))))</f>
         <v>Neutro</v>
       </c>
-      <c r="AB11" s="73" t="n">
+      <c r="AB11" s="74" t="n">
         <v>1.2112</v>
       </c>
-      <c r="AC11" s="74" t="str">
+      <c r="AC11" s="75" t="str">
         <f aca="false">IF(OR(AB11="",$L11="",$M11=""),"",IF($E11="+",IF(AB11&gt;$M11,"Força",IF(AB11&lt;$L11,"Fraqueza","Neutro")),IF(AB11&lt;$L11,"Força",IF(AB11&gt;$M11,"Fraqueza","Neutro"))))</f>
         <v>Força</v>
       </c>
-      <c r="AD11" s="73" t="n">
+      <c r="AD11" s="74" t="n">
         <v>2.0033</v>
       </c>
-      <c r="AE11" s="74" t="str">
+      <c r="AE11" s="75" t="str">
         <f aca="false">IF(OR(AD11="",$L11="",$M11=""),"",IF($E11="+",IF(AD11&gt;$M11,"Força",IF(AD11&lt;$L11,"Fraqueza","Neutro")),IF(AD11&lt;$L11,"Força",IF(AD11&gt;$M11,"Fraqueza","Neutro"))))</f>
         <v>Força</v>
       </c>
-      <c r="AF11" s="73" t="n">
+      <c r="AF11" s="74" t="n">
         <v>0.5947</v>
       </c>
-      <c r="AG11" s="74" t="str">
+      <c r="AG11" s="75" t="str">
         <f aca="false">IF(OR(AF11="",$L11="",$M11=""),"",IF($E11="+",IF(AF11&gt;$M11,"Força",IF(AF11&lt;$L11,"Fraqueza","Neutro")),IF(AF11&lt;$L11,"Força",IF(AF11&gt;$M11,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="AH11" s="73" t="n">
+      <c r="AH11" s="74" t="n">
         <v>1.0107</v>
       </c>
-      <c r="AI11" s="74" t="str">
+      <c r="AI11" s="75" t="str">
         <f aca="false">IF(OR(AH11="",$L11="",$M11=""),"",IF($E11="+",IF(AH11&gt;$M11,"Força",IF(AH11&lt;$L11,"Fraqueza","Neutro")),IF(AH11&lt;$L11,"Força",IF(AH11&gt;$M11,"Fraqueza","Neutro"))))</f>
         <v>Neutro</v>
       </c>
-      <c r="AJ11" s="73" t="n">
+      <c r="AJ11" s="74" t="n">
         <v>1.8691</v>
       </c>
-      <c r="AK11" s="74" t="str">
+      <c r="AK11" s="75" t="str">
         <f aca="false">IF(OR(AJ11="",$L11="",$M11=""),"",IF($E11="+",IF(AJ11&gt;$M11,"Força",IF(AJ11&lt;$L11,"Fraqueza","Neutro")),IF(AJ11&lt;$L11,"Força",IF(AJ11&gt;$M11,"Fraqueza","Neutro"))))</f>
         <v>Força</v>
       </c>
-      <c r="AL11" s="73" t="n">
+      <c r="AL11" s="74" t="n">
         <v>0.4719</v>
       </c>
-      <c r="AM11" s="74" t="str">
+      <c r="AM11" s="75" t="str">
         <f aca="false">IF(OR(AL11="",$L11="",$M11=""),"",IF($E11="+",IF(AL11&gt;$M11,"Força",IF(AL11&lt;$L11,"Fraqueza","Neutro")),IF(AL11&lt;$L11,"Força",IF(AL11&gt;$M11,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="75" t="s">
+      <c r="A12" s="76" t="s">
+        <v>229</v>
+      </c>
+      <c r="B12" s="77" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="77" t="s">
+        <v>230</v>
+      </c>
+      <c r="D12" s="76" t="s">
+        <v>219</v>
+      </c>
+      <c r="E12" s="71" t="s">
+        <v>211</v>
+      </c>
+      <c r="F12" s="77" t="s">
+        <v>231</v>
+      </c>
+      <c r="G12" s="71"/>
+      <c r="H12" s="71" t="s">
+        <v>221</v>
+      </c>
+      <c r="I12" s="72"/>
+      <c r="J12" s="72"/>
+      <c r="K12" s="72"/>
+      <c r="L12" s="73" t="str">
+        <f aca="false">IF($H12="Absoluto",IF($J12="","",$J12),IF($I12="","",IF($H12="Razão MT",MIN($I12*(1-Parâmetros!$B$3),$I12*(1+Parâmetros!$B$3)),$I12-Parâmetros!$B$4)))</f>
+        <v/>
+      </c>
+      <c r="M12" s="73" t="str">
+        <f aca="false">IF($H12="Absoluto",IF($K12="","",$K12),IF($I12="","",IF($H12="Razão MT",MAX($I12*(1-Parâmetros!$B$3),$I12*(1+Parâmetros!$B$3)),$I12+Parâmetros!$B$4)))</f>
+        <v/>
+      </c>
+      <c r="N12" s="72"/>
+      <c r="O12" s="75" t="str">
+        <f aca="false">IF(OR(N12="",$L12="",$M12=""),"",IF($E12="+",IF(N12&gt;$M12,"Força",IF(N12&lt;$L12,"Fraqueza","Neutro")),IF(N12&lt;$L12,"Força",IF(N12&gt;$M12,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="P12" s="72"/>
+      <c r="Q12" s="75" t="str">
+        <f aca="false">IF(OR(P12="",$L12="",$M12=""),"",IF($E12="+",IF(P12&gt;$M12,"Força",IF(P12&lt;$L12,"Fraqueza","Neutro")),IF(P12&lt;$L12,"Força",IF(P12&gt;$M12,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="R12" s="72"/>
+      <c r="S12" s="75" t="str">
+        <f aca="false">IF(OR(R12="",$L12="",$M12=""),"",IF($E12="+",IF(R12&gt;$M12,"Força",IF(R12&lt;$L12,"Fraqueza","Neutro")),IF(R12&lt;$L12,"Força",IF(R12&gt;$M12,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="T12" s="72"/>
+      <c r="U12" s="75" t="str">
+        <f aca="false">IF(OR(T12="",$L12="",$M12=""),"",IF($E12="+",IF(T12&gt;$M12,"Força",IF(T12&lt;$L12,"Fraqueza","Neutro")),IF(T12&lt;$L12,"Força",IF(T12&gt;$M12,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="V12" s="72"/>
+      <c r="W12" s="75" t="str">
+        <f aca="false">IF(OR(V12="",$L12="",$M12=""),"",IF($E12="+",IF(V12&gt;$M12,"Força",IF(V12&lt;$L12,"Fraqueza","Neutro")),IF(V12&lt;$L12,"Força",IF(V12&gt;$M12,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="X12" s="72"/>
+      <c r="Y12" s="75" t="str">
+        <f aca="false">IF(OR(X12="",$L12="",$M12=""),"",IF($E12="+",IF(X12&gt;$M12,"Força",IF(X12&lt;$L12,"Fraqueza","Neutro")),IF(X12&lt;$L12,"Força",IF(X12&gt;$M12,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="Z12" s="72"/>
+      <c r="AA12" s="75" t="str">
+        <f aca="false">IF(OR(Z12="",$L12="",$M12=""),"",IF($E12="+",IF(Z12&gt;$M12,"Força",IF(Z12&lt;$L12,"Fraqueza","Neutro")),IF(Z12&lt;$L12,"Força",IF(Z12&gt;$M12,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="AB12" s="72"/>
+      <c r="AC12" s="75" t="str">
+        <f aca="false">IF(OR(AB12="",$L12="",$M12=""),"",IF($E12="+",IF(AB12&gt;$M12,"Força",IF(AB12&lt;$L12,"Fraqueza","Neutro")),IF(AB12&lt;$L12,"Força",IF(AB12&gt;$M12,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="AD12" s="72"/>
+      <c r="AE12" s="75" t="str">
+        <f aca="false">IF(OR(AD12="",$L12="",$M12=""),"",IF($E12="+",IF(AD12&gt;$M12,"Força",IF(AD12&lt;$L12,"Fraqueza","Neutro")),IF(AD12&lt;$L12,"Força",IF(AD12&gt;$M12,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="AF12" s="72"/>
+      <c r="AG12" s="75" t="str">
+        <f aca="false">IF(OR(AF12="",$L12="",$M12=""),"",IF($E12="+",IF(AF12&gt;$M12,"Força",IF(AF12&lt;$L12,"Fraqueza","Neutro")),IF(AF12&lt;$L12,"Força",IF(AF12&gt;$M12,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="AH12" s="72"/>
+      <c r="AI12" s="75" t="str">
+        <f aca="false">IF(OR(AH12="",$L12="",$M12=""),"",IF($E12="+",IF(AH12&gt;$M12,"Força",IF(AH12&lt;$L12,"Fraqueza","Neutro")),IF(AH12&lt;$L12,"Força",IF(AH12&gt;$M12,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="AJ12" s="72"/>
+      <c r="AK12" s="75" t="str">
+        <f aca="false">IF(OR(AJ12="",$L12="",$M12=""),"",IF($E12="+",IF(AJ12&gt;$M12,"Força",IF(AJ12&lt;$L12,"Fraqueza","Neutro")),IF(AJ12&lt;$L12,"Força",IF(AJ12&gt;$M12,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="AL12" s="72"/>
+      <c r="AM12" s="75" t="str">
+        <f aca="false">IF(OR(AL12="",$L12="",$M12=""),"",IF($E12="+",IF(AL12&gt;$M12,"Força",IF(AL12&lt;$L12,"Fraqueza","Neutro")),IF(AL12&lt;$L12,"Força",IF(AL12&gt;$M12,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="76" t="s">
+        <v>232</v>
+      </c>
+      <c r="B13" s="77" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="77" t="s">
+        <v>233</v>
+      </c>
+      <c r="D13" s="76" t="s">
+        <v>234</v>
+      </c>
+      <c r="E13" s="71" t="s">
+        <v>211</v>
+      </c>
+      <c r="F13" s="77" t="s">
+        <v>231</v>
+      </c>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71" t="s">
+        <v>217</v>
+      </c>
+      <c r="I13" s="72"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="73" t="str">
+        <f aca="false">IF($H13="Absoluto",IF($J13="","",$J13),IF($I13="","",IF($H13="Razão MT",MIN($I13*(1-Parâmetros!$B$3),$I13*(1+Parâmetros!$B$3)),$I13-Parâmetros!$B$4)))</f>
+        <v/>
+      </c>
+      <c r="M13" s="73" t="str">
+        <f aca="false">IF($H13="Absoluto",IF($K13="","",$K13),IF($I13="","",IF($H13="Razão MT",MAX($I13*(1-Parâmetros!$B$3),$I13*(1+Parâmetros!$B$3)),$I13+Parâmetros!$B$4)))</f>
+        <v/>
+      </c>
+      <c r="N13" s="72"/>
+      <c r="O13" s="75" t="str">
+        <f aca="false">IF(OR(N13="",$L13="",$M13=""),"",IF($E13="+",IF(N13&gt;$M13,"Força",IF(N13&lt;$L13,"Fraqueza","Neutro")),IF(N13&lt;$L13,"Força",IF(N13&gt;$M13,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="P13" s="72"/>
+      <c r="Q13" s="75" t="str">
+        <f aca="false">IF(OR(P13="",$L13="",$M13=""),"",IF($E13="+",IF(P13&gt;$M13,"Força",IF(P13&lt;$L13,"Fraqueza","Neutro")),IF(P13&lt;$L13,"Força",IF(P13&gt;$M13,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="R13" s="72"/>
+      <c r="S13" s="75" t="str">
+        <f aca="false">IF(OR(R13="",$L13="",$M13=""),"",IF($E13="+",IF(R13&gt;$M13,"Força",IF(R13&lt;$L13,"Fraqueza","Neutro")),IF(R13&lt;$L13,"Força",IF(R13&gt;$M13,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="T13" s="72"/>
+      <c r="U13" s="75" t="str">
+        <f aca="false">IF(OR(T13="",$L13="",$M13=""),"",IF($E13="+",IF(T13&gt;$M13,"Força",IF(T13&lt;$L13,"Fraqueza","Neutro")),IF(T13&lt;$L13,"Força",IF(T13&gt;$M13,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="V13" s="72"/>
+      <c r="W13" s="75" t="str">
+        <f aca="false">IF(OR(V13="",$L13="",$M13=""),"",IF($E13="+",IF(V13&gt;$M13,"Força",IF(V13&lt;$L13,"Fraqueza","Neutro")),IF(V13&lt;$L13,"Força",IF(V13&gt;$M13,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="X13" s="72"/>
+      <c r="Y13" s="75" t="str">
+        <f aca="false">IF(OR(X13="",$L13="",$M13=""),"",IF($E13="+",IF(X13&gt;$M13,"Força",IF(X13&lt;$L13,"Fraqueza","Neutro")),IF(X13&lt;$L13,"Força",IF(X13&gt;$M13,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="Z13" s="72"/>
+      <c r="AA13" s="75" t="str">
+        <f aca="false">IF(OR(Z13="",$L13="",$M13=""),"",IF($E13="+",IF(Z13&gt;$M13,"Força",IF(Z13&lt;$L13,"Fraqueza","Neutro")),IF(Z13&lt;$L13,"Força",IF(Z13&gt;$M13,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="AB13" s="72"/>
+      <c r="AC13" s="75" t="str">
+        <f aca="false">IF(OR(AB13="",$L13="",$M13=""),"",IF($E13="+",IF(AB13&gt;$M13,"Força",IF(AB13&lt;$L13,"Fraqueza","Neutro")),IF(AB13&lt;$L13,"Força",IF(AB13&gt;$M13,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="AD13" s="72"/>
+      <c r="AE13" s="75" t="str">
+        <f aca="false">IF(OR(AD13="",$L13="",$M13=""),"",IF($E13="+",IF(AD13&gt;$M13,"Força",IF(AD13&lt;$L13,"Fraqueza","Neutro")),IF(AD13&lt;$L13,"Força",IF(AD13&gt;$M13,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="AF13" s="72"/>
+      <c r="AG13" s="75" t="str">
+        <f aca="false">IF(OR(AF13="",$L13="",$M13=""),"",IF($E13="+",IF(AF13&gt;$M13,"Força",IF(AF13&lt;$L13,"Fraqueza","Neutro")),IF(AF13&lt;$L13,"Força",IF(AF13&gt;$M13,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="AH13" s="72"/>
+      <c r="AI13" s="75" t="str">
+        <f aca="false">IF(OR(AH13="",$L13="",$M13=""),"",IF($E13="+",IF(AH13&gt;$M13,"Força",IF(AH13&lt;$L13,"Fraqueza","Neutro")),IF(AH13&lt;$L13,"Força",IF(AH13&gt;$M13,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="AJ13" s="72"/>
+      <c r="AK13" s="75" t="str">
+        <f aca="false">IF(OR(AJ13="",$L13="",$M13=""),"",IF($E13="+",IF(AJ13&gt;$M13,"Força",IF(AJ13&lt;$L13,"Fraqueza","Neutro")),IF(AJ13&lt;$L13,"Força",IF(AJ13&gt;$M13,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="AL13" s="72"/>
+      <c r="AM13" s="75" t="str">
+        <f aca="false">IF(OR(AL13="",$L13="",$M13=""),"",IF($E13="+",IF(AL13&gt;$M13,"Força",IF(AL13&lt;$L13,"Fraqueza","Neutro")),IF(AL13&lt;$L13,"Força",IF(AL13&gt;$M13,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="78" t="s">
+        <v>235</v>
+      </c>
+      <c r="B14" s="79" t="s">
+        <v>236</v>
+      </c>
+      <c r="C14" s="79" t="s">
+        <v>237</v>
+      </c>
+      <c r="D14" s="78" t="s">
+        <v>210</v>
+      </c>
+      <c r="E14" s="71" t="s">
+        <v>211</v>
+      </c>
+      <c r="F14" s="79" t="s">
         <v>212</v>
       </c>
-      <c r="B12" s="76" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" s="76" t="s">
+      <c r="G14" s="71" t="n">
+        <v>2021</v>
+      </c>
+      <c r="H14" s="71" t="s">
         <v>213</v>
       </c>
-      <c r="D12" s="75" t="s">
-        <v>201</v>
-      </c>
-      <c r="E12" s="70" t="s">
-        <v>192</v>
-      </c>
-      <c r="F12" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="G12" s="70"/>
-      <c r="H12" s="70" t="s">
-        <v>203</v>
-      </c>
-      <c r="I12" s="71"/>
-      <c r="J12" s="71"/>
-      <c r="K12" s="71"/>
-      <c r="L12" s="72" t="str">
-        <f aca="false">IF($H12="Absoluto",IF($J12="","",$J12),IF($I12="","",IF($H12="Razão MT",MIN($I12*(1-Parâmetros!$B$3),$I12*(1+Parâmetros!$B$3)),$I12-Parâmetros!$B$4)))</f>
-        <v/>
-      </c>
-      <c r="M12" s="72" t="str">
-        <f aca="false">IF($H12="Absoluto",IF($K12="","",$K12),IF($I12="","",IF($H12="Razão MT",MAX($I12*(1-Parâmetros!$B$3),$I12*(1+Parâmetros!$B$3)),$I12+Parâmetros!$B$4)))</f>
-        <v/>
-      </c>
-      <c r="N12" s="71"/>
-      <c r="O12" s="74" t="str">
-        <f aca="false">IF(OR(N12="",$L12="",$M12=""),"",IF($E12="+",IF(N12&gt;$M12,"Força",IF(N12&lt;$L12,"Fraqueza","Neutro")),IF(N12&lt;$L12,"Força",IF(N12&gt;$M12,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="P12" s="71"/>
-      <c r="Q12" s="74" t="str">
-        <f aca="false">IF(OR(P12="",$L12="",$M12=""),"",IF($E12="+",IF(P12&gt;$M12,"Força",IF(P12&lt;$L12,"Fraqueza","Neutro")),IF(P12&lt;$L12,"Força",IF(P12&gt;$M12,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="R12" s="71"/>
-      <c r="S12" s="74" t="str">
-        <f aca="false">IF(OR(R12="",$L12="",$M12=""),"",IF($E12="+",IF(R12&gt;$M12,"Força",IF(R12&lt;$L12,"Fraqueza","Neutro")),IF(R12&lt;$L12,"Força",IF(R12&gt;$M12,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="T12" s="71"/>
-      <c r="U12" s="74" t="str">
-        <f aca="false">IF(OR(T12="",$L12="",$M12=""),"",IF($E12="+",IF(T12&gt;$M12,"Força",IF(T12&lt;$L12,"Fraqueza","Neutro")),IF(T12&lt;$L12,"Força",IF(T12&gt;$M12,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="V12" s="71"/>
-      <c r="W12" s="74" t="str">
-        <f aca="false">IF(OR(V12="",$L12="",$M12=""),"",IF($E12="+",IF(V12&gt;$M12,"Força",IF(V12&lt;$L12,"Fraqueza","Neutro")),IF(V12&lt;$L12,"Força",IF(V12&gt;$M12,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="X12" s="71"/>
-      <c r="Y12" s="74" t="str">
-        <f aca="false">IF(OR(X12="",$L12="",$M12=""),"",IF($E12="+",IF(X12&gt;$M12,"Força",IF(X12&lt;$L12,"Fraqueza","Neutro")),IF(X12&lt;$L12,"Força",IF(X12&gt;$M12,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="Z12" s="71"/>
-      <c r="AA12" s="74" t="str">
-        <f aca="false">IF(OR(Z12="",$L12="",$M12=""),"",IF($E12="+",IF(Z12&gt;$M12,"Força",IF(Z12&lt;$L12,"Fraqueza","Neutro")),IF(Z12&lt;$L12,"Força",IF(Z12&gt;$M12,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AB12" s="71"/>
-      <c r="AC12" s="74" t="str">
-        <f aca="false">IF(OR(AB12="",$L12="",$M12=""),"",IF($E12="+",IF(AB12&gt;$M12,"Força",IF(AB12&lt;$L12,"Fraqueza","Neutro")),IF(AB12&lt;$L12,"Força",IF(AB12&gt;$M12,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AD12" s="71"/>
-      <c r="AE12" s="74" t="str">
-        <f aca="false">IF(OR(AD12="",$L12="",$M12=""),"",IF($E12="+",IF(AD12&gt;$M12,"Força",IF(AD12&lt;$L12,"Fraqueza","Neutro")),IF(AD12&lt;$L12,"Força",IF(AD12&gt;$M12,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AF12" s="71"/>
-      <c r="AG12" s="74" t="str">
-        <f aca="false">IF(OR(AF12="",$L12="",$M12=""),"",IF($E12="+",IF(AF12&gt;$M12,"Força",IF(AF12&lt;$L12,"Fraqueza","Neutro")),IF(AF12&lt;$L12,"Força",IF(AF12&gt;$M12,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AH12" s="71"/>
-      <c r="AI12" s="74" t="str">
-        <f aca="false">IF(OR(AH12="",$L12="",$M12=""),"",IF($E12="+",IF(AH12&gt;$M12,"Força",IF(AH12&lt;$L12,"Fraqueza","Neutro")),IF(AH12&lt;$L12,"Força",IF(AH12&gt;$M12,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AJ12" s="71"/>
-      <c r="AK12" s="74" t="str">
-        <f aca="false">IF(OR(AJ12="",$L12="",$M12=""),"",IF($E12="+",IF(AJ12&gt;$M12,"Força",IF(AJ12&lt;$L12,"Fraqueza","Neutro")),IF(AJ12&lt;$L12,"Força",IF(AJ12&gt;$M12,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AL12" s="71"/>
-      <c r="AM12" s="74" t="str">
-        <f aca="false">IF(OR(AL12="",$L12="",$M12=""),"",IF($E12="+",IF(AL12&gt;$M12,"Força",IF(AL12&lt;$L12,"Fraqueza","Neutro")),IF(AL12&lt;$L12,"Força",IF(AL12&gt;$M12,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="75" t="s">
-        <v>215</v>
-      </c>
-      <c r="B13" s="76" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" s="76" t="s">
-        <v>216</v>
-      </c>
-      <c r="D13" s="75" t="s">
-        <v>217</v>
-      </c>
-      <c r="E13" s="70" t="s">
-        <v>192</v>
-      </c>
-      <c r="F13" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="G13" s="70"/>
-      <c r="H13" s="70" t="s">
-        <v>199</v>
-      </c>
-      <c r="I13" s="71"/>
-      <c r="J13" s="71"/>
-      <c r="K13" s="71"/>
-      <c r="L13" s="72" t="str">
-        <f aca="false">IF($H13="Absoluto",IF($J13="","",$J13),IF($I13="","",IF($H13="Razão MT",MIN($I13*(1-Parâmetros!$B$3),$I13*(1+Parâmetros!$B$3)),$I13-Parâmetros!$B$4)))</f>
-        <v/>
-      </c>
-      <c r="M13" s="72" t="str">
-        <f aca="false">IF($H13="Absoluto",IF($K13="","",$K13),IF($I13="","",IF($H13="Razão MT",MAX($I13*(1-Parâmetros!$B$3),$I13*(1+Parâmetros!$B$3)),$I13+Parâmetros!$B$4)))</f>
-        <v/>
-      </c>
-      <c r="N13" s="71"/>
-      <c r="O13" s="74" t="str">
-        <f aca="false">IF(OR(N13="",$L13="",$M13=""),"",IF($E13="+",IF(N13&gt;$M13,"Força",IF(N13&lt;$L13,"Fraqueza","Neutro")),IF(N13&lt;$L13,"Força",IF(N13&gt;$M13,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="P13" s="71"/>
-      <c r="Q13" s="74" t="str">
-        <f aca="false">IF(OR(P13="",$L13="",$M13=""),"",IF($E13="+",IF(P13&gt;$M13,"Força",IF(P13&lt;$L13,"Fraqueza","Neutro")),IF(P13&lt;$L13,"Força",IF(P13&gt;$M13,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="R13" s="71"/>
-      <c r="S13" s="74" t="str">
-        <f aca="false">IF(OR(R13="",$L13="",$M13=""),"",IF($E13="+",IF(R13&gt;$M13,"Força",IF(R13&lt;$L13,"Fraqueza","Neutro")),IF(R13&lt;$L13,"Força",IF(R13&gt;$M13,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="T13" s="71"/>
-      <c r="U13" s="74" t="str">
-        <f aca="false">IF(OR(T13="",$L13="",$M13=""),"",IF($E13="+",IF(T13&gt;$M13,"Força",IF(T13&lt;$L13,"Fraqueza","Neutro")),IF(T13&lt;$L13,"Força",IF(T13&gt;$M13,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="V13" s="71"/>
-      <c r="W13" s="74" t="str">
-        <f aca="false">IF(OR(V13="",$L13="",$M13=""),"",IF($E13="+",IF(V13&gt;$M13,"Força",IF(V13&lt;$L13,"Fraqueza","Neutro")),IF(V13&lt;$L13,"Força",IF(V13&gt;$M13,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="X13" s="71"/>
-      <c r="Y13" s="74" t="str">
-        <f aca="false">IF(OR(X13="",$L13="",$M13=""),"",IF($E13="+",IF(X13&gt;$M13,"Força",IF(X13&lt;$L13,"Fraqueza","Neutro")),IF(X13&lt;$L13,"Força",IF(X13&gt;$M13,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="Z13" s="71"/>
-      <c r="AA13" s="74" t="str">
-        <f aca="false">IF(OR(Z13="",$L13="",$M13=""),"",IF($E13="+",IF(Z13&gt;$M13,"Força",IF(Z13&lt;$L13,"Fraqueza","Neutro")),IF(Z13&lt;$L13,"Força",IF(Z13&gt;$M13,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AB13" s="71"/>
-      <c r="AC13" s="74" t="str">
-        <f aca="false">IF(OR(AB13="",$L13="",$M13=""),"",IF($E13="+",IF(AB13&gt;$M13,"Força",IF(AB13&lt;$L13,"Fraqueza","Neutro")),IF(AB13&lt;$L13,"Força",IF(AB13&gt;$M13,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AD13" s="71"/>
-      <c r="AE13" s="74" t="str">
-        <f aca="false">IF(OR(AD13="",$L13="",$M13=""),"",IF($E13="+",IF(AD13&gt;$M13,"Força",IF(AD13&lt;$L13,"Fraqueza","Neutro")),IF(AD13&lt;$L13,"Força",IF(AD13&gt;$M13,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AF13" s="71"/>
-      <c r="AG13" s="74" t="str">
-        <f aca="false">IF(OR(AF13="",$L13="",$M13=""),"",IF($E13="+",IF(AF13&gt;$M13,"Força",IF(AF13&lt;$L13,"Fraqueza","Neutro")),IF(AF13&lt;$L13,"Força",IF(AF13&gt;$M13,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AH13" s="71"/>
-      <c r="AI13" s="74" t="str">
-        <f aca="false">IF(OR(AH13="",$L13="",$M13=""),"",IF($E13="+",IF(AH13&gt;$M13,"Força",IF(AH13&lt;$L13,"Fraqueza","Neutro")),IF(AH13&lt;$L13,"Força",IF(AH13&gt;$M13,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AJ13" s="71"/>
-      <c r="AK13" s="74" t="str">
-        <f aca="false">IF(OR(AJ13="",$L13="",$M13=""),"",IF($E13="+",IF(AJ13&gt;$M13,"Força",IF(AJ13&lt;$L13,"Fraqueza","Neutro")),IF(AJ13&lt;$L13,"Força",IF(AJ13&gt;$M13,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AL13" s="71"/>
-      <c r="AM13" s="74" t="str">
-        <f aca="false">IF(OR(AL13="",$L13="",$M13=""),"",IF($E13="+",IF(AL13&gt;$M13,"Força",IF(AL13&lt;$L13,"Fraqueza","Neutro")),IF(AL13&lt;$L13,"Força",IF(AL13&gt;$M13,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="77" t="s">
-        <v>218</v>
-      </c>
-      <c r="B14" s="78" t="s">
-        <v>219</v>
-      </c>
-      <c r="C14" s="78" t="s">
-        <v>220</v>
-      </c>
-      <c r="D14" s="77" t="s">
-        <v>191</v>
-      </c>
-      <c r="E14" s="70" t="s">
-        <v>192</v>
-      </c>
-      <c r="F14" s="78" t="s">
-        <v>193</v>
-      </c>
-      <c r="G14" s="70" t="n">
-        <v>2021</v>
-      </c>
-      <c r="H14" s="70" t="s">
-        <v>194</v>
-      </c>
-      <c r="I14" s="71" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="71" t="n">
+      <c r="I14" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="72" t="n">
         <v>0.8</v>
       </c>
-      <c r="K14" s="71" t="n">
+      <c r="K14" s="72" t="n">
         <v>1.2</v>
       </c>
-      <c r="L14" s="72" t="n">
+      <c r="L14" s="73" t="n">
         <f aca="false">IF($H14="Absoluto",IF($J14="","",$J14),IF($I14="","",IF($H14="Razão MT",MIN($I14*(1-Parâmetros!$B$3),$I14*(1+Parâmetros!$B$3)),$I14-Parâmetros!$B$4)))</f>
         <v>0.8</v>
       </c>
-      <c r="M14" s="72" t="n">
+      <c r="M14" s="73" t="n">
         <f aca="false">IF($H14="Absoluto",IF($K14="","",$K14),IF($I14="","",IF($H14="Razão MT",MAX($I14*(1-Parâmetros!$B$3),$I14*(1+Parâmetros!$B$3)),$I14+Parâmetros!$B$4)))</f>
         <v>1.2</v>
       </c>
-      <c r="N14" s="73" t="n">
+      <c r="N14" s="74" t="n">
         <v>0.4274</v>
       </c>
-      <c r="O14" s="74" t="str">
+      <c r="O14" s="75" t="str">
         <f aca="false">IF(OR(N14="",$L14="",$M14=""),"",IF($E14="+",IF(N14&gt;$M14,"Força",IF(N14&lt;$L14,"Fraqueza","Neutro")),IF(N14&lt;$L14,"Força",IF(N14&gt;$M14,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="P14" s="73" t="n">
+      <c r="P14" s="74" t="n">
         <v>1.3013</v>
       </c>
-      <c r="Q14" s="74" t="str">
+      <c r="Q14" s="75" t="str">
         <f aca="false">IF(OR(P14="",$L14="",$M14=""),"",IF($E14="+",IF(P14&gt;$M14,"Força",IF(P14&lt;$L14,"Fraqueza","Neutro")),IF(P14&lt;$L14,"Força",IF(P14&gt;$M14,"Fraqueza","Neutro"))))</f>
         <v>Força</v>
       </c>
-      <c r="R14" s="73" t="n">
+      <c r="R14" s="74" t="n">
         <v>0.5029</v>
       </c>
-      <c r="S14" s="74" t="str">
+      <c r="S14" s="75" t="str">
         <f aca="false">IF(OR(R14="",$L14="",$M14=""),"",IF($E14="+",IF(R14&gt;$M14,"Força",IF(R14&lt;$L14,"Fraqueza","Neutro")),IF(R14&lt;$L14,"Força",IF(R14&gt;$M14,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="T14" s="73" t="n">
+      <c r="T14" s="74" t="n">
         <v>0.4636</v>
       </c>
-      <c r="U14" s="74" t="str">
+      <c r="U14" s="75" t="str">
         <f aca="false">IF(OR(T14="",$L14="",$M14=""),"",IF($E14="+",IF(T14&gt;$M14,"Força",IF(T14&lt;$L14,"Fraqueza","Neutro")),IF(T14&lt;$L14,"Força",IF(T14&gt;$M14,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="V14" s="73" t="n">
+      <c r="V14" s="74" t="n">
         <v>0.3623</v>
       </c>
-      <c r="W14" s="74" t="str">
+      <c r="W14" s="75" t="str">
         <f aca="false">IF(OR(V14="",$L14="",$M14=""),"",IF($E14="+",IF(V14&gt;$M14,"Força",IF(V14&lt;$L14,"Fraqueza","Neutro")),IF(V14&lt;$L14,"Força",IF(V14&gt;$M14,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="X14" s="73" t="n">
+      <c r="X14" s="74" t="n">
         <v>0.4388</v>
       </c>
-      <c r="Y14" s="74" t="str">
+      <c r="Y14" s="75" t="str">
         <f aca="false">IF(OR(X14="",$L14="",$M14=""),"",IF($E14="+",IF(X14&gt;$M14,"Força",IF(X14&lt;$L14,"Fraqueza","Neutro")),IF(X14&lt;$L14,"Força",IF(X14&gt;$M14,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="Z14" s="73" t="n">
+      <c r="Z14" s="74" t="n">
         <v>0.3227</v>
       </c>
-      <c r="AA14" s="74" t="str">
+      <c r="AA14" s="75" t="str">
         <f aca="false">IF(OR(Z14="",$L14="",$M14=""),"",IF($E14="+",IF(Z14&gt;$M14,"Força",IF(Z14&lt;$L14,"Fraqueza","Neutro")),IF(Z14&lt;$L14,"Força",IF(Z14&gt;$M14,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="AB14" s="73" t="n">
+      <c r="AB14" s="74" t="n">
         <v>1.1498</v>
       </c>
-      <c r="AC14" s="74" t="str">
+      <c r="AC14" s="75" t="str">
         <f aca="false">IF(OR(AB14="",$L14="",$M14=""),"",IF($E14="+",IF(AB14&gt;$M14,"Força",IF(AB14&lt;$L14,"Fraqueza","Neutro")),IF(AB14&lt;$L14,"Força",IF(AB14&gt;$M14,"Fraqueza","Neutro"))))</f>
         <v>Neutro</v>
       </c>
-      <c r="AD14" s="73" t="n">
+      <c r="AD14" s="74" t="n">
         <v>0.7089</v>
       </c>
-      <c r="AE14" s="74" t="str">
+      <c r="AE14" s="75" t="str">
         <f aca="false">IF(OR(AD14="",$L14="",$M14=""),"",IF($E14="+",IF(AD14&gt;$M14,"Força",IF(AD14&lt;$L14,"Fraqueza","Neutro")),IF(AD14&lt;$L14,"Força",IF(AD14&gt;$M14,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="AF14" s="73" t="n">
+      <c r="AF14" s="74" t="n">
         <v>1.1034</v>
       </c>
-      <c r="AG14" s="74" t="str">
+      <c r="AG14" s="75" t="str">
         <f aca="false">IF(OR(AF14="",$L14="",$M14=""),"",IF($E14="+",IF(AF14&gt;$M14,"Força",IF(AF14&lt;$L14,"Fraqueza","Neutro")),IF(AF14&lt;$L14,"Força",IF(AF14&gt;$M14,"Fraqueza","Neutro"))))</f>
         <v>Neutro</v>
       </c>
-      <c r="AH14" s="73" t="n">
+      <c r="AH14" s="74" t="n">
         <v>0.505</v>
       </c>
-      <c r="AI14" s="74" t="str">
+      <c r="AI14" s="75" t="str">
         <f aca="false">IF(OR(AH14="",$L14="",$M14=""),"",IF($E14="+",IF(AH14&gt;$M14,"Força",IF(AH14&lt;$L14,"Fraqueza","Neutro")),IF(AH14&lt;$L14,"Força",IF(AH14&gt;$M14,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="AJ14" s="73" t="n">
+      <c r="AJ14" s="74" t="n">
         <v>1.5988</v>
       </c>
-      <c r="AK14" s="74" t="str">
+      <c r="AK14" s="75" t="str">
         <f aca="false">IF(OR(AJ14="",$L14="",$M14=""),"",IF($E14="+",IF(AJ14&gt;$M14,"Força",IF(AJ14&lt;$L14,"Fraqueza","Neutro")),IF(AJ14&lt;$L14,"Força",IF(AJ14&gt;$M14,"Fraqueza","Neutro"))))</f>
         <v>Força</v>
       </c>
-      <c r="AL14" s="73" t="n">
+      <c r="AL14" s="74" t="n">
         <v>0.3417</v>
       </c>
-      <c r="AM14" s="74" t="str">
+      <c r="AM14" s="75" t="str">
         <f aca="false">IF(OR(AL14="",$L14="",$M14=""),"",IF($E14="+",IF(AL14&gt;$M14,"Força",IF(AL14&lt;$L14,"Fraqueza","Neutro")),IF(AL14&lt;$L14,"Força",IF(AL14&gt;$M14,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="77" t="s">
+      <c r="A15" s="78" t="s">
+        <v>238</v>
+      </c>
+      <c r="B15" s="79" t="s">
+        <v>236</v>
+      </c>
+      <c r="C15" s="79" t="s">
+        <v>239</v>
+      </c>
+      <c r="D15" s="78" t="s">
+        <v>219</v>
+      </c>
+      <c r="E15" s="71" t="s">
+        <v>211</v>
+      </c>
+      <c r="F15" s="79" t="s">
+        <v>231</v>
+      </c>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71" t="s">
         <v>221</v>
       </c>
-      <c r="B15" s="78" t="s">
-        <v>219</v>
-      </c>
-      <c r="C15" s="78" t="s">
-        <v>222</v>
-      </c>
-      <c r="D15" s="77" t="s">
-        <v>201</v>
-      </c>
-      <c r="E15" s="70" t="s">
-        <v>192</v>
-      </c>
-      <c r="F15" s="78" t="s">
-        <v>214</v>
-      </c>
-      <c r="G15" s="70"/>
-      <c r="H15" s="70" t="s">
-        <v>203</v>
-      </c>
-      <c r="I15" s="71"/>
-      <c r="J15" s="71"/>
-      <c r="K15" s="71"/>
-      <c r="L15" s="72" t="str">
+      <c r="I15" s="72"/>
+      <c r="J15" s="72"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="73" t="str">
         <f aca="false">IF($H15="Absoluto",IF($J15="","",$J15),IF($I15="","",IF($H15="Razão MT",MIN($I15*(1-Parâmetros!$B$3),$I15*(1+Parâmetros!$B$3)),$I15-Parâmetros!$B$4)))</f>
         <v/>
       </c>
-      <c r="M15" s="72" t="str">
+      <c r="M15" s="73" t="str">
         <f aca="false">IF($H15="Absoluto",IF($K15="","",$K15),IF($I15="","",IF($H15="Razão MT",MAX($I15*(1-Parâmetros!$B$3),$I15*(1+Parâmetros!$B$3)),$I15+Parâmetros!$B$4)))</f>
         <v/>
       </c>
-      <c r="N15" s="71"/>
-      <c r="O15" s="74" t="str">
+      <c r="N15" s="72"/>
+      <c r="O15" s="75" t="str">
         <f aca="false">IF(OR(N15="",$L15="",$M15=""),"",IF($E15="+",IF(N15&gt;$M15,"Força",IF(N15&lt;$L15,"Fraqueza","Neutro")),IF(N15&lt;$L15,"Força",IF(N15&gt;$M15,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="P15" s="71"/>
-      <c r="Q15" s="74" t="str">
+      <c r="P15" s="72"/>
+      <c r="Q15" s="75" t="str">
         <f aca="false">IF(OR(P15="",$L15="",$M15=""),"",IF($E15="+",IF(P15&gt;$M15,"Força",IF(P15&lt;$L15,"Fraqueza","Neutro")),IF(P15&lt;$L15,"Força",IF(P15&gt;$M15,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="R15" s="71"/>
-      <c r="S15" s="74" t="str">
+      <c r="R15" s="72"/>
+      <c r="S15" s="75" t="str">
         <f aca="false">IF(OR(R15="",$L15="",$M15=""),"",IF($E15="+",IF(R15&gt;$M15,"Força",IF(R15&lt;$L15,"Fraqueza","Neutro")),IF(R15&lt;$L15,"Força",IF(R15&gt;$M15,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="T15" s="71"/>
-      <c r="U15" s="74" t="str">
+      <c r="T15" s="72"/>
+      <c r="U15" s="75" t="str">
         <f aca="false">IF(OR(T15="",$L15="",$M15=""),"",IF($E15="+",IF(T15&gt;$M15,"Força",IF(T15&lt;$L15,"Fraqueza","Neutro")),IF(T15&lt;$L15,"Força",IF(T15&gt;$M15,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="V15" s="71"/>
-      <c r="W15" s="74" t="str">
+      <c r="V15" s="72"/>
+      <c r="W15" s="75" t="str">
         <f aca="false">IF(OR(V15="",$L15="",$M15=""),"",IF($E15="+",IF(V15&gt;$M15,"Força",IF(V15&lt;$L15,"Fraqueza","Neutro")),IF(V15&lt;$L15,"Força",IF(V15&gt;$M15,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="X15" s="71"/>
-      <c r="Y15" s="74" t="str">
+      <c r="X15" s="72"/>
+      <c r="Y15" s="75" t="str">
         <f aca="false">IF(OR(X15="",$L15="",$M15=""),"",IF($E15="+",IF(X15&gt;$M15,"Força",IF(X15&lt;$L15,"Fraqueza","Neutro")),IF(X15&lt;$L15,"Força",IF(X15&gt;$M15,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="Z15" s="71"/>
-      <c r="AA15" s="74" t="str">
+      <c r="Z15" s="72"/>
+      <c r="AA15" s="75" t="str">
         <f aca="false">IF(OR(Z15="",$L15="",$M15=""),"",IF($E15="+",IF(Z15&gt;$M15,"Força",IF(Z15&lt;$L15,"Fraqueza","Neutro")),IF(Z15&lt;$L15,"Força",IF(Z15&gt;$M15,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AB15" s="71"/>
-      <c r="AC15" s="74" t="str">
+      <c r="AB15" s="72"/>
+      <c r="AC15" s="75" t="str">
         <f aca="false">IF(OR(AB15="",$L15="",$M15=""),"",IF($E15="+",IF(AB15&gt;$M15,"Força",IF(AB15&lt;$L15,"Fraqueza","Neutro")),IF(AB15&lt;$L15,"Força",IF(AB15&gt;$M15,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AD15" s="71"/>
-      <c r="AE15" s="74" t="str">
+      <c r="AD15" s="72"/>
+      <c r="AE15" s="75" t="str">
         <f aca="false">IF(OR(AD15="",$L15="",$M15=""),"",IF($E15="+",IF(AD15&gt;$M15,"Força",IF(AD15&lt;$L15,"Fraqueza","Neutro")),IF(AD15&lt;$L15,"Força",IF(AD15&gt;$M15,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AF15" s="71"/>
-      <c r="AG15" s="74" t="str">
+      <c r="AF15" s="72"/>
+      <c r="AG15" s="75" t="str">
         <f aca="false">IF(OR(AF15="",$L15="",$M15=""),"",IF($E15="+",IF(AF15&gt;$M15,"Força",IF(AF15&lt;$L15,"Fraqueza","Neutro")),IF(AF15&lt;$L15,"Força",IF(AF15&gt;$M15,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AH15" s="71"/>
-      <c r="AI15" s="74" t="str">
+      <c r="AH15" s="72"/>
+      <c r="AI15" s="75" t="str">
         <f aca="false">IF(OR(AH15="",$L15="",$M15=""),"",IF($E15="+",IF(AH15&gt;$M15,"Força",IF(AH15&lt;$L15,"Fraqueza","Neutro")),IF(AH15&lt;$L15,"Força",IF(AH15&gt;$M15,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AJ15" s="71"/>
-      <c r="AK15" s="74" t="str">
+      <c r="AJ15" s="72"/>
+      <c r="AK15" s="75" t="str">
         <f aca="false">IF(OR(AJ15="",$L15="",$M15=""),"",IF($E15="+",IF(AJ15&gt;$M15,"Força",IF(AJ15&lt;$L15,"Fraqueza","Neutro")),IF(AJ15&lt;$L15,"Força",IF(AJ15&gt;$M15,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AL15" s="71"/>
-      <c r="AM15" s="74" t="str">
+      <c r="AL15" s="72"/>
+      <c r="AM15" s="75" t="str">
         <f aca="false">IF(OR(AL15="",$L15="",$M15=""),"",IF($E15="+",IF(AL15&gt;$M15,"Força",IF(AL15&lt;$L15,"Fraqueza","Neutro")),IF(AL15&lt;$L15,"Força",IF(AL15&gt;$M15,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="77" t="s">
+      <c r="A16" s="78" t="s">
         <v>158</v>
       </c>
-      <c r="B16" s="78" t="s">
-        <v>219</v>
-      </c>
-      <c r="C16" s="78" t="s">
-        <v>223</v>
-      </c>
-      <c r="D16" s="77" t="s">
-        <v>224</v>
-      </c>
-      <c r="E16" s="70" t="s">
-        <v>192</v>
-      </c>
-      <c r="F16" s="78" t="s">
+      <c r="B16" s="79" t="s">
+        <v>236</v>
+      </c>
+      <c r="C16" s="79" t="s">
+        <v>240</v>
+      </c>
+      <c r="D16" s="78" t="s">
+        <v>241</v>
+      </c>
+      <c r="E16" s="71" t="s">
+        <v>211</v>
+      </c>
+      <c r="F16" s="79" t="s">
         <v>159</v>
       </c>
-      <c r="G16" s="70"/>
-      <c r="H16" s="70" t="s">
-        <v>199</v>
-      </c>
-      <c r="I16" s="71"/>
-      <c r="J16" s="71"/>
-      <c r="K16" s="71"/>
-      <c r="L16" s="72" t="str">
+      <c r="G16" s="71"/>
+      <c r="H16" s="71" t="s">
+        <v>217</v>
+      </c>
+      <c r="I16" s="72"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="73" t="str">
         <f aca="false">IF($H16="Absoluto",IF($J16="","",$J16),IF($I16="","",IF($H16="Razão MT",MIN($I16*(1-Parâmetros!$B$3),$I16*(1+Parâmetros!$B$3)),$I16-Parâmetros!$B$4)))</f>
         <v/>
       </c>
-      <c r="M16" s="72" t="str">
+      <c r="M16" s="73" t="str">
         <f aca="false">IF($H16="Absoluto",IF($K16="","",$K16),IF($I16="","",IF($H16="Razão MT",MAX($I16*(1-Parâmetros!$B$3),$I16*(1+Parâmetros!$B$3)),$I16+Parâmetros!$B$4)))</f>
         <v/>
       </c>
-      <c r="N16" s="71"/>
-      <c r="O16" s="74" t="str">
+      <c r="N16" s="72"/>
+      <c r="O16" s="75" t="str">
         <f aca="false">IF(OR(N16="",$L16="",$M16=""),"",IF($E16="+",IF(N16&gt;$M16,"Força",IF(N16&lt;$L16,"Fraqueza","Neutro")),IF(N16&lt;$L16,"Força",IF(N16&gt;$M16,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="P16" s="71"/>
-      <c r="Q16" s="74" t="str">
+      <c r="P16" s="72"/>
+      <c r="Q16" s="75" t="str">
         <f aca="false">IF(OR(P16="",$L16="",$M16=""),"",IF($E16="+",IF(P16&gt;$M16,"Força",IF(P16&lt;$L16,"Fraqueza","Neutro")),IF(P16&lt;$L16,"Força",IF(P16&gt;$M16,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="R16" s="71"/>
-      <c r="S16" s="74" t="str">
+      <c r="R16" s="72"/>
+      <c r="S16" s="75" t="str">
         <f aca="false">IF(OR(R16="",$L16="",$M16=""),"",IF($E16="+",IF(R16&gt;$M16,"Força",IF(R16&lt;$L16,"Fraqueza","Neutro")),IF(R16&lt;$L16,"Força",IF(R16&gt;$M16,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="T16" s="71"/>
-      <c r="U16" s="74" t="str">
+      <c r="T16" s="72"/>
+      <c r="U16" s="75" t="str">
         <f aca="false">IF(OR(T16="",$L16="",$M16=""),"",IF($E16="+",IF(T16&gt;$M16,"Força",IF(T16&lt;$L16,"Fraqueza","Neutro")),IF(T16&lt;$L16,"Força",IF(T16&gt;$M16,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="V16" s="71"/>
-      <c r="W16" s="74" t="str">
+      <c r="V16" s="72"/>
+      <c r="W16" s="75" t="str">
         <f aca="false">IF(OR(V16="",$L16="",$M16=""),"",IF($E16="+",IF(V16&gt;$M16,"Força",IF(V16&lt;$L16,"Fraqueza","Neutro")),IF(V16&lt;$L16,"Força",IF(V16&gt;$M16,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="X16" s="71"/>
-      <c r="Y16" s="74" t="str">
+      <c r="X16" s="72"/>
+      <c r="Y16" s="75" t="str">
         <f aca="false">IF(OR(X16="",$L16="",$M16=""),"",IF($E16="+",IF(X16&gt;$M16,"Força",IF(X16&lt;$L16,"Fraqueza","Neutro")),IF(X16&lt;$L16,"Força",IF(X16&gt;$M16,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="Z16" s="71"/>
-      <c r="AA16" s="74" t="str">
+      <c r="Z16" s="72"/>
+      <c r="AA16" s="75" t="str">
         <f aca="false">IF(OR(Z16="",$L16="",$M16=""),"",IF($E16="+",IF(Z16&gt;$M16,"Força",IF(Z16&lt;$L16,"Fraqueza","Neutro")),IF(Z16&lt;$L16,"Força",IF(Z16&gt;$M16,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AB16" s="71"/>
-      <c r="AC16" s="74" t="str">
+      <c r="AB16" s="72"/>
+      <c r="AC16" s="75" t="str">
         <f aca="false">IF(OR(AB16="",$L16="",$M16=""),"",IF($E16="+",IF(AB16&gt;$M16,"Força",IF(AB16&lt;$L16,"Fraqueza","Neutro")),IF(AB16&lt;$L16,"Força",IF(AB16&gt;$M16,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AD16" s="71"/>
-      <c r="AE16" s="74" t="str">
+      <c r="AD16" s="72"/>
+      <c r="AE16" s="75" t="str">
         <f aca="false">IF(OR(AD16="",$L16="",$M16=""),"",IF($E16="+",IF(AD16&gt;$M16,"Força",IF(AD16&lt;$L16,"Fraqueza","Neutro")),IF(AD16&lt;$L16,"Força",IF(AD16&gt;$M16,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AF16" s="71"/>
-      <c r="AG16" s="74" t="str">
+      <c r="AF16" s="72"/>
+      <c r="AG16" s="75" t="str">
         <f aca="false">IF(OR(AF16="",$L16="",$M16=""),"",IF($E16="+",IF(AF16&gt;$M16,"Força",IF(AF16&lt;$L16,"Fraqueza","Neutro")),IF(AF16&lt;$L16,"Força",IF(AF16&gt;$M16,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AH16" s="71"/>
-      <c r="AI16" s="74" t="str">
+      <c r="AH16" s="72"/>
+      <c r="AI16" s="75" t="str">
         <f aca="false">IF(OR(AH16="",$L16="",$M16=""),"",IF($E16="+",IF(AH16&gt;$M16,"Força",IF(AH16&lt;$L16,"Fraqueza","Neutro")),IF(AH16&lt;$L16,"Força",IF(AH16&gt;$M16,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AJ16" s="71"/>
-      <c r="AK16" s="74" t="str">
+      <c r="AJ16" s="72"/>
+      <c r="AK16" s="75" t="str">
         <f aca="false">IF(OR(AJ16="",$L16="",$M16=""),"",IF($E16="+",IF(AJ16&gt;$M16,"Força",IF(AJ16&lt;$L16,"Fraqueza","Neutro")),IF(AJ16&lt;$L16,"Força",IF(AJ16&gt;$M16,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AL16" s="71"/>
-      <c r="AM16" s="74" t="str">
+      <c r="AL16" s="72"/>
+      <c r="AM16" s="75" t="str">
         <f aca="false">IF(OR(AL16="",$L16="",$M16=""),"",IF($E16="+",IF(AL16&gt;$M16,"Força",IF(AL16&lt;$L16,"Fraqueza","Neutro")),IF(AL16&lt;$L16,"Força",IF(AL16&gt;$M16,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="79" t="s">
+      <c r="A17" s="80" t="s">
         <v>142</v>
       </c>
-      <c r="B17" s="80" t="s">
-        <v>225</v>
-      </c>
-      <c r="C17" s="80" t="s">
-        <v>226</v>
-      </c>
-      <c r="D17" s="79" t="s">
+      <c r="B17" s="81" t="s">
+        <v>242</v>
+      </c>
+      <c r="C17" s="81" t="s">
+        <v>243</v>
+      </c>
+      <c r="D17" s="80" t="s">
+        <v>234</v>
+      </c>
+      <c r="E17" s="71" t="s">
+        <v>211</v>
+      </c>
+      <c r="F17" s="81" t="s">
+        <v>212</v>
+      </c>
+      <c r="G17" s="71" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H17" s="71" t="s">
         <v>217</v>
       </c>
-      <c r="E17" s="70" t="s">
-        <v>192</v>
-      </c>
-      <c r="F17" s="80" t="s">
-        <v>193</v>
-      </c>
-      <c r="G17" s="70" t="n">
-        <v>2023</v>
-      </c>
-      <c r="H17" s="70" t="s">
-        <v>199</v>
-      </c>
-      <c r="I17" s="71" t="n">
+      <c r="I17" s="72" t="n">
         <v>74620.05</v>
       </c>
-      <c r="J17" s="71"/>
-      <c r="K17" s="71"/>
-      <c r="L17" s="72" t="n">
+      <c r="J17" s="72"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="73" t="n">
         <f aca="false">IF($H17="Absoluto",IF($J17="","",$J17),IF($I17="","",IF($H17="Razão MT",MIN($I17*(1-Parâmetros!$B$3),$I17*(1+Parâmetros!$B$3)),$I17-Parâmetros!$B$4)))</f>
         <v>67158.045</v>
       </c>
-      <c r="M17" s="72" t="n">
+      <c r="M17" s="73" t="n">
         <f aca="false">IF($H17="Absoluto",IF($K17="","",$K17),IF($I17="","",IF($H17="Razão MT",MAX($I17*(1-Parâmetros!$B$3),$I17*(1+Parâmetros!$B$3)),$I17+Parâmetros!$B$4)))</f>
         <v>82082.055</v>
       </c>
-      <c r="N17" s="81" t="n">
+      <c r="N17" s="82" t="n">
         <v>19806.58</v>
       </c>
-      <c r="O17" s="74" t="str">
+      <c r="O17" s="75" t="str">
         <f aca="false">IF(OR(N17="",$L17="",$M17=""),"",IF($E17="+",IF(N17&gt;$M17,"Força",IF(N17&lt;$L17,"Fraqueza","Neutro")),IF(N17&lt;$L17,"Força",IF(N17&gt;$M17,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="P17" s="81" t="n">
+      <c r="P17" s="82" t="n">
         <v>31174.15</v>
       </c>
-      <c r="Q17" s="74" t="str">
+      <c r="Q17" s="75" t="str">
         <f aca="false">IF(OR(P17="",$L17="",$M17=""),"",IF($E17="+",IF(P17&gt;$M17,"Força",IF(P17&lt;$L17,"Fraqueza","Neutro")),IF(P17&lt;$L17,"Força",IF(P17&gt;$M17,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="R17" s="81" t="n">
+      <c r="R17" s="82" t="n">
         <v>27693.14</v>
       </c>
-      <c r="S17" s="74" t="str">
+      <c r="S17" s="75" t="str">
         <f aca="false">IF(OR(R17="",$L17="",$M17=""),"",IF($E17="+",IF(R17&gt;$M17,"Força",IF(R17&lt;$L17,"Fraqueza","Neutro")),IF(R17&lt;$L17,"Força",IF(R17&gt;$M17,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="T17" s="81" t="n">
+      <c r="T17" s="82" t="n">
         <v>39644.82</v>
       </c>
-      <c r="U17" s="74" t="str">
+      <c r="U17" s="75" t="str">
         <f aca="false">IF(OR(T17="",$L17="",$M17=""),"",IF($E17="+",IF(T17&gt;$M17,"Força",IF(T17&lt;$L17,"Fraqueza","Neutro")),IF(T17&lt;$L17,"Força",IF(T17&gt;$M17,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="V17" s="81" t="n">
+      <c r="V17" s="82" t="n">
         <v>167482.75</v>
       </c>
-      <c r="W17" s="74" t="str">
+      <c r="W17" s="75" t="str">
         <f aca="false">IF(OR(V17="",$L17="",$M17=""),"",IF($E17="+",IF(V17&gt;$M17,"Força",IF(V17&lt;$L17,"Fraqueza","Neutro")),IF(V17&lt;$L17,"Força",IF(V17&gt;$M17,"Fraqueza","Neutro"))))</f>
         <v>Força</v>
       </c>
-      <c r="X17" s="81" t="n">
+      <c r="X17" s="82" t="n">
         <v>48349.24</v>
       </c>
-      <c r="Y17" s="74" t="str">
+      <c r="Y17" s="75" t="str">
         <f aca="false">IF(OR(X17="",$L17="",$M17=""),"",IF($E17="+",IF(X17&gt;$M17,"Força",IF(X17&lt;$L17,"Fraqueza","Neutro")),IF(X17&lt;$L17,"Força",IF(X17&gt;$M17,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="Z17" s="81" t="n">
+      <c r="Z17" s="82" t="n">
         <v>59335.82</v>
       </c>
-      <c r="AA17" s="74" t="str">
+      <c r="AA17" s="75" t="str">
         <f aca="false">IF(OR(Z17="",$L17="",$M17=""),"",IF($E17="+",IF(Z17&gt;$M17,"Força",IF(Z17&lt;$L17,"Fraqueza","Neutro")),IF(Z17&lt;$L17,"Força",IF(Z17&gt;$M17,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="AB17" s="81" t="n">
+      <c r="AB17" s="82" t="n">
         <v>43433.97</v>
       </c>
-      <c r="AC17" s="74" t="str">
+      <c r="AC17" s="75" t="str">
         <f aca="false">IF(OR(AB17="",$L17="",$M17=""),"",IF($E17="+",IF(AB17&gt;$M17,"Força",IF(AB17&lt;$L17,"Fraqueza","Neutro")),IF(AB17&lt;$L17,"Força",IF(AB17&gt;$M17,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="AD17" s="81" t="n">
+      <c r="AD17" s="82" t="n">
         <v>33510.51</v>
       </c>
-      <c r="AE17" s="74" t="str">
+      <c r="AE17" s="75" t="str">
         <f aca="false">IF(OR(AD17="",$L17="",$M17=""),"",IF($E17="+",IF(AD17&gt;$M17,"Força",IF(AD17&lt;$L17,"Fraqueza","Neutro")),IF(AD17&lt;$L17,"Força",IF(AD17&gt;$M17,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="AF17" s="81" t="n">
+      <c r="AF17" s="82" t="n">
         <v>27609.14</v>
       </c>
-      <c r="AG17" s="74" t="str">
+      <c r="AG17" s="75" t="str">
         <f aca="false">IF(OR(AF17="",$L17="",$M17=""),"",IF($E17="+",IF(AF17&gt;$M17,"Força",IF(AF17&lt;$L17,"Fraqueza","Neutro")),IF(AF17&lt;$L17,"Força",IF(AF17&gt;$M17,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="AH17" s="81" t="n">
+      <c r="AH17" s="82" t="n">
         <v>31726.19</v>
       </c>
-      <c r="AI17" s="74" t="str">
+      <c r="AI17" s="75" t="str">
         <f aca="false">IF(OR(AH17="",$L17="",$M17=""),"",IF($E17="+",IF(AH17&gt;$M17,"Força",IF(AH17&lt;$L17,"Fraqueza","Neutro")),IF(AH17&lt;$L17,"Força",IF(AH17&gt;$M17,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="AJ17" s="81" t="n">
+      <c r="AJ17" s="82" t="n">
         <v>67650.09</v>
       </c>
-      <c r="AK17" s="74" t="str">
+      <c r="AK17" s="75" t="str">
         <f aca="false">IF(OR(AJ17="",$L17="",$M17=""),"",IF($E17="+",IF(AJ17&gt;$M17,"Força",IF(AJ17&lt;$L17,"Fraqueza","Neutro")),IF(AJ17&lt;$L17,"Força",IF(AJ17&gt;$M17,"Fraqueza","Neutro"))))</f>
         <v>Neutro</v>
       </c>
-      <c r="AL17" s="81" t="n">
+      <c r="AL17" s="82" t="n">
         <v>48781.11</v>
       </c>
-      <c r="AM17" s="74" t="str">
+      <c r="AM17" s="75" t="str">
         <f aca="false">IF(OR(AL17="",$L17="",$M17=""),"",IF($E17="+",IF(AL17&gt;$M17,"Força",IF(AL17&lt;$L17,"Fraqueza","Neutro")),IF(AL17&lt;$L17,"Força",IF(AL17&gt;$M17,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="79" t="s">
+      <c r="A18" s="80" t="s">
         <v>138</v>
       </c>
-      <c r="B18" s="80" t="s">
-        <v>225</v>
-      </c>
-      <c r="C18" s="80" t="s">
-        <v>227</v>
-      </c>
-      <c r="D18" s="79" t="s">
-        <v>201</v>
-      </c>
-      <c r="E18" s="70" t="s">
-        <v>228</v>
-      </c>
-      <c r="F18" s="80" t="s">
-        <v>193</v>
-      </c>
-      <c r="G18" s="70" t="n">
+      <c r="B18" s="81" t="s">
+        <v>242</v>
+      </c>
+      <c r="C18" s="81" t="s">
+        <v>244</v>
+      </c>
+      <c r="D18" s="80" t="s">
+        <v>219</v>
+      </c>
+      <c r="E18" s="71" t="s">
+        <v>245</v>
+      </c>
+      <c r="F18" s="81" t="s">
+        <v>212</v>
+      </c>
+      <c r="G18" s="71" t="n">
         <v>2021</v>
       </c>
-      <c r="H18" s="70" t="s">
-        <v>203</v>
-      </c>
-      <c r="I18" s="71" t="n">
+      <c r="H18" s="71" t="s">
+        <v>221</v>
+      </c>
+      <c r="I18" s="72" t="n">
         <v>11.89</v>
       </c>
-      <c r="J18" s="71"/>
-      <c r="K18" s="71"/>
-      <c r="L18" s="72" t="n">
+      <c r="J18" s="72"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="73" t="n">
         <f aca="false">IF($H18="Absoluto",IF($J18="","",$J18),IF($I18="","",IF($H18="Razão MT",MIN($I18*(1-Parâmetros!$B$3),$I18*(1+Parâmetros!$B$3)),$I18-Parâmetros!$B$4)))</f>
         <v>9.89</v>
       </c>
-      <c r="M18" s="72" t="n">
+      <c r="M18" s="73" t="n">
         <f aca="false">IF($H18="Absoluto",IF($K18="","",$K18),IF($I18="","",IF($H18="Razão MT",MAX($I18*(1-Parâmetros!$B$3),$I18*(1+Parâmetros!$B$3)),$I18+Parâmetros!$B$4)))</f>
         <v>13.89</v>
       </c>
-      <c r="N18" s="82" t="n">
+      <c r="N18" s="83" t="n">
         <v>45.95</v>
       </c>
-      <c r="O18" s="74" t="str">
+      <c r="O18" s="75" t="str">
         <f aca="false">IF(OR(N18="",$L18="",$M18=""),"",IF($E18="+",IF(N18&gt;$M18,"Força",IF(N18&lt;$L18,"Fraqueza","Neutro")),IF(N18&lt;$L18,"Força",IF(N18&gt;$M18,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="P18" s="82" t="n">
+      <c r="P18" s="83" t="n">
         <v>30.82</v>
       </c>
-      <c r="Q18" s="74" t="str">
+      <c r="Q18" s="75" t="str">
         <f aca="false">IF(OR(P18="",$L18="",$M18=""),"",IF($E18="+",IF(P18&gt;$M18,"Força",IF(P18&lt;$L18,"Fraqueza","Neutro")),IF(P18&lt;$L18,"Força",IF(P18&gt;$M18,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="R18" s="82" t="n">
+      <c r="R18" s="83" t="n">
         <v>29.61</v>
       </c>
-      <c r="S18" s="74" t="str">
+      <c r="S18" s="75" t="str">
         <f aca="false">IF(OR(R18="",$L18="",$M18=""),"",IF($E18="+",IF(R18&gt;$M18,"Força",IF(R18&lt;$L18,"Fraqueza","Neutro")),IF(R18&lt;$L18,"Força",IF(R18&gt;$M18,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="T18" s="82" t="n">
+      <c r="T18" s="83" t="n">
         <v>26.83</v>
       </c>
-      <c r="U18" s="74" t="str">
+      <c r="U18" s="75" t="str">
         <f aca="false">IF(OR(T18="",$L18="",$M18=""),"",IF($E18="+",IF(T18&gt;$M18,"Força",IF(T18&lt;$L18,"Fraqueza","Neutro")),IF(T18&lt;$L18,"Força",IF(T18&gt;$M18,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="V18" s="82" t="n">
+      <c r="V18" s="83" t="n">
         <v>5.88</v>
       </c>
-      <c r="W18" s="74" t="str">
+      <c r="W18" s="75" t="str">
         <f aca="false">IF(OR(V18="",$L18="",$M18=""),"",IF($E18="+",IF(V18&gt;$M18,"Força",IF(V18&lt;$L18,"Fraqueza","Neutro")),IF(V18&lt;$L18,"Força",IF(V18&gt;$M18,"Fraqueza","Neutro"))))</f>
         <v>Força</v>
       </c>
-      <c r="X18" s="82" t="n">
+      <c r="X18" s="83" t="n">
         <v>16.77</v>
       </c>
-      <c r="Y18" s="74" t="str">
+      <c r="Y18" s="75" t="str">
         <f aca="false">IF(OR(X18="",$L18="",$M18=""),"",IF($E18="+",IF(X18&gt;$M18,"Força",IF(X18&lt;$L18,"Fraqueza","Neutro")),IF(X18&lt;$L18,"Força",IF(X18&gt;$M18,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="Z18" s="82" t="n">
+      <c r="Z18" s="83" t="n">
         <v>18.67</v>
       </c>
-      <c r="AA18" s="74" t="str">
+      <c r="AA18" s="75" t="str">
         <f aca="false">IF(OR(Z18="",$L18="",$M18=""),"",IF($E18="+",IF(Z18&gt;$M18,"Força",IF(Z18&lt;$L18,"Fraqueza","Neutro")),IF(Z18&lt;$L18,"Força",IF(Z18&gt;$M18,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="AB18" s="82" t="n">
+      <c r="AB18" s="83" t="n">
         <v>25.62</v>
       </c>
-      <c r="AC18" s="74" t="str">
+      <c r="AC18" s="75" t="str">
         <f aca="false">IF(OR(AB18="",$L18="",$M18=""),"",IF($E18="+",IF(AB18&gt;$M18,"Força",IF(AB18&lt;$L18,"Fraqueza","Neutro")),IF(AB18&lt;$L18,"Força",IF(AB18&gt;$M18,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="AD18" s="82" t="n">
+      <c r="AD18" s="83" t="n">
         <v>24.97</v>
       </c>
-      <c r="AE18" s="74" t="str">
+      <c r="AE18" s="75" t="str">
         <f aca="false">IF(OR(AD18="",$L18="",$M18=""),"",IF($E18="+",IF(AD18&gt;$M18,"Força",IF(AD18&lt;$L18,"Fraqueza","Neutro")),IF(AD18&lt;$L18,"Força",IF(AD18&gt;$M18,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="AF18" s="82" t="n">
+      <c r="AF18" s="83" t="n">
         <v>33.23</v>
       </c>
-      <c r="AG18" s="74" t="str">
+      <c r="AG18" s="75" t="str">
         <f aca="false">IF(OR(AF18="",$L18="",$M18=""),"",IF($E18="+",IF(AF18&gt;$M18,"Força",IF(AF18&lt;$L18,"Fraqueza","Neutro")),IF(AF18&lt;$L18,"Força",IF(AF18&gt;$M18,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="AH18" s="82" t="n">
+      <c r="AH18" s="83" t="n">
         <v>28.79</v>
       </c>
-      <c r="AI18" s="74" t="str">
+      <c r="AI18" s="75" t="str">
         <f aca="false">IF(OR(AH18="",$L18="",$M18=""),"",IF($E18="+",IF(AH18&gt;$M18,"Força",IF(AH18&lt;$L18,"Fraqueza","Neutro")),IF(AH18&lt;$L18,"Força",IF(AH18&gt;$M18,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
-      <c r="AJ18" s="82" t="n">
+      <c r="AJ18" s="83" t="n">
         <v>11.66</v>
       </c>
-      <c r="AK18" s="74" t="str">
+      <c r="AK18" s="75" t="str">
         <f aca="false">IF(OR(AJ18="",$L18="",$M18=""),"",IF($E18="+",IF(AJ18&gt;$M18,"Força",IF(AJ18&lt;$L18,"Fraqueza","Neutro")),IF(AJ18&lt;$L18,"Força",IF(AJ18&gt;$M18,"Fraqueza","Neutro"))))</f>
         <v>Neutro</v>
       </c>
-      <c r="AL18" s="82" t="n">
+      <c r="AL18" s="83" t="n">
         <v>15.78</v>
       </c>
-      <c r="AM18" s="74" t="str">
+      <c r="AM18" s="75" t="str">
         <f aca="false">IF(OR(AL18="",$L18="",$M18=""),"",IF($E18="+",IF(AL18&gt;$M18,"Força",IF(AL18&lt;$L18,"Fraqueza","Neutro")),IF(AL18&lt;$L18,"Força",IF(AL18&gt;$M18,"Fraqueza","Neutro"))))</f>
         <v>Fraqueza</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="79" t="s">
-        <v>229</v>
-      </c>
-      <c r="B19" s="80" t="s">
+      <c r="A19" s="80" t="s">
+        <v>246</v>
+      </c>
+      <c r="B19" s="81" t="s">
+        <v>242</v>
+      </c>
+      <c r="C19" s="81" t="s">
+        <v>247</v>
+      </c>
+      <c r="D19" s="80" t="s">
+        <v>248</v>
+      </c>
+      <c r="E19" s="71" t="s">
+        <v>211</v>
+      </c>
+      <c r="F19" s="81" t="s">
+        <v>249</v>
+      </c>
+      <c r="G19" s="71"/>
+      <c r="H19" s="71" t="s">
+        <v>217</v>
+      </c>
+      <c r="I19" s="72"/>
+      <c r="J19" s="72"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="73" t="str">
+        <f aca="false">IF($H19="Absoluto",IF($J19="","",$J19),IF($I19="","",IF($H19="Razão MT",MIN($I19*(1-Parâmetros!$B$3),$I19*(1+Parâmetros!$B$3)),$I19-Parâmetros!$B$4)))</f>
+        <v/>
+      </c>
+      <c r="M19" s="73" t="str">
+        <f aca="false">IF($H19="Absoluto",IF($K19="","",$K19),IF($I19="","",IF($H19="Razão MT",MAX($I19*(1-Parâmetros!$B$3),$I19*(1+Parâmetros!$B$3)),$I19+Parâmetros!$B$4)))</f>
+        <v/>
+      </c>
+      <c r="N19" s="72"/>
+      <c r="O19" s="75" t="str">
+        <f aca="false">IF(OR(N19="",$L19="",$M19=""),"",IF($E19="+",IF(N19&gt;$M19,"Força",IF(N19&lt;$L19,"Fraqueza","Neutro")),IF(N19&lt;$L19,"Força",IF(N19&gt;$M19,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="P19" s="72"/>
+      <c r="Q19" s="75" t="str">
+        <f aca="false">IF(OR(P19="",$L19="",$M19=""),"",IF($E19="+",IF(P19&gt;$M19,"Força",IF(P19&lt;$L19,"Fraqueza","Neutro")),IF(P19&lt;$L19,"Força",IF(P19&gt;$M19,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="R19" s="72"/>
+      <c r="S19" s="75" t="str">
+        <f aca="false">IF(OR(R19="",$L19="",$M19=""),"",IF($E19="+",IF(R19&gt;$M19,"Força",IF(R19&lt;$L19,"Fraqueza","Neutro")),IF(R19&lt;$L19,"Força",IF(R19&gt;$M19,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="T19" s="72"/>
+      <c r="U19" s="75" t="str">
+        <f aca="false">IF(OR(T19="",$L19="",$M19=""),"",IF($E19="+",IF(T19&gt;$M19,"Força",IF(T19&lt;$L19,"Fraqueza","Neutro")),IF(T19&lt;$L19,"Força",IF(T19&gt;$M19,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="V19" s="72"/>
+      <c r="W19" s="75" t="str">
+        <f aca="false">IF(OR(V19="",$L19="",$M19=""),"",IF($E19="+",IF(V19&gt;$M19,"Força",IF(V19&lt;$L19,"Fraqueza","Neutro")),IF(V19&lt;$L19,"Força",IF(V19&gt;$M19,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="X19" s="72"/>
+      <c r="Y19" s="75" t="str">
+        <f aca="false">IF(OR(X19="",$L19="",$M19=""),"",IF($E19="+",IF(X19&gt;$M19,"Força",IF(X19&lt;$L19,"Fraqueza","Neutro")),IF(X19&lt;$L19,"Força",IF(X19&gt;$M19,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="Z19" s="72"/>
+      <c r="AA19" s="75" t="str">
+        <f aca="false">IF(OR(Z19="",$L19="",$M19=""),"",IF($E19="+",IF(Z19&gt;$M19,"Força",IF(Z19&lt;$L19,"Fraqueza","Neutro")),IF(Z19&lt;$L19,"Força",IF(Z19&gt;$M19,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="AB19" s="72"/>
+      <c r="AC19" s="75" t="str">
+        <f aca="false">IF(OR(AB19="",$L19="",$M19=""),"",IF($E19="+",IF(AB19&gt;$M19,"Força",IF(AB19&lt;$L19,"Fraqueza","Neutro")),IF(AB19&lt;$L19,"Força",IF(AB19&gt;$M19,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="AD19" s="72"/>
+      <c r="AE19" s="75" t="str">
+        <f aca="false">IF(OR(AD19="",$L19="",$M19=""),"",IF($E19="+",IF(AD19&gt;$M19,"Força",IF(AD19&lt;$L19,"Fraqueza","Neutro")),IF(AD19&lt;$L19,"Força",IF(AD19&gt;$M19,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="AF19" s="72"/>
+      <c r="AG19" s="75" t="str">
+        <f aca="false">IF(OR(AF19="",$L19="",$M19=""),"",IF($E19="+",IF(AF19&gt;$M19,"Força",IF(AF19&lt;$L19,"Fraqueza","Neutro")),IF(AF19&lt;$L19,"Força",IF(AF19&gt;$M19,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="AH19" s="72"/>
+      <c r="AI19" s="75" t="str">
+        <f aca="false">IF(OR(AH19="",$L19="",$M19=""),"",IF($E19="+",IF(AH19&gt;$M19,"Força",IF(AH19&lt;$L19,"Fraqueza","Neutro")),IF(AH19&lt;$L19,"Força",IF(AH19&gt;$M19,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="AJ19" s="72"/>
+      <c r="AK19" s="75" t="str">
+        <f aca="false">IF(OR(AJ19="",$L19="",$M19=""),"",IF($E19="+",IF(AJ19&gt;$M19,"Força",IF(AJ19&lt;$L19,"Fraqueza","Neutro")),IF(AJ19&lt;$L19,"Força",IF(AJ19&gt;$M19,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+      <c r="AL19" s="72"/>
+      <c r="AM19" s="75" t="str">
+        <f aca="false">IF(OR(AL19="",$L19="",$M19=""),"",IF($E19="+",IF(AL19&gt;$M19,"Força",IF(AL19&lt;$L19,"Fraqueza","Neutro")),IF(AL19&lt;$L19,"Força",IF(AL19&gt;$M19,"Fraqueza","Neutro"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="80" t="s">
+        <v>250</v>
+      </c>
+      <c r="B20" s="81" t="s">
+        <v>242</v>
+      </c>
+      <c r="C20" s="81" t="s">
+        <v>251</v>
+      </c>
+      <c r="D20" s="80" t="s">
         <v>225</v>
       </c>
-      <c r="C19" s="80" t="s">
-        <v>230</v>
-      </c>
-      <c r="D19" s="79" t="s">
+      <c r="E20" s="71" t="s">
+        <v>245</v>
+      </c>
+      <c r="F20" s="81" t="s">
         <v>231</v>
       </c>
-      <c r="E19" s="70" t="s">
-        <v>192</v>
-      </c>
-      <c r="F19" s="80" t="s">
-        <v>232</v>
-      </c>
-      <c r="G19" s="70"/>
-      <c r="H19" s="70" t="s">
-        <v>199</v>
-      </c>
-      <c r="I19" s="71"/>
-      <c r="J19" s="71"/>
-      <c r="K19" s="71"/>
-      <c r="L19" s="72" t="str">
-        <f aca="false">IF($H19="Absoluto",IF($J19="","",$J19),IF($I19="","",IF($H19="Razão MT",MIN($I19*(1-Parâmetros!$B$3),$I19*(1+Parâmetros!$B$3)),$I19-Parâmetros!$B$4)))</f>
-        <v/>
-      </c>
-      <c r="M19" s="72" t="str">
-        <f aca="false">IF($H19="Absoluto",IF($K19="","",$K19),IF($I19="","",IF($H19="Razão MT",MAX($I19*(1-Parâmetros!$B$3),$I19*(1+Parâmetros!$B$3)),$I19+Parâmetros!$B$4)))</f>
-        <v/>
-      </c>
-      <c r="N19" s="71"/>
-      <c r="O19" s="74" t="str">
-        <f aca="false">IF(OR(N19="",$L19="",$M19=""),"",IF($E19="+",IF(N19&gt;$M19,"Força",IF(N19&lt;$L19,"Fraqueza","Neutro")),IF(N19&lt;$L19,"Força",IF(N19&gt;$M19,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="P19" s="71"/>
-      <c r="Q19" s="74" t="str">
-        <f aca="false">IF(OR(P19="",$L19="",$M19=""),"",IF($E19="+",IF(P19&gt;$M19,"Força",IF(P19&lt;$L19,"Fraqueza","Neutro")),IF(P19&lt;$L19,"Força",IF(P19&gt;$M19,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="R19" s="71"/>
-      <c r="S19" s="74" t="str">
-        <f aca="false">IF(OR(R19="",$L19="",$M19=""),"",IF($E19="+",IF(R19&gt;$M19,"Força",IF(R19&lt;$L19,"Fraqueza","Neutro")),IF(R19&lt;$L19,"Força",IF(R19&gt;$M19,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="T19" s="71"/>
-      <c r="U19" s="74" t="str">
-        <f aca="false">IF(OR(T19="",$L19="",$M19=""),"",IF($E19="+",IF(T19&gt;$M19,"Força",IF(T19&lt;$L19,"Fraqueza","Neutro")),IF(T19&lt;$L19,"Força",IF(T19&gt;$M19,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="V19" s="71"/>
-      <c r="W19" s="74" t="str">
-        <f aca="false">IF(OR(V19="",$L19="",$M19=""),"",IF($E19="+",IF(V19&gt;$M19,"Força",IF(V19&lt;$L19,"Fraqueza","Neutro")),IF(V19&lt;$L19,"Força",IF(V19&gt;$M19,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="X19" s="71"/>
-      <c r="Y19" s="74" t="str">
-        <f aca="false">IF(OR(X19="",$L19="",$M19=""),"",IF($E19="+",IF(X19&gt;$M19,"Força",IF(X19&lt;$L19,"Fraqueza","Neutro")),IF(X19&lt;$L19,"Força",IF(X19&gt;$M19,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="Z19" s="71"/>
-      <c r="AA19" s="74" t="str">
-        <f aca="false">IF(OR(Z19="",$L19="",$M19=""),"",IF($E19="+",IF(Z19&gt;$M19,"Força",IF(Z19&lt;$L19,"Fraqueza","Neutro")),IF(Z19&lt;$L19,"Força",IF(Z19&gt;$M19,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AB19" s="71"/>
-      <c r="AC19" s="74" t="str">
-        <f aca="false">IF(OR(AB19="",$L19="",$M19=""),"",IF($E19="+",IF(AB19&gt;$M19,"Força",IF(AB19&lt;$L19,"Fraqueza","Neutro")),IF(AB19&lt;$L19,"Força",IF(AB19&gt;$M19,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AD19" s="71"/>
-      <c r="AE19" s="74" t="str">
-        <f aca="false">IF(OR(AD19="",$L19="",$M19=""),"",IF($E19="+",IF(AD19&gt;$M19,"Força",IF(AD19&lt;$L19,"Fraqueza","Neutro")),IF(AD19&lt;$L19,"Força",IF(AD19&gt;$M19,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AF19" s="71"/>
-      <c r="AG19" s="74" t="str">
-        <f aca="false">IF(OR(AF19="",$L19="",$M19=""),"",IF($E19="+",IF(AF19&gt;$M19,"Força",IF(AF19&lt;$L19,"Fraqueza","Neutro")),IF(AF19&lt;$L19,"Força",IF(AF19&gt;$M19,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AH19" s="71"/>
-      <c r="AI19" s="74" t="str">
-        <f aca="false">IF(OR(AH19="",$L19="",$M19=""),"",IF($E19="+",IF(AH19&gt;$M19,"Força",IF(AH19&lt;$L19,"Fraqueza","Neutro")),IF(AH19&lt;$L19,"Força",IF(AH19&gt;$M19,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AJ19" s="71"/>
-      <c r="AK19" s="74" t="str">
-        <f aca="false">IF(OR(AJ19="",$L19="",$M19=""),"",IF($E19="+",IF(AJ19&gt;$M19,"Força",IF(AJ19&lt;$L19,"Fraqueza","Neutro")),IF(AJ19&lt;$L19,"Força",IF(AJ19&gt;$M19,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AL19" s="71"/>
-      <c r="AM19" s="74" t="str">
-        <f aca="false">IF(OR(AL19="",$L19="",$M19=""),"",IF($E19="+",IF(AL19&gt;$M19,"Força",IF(AL19&lt;$L19,"Fraqueza","Neutro")),IF(AL19&lt;$L19,"Força",IF(AL19&gt;$M19,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="79" t="s">
-        <v>233</v>
-      </c>
-      <c r="B20" s="80" t="s">
-        <v>225</v>
-      </c>
-      <c r="C20" s="80" t="s">
-        <v>234</v>
-      </c>
-      <c r="D20" s="79" t="s">
-        <v>208</v>
-      </c>
-      <c r="E20" s="70" t="s">
-        <v>228</v>
-      </c>
-      <c r="F20" s="80" t="s">
-        <v>214</v>
-      </c>
-      <c r="G20" s="70"/>
-      <c r="H20" s="70" t="s">
-        <v>199</v>
-      </c>
-      <c r="I20" s="71"/>
-      <c r="J20" s="71"/>
-      <c r="K20" s="71"/>
-      <c r="L20" s="72" t="str">
+      <c r="G20" s="71"/>
+      <c r="H20" s="71" t="s">
+        <v>217</v>
+      </c>
+      <c r="I20" s="72"/>
+      <c r="J20" s="72"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="73" t="str">
         <f aca="false">IF($H20="Absoluto",IF($J20="","",$J20),IF($I20="","",IF($H20="Razão MT",MIN($I20*(1-Parâmetros!$B$3),$I20*(1+Parâmetros!$B$3)),$I20-Parâmetros!$B$4)))</f>
         <v/>
       </c>
-      <c r="M20" s="72" t="str">
+      <c r="M20" s="73" t="str">
         <f aca="false">IF($H20="Absoluto",IF($K20="","",$K20),IF($I20="","",IF($H20="Razão MT",MAX($I20*(1-Parâmetros!$B$3),$I20*(1+Parâmetros!$B$3)),$I20+Parâmetros!$B$4)))</f>
         <v/>
       </c>
-      <c r="N20" s="71"/>
-      <c r="O20" s="74" t="str">
+      <c r="N20" s="72"/>
+      <c r="O20" s="75" t="str">
         <f aca="false">IF(OR(N20="",$L20="",$M20=""),"",IF($E20="+",IF(N20&gt;$M20,"Força",IF(N20&lt;$L20,"Fraqueza","Neutro")),IF(N20&lt;$L20,"Força",IF(N20&gt;$M20,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="P20" s="71"/>
-      <c r="Q20" s="74" t="str">
+      <c r="P20" s="72"/>
+      <c r="Q20" s="75" t="str">
         <f aca="false">IF(OR(P20="",$L20="",$M20=""),"",IF($E20="+",IF(P20&gt;$M20,"Força",IF(P20&lt;$L20,"Fraqueza","Neutro")),IF(P20&lt;$L20,"Força",IF(P20&gt;$M20,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="R20" s="71"/>
-      <c r="S20" s="74" t="str">
+      <c r="R20" s="72"/>
+      <c r="S20" s="75" t="str">
         <f aca="false">IF(OR(R20="",$L20="",$M20=""),"",IF($E20="+",IF(R20&gt;$M20,"Força",IF(R20&lt;$L20,"Fraqueza","Neutro")),IF(R20&lt;$L20,"Força",IF(R20&gt;$M20,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="T20" s="71"/>
-      <c r="U20" s="74" t="str">
+      <c r="T20" s="72"/>
+      <c r="U20" s="75" t="str">
         <f aca="false">IF(OR(T20="",$L20="",$M20=""),"",IF($E20="+",IF(T20&gt;$M20,"Força",IF(T20&lt;$L20,"Fraqueza","Neutro")),IF(T20&lt;$L20,"Força",IF(T20&gt;$M20,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="V20" s="71"/>
-      <c r="W20" s="74" t="str">
+      <c r="V20" s="72"/>
+      <c r="W20" s="75" t="str">
         <f aca="false">IF(OR(V20="",$L20="",$M20=""),"",IF($E20="+",IF(V20&gt;$M20,"Força",IF(V20&lt;$L20,"Fraqueza","Neutro")),IF(V20&lt;$L20,"Força",IF(V20&gt;$M20,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="X20" s="71"/>
-      <c r="Y20" s="74" t="str">
+      <c r="X20" s="72"/>
+      <c r="Y20" s="75" t="str">
         <f aca="false">IF(OR(X20="",$L20="",$M20=""),"",IF($E20="+",IF(X20&gt;$M20,"Força",IF(X20&lt;$L20,"Fraqueza","Neutro")),IF(X20&lt;$L20,"Força",IF(X20&gt;$M20,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="Z20" s="71"/>
-      <c r="AA20" s="74" t="str">
+      <c r="Z20" s="72"/>
+      <c r="AA20" s="75" t="str">
         <f aca="false">IF(OR(Z20="",$L20="",$M20=""),"",IF($E20="+",IF(Z20&gt;$M20,"Força",IF(Z20&lt;$L20,"Fraqueza","Neutro")),IF(Z20&lt;$L20,"Força",IF(Z20&gt;$M20,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AB20" s="71"/>
-      <c r="AC20" s="74" t="str">
+      <c r="AB20" s="72"/>
+      <c r="AC20" s="75" t="str">
         <f aca="false">IF(OR(AB20="",$L20="",$M20=""),"",IF($E20="+",IF(AB20&gt;$M20,"Força",IF(AB20&lt;$L20,"Fraqueza","Neutro")),IF(AB20&lt;$L20,"Força",IF(AB20&gt;$M20,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AD20" s="71"/>
-      <c r="AE20" s="74" t="str">
+      <c r="AD20" s="72"/>
+      <c r="AE20" s="75" t="str">
         <f aca="false">IF(OR(AD20="",$L20="",$M20=""),"",IF($E20="+",IF(AD20&gt;$M20,"Força",IF(AD20&lt;$L20,"Fraqueza","Neutro")),IF(AD20&lt;$L20,"Força",IF(AD20&gt;$M20,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AF20" s="71"/>
-      <c r="AG20" s="74" t="str">
+      <c r="AF20" s="72"/>
+      <c r="AG20" s="75" t="str">
         <f aca="false">IF(OR(AF20="",$L20="",$M20=""),"",IF($E20="+",IF(AF20&gt;$M20,"Força",IF(AF20&lt;$L20,"Fraqueza","Neutro")),IF(AF20&lt;$L20,"Força",IF(AF20&gt;$M20,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AH20" s="71"/>
-      <c r="AI20" s="74" t="str">
+      <c r="AH20" s="72"/>
+      <c r="AI20" s="75" t="str">
         <f aca="false">IF(OR(AH20="",$L20="",$M20=""),"",IF($E20="+",IF(AH20&gt;$M20,"Força",IF(AH20&lt;$L20,"Fraqueza","Neutro")),IF(AH20&lt;$L20,"Força",IF(AH20&gt;$M20,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AJ20" s="71"/>
-      <c r="AK20" s="74" t="str">
+      <c r="AJ20" s="72"/>
+      <c r="AK20" s="75" t="str">
         <f aca="false">IF(OR(AJ20="",$L20="",$M20=""),"",IF($E20="+",IF(AJ20&gt;$M20,"Força",IF(AJ20&lt;$L20,"Fraqueza","Neutro")),IF(AJ20&lt;$L20,"Força",IF(AJ20&gt;$M20,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AL20" s="71"/>
-      <c r="AM20" s="74" t="str">
+      <c r="AL20" s="72"/>
+      <c r="AM20" s="75" t="str">
         <f aca="false">IF(OR(AL20="",$L20="",$M20=""),"",IF($E20="+",IF(AL20&gt;$M20,"Força",IF(AL20&lt;$L20,"Fraqueza","Neutro")),IF(AL20&lt;$L20,"Força",IF(AL20&gt;$M20,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="79" t="s">
+      <c r="A21" s="80" t="s">
         <v>160</v>
       </c>
-      <c r="B21" s="80" t="s">
-        <v>225</v>
-      </c>
-      <c r="C21" s="80" t="s">
-        <v>235</v>
-      </c>
-      <c r="D21" s="79" t="s">
-        <v>201</v>
-      </c>
-      <c r="E21" s="70" t="s">
-        <v>192</v>
-      </c>
-      <c r="F21" s="80" t="s">
-        <v>236</v>
-      </c>
-      <c r="G21" s="70"/>
-      <c r="H21" s="70" t="s">
-        <v>203</v>
-      </c>
-      <c r="I21" s="71"/>
-      <c r="J21" s="71"/>
-      <c r="K21" s="71"/>
-      <c r="L21" s="72" t="str">
+      <c r="B21" s="81" t="s">
+        <v>242</v>
+      </c>
+      <c r="C21" s="81" t="s">
+        <v>252</v>
+      </c>
+      <c r="D21" s="80" t="s">
+        <v>219</v>
+      </c>
+      <c r="E21" s="71" t="s">
+        <v>211</v>
+      </c>
+      <c r="F21" s="81" t="s">
+        <v>253</v>
+      </c>
+      <c r="G21" s="71"/>
+      <c r="H21" s="71" t="s">
+        <v>221</v>
+      </c>
+      <c r="I21" s="72"/>
+      <c r="J21" s="72"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="73" t="str">
         <f aca="false">IF($H21="Absoluto",IF($J21="","",$J21),IF($I21="","",IF($H21="Razão MT",MIN($I21*(1-Parâmetros!$B$3),$I21*(1+Parâmetros!$B$3)),$I21-Parâmetros!$B$4)))</f>
         <v/>
       </c>
-      <c r="M21" s="72" t="str">
+      <c r="M21" s="73" t="str">
         <f aca="false">IF($H21="Absoluto",IF($K21="","",$K21),IF($I21="","",IF($H21="Razão MT",MAX($I21*(1-Parâmetros!$B$3),$I21*(1+Parâmetros!$B$3)),$I21+Parâmetros!$B$4)))</f>
         <v/>
       </c>
-      <c r="N21" s="71"/>
-      <c r="O21" s="74" t="str">
+      <c r="N21" s="72"/>
+      <c r="O21" s="75" t="str">
         <f aca="false">IF(OR(N21="",$L21="",$M21=""),"",IF($E21="+",IF(N21&gt;$M21,"Força",IF(N21&lt;$L21,"Fraqueza","Neutro")),IF(N21&lt;$L21,"Força",IF(N21&gt;$M21,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="P21" s="71"/>
-      <c r="Q21" s="74" t="str">
+      <c r="P21" s="72"/>
+      <c r="Q21" s="75" t="str">
         <f aca="false">IF(OR(P21="",$L21="",$M21=""),"",IF($E21="+",IF(P21&gt;$M21,"Força",IF(P21&lt;$L21,"Fraqueza","Neutro")),IF(P21&lt;$L21,"Força",IF(P21&gt;$M21,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="R21" s="71"/>
-      <c r="S21" s="74" t="str">
+      <c r="R21" s="72"/>
+      <c r="S21" s="75" t="str">
         <f aca="false">IF(OR(R21="",$L21="",$M21=""),"",IF($E21="+",IF(R21&gt;$M21,"Força",IF(R21&lt;$L21,"Fraqueza","Neutro")),IF(R21&lt;$L21,"Força",IF(R21&gt;$M21,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="T21" s="71"/>
-      <c r="U21" s="74" t="str">
+      <c r="T21" s="72"/>
+      <c r="U21" s="75" t="str">
         <f aca="false">IF(OR(T21="",$L21="",$M21=""),"",IF($E21="+",IF(T21&gt;$M21,"Força",IF(T21&lt;$L21,"Fraqueza","Neutro")),IF(T21&lt;$L21,"Força",IF(T21&gt;$M21,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="V21" s="71"/>
-      <c r="W21" s="74" t="str">
+      <c r="V21" s="72"/>
+      <c r="W21" s="75" t="str">
         <f aca="false">IF(OR(V21="",$L21="",$M21=""),"",IF($E21="+",IF(V21&gt;$M21,"Força",IF(V21&lt;$L21,"Fraqueza","Neutro")),IF(V21&lt;$L21,"Força",IF(V21&gt;$M21,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="X21" s="71"/>
-      <c r="Y21" s="74" t="str">
+      <c r="X21" s="72"/>
+      <c r="Y21" s="75" t="str">
         <f aca="false">IF(OR(X21="",$L21="",$M21=""),"",IF($E21="+",IF(X21&gt;$M21,"Força",IF(X21&lt;$L21,"Fraqueza","Neutro")),IF(X21&lt;$L21,"Força",IF(X21&gt;$M21,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="Z21" s="71"/>
-      <c r="AA21" s="74" t="str">
+      <c r="Z21" s="72"/>
+      <c r="AA21" s="75" t="str">
         <f aca="false">IF(OR(Z21="",$L21="",$M21=""),"",IF($E21="+",IF(Z21&gt;$M21,"Força",IF(Z21&lt;$L21,"Fraqueza","Neutro")),IF(Z21&lt;$L21,"Força",IF(Z21&gt;$M21,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AB21" s="71"/>
-      <c r="AC21" s="74" t="str">
+      <c r="AB21" s="72"/>
+      <c r="AC21" s="75" t="str">
         <f aca="false">IF(OR(AB21="",$L21="",$M21=""),"",IF($E21="+",IF(AB21&gt;$M21,"Força",IF(AB21&lt;$L21,"Fraqueza","Neutro")),IF(AB21&lt;$L21,"Força",IF(AB21&gt;$M21,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AD21" s="71"/>
-      <c r="AE21" s="74" t="str">
+      <c r="AD21" s="72"/>
+      <c r="AE21" s="75" t="str">
         <f aca="false">IF(OR(AD21="",$L21="",$M21=""),"",IF($E21="+",IF(AD21&gt;$M21,"Força",IF(AD21&lt;$L21,"Fraqueza","Neutro")),IF(AD21&lt;$L21,"Força",IF(AD21&gt;$M21,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AF21" s="71"/>
-      <c r="AG21" s="74" t="str">
+      <c r="AF21" s="72"/>
+      <c r="AG21" s="75" t="str">
         <f aca="false">IF(OR(AF21="",$L21="",$M21=""),"",IF($E21="+",IF(AF21&gt;$M21,"Força",IF(AF21&lt;$L21,"Fraqueza","Neutro")),IF(AF21&lt;$L21,"Força",IF(AF21&gt;$M21,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AH21" s="71"/>
-      <c r="AI21" s="74" t="str">
+      <c r="AH21" s="72"/>
+      <c r="AI21" s="75" t="str">
         <f aca="false">IF(OR(AH21="",$L21="",$M21=""),"",IF($E21="+",IF(AH21&gt;$M21,"Força",IF(AH21&lt;$L21,"Fraqueza","Neutro")),IF(AH21&lt;$L21,"Força",IF(AH21&gt;$M21,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AJ21" s="71"/>
-      <c r="AK21" s="74" t="str">
+      <c r="AJ21" s="72"/>
+      <c r="AK21" s="75" t="str">
         <f aca="false">IF(OR(AJ21="",$L21="",$M21=""),"",IF($E21="+",IF(AJ21&gt;$M21,"Força",IF(AJ21&lt;$L21,"Fraqueza","Neutro")),IF(AJ21&lt;$L21,"Força",IF(AJ21&gt;$M21,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
-      <c r="AL21" s="71"/>
-      <c r="AM21" s="74" t="str">
+      <c r="AL21" s="72"/>
+      <c r="AM21" s="75" t="str">
         <f aca="false">IF(OR(AL21="",$L21="",$M21=""),"",IF($E21="+",IF(AL21&gt;$M21,"Força",IF(AL21&lt;$L21,"Fraqueza","Neutro")),IF(AL21&lt;$L21,"Força",IF(AL21&gt;$M21,"Fraqueza","Neutro"))))</f>
         <v/>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="33" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -30502,694 +30743,694 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="83" t="s">
+      <c r="A4" s="84" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="83" t="s">
+      <c r="B4" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="83" t="s">
-        <v>177</v>
-      </c>
-      <c r="D4" s="83" t="s">
+      <c r="C4" s="84" t="s">
+        <v>196</v>
+      </c>
+      <c r="D4" s="84" t="s">
         <v>66</v>
       </c>
-      <c r="E4" s="83" t="s">
-        <v>240</v>
-      </c>
-      <c r="F4" s="83" t="s">
+      <c r="E4" s="84" t="s">
+        <v>257</v>
+      </c>
+      <c r="F4" s="84" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="83" t="s">
+      <c r="G4" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="83" t="s">
+      <c r="H4" s="84" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="83" t="s">
+      <c r="I4" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="83" t="s">
+      <c r="J4" s="84" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="83" t="s">
+      <c r="K4" s="84" t="s">
         <v>50</v>
       </c>
-      <c r="L4" s="83" t="s">
+      <c r="L4" s="84" t="s">
         <v>51</v>
       </c>
-      <c r="M4" s="83" t="s">
+      <c r="M4" s="84" t="s">
         <v>52</v>
       </c>
-      <c r="N4" s="83" t="s">
+      <c r="N4" s="84" t="s">
         <v>53</v>
       </c>
-      <c r="O4" s="83" t="s">
+      <c r="O4" s="84" t="s">
         <v>54</v>
       </c>
-      <c r="P4" s="83" t="s">
+      <c r="P4" s="84" t="s">
         <v>55</v>
       </c>
-      <c r="Q4" s="83" t="s">
+      <c r="Q4" s="84" t="s">
         <v>56</v>
       </c>
-      <c r="R4" s="83" t="s">
+      <c r="R4" s="84" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="C6" s="28" t="s">
         <v>74</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>245</v>
-      </c>
-      <c r="F6" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="70" t="n">
+        <v>262</v>
+      </c>
+      <c r="F6" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="H6" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="N6" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="O6" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="P6" s="70" t="n">
+      <c r="H6" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="Q6" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" s="70" t="n">
+      <c r="Q6" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" s="71" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="C7" s="28" t="s">
         <v>74</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>248</v>
-      </c>
-      <c r="F7" s="70" t="n">
+        <v>265</v>
+      </c>
+      <c r="F7" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="70" t="n">
+      <c r="G7" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="H7" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="O7" s="70" t="n">
+      <c r="H7" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="P7" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" s="70" t="n">
+      <c r="P7" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="71" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>251</v>
-      </c>
-      <c r="F8" s="70" t="n">
+        <v>268</v>
+      </c>
+      <c r="F8" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="70" t="n">
+      <c r="G8" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="H8" s="70" t="n">
+      <c r="H8" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" s="70" t="n">
+      <c r="I8" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="P8" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" s="70" t="n">
+      <c r="P8" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" s="71" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="C9" s="28" t="s">
         <v>76</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>254</v>
-      </c>
-      <c r="F9" s="70" t="n">
+        <v>271</v>
+      </c>
+      <c r="F9" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" s="70" t="n">
+      <c r="G9" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="M9" s="70" t="n">
+      <c r="M9" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="N9" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="70" t="n">
+      <c r="N9" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="R9" s="70" t="n">
+      <c r="R9" s="71" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>257</v>
-      </c>
-      <c r="F10" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="70" t="n">
+        <v>274</v>
+      </c>
+      <c r="F10" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="H10" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="N10" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q10" s="70" t="n">
+      <c r="H10" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="R10" s="70" t="n">
+      <c r="R10" s="71" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>260</v>
-      </c>
-      <c r="F11" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" s="70" t="n">
+        <v>277</v>
+      </c>
+      <c r="F11" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="I11" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="J11" s="70" t="n">
+      <c r="H11" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="K11" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="N11" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="O11" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="P11" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q11" s="70" t="n">
+      <c r="K11" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="R11" s="70" t="n">
+      <c r="R11" s="71" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="84" t="s">
-        <v>261</v>
-      </c>
-      <c r="B12" s="84" t="s">
-        <v>262</v>
-      </c>
-      <c r="C12" s="85" t="s">
+      <c r="A12" s="85" t="s">
+        <v>278</v>
+      </c>
+      <c r="B12" s="85" t="s">
+        <v>279</v>
+      </c>
+      <c r="C12" s="86" t="s">
         <v>74</v>
       </c>
-      <c r="D12" s="85" t="s">
-        <v>263</v>
-      </c>
-      <c r="E12" s="85" t="s">
-        <v>264</v>
-      </c>
-      <c r="F12" s="70" t="n">
+      <c r="D12" s="86" t="s">
+        <v>280</v>
+      </c>
+      <c r="E12" s="86" t="s">
+        <v>281</v>
+      </c>
+      <c r="F12" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="G12" s="70" t="n">
+      <c r="G12" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="H12" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="O12" s="70" t="n">
+      <c r="H12" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="P12" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q12" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" s="70" t="n">
+      <c r="P12" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" s="71" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="84" t="s">
-        <v>265</v>
-      </c>
-      <c r="B13" s="84" t="s">
-        <v>262</v>
-      </c>
-      <c r="C13" s="85" t="s">
+      <c r="A13" s="85" t="s">
+        <v>282</v>
+      </c>
+      <c r="B13" s="85" t="s">
+        <v>279</v>
+      </c>
+      <c r="C13" s="86" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="85" t="s">
-        <v>266</v>
-      </c>
-      <c r="E13" s="85" t="s">
-        <v>267</v>
-      </c>
-      <c r="F13" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" s="70" t="n">
+      <c r="D13" s="86" t="s">
+        <v>283</v>
+      </c>
+      <c r="E13" s="86" t="s">
+        <v>284</v>
+      </c>
+      <c r="F13" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" s="70" t="n">
+      <c r="H13" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="K13" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="M13" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="O13" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="P13" s="70" t="n">
+      <c r="K13" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="P13" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="Q13" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" s="70" t="n">
+      <c r="Q13" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" s="71" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="84" t="s">
-        <v>268</v>
-      </c>
-      <c r="B14" s="84" t="s">
-        <v>262</v>
-      </c>
-      <c r="C14" s="85" t="s">
+      <c r="A14" s="85" t="s">
+        <v>285</v>
+      </c>
+      <c r="B14" s="85" t="s">
+        <v>279</v>
+      </c>
+      <c r="C14" s="86" t="s">
         <v>74</v>
       </c>
-      <c r="D14" s="85" t="s">
-        <v>269</v>
-      </c>
-      <c r="E14" s="85" t="s">
-        <v>270</v>
-      </c>
-      <c r="F14" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="G14" s="70" t="n">
+      <c r="D14" s="86" t="s">
+        <v>286</v>
+      </c>
+      <c r="E14" s="86" t="s">
+        <v>287</v>
+      </c>
+      <c r="F14" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="H14" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" s="70" t="n">
+      <c r="H14" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="K14" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="L14" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="P14" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q14" s="70" t="n">
+      <c r="K14" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="P14" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="R14" s="70" t="n">
+      <c r="R14" s="71" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="84" t="s">
-        <v>271</v>
-      </c>
-      <c r="B15" s="84" t="s">
-        <v>262</v>
-      </c>
-      <c r="C15" s="85" t="s">
-        <v>225</v>
-      </c>
-      <c r="D15" s="85" t="s">
-        <v>272</v>
-      </c>
-      <c r="E15" s="85" t="s">
-        <v>273</v>
-      </c>
-      <c r="F15" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="H15" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="70" t="n">
+      <c r="A15" s="85" t="s">
+        <v>288</v>
+      </c>
+      <c r="B15" s="85" t="s">
+        <v>279</v>
+      </c>
+      <c r="C15" s="86" t="s">
+        <v>242</v>
+      </c>
+      <c r="D15" s="86" t="s">
+        <v>289</v>
+      </c>
+      <c r="E15" s="86" t="s">
+        <v>290</v>
+      </c>
+      <c r="F15" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="K15" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="N15" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="70" t="n">
+      <c r="K15" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="N15" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="R15" s="70" t="n">
+      <c r="R15" s="71" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="84" t="s">
-        <v>274</v>
-      </c>
-      <c r="B16" s="84" t="s">
-        <v>262</v>
-      </c>
-      <c r="C16" s="85" t="s">
-        <v>219</v>
-      </c>
-      <c r="D16" s="85" t="s">
-        <v>275</v>
-      </c>
-      <c r="E16" s="85" t="s">
-        <v>276</v>
-      </c>
-      <c r="F16" s="70" t="n">
+      <c r="A16" s="85" t="s">
+        <v>291</v>
+      </c>
+      <c r="B16" s="85" t="s">
+        <v>279</v>
+      </c>
+      <c r="C16" s="86" t="s">
+        <v>236</v>
+      </c>
+      <c r="D16" s="86" t="s">
+        <v>292</v>
+      </c>
+      <c r="E16" s="86" t="s">
+        <v>293</v>
+      </c>
+      <c r="F16" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="G16" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="70" t="n">
+      <c r="G16" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="I16" s="70" t="n">
+      <c r="I16" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="J16" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" s="70" t="n">
+      <c r="J16" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="L16" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" s="70" t="n">
+      <c r="L16" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="O16" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="P16" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q16" s="70" t="n">
+      <c r="O16" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="P16" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="R16" s="70" t="n">
+      <c r="R16" s="71" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="33" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>

--- a/pesm-pantanal-norte/dados/Matriz_SWOT_PESM_Pantanal_Norte.xlsx
+++ b/pesm-pantanal-norte/dados/Matriz_SWOT_PESM_Pantanal_Norte.xlsx
@@ -295,7 +295,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="338">
   <si>
     <t xml:space="preserve">MATRIZ SWOT DO PERFIL ECONÔMICO-PRODUTIVO SETORIAL MUNICIPAL (PESM) — PANTANAL NORTE</t>
   </si>
@@ -910,6 +910,21 @@
   </si>
   <si>
     <t xml:space="preserve">Os 16 grupos da base tratada aproximam as seções CNAE; o HHI é comparável entre municípios e MT porque usa o mesmo recorte.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conferência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021 / 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d1_pib_vab.csv (IBGE – PIB dos Municípios)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QLs (AGR-01, IND-01, CS-01) e EST-02 de 2021 recalculados com lq_agro, lq_ind, lq_serv e sh_adespss_va; participações setoriais de MT; vinculos_31dez 2023 comparado com a RAIS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diferença máxima menor que 0,001 nos QLs e no EST-02; participações de MT idênticas às da aba Ranking Locacional; vínculos idênticos. O VAB setorial da base também termina em 2021, então a LIMITAÇÃO acima continua valendo.</t>
   </si>
   <si>
     <t xml:space="preserve">PARÂMETROS</t>
@@ -2503,7 +2518,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B2" s="1" t="n">
         <f aca="false">IFERROR(MATCH($B$1,'Indicadores (F-W)'!$A$4:$AM$4,0),"")</f>
@@ -2512,7 +2527,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B3" s="1" t="n">
         <f aca="false">IFERROR(MATCH($B$1,'Fatores Externos (O-A)'!$A$4:$R$4,0),"")</f>
@@ -2524,7 +2539,7 @@
         <v>59</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>102</v>
@@ -2533,16 +2548,16 @@
         <v>31</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>59</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>67</v>
@@ -2551,16 +2566,16 @@
         <v>33</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3364,12 +3379,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4762,7 +4777,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -4808,12 +4823,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6206,7 +6221,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -6252,12 +6267,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7650,7 +7665,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -7696,12 +7711,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9094,7 +9109,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -9140,12 +9155,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10538,7 +10553,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -10584,12 +10599,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11982,7 +11997,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -12028,12 +12043,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13426,7 +13441,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -13472,12 +13487,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14870,7 +14885,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -14916,12 +14931,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16314,7 +16329,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -17181,12 +17196,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18579,7 +18594,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -18625,12 +18640,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20023,7 +20038,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -20069,12 +20084,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21467,7 +21482,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -21513,12 +21528,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22911,7 +22926,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -28353,7 +28368,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
@@ -28724,6 +28739,23 @@
       </c>
       <c r="E34" s="58" t="s">
         <v>204</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="58" t="s">
+        <v>205</v>
+      </c>
+      <c r="B35" s="58" t="s">
+        <v>206</v>
+      </c>
+      <c r="C35" s="58" t="s">
+        <v>207</v>
+      </c>
+      <c r="D35" s="58" t="s">
+        <v>208</v>
+      </c>
+      <c r="E35" s="58" t="s">
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -28758,23 +28790,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="47" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="40" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B3" s="63" t="n">
         <v>0.1</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="40" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B4" s="64" t="n">
         <v>2</v>
@@ -28782,18 +28814,18 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="40" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B5" s="65" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28920,12 +28952,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28933,40 +28965,40 @@
         <v>59</v>
       </c>
       <c r="B4" s="66" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C4" s="66" t="s">
         <v>60</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="E4" s="66" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F4" s="66" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="G4" s="66" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="H4" s="66" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="I4" s="66" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="J4" s="66" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="K4" s="66" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="L4" s="66" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="M4" s="66" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="N4" s="66" t="s">
         <v>46</v>
@@ -29036,79 +29068,79 @@
       <c r="L5" s="66"/>
       <c r="M5" s="66"/>
       <c r="N5" s="67" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="O5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="P5" s="67" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="Q5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="R5" s="67" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="S5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="T5" s="67" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="U5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="V5" s="67" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="W5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="X5" s="67" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="Y5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="Z5" s="67" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AA5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AB5" s="67" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AC5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AD5" s="67" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AE5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AF5" s="67" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AG5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AH5" s="67" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AI5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AJ5" s="67" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AK5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AL5" s="67" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AM5" s="67" t="s">
         <v>102</v>
@@ -29116,28 +29148,28 @@
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="68" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B6" s="69" t="s">
         <v>74</v>
       </c>
       <c r="C6" s="69" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="D6" s="68" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="E6" s="70" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F6" s="69" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="G6" s="70" t="n">
         <v>2021</v>
       </c>
       <c r="H6" s="70" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I6" s="71" t="n">
         <v>1</v>
@@ -29256,22 +29288,22 @@
         <v>74</v>
       </c>
       <c r="C7" s="69" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="D7" s="68" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="E7" s="70" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F7" s="69" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="G7" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H7" s="70" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="I7" s="71" t="n">
         <v>5602.9</v>
@@ -29386,22 +29418,22 @@
         <v>74</v>
       </c>
       <c r="C8" s="69" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D8" s="68" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E8" s="70" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F8" s="69" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="G8" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H8" s="70" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="I8" s="71" t="n">
         <v>3.79</v>
@@ -29516,20 +29548,20 @@
         <v>74</v>
       </c>
       <c r="C9" s="69" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D9" s="68" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E9" s="70" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F9" s="69" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="G9" s="70"/>
       <c r="H9" s="70" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="I9" s="71"/>
       <c r="J9" s="71"/>
@@ -29616,20 +29648,20 @@
         <v>74</v>
       </c>
       <c r="C10" s="69" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="D10" s="68" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E10" s="70" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F10" s="69" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="G10" s="70"/>
       <c r="H10" s="70" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="I10" s="71"/>
       <c r="J10" s="71"/>
@@ -29710,28 +29742,28 @@
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="75" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B11" s="76" t="s">
         <v>76</v>
       </c>
       <c r="C11" s="76" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="D11" s="75" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="E11" s="70" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F11" s="76" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="G11" s="70" t="n">
         <v>2021</v>
       </c>
       <c r="H11" s="70" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I11" s="71" t="n">
         <v>1</v>
@@ -29850,22 +29882,22 @@
         <v>76</v>
       </c>
       <c r="C12" s="76" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D12" s="75" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E12" s="70" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F12" s="76" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="G12" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H12" s="70" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="I12" s="71" t="n">
         <v>36.92</v>
@@ -29980,22 +30012,22 @@
         <v>76</v>
       </c>
       <c r="C13" s="76" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D13" s="75" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E13" s="70" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F13" s="76" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="G13" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H13" s="70" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="I13" s="71" t="n">
         <v>2956.72</v>
@@ -30104,28 +30136,28 @@
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="77" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B14" s="78" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C14" s="78" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="D14" s="77" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="E14" s="70" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F14" s="78" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="G14" s="70" t="n">
         <v>2021</v>
       </c>
       <c r="H14" s="70" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I14" s="71" t="n">
         <v>1</v>
@@ -30241,25 +30273,25 @@
         <v>194</v>
       </c>
       <c r="B15" s="78" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C15" s="78" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="D15" s="77" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E15" s="70" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F15" s="78" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="G15" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H15" s="70" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="I15" s="71" t="n">
         <v>38.11</v>
@@ -30371,25 +30403,25 @@
         <v>158</v>
       </c>
       <c r="B16" s="78" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C16" s="78" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="D16" s="77" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E16" s="70" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F16" s="78" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="G16" s="70" t="n">
         <v>2021</v>
       </c>
       <c r="H16" s="70" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="I16" s="71" t="n">
         <v>33.22</v>
@@ -30501,25 +30533,25 @@
         <v>142</v>
       </c>
       <c r="B17" s="80" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C17" s="80" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D17" s="79" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E17" s="70" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F17" s="80" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="G17" s="70" t="n">
         <v>2023</v>
       </c>
       <c r="H17" s="70" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="I17" s="71" t="n">
         <v>74620.05</v>
@@ -30631,25 +30663,25 @@
         <v>138</v>
       </c>
       <c r="B18" s="80" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C18" s="80" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D18" s="79" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E18" s="70" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="F18" s="80" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="G18" s="70" t="n">
         <v>2021</v>
       </c>
       <c r="H18" s="70" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="I18" s="71" t="n">
         <v>11.89</v>
@@ -30761,25 +30793,25 @@
         <v>199</v>
       </c>
       <c r="B19" s="80" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C19" s="80" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D19" s="79" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="E19" s="70" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F19" s="80" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="G19" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H19" s="70" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="I19" s="71" t="n">
         <v>31.51</v>
@@ -30891,25 +30923,25 @@
         <v>202</v>
       </c>
       <c r="B20" s="80" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C20" s="80" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D20" s="79" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E20" s="70" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="F20" s="80" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="G20" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H20" s="70" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="I20" s="83" t="n">
         <v>0.1254</v>
@@ -31021,23 +31053,23 @@
         <v>160</v>
       </c>
       <c r="B21" s="80" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C21" s="80" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D21" s="79" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E21" s="70" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F21" s="80" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="G21" s="70"/>
       <c r="H21" s="70" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="I21" s="71"/>
       <c r="J21" s="71"/>
@@ -31118,7 +31150,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="33" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -31200,12 +31232,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31216,13 +31248,13 @@
         <v>67</v>
       </c>
       <c r="C4" s="84" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D4" s="84" t="s">
         <v>66</v>
       </c>
       <c r="E4" s="84" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F4" s="84" t="s">
         <v>46</v>
@@ -31266,24 +31298,24 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C6" s="28" t="s">
         <v>74</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="F6" s="70" t="n">
         <v>1</v>
@@ -31327,19 +31359,19 @@
     </row>
     <row r="7" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C7" s="28" t="s">
         <v>74</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="F7" s="70" t="n">
         <v>3</v>
@@ -31383,19 +31415,19 @@
     </row>
     <row r="8" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F8" s="70" t="n">
         <v>3</v>
@@ -31439,19 +31471,19 @@
     </row>
     <row r="9" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C9" s="28" t="s">
         <v>76</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="F9" s="70" t="n">
         <v>0</v>
@@ -31495,19 +31527,19 @@
     </row>
     <row r="10" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="F10" s="70" t="n">
         <v>1</v>
@@ -31551,19 +31583,19 @@
     </row>
     <row r="11" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="F11" s="70" t="n">
         <v>2</v>
@@ -31607,19 +31639,19 @@
     </row>
     <row r="12" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="85" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B12" s="85" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C12" s="86" t="s">
         <v>74</v>
       </c>
       <c r="D12" s="86" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="E12" s="86" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="F12" s="70" t="n">
         <v>3</v>
@@ -31663,19 +31695,19 @@
     </row>
     <row r="13" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="85" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B13" s="85" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C13" s="86" t="s">
         <v>74</v>
       </c>
       <c r="D13" s="86" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="E13" s="86" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="F13" s="70" t="n">
         <v>2</v>
@@ -31719,19 +31751,19 @@
     </row>
     <row r="14" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="85" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B14" s="85" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C14" s="86" t="s">
         <v>74</v>
       </c>
       <c r="D14" s="86" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="E14" s="86" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="F14" s="70" t="n">
         <v>2</v>
@@ -31775,19 +31807,19 @@
     </row>
     <row r="15" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="85" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B15" s="85" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C15" s="86" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="D15" s="86" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="E15" s="86" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="F15" s="70" t="n">
         <v>1</v>
@@ -31831,19 +31863,19 @@
     </row>
     <row r="16" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="85" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B16" s="85" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C16" s="86" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="D16" s="86" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="E16" s="86" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F16" s="70" t="n">
         <v>3</v>
@@ -31887,7 +31919,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="33" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
     </row>
   </sheetData>

--- a/pesm-pantanal-norte/dados/Matriz_SWOT_PESM_Pantanal_Norte.xlsx
+++ b/pesm-pantanal-norte/dados/Matriz_SWOT_PESM_Pantanal_Norte.xlsx
@@ -206,6 +206,18 @@
         </r>
       </text>
     </comment>
+    <comment ref="G21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">2022: último ano com os 13 municípios (2023 não tem Santo Antônio do Leverger). Fonte: d6_financas.csv (Siconfi/FINBRA), coluna autonomia_fiscal_pct = receita própria ÷ receita TOTAL. Aproxima receita própria ÷ receita corrente; como as receitas de capital são pequenas, a diferença tende a ser pequena, mas o denominador não é o mesmo.</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="I7" authorId="0">
       <text>
         <r>
@@ -227,6 +239,18 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">MT: 31.654.882 cab. (2019) → 32.853.368 cab. (2024) = +3,79%.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">MT = Σ receita própria ÷ Σ receita total dos 141 municípios em 2022 (não é o governo estadual).</t>
         </r>
       </text>
     </comment>
@@ -295,7 +319,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="342">
   <si>
     <t xml:space="preserve">MATRIZ SWOT DO PERFIL ECONÔMICO-PRODUTIVO SETORIAL MUNICIPAL (PESM) — PANTANAL NORTE</t>
   </si>
@@ -639,7 +663,7 @@
     <t xml:space="preserve">⚠ RANKING SWOT — COBERTURA MÍNIMA ATINGIDA; NOTAS EXTERNAS A VALIDAR</t>
   </si>
   <si>
-    <t xml:space="preserve">A regra de 75% de cobertura foi atingida em 25/09/2026: 13 de 16 indicadores internos com dado e 11 de 11 fatores externos pontuados. As notas externas ainda são preliminares (uma rodada, pesquisa web-based) e precisam de consenso da equipe antes de uso em relatório.</t>
+    <t xml:space="preserve">A regra de 75% de cobertura foi atingida em 25/09/2026: 14 de 16 indicadores internos com dado e 11 de 11 fatores externos pontuados. As notas externas ainda são preliminares (uma rodada, pesquisa web-based) e precisam de consenso da equipe antes de uso em relatório.</t>
   </si>
   <si>
     <t xml:space="preserve">Indicadores com dado</t>
@@ -744,7 +768,7 @@
     <t xml:space="preserve">O VAB setorial de 2022–2023 já foi divulgado pelo IBGE (dez/2025), mas não estava acessível no ambiente em que esta planilha foi preenchida. Os QLs e o EST-02 usam 2021 e devem ser atualizados pela Tabela 5938 do SIDRA (variáveis de VAB, anos 2022–2023). O PIB per capita (EST-01) já está em 2023.</t>
   </si>
   <si>
-    <t xml:space="preserve">PENDENTES (3 indicadores)</t>
+    <t xml:space="preserve">PENDENTES (2 indicadores)</t>
   </si>
   <si>
     <t xml:space="preserve">AGR-05</t>
@@ -780,7 +804,7 @@
     <t xml:space="preserve">EST-05</t>
   </si>
   <si>
-    <t xml:space="preserve">Siconfi/STN – DCA Anexo I-C (receitas próprias e receita corrente)</t>
+    <t xml:space="preserve">Preenchido em 25/09/2026 com d6_financas.csv (ver bloco "BASES TRATADAS" abaixo).</t>
   </si>
   <si>
     <t xml:space="preserve">RODADA DE 25/09/2026 — FATORES EXTERNOS (O-A)</t>
@@ -798,7 +822,7 @@
     <t xml:space="preserve">Indicadores internos pendentes</t>
   </si>
   <si>
-    <t xml:space="preserve">Pendentes: AGR-04 (Censo Agro 2017, fora do catálogo), AGR-05 (a base só tem diversificação entre lavoura, pecuária, extrativismo e pesca) e EST-05 (depende de d6_financas.csv, ainda não enviado).</t>
+    <t xml:space="preserve">Pendentes: AGR-04 (Censo Agro 2017, fora do catálogo) e AGR-05 (a base só tem diversificação entre lavoura, pecuária, extrativismo e pesca).</t>
   </si>
   <si>
     <t xml:space="preserve">RODADA DE 25/09/2026 — BASES TRATADAS (CATALOGO_BASES_TRATADAS, dimensão D1_PESM)</t>
@@ -925,6 +949,18 @@
   </si>
   <si>
     <t xml:space="preserve">Diferença máxima menor que 0,001 nos QLs e no EST-02; participações de MT idênticas às da aba Ranking Locacional; vínculos idênticos. O VAB setorial da base também termina em 2021, então a LIMITAÇÃO acima continua valendo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d6_financas.csv (Siconfi/FINBRA), coluna autonomia_fiscal_pct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receita própria ÷ receita total × 100 (a base não traz a receita corrente). Ref. MT = Σ receita própria ÷ Σ receita total dos 141 municípios = 18.24%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O cálculo com receita_propria_real ÷ receita_total_real reproduz a coluna (diferença &lt; 0,01 p.p.). Denominador diferente do previsto (receita total em vez de corrente): tratar como aproximação.</t>
   </si>
   <si>
     <t xml:space="preserve">PARÂMETROS</t>
@@ -2518,7 +2554,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B2" s="1" t="n">
         <f aca="false">IFERROR(MATCH($B$1,'Indicadores (F-W)'!$A$4:$AM$4,0),"")</f>
@@ -2527,7 +2563,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B3" s="1" t="n">
         <f aca="false">IFERROR(MATCH($B$1,'Fatores Externos (O-A)'!$A$4:$R$4,0),"")</f>
@@ -2539,7 +2575,7 @@
         <v>59</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>102</v>
@@ -2548,16 +2584,16 @@
         <v>31</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>59</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>67</v>
@@ -2566,16 +2602,16 @@
         <v>33</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3331,11 +3367,11 @@
       </c>
       <c r="C21" s="1" t="str">
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A21:$AM21,1,$B$2+1))</f>
-        <v/>
+        <v>Neutro</v>
       </c>
       <c r="D21" s="88" t="n">
         <f aca="false">IF($B$2="","",INDEX('Indicadores (F-W)'!$A21:$AM21,1,$B$2))</f>
-        <v>0</v>
+        <v>17.68</v>
       </c>
       <c r="E21" s="1" t="str">
         <f aca="false">IF(C21="Força",COUNTIF(C$6:C21,"Força"),"")</f>
@@ -3379,18 +3415,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="92" t="str">
         <f aca="false">"Indicadores internos com dado: "&amp;(COUNTA(L6:L21)-COUNTBLANK(L6:L21))&amp;" de 16  |  Neutros: "&amp;COUNTIF(L6:L21,"Neutro")&amp;"  |  Fatores externos pontuados: "&amp;COUNT(S6:S16)&amp;" de 11"</f>
-        <v>Indicadores internos com dado: 13 de 16  |  Neutros: 1  |  Fatores externos pontuados: 11 de 11</v>
+        <v>Indicadores internos com dado: 14 de 16  |  Neutros: 1  |  Fatores externos pontuados: 11 de 11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3414,7 +3450,7 @@
       <c r="D6" s="11"/>
       <c r="F6" s="12" t="str">
         <f aca="false">"FRAQUEZAS (W) — "&amp;COUNTIF($L$6:$L$21,"Fraqueza")&amp;" item(ns)"</f>
-        <v>FRAQUEZAS (W) — 9 item(ns)</v>
+        <v>FRAQUEZAS (W) — 10 item(ns)</v>
       </c>
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
@@ -4226,17 +4262,17 @@
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(10,$N$6:$N$21,0)),"")</f>
         <v/>
       </c>
-      <c r="F17" s="19" t="str">
+      <c r="F17" s="19" t="n">
         <f aca="false">IF(G17="","",10)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="G17" s="20" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(10,$O$6:$O$21,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="21" t="str">
+        <v>[Estrutura Econômica e Fiscal] EST-05 – Receitas próprias / receita corrente (%)</v>
+      </c>
+      <c r="H17" s="21" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(10,$O$6:$O$21,0)),"")</f>
-        <v/>
+        <v>6.34</v>
       </c>
       <c r="K17" s="1" t="str">
         <f aca="false">Aux!B17</f>
@@ -4390,19 +4426,19 @@
       </c>
       <c r="L21" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!O21</f>
-        <v/>
-      </c>
-      <c r="M21" s="1" t="str">
+        <v>Fraqueza</v>
+      </c>
+      <c r="M21" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!N21="","",'Indicadores (F-W)'!N21)</f>
-        <v/>
+        <v>6.34</v>
       </c>
       <c r="N21" s="1" t="str">
         <f aca="false">IF(L21="Força",COUNTIF(L$6:L21,"Força"),"")</f>
         <v/>
       </c>
-      <c r="O21" s="1" t="str">
+      <c r="O21" s="1" t="n">
         <f aca="false">IF(L21="Fraqueza",COUNTIF(L$6:L21,"Fraqueza"),"")</f>
-        <v/>
+        <v>10</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4777,7 +4813,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -4823,18 +4859,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="92" t="str">
         <f aca="false">"Indicadores internos com dado: "&amp;(COUNTA(L6:L21)-COUNTBLANK(L6:L21))&amp;" de 16  |  Neutros: "&amp;COUNTIF(L6:L21,"Neutro")&amp;"  |  Fatores externos pontuados: "&amp;COUNT(S6:S16)&amp;" de 11"</f>
-        <v>Indicadores internos com dado: 13 de 16  |  Neutros: 2  |  Fatores externos pontuados: 11 de 11</v>
+        <v>Indicadores internos com dado: 14 de 16  |  Neutros: 3  |  Fatores externos pontuados: 11 de 11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5834,11 +5870,11 @@
       </c>
       <c r="L21" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!Q21</f>
-        <v/>
-      </c>
-      <c r="M21" s="1" t="str">
+        <v>Neutro</v>
+      </c>
+      <c r="M21" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!P21="","",'Indicadores (F-W)'!P21)</f>
-        <v/>
+        <v>17.68</v>
       </c>
       <c r="N21" s="1" t="str">
         <f aca="false">IF(L21="Força",COUNTIF(L$6:L21,"Força"),"")</f>
@@ -6221,7 +6257,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -6267,18 +6303,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="92" t="str">
         <f aca="false">"Indicadores internos com dado: "&amp;(COUNTA(L6:L21)-COUNTBLANK(L6:L21))&amp;" de 16  |  Neutros: "&amp;COUNTIF(L6:L21,"Neutro")&amp;"  |  Fatores externos pontuados: "&amp;COUNT(S6:S16)&amp;" de 11"</f>
-        <v>Indicadores internos com dado: 13 de 16  |  Neutros: 1  |  Fatores externos pontuados: 11 de 11</v>
+        <v>Indicadores internos com dado: 14 de 16  |  Neutros: 1  |  Fatores externos pontuados: 11 de 11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6302,7 +6338,7 @@
       <c r="D6" s="11"/>
       <c r="F6" s="12" t="str">
         <f aca="false">"FRAQUEZAS (W) — "&amp;COUNTIF($L$6:$L$21,"Fraqueza")&amp;" item(ns)"</f>
-        <v>FRAQUEZAS (W) — 9 item(ns)</v>
+        <v>FRAQUEZAS (W) — 10 item(ns)</v>
       </c>
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
@@ -7114,17 +7150,17 @@
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(10,$N$6:$N$21,0)),"")</f>
         <v/>
       </c>
-      <c r="F17" s="19" t="str">
+      <c r="F17" s="19" t="n">
         <f aca="false">IF(G17="","",10)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="G17" s="20" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(10,$O$6:$O$21,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="21" t="str">
+        <v>[Estrutura Econômica e Fiscal] EST-05 – Receitas próprias / receita corrente (%)</v>
+      </c>
+      <c r="H17" s="21" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(10,$O$6:$O$21,0)),"")</f>
-        <v/>
+        <v>5.5</v>
       </c>
       <c r="K17" s="1" t="str">
         <f aca="false">Aux!B17</f>
@@ -7278,19 +7314,19 @@
       </c>
       <c r="L21" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!S21</f>
-        <v/>
-      </c>
-      <c r="M21" s="1" t="str">
+        <v>Fraqueza</v>
+      </c>
+      <c r="M21" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!R21="","",'Indicadores (F-W)'!R21)</f>
-        <v/>
+        <v>5.5</v>
       </c>
       <c r="N21" s="1" t="str">
         <f aca="false">IF(L21="Força",COUNTIF(L$6:L21,"Força"),"")</f>
         <v/>
       </c>
-      <c r="O21" s="1" t="str">
+      <c r="O21" s="1" t="n">
         <f aca="false">IF(L21="Fraqueza",COUNTIF(L$6:L21,"Fraqueza"),"")</f>
-        <v/>
+        <v>10</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7665,7 +7701,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -7711,18 +7747,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="92" t="str">
         <f aca="false">"Indicadores internos com dado: "&amp;(COUNTA(L6:L21)-COUNTBLANK(L6:L21))&amp;" de 16  |  Neutros: "&amp;COUNTIF(L6:L21,"Neutro")&amp;"  |  Fatores externos pontuados: "&amp;COUNT(S6:S16)&amp;" de 11"</f>
-        <v>Indicadores internos com dado: 13 de 16  |  Neutros: 1  |  Fatores externos pontuados: 11 de 11</v>
+        <v>Indicadores internos com dado: 14 de 16  |  Neutros: 1  |  Fatores externos pontuados: 11 de 11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7746,7 +7782,7 @@
       <c r="D6" s="11"/>
       <c r="F6" s="12" t="str">
         <f aca="false">"FRAQUEZAS (W) — "&amp;COUNTIF($L$6:$L$21,"Fraqueza")&amp;" item(ns)"</f>
-        <v>FRAQUEZAS (W) — 9 item(ns)</v>
+        <v>FRAQUEZAS (W) — 10 item(ns)</v>
       </c>
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
@@ -8558,17 +8594,17 @@
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(10,$N$6:$N$21,0)),"")</f>
         <v/>
       </c>
-      <c r="F17" s="19" t="str">
+      <c r="F17" s="19" t="n">
         <f aca="false">IF(G17="","",10)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="G17" s="20" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(10,$O$6:$O$21,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="21" t="str">
+        <v>[Estrutura Econômica e Fiscal] EST-05 – Receitas próprias / receita corrente (%)</v>
+      </c>
+      <c r="H17" s="21" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(10,$O$6:$O$21,0)),"")</f>
-        <v/>
+        <v>5.76</v>
       </c>
       <c r="K17" s="1" t="str">
         <f aca="false">Aux!B17</f>
@@ -8722,19 +8758,19 @@
       </c>
       <c r="L21" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!U21</f>
-        <v/>
-      </c>
-      <c r="M21" s="1" t="str">
+        <v>Fraqueza</v>
+      </c>
+      <c r="M21" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!T21="","",'Indicadores (F-W)'!T21)</f>
-        <v/>
+        <v>5.76</v>
       </c>
       <c r="N21" s="1" t="str">
         <f aca="false">IF(L21="Força",COUNTIF(L$6:L21,"Força"),"")</f>
         <v/>
       </c>
-      <c r="O21" s="1" t="str">
+      <c r="O21" s="1" t="n">
         <f aca="false">IF(L21="Fraqueza",COUNTIF(L$6:L21,"Fraqueza"),"")</f>
-        <v/>
+        <v>10</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9109,7 +9145,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -9155,18 +9191,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="92" t="str">
         <f aca="false">"Indicadores internos com dado: "&amp;(COUNTA(L6:L21)-COUNTBLANK(L6:L21))&amp;" de 16  |  Neutros: "&amp;COUNTIF(L6:L21,"Neutro")&amp;"  |  Fatores externos pontuados: "&amp;COUNT(S6:S16)&amp;" de 11"</f>
-        <v>Indicadores internos com dado: 13 de 16  |  Neutros: 1  |  Fatores externos pontuados: 11 de 11</v>
+        <v>Indicadores internos com dado: 14 de 16  |  Neutros: 1  |  Fatores externos pontuados: 11 de 11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9190,7 +9226,7 @@
       <c r="D6" s="11"/>
       <c r="F6" s="12" t="str">
         <f aca="false">"FRAQUEZAS (W) — "&amp;COUNTIF($L$6:$L$21,"Fraqueza")&amp;" item(ns)"</f>
-        <v>FRAQUEZAS (W) — 5 item(ns)</v>
+        <v>FRAQUEZAS (W) — 6 item(ns)</v>
       </c>
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
@@ -9702,17 +9738,17 @@
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(6,$N$6:$N$21,0)),"")</f>
         <v>5.88</v>
       </c>
-      <c r="F13" s="19" t="str">
+      <c r="F13" s="19" t="n">
         <f aca="false">IF(G13="","",6)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="G13" s="20" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(6,$O$6:$O$21,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H13" s="21" t="str">
+        <v>[Estrutura Econômica e Fiscal] EST-05 – Receitas próprias / receita corrente (%)</v>
+      </c>
+      <c r="H13" s="21" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(6,$O$6:$O$21,0)),"")</f>
-        <v/>
+        <v>11.87</v>
       </c>
       <c r="K13" s="1" t="str">
         <f aca="false">Aux!B13</f>
@@ -10166,19 +10202,19 @@
       </c>
       <c r="L21" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!W21</f>
-        <v/>
-      </c>
-      <c r="M21" s="1" t="str">
+        <v>Fraqueza</v>
+      </c>
+      <c r="M21" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!V21="","",'Indicadores (F-W)'!V21)</f>
-        <v/>
+        <v>11.87</v>
       </c>
       <c r="N21" s="1" t="str">
         <f aca="false">IF(L21="Força",COUNTIF(L$6:L21,"Força"),"")</f>
         <v/>
       </c>
-      <c r="O21" s="1" t="str">
+      <c r="O21" s="1" t="n">
         <f aca="false">IF(L21="Fraqueza",COUNTIF(L$6:L21,"Fraqueza"),"")</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10553,7 +10589,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -10599,18 +10635,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="92" t="str">
         <f aca="false">"Indicadores internos com dado: "&amp;(COUNTA(L6:L21)-COUNTBLANK(L6:L21))&amp;" de 16  |  Neutros: "&amp;COUNTIF(L6:L21,"Neutro")&amp;"  |  Fatores externos pontuados: "&amp;COUNT(S6:S16)&amp;" de 11"</f>
-        <v>Indicadores internos com dado: 13 de 16  |  Neutros: 4  |  Fatores externos pontuados: 11 de 11</v>
+        <v>Indicadores internos com dado: 14 de 16  |  Neutros: 4  |  Fatores externos pontuados: 11 de 11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10634,7 +10670,7 @@
       <c r="D6" s="11"/>
       <c r="F6" s="12" t="str">
         <f aca="false">"FRAQUEZAS (W) — "&amp;COUNTIF($L$6:$L$21,"Fraqueza")&amp;" item(ns)"</f>
-        <v>FRAQUEZAS (W) — 6 item(ns)</v>
+        <v>FRAQUEZAS (W) — 7 item(ns)</v>
       </c>
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
@@ -11221,17 +11257,17 @@
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(7,$N$6:$N$21,0)),"")</f>
         <v/>
       </c>
-      <c r="F14" s="19" t="str">
+      <c r="F14" s="19" t="n">
         <f aca="false">IF(G14="","",7)</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G14" s="20" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(7,$O$6:$O$21,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H14" s="21" t="str">
+        <v>[Estrutura Econômica e Fiscal] EST-05 – Receitas próprias / receita corrente (%)</v>
+      </c>
+      <c r="H14" s="21" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(7,$O$6:$O$21,0)),"")</f>
-        <v/>
+        <v>11.71</v>
       </c>
       <c r="K14" s="1" t="str">
         <f aca="false">Aux!B14</f>
@@ -11610,19 +11646,19 @@
       </c>
       <c r="L21" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!Y21</f>
-        <v/>
-      </c>
-      <c r="M21" s="1" t="str">
+        <v>Fraqueza</v>
+      </c>
+      <c r="M21" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!X21="","",'Indicadores (F-W)'!X21)</f>
-        <v/>
+        <v>11.71</v>
       </c>
       <c r="N21" s="1" t="str">
         <f aca="false">IF(L21="Força",COUNTIF(L$6:L21,"Força"),"")</f>
         <v/>
       </c>
-      <c r="O21" s="1" t="str">
+      <c r="O21" s="1" t="n">
         <f aca="false">IF(L21="Fraqueza",COUNTIF(L$6:L21,"Fraqueza"),"")</f>
-        <v/>
+        <v>7</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11997,7 +12033,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -12043,18 +12079,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="92" t="str">
         <f aca="false">"Indicadores internos com dado: "&amp;(COUNTA(L6:L21)-COUNTBLANK(L6:L21))&amp;" de 16  |  Neutros: "&amp;COUNTIF(L6:L21,"Neutro")&amp;"  |  Fatores externos pontuados: "&amp;COUNT(S6:S16)&amp;" de 11"</f>
-        <v>Indicadores internos com dado: 13 de 16  |  Neutros: 3  |  Fatores externos pontuados: 11 de 11</v>
+        <v>Indicadores internos com dado: 14 de 16  |  Neutros: 3  |  Fatores externos pontuados: 11 de 11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12078,7 +12114,7 @@
       <c r="D6" s="11"/>
       <c r="F6" s="12" t="str">
         <f aca="false">"FRAQUEZAS (W) — "&amp;COUNTIF($L$6:$L$21,"Fraqueza")&amp;" item(ns)"</f>
-        <v>FRAQUEZAS (W) — 8 item(ns)</v>
+        <v>FRAQUEZAS (W) — 9 item(ns)</v>
       </c>
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
@@ -12815,17 +12851,17 @@
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(9,$N$6:$N$21,0)),"")</f>
         <v/>
       </c>
-      <c r="F16" s="19" t="str">
+      <c r="F16" s="19" t="n">
         <f aca="false">IF(G16="","",9)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="G16" s="20" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(9,$O$6:$O$21,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="21" t="str">
+        <v>[Estrutura Econômica e Fiscal] EST-05 – Receitas próprias / receita corrente (%)</v>
+      </c>
+      <c r="H16" s="21" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(9,$O$6:$O$21,0)),"")</f>
-        <v/>
+        <v>7.14</v>
       </c>
       <c r="K16" s="1" t="str">
         <f aca="false">Aux!B16</f>
@@ -13054,19 +13090,19 @@
       </c>
       <c r="L21" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!AA21</f>
-        <v/>
-      </c>
-      <c r="M21" s="1" t="str">
+        <v>Fraqueza</v>
+      </c>
+      <c r="M21" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!Z21="","",'Indicadores (F-W)'!Z21)</f>
-        <v/>
+        <v>7.14</v>
       </c>
       <c r="N21" s="1" t="str">
         <f aca="false">IF(L21="Força",COUNTIF(L$6:L21,"Força"),"")</f>
         <v/>
       </c>
-      <c r="O21" s="1" t="str">
+      <c r="O21" s="1" t="n">
         <f aca="false">IF(L21="Fraqueza",COUNTIF(L$6:L21,"Fraqueza"),"")</f>
-        <v/>
+        <v>9</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13441,7 +13477,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -13487,18 +13523,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="92" t="str">
         <f aca="false">"Indicadores internos com dado: "&amp;(COUNTA(L6:L21)-COUNTBLANK(L6:L21))&amp;" de 16  |  Neutros: "&amp;COUNTIF(L6:L21,"Neutro")&amp;"  |  Fatores externos pontuados: "&amp;COUNT(S6:S16)&amp;" de 11"</f>
-        <v>Indicadores internos com dado: 13 de 16  |  Neutros: 4  |  Fatores externos pontuados: 11 de 11</v>
+        <v>Indicadores internos com dado: 14 de 16  |  Neutros: 4  |  Fatores externos pontuados: 11 de 11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13522,7 +13558,7 @@
       <c r="D6" s="11"/>
       <c r="F6" s="12" t="str">
         <f aca="false">"FRAQUEZAS (W) — "&amp;COUNTIF($L$6:$L$21,"Fraqueza")&amp;" item(ns)"</f>
-        <v>FRAQUEZAS (W) — 7 item(ns)</v>
+        <v>FRAQUEZAS (W) — 8 item(ns)</v>
       </c>
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
@@ -14184,17 +14220,17 @@
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(8,$N$6:$N$21,0)),"")</f>
         <v/>
       </c>
-      <c r="F15" s="19" t="str">
+      <c r="F15" s="19" t="n">
         <f aca="false">IF(G15="","",8)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="G15" s="20" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(8,$O$6:$O$21,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H15" s="21" t="str">
+        <v>[Estrutura Econômica e Fiscal] EST-05 – Receitas próprias / receita corrente (%)</v>
+      </c>
+      <c r="H15" s="21" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(8,$O$6:$O$21,0)),"")</f>
-        <v/>
+        <v>14.35</v>
       </c>
       <c r="K15" s="1" t="str">
         <f aca="false">Aux!B15</f>
@@ -14498,19 +14534,19 @@
       </c>
       <c r="L21" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!AC21</f>
-        <v/>
-      </c>
-      <c r="M21" s="1" t="str">
+        <v>Fraqueza</v>
+      </c>
+      <c r="M21" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AB21="","",'Indicadores (F-W)'!AB21)</f>
-        <v/>
+        <v>14.35</v>
       </c>
       <c r="N21" s="1" t="str">
         <f aca="false">IF(L21="Força",COUNTIF(L$6:L21,"Força"),"")</f>
         <v/>
       </c>
-      <c r="O21" s="1" t="str">
+      <c r="O21" s="1" t="n">
         <f aca="false">IF(L21="Fraqueza",COUNTIF(L$6:L21,"Fraqueza"),"")</f>
-        <v/>
+        <v>8</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14885,7 +14921,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -14931,18 +14967,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="92" t="str">
         <f aca="false">"Indicadores internos com dado: "&amp;(COUNTA(L6:L21)-COUNTBLANK(L6:L21))&amp;" de 16  |  Neutros: "&amp;COUNTIF(L6:L21,"Neutro")&amp;"  |  Fatores externos pontuados: "&amp;COUNT(S6:S16)&amp;" de 11"</f>
-        <v>Indicadores internos com dado: 13 de 16  |  Neutros: 2  |  Fatores externos pontuados: 11 de 11</v>
+        <v>Indicadores internos com dado: 14 de 16  |  Neutros: 2  |  Fatores externos pontuados: 11 de 11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14966,7 +15002,7 @@
       <c r="D6" s="11"/>
       <c r="F6" s="12" t="str">
         <f aca="false">"FRAQUEZAS (W) — "&amp;COUNTIF($L$6:$L$21,"Fraqueza")&amp;" item(ns)"</f>
-        <v>FRAQUEZAS (W) — 7 item(ns)</v>
+        <v>FRAQUEZAS (W) — 8 item(ns)</v>
       </c>
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
@@ -15628,17 +15664,17 @@
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(8,$N$6:$N$21,0)),"")</f>
         <v/>
       </c>
-      <c r="F15" s="19" t="str">
+      <c r="F15" s="19" t="n">
         <f aca="false">IF(G15="","",8)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="G15" s="20" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(8,$O$6:$O$21,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H15" s="21" t="str">
+        <v>[Estrutura Econômica e Fiscal] EST-05 – Receitas próprias / receita corrente (%)</v>
+      </c>
+      <c r="H15" s="21" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(8,$O$6:$O$21,0)),"")</f>
-        <v/>
+        <v>5.15</v>
       </c>
       <c r="K15" s="1" t="str">
         <f aca="false">Aux!B15</f>
@@ -15942,19 +15978,19 @@
       </c>
       <c r="L21" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!AE21</f>
-        <v/>
-      </c>
-      <c r="M21" s="1" t="str">
+        <v>Fraqueza</v>
+      </c>
+      <c r="M21" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AD21="","",'Indicadores (F-W)'!AD21)</f>
-        <v/>
+        <v>5.15</v>
       </c>
       <c r="N21" s="1" t="str">
         <f aca="false">IF(L21="Força",COUNTIF(L$6:L21,"Força"),"")</f>
         <v/>
       </c>
-      <c r="O21" s="1" t="str">
+      <c r="O21" s="1" t="n">
         <f aca="false">IF(L21="Fraqueza",COUNTIF(L$6:L21,"Fraqueza"),"")</f>
-        <v/>
+        <v>8</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16329,7 +16365,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -16386,7 +16422,7 @@
       <c r="D3" s="8"/>
       <c r="F3" s="9" t="str">
         <f aca="false">"Indicadores: "&amp;COUNTIF(Aux!$C$6:$C$21,"Neutro")&amp;" neutros | "&amp;(COUNTA(Aux!$A$6:$A$21)-COUNTIF(Aux!$C$6:$C$21,"Força")-COUNTIF(Aux!$C$6:$C$21,"Fraqueza")-COUNTIF(Aux!$C$6:$C$21,"Neutro"))&amp;" sem dado"</f>
-        <v>Indicadores: 2 neutros | 3 sem dado</v>
+        <v>Indicadores: 3 neutros | 2 sem dado</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17196,18 +17232,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="92" t="str">
         <f aca="false">"Indicadores internos com dado: "&amp;(COUNTA(L6:L21)-COUNTBLANK(L6:L21))&amp;" de 16  |  Neutros: "&amp;COUNTIF(L6:L21,"Neutro")&amp;"  |  Fatores externos pontuados: "&amp;COUNT(S6:S16)&amp;" de 11"</f>
-        <v>Indicadores internos com dado: 13 de 16  |  Neutros: 2  |  Fatores externos pontuados: 11 de 11</v>
+        <v>Indicadores internos com dado: 14 de 16  |  Neutros: 2  |  Fatores externos pontuados: 11 de 11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17231,7 +17267,7 @@
       <c r="D6" s="11"/>
       <c r="F6" s="12" t="str">
         <f aca="false">"FRAQUEZAS (W) — "&amp;COUNTIF($L$6:$L$21,"Fraqueza")&amp;" item(ns)"</f>
-        <v>FRAQUEZAS (W) — 10 item(ns)</v>
+        <v>FRAQUEZAS (W) — 11 item(ns)</v>
       </c>
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
@@ -18090,17 +18126,17 @@
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(11,$N$6:$N$21,0)),"")</f>
         <v/>
       </c>
-      <c r="F18" s="19" t="str">
+      <c r="F18" s="19" t="n">
         <f aca="false">IF(G18="","",11)</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="G18" s="20" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(11,$O$6:$O$21,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H18" s="21" t="str">
+        <v>[Estrutura Econômica e Fiscal] EST-05 – Receitas próprias / receita corrente (%)</v>
+      </c>
+      <c r="H18" s="21" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(11,$O$6:$O$21,0)),"")</f>
-        <v/>
+        <v>9.51</v>
       </c>
       <c r="K18" s="1" t="str">
         <f aca="false">Aux!B18</f>
@@ -18207,19 +18243,19 @@
       </c>
       <c r="L21" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!AG21</f>
-        <v/>
-      </c>
-      <c r="M21" s="1" t="str">
+        <v>Fraqueza</v>
+      </c>
+      <c r="M21" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AF21="","",'Indicadores (F-W)'!AF21)</f>
-        <v/>
+        <v>9.51</v>
       </c>
       <c r="N21" s="1" t="str">
         <f aca="false">IF(L21="Força",COUNTIF(L$6:L21,"Força"),"")</f>
         <v/>
       </c>
-      <c r="O21" s="1" t="str">
+      <c r="O21" s="1" t="n">
         <f aca="false">IF(L21="Fraqueza",COUNTIF(L$6:L21,"Fraqueza"),"")</f>
-        <v/>
+        <v>11</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18594,7 +18630,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -18640,18 +18676,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="92" t="str">
         <f aca="false">"Indicadores internos com dado: "&amp;(COUNTA(L6:L21)-COUNTBLANK(L6:L21))&amp;" de 16  |  Neutros: "&amp;COUNTIF(L6:L21,"Neutro")&amp;"  |  Fatores externos pontuados: "&amp;COUNT(S6:S16)&amp;" de 11"</f>
-        <v>Indicadores internos com dado: 13 de 16  |  Neutros: 2  |  Fatores externos pontuados: 11 de 11</v>
+        <v>Indicadores internos com dado: 14 de 16  |  Neutros: 2  |  Fatores externos pontuados: 11 de 11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18675,7 +18711,7 @@
       <c r="D6" s="11"/>
       <c r="F6" s="12" t="str">
         <f aca="false">"FRAQUEZAS (W) — "&amp;COUNTIF($L$6:$L$21,"Fraqueza")&amp;" item(ns)"</f>
-        <v>FRAQUEZAS (W) — 8 item(ns)</v>
+        <v>FRAQUEZAS (W) — 9 item(ns)</v>
       </c>
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
@@ -19412,17 +19448,17 @@
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(9,$N$6:$N$21,0)),"")</f>
         <v/>
       </c>
-      <c r="F16" s="19" t="str">
+      <c r="F16" s="19" t="n">
         <f aca="false">IF(G16="","",9)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="G16" s="20" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(9,$O$6:$O$21,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="21" t="str">
+        <v>[Estrutura Econômica e Fiscal] EST-05 – Receitas próprias / receita corrente (%)</v>
+      </c>
+      <c r="H16" s="21" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(9,$O$6:$O$21,0)),"")</f>
-        <v/>
+        <v>6.54</v>
       </c>
       <c r="K16" s="1" t="str">
         <f aca="false">Aux!B16</f>
@@ -19651,19 +19687,19 @@
       </c>
       <c r="L21" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!AI21</f>
-        <v/>
-      </c>
-      <c r="M21" s="1" t="str">
+        <v>Fraqueza</v>
+      </c>
+      <c r="M21" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AH21="","",'Indicadores (F-W)'!AH21)</f>
-        <v/>
+        <v>6.54</v>
       </c>
       <c r="N21" s="1" t="str">
         <f aca="false">IF(L21="Força",COUNTIF(L$6:L21,"Força"),"")</f>
         <v/>
       </c>
-      <c r="O21" s="1" t="str">
+      <c r="O21" s="1" t="n">
         <f aca="false">IF(L21="Fraqueza",COUNTIF(L$6:L21,"Fraqueza"),"")</f>
-        <v/>
+        <v>9</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20038,7 +20074,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -20084,18 +20120,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="92" t="str">
         <f aca="false">"Indicadores internos com dado: "&amp;(COUNTA(L6:L21)-COUNTBLANK(L6:L21))&amp;" de 16  |  Neutros: "&amp;COUNTIF(L6:L21,"Neutro")&amp;"  |  Fatores externos pontuados: "&amp;COUNT(S6:S16)&amp;" de 11"</f>
-        <v>Indicadores internos com dado: 13 de 16  |  Neutros: 7  |  Fatores externos pontuados: 11 de 11</v>
+        <v>Indicadores internos com dado: 14 de 16  |  Neutros: 7  |  Fatores externos pontuados: 11 de 11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20113,7 +20149,7 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="11" t="str">
         <f aca="false">"FORÇAS (S) — "&amp;COUNTIF($L$6:$L$21,"Força")&amp;" item(ns)"</f>
-        <v>FORÇAS (S) — 3 item(ns)</v>
+        <v>FORÇAS (S) — 4 item(ns)</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
@@ -20469,17 +20505,17 @@
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15"/>
-      <c r="B11" s="16" t="str">
+      <c r="B11" s="16" t="n">
         <f aca="false">IF(C11="","",4)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="C11" s="17" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(4,$N$6:$N$21,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D11" s="18" t="str">
+        <v>[Estrutura Econômica e Fiscal] EST-05 – Receitas próprias / receita corrente (%)</v>
+      </c>
+      <c r="D11" s="18" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(4,$N$6:$N$21,0)),"")</f>
-        <v/>
+        <v>21.61</v>
       </c>
       <c r="F11" s="19" t="str">
         <f aca="false">IF(G11="","",4)</f>
@@ -21095,15 +21131,15 @@
       </c>
       <c r="L21" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!AK21</f>
-        <v/>
-      </c>
-      <c r="M21" s="1" t="str">
+        <v>Força</v>
+      </c>
+      <c r="M21" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AJ21="","",'Indicadores (F-W)'!AJ21)</f>
-        <v/>
-      </c>
-      <c r="N21" s="1" t="str">
+        <v>21.61</v>
+      </c>
+      <c r="N21" s="1" t="n">
         <f aca="false">IF(L21="Força",COUNTIF(L$6:L21,"Força"),"")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="O21" s="1" t="str">
         <f aca="false">IF(L21="Fraqueza",COUNTIF(L$6:L21,"Fraqueza"),"")</f>
@@ -21482,7 +21518,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -21528,18 +21564,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="92" t="str">
         <f aca="false">"Indicadores internos com dado: "&amp;(COUNTA(L6:L21)-COUNTBLANK(L6:L21))&amp;" de 16  |  Neutros: "&amp;COUNTIF(L6:L21,"Neutro")&amp;"  |  Fatores externos pontuados: "&amp;COUNT(S6:S16)&amp;" de 11"</f>
-        <v>Indicadores internos com dado: 13 de 16  |  Neutros: 1  |  Fatores externos pontuados: 11 de 11</v>
+        <v>Indicadores internos com dado: 14 de 16  |  Neutros: 1  |  Fatores externos pontuados: 11 de 11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21563,7 +21599,7 @@
       <c r="D6" s="11"/>
       <c r="F6" s="12" t="str">
         <f aca="false">"FRAQUEZAS (W) — "&amp;COUNTIF($L$6:$L$21,"Fraqueza")&amp;" item(ns)"</f>
-        <v>FRAQUEZAS (W) — 10 item(ns)</v>
+        <v>FRAQUEZAS (W) — 11 item(ns)</v>
       </c>
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
@@ -22422,17 +22458,17 @@
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(11,$N$6:$N$21,0)),"")</f>
         <v/>
       </c>
-      <c r="F18" s="19" t="str">
+      <c r="F18" s="19" t="n">
         <f aca="false">IF(G18="","",11)</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="G18" s="20" t="str">
         <f aca="false">IFERROR(INDEX($K$6:$K$21,MATCH(11,$O$6:$O$21,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H18" s="21" t="str">
+        <v>[Estrutura Econômica e Fiscal] EST-05 – Receitas próprias / receita corrente (%)</v>
+      </c>
+      <c r="H18" s="21" t="n">
         <f aca="false">IFERROR(INDEX($M$6:$M$21,MATCH(11,$O$6:$O$21,0)),"")</f>
-        <v/>
+        <v>9.96</v>
       </c>
       <c r="K18" s="1" t="str">
         <f aca="false">Aux!B18</f>
@@ -22539,19 +22575,19 @@
       </c>
       <c r="L21" s="1" t="str">
         <f aca="false">'Indicadores (F-W)'!AM21</f>
-        <v/>
-      </c>
-      <c r="M21" s="1" t="str">
+        <v>Fraqueza</v>
+      </c>
+      <c r="M21" s="88" t="n">
         <f aca="false">IF('Indicadores (F-W)'!AL21="","",'Indicadores (F-W)'!AL21)</f>
-        <v/>
+        <v>9.96</v>
       </c>
       <c r="N21" s="1" t="str">
         <f aca="false">IF(L21="Força",COUNTIF(L$6:L21,"Força"),"")</f>
         <v/>
       </c>
-      <c r="O21" s="1" t="str">
+      <c r="O21" s="1" t="n">
         <f aca="false">IF(L21="Fraqueza",COUNTIF(L$6:L21,"Fraqueza"),"")</f>
-        <v/>
+        <v>11</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22926,7 +22962,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -23012,7 +23048,7 @@
       </c>
       <c r="C4" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!O$6:O$21,"Fraqueza")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!O$6:O$21,"Neutro")</f>
@@ -23020,11 +23056,11 @@
       </c>
       <c r="E4" s="36" t="n">
         <f aca="false">COUNTBLANK('Indicadores (F-W)'!N$6:N$21)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="36" t="n">
         <f aca="false">B4-C4</f>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="G4" s="36" t="n">
         <f aca="false">COUNTIFS('Fatores Externos (O-A)'!$B$6:$B$16,"Oportunidade",'Fatores Externos (O-A)'!F$6:F$16,"&gt;="&amp;Parâmetros!$B$5)</f>
@@ -23053,11 +23089,11 @@
       </c>
       <c r="D5" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!Q$6:Q$21,"Neutro")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" s="36" t="n">
         <f aca="false">COUNTBLANK('Indicadores (F-W)'!P$6:P$21)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="36" t="n">
         <f aca="false">B5-C5</f>
@@ -23086,7 +23122,7 @@
       </c>
       <c r="C6" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!S$6:S$21,"Fraqueza")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!S$6:S$21,"Neutro")</f>
@@ -23094,11 +23130,11 @@
       </c>
       <c r="E6" s="36" t="n">
         <f aca="false">COUNTBLANK('Indicadores (F-W)'!R$6:R$21)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="36" t="n">
         <f aca="false">B6-C6</f>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="G6" s="36" t="n">
         <f aca="false">COUNTIFS('Fatores Externos (O-A)'!$B$6:$B$16,"Oportunidade",'Fatores Externos (O-A)'!H$6:H$16,"&gt;="&amp;Parâmetros!$B$5)</f>
@@ -23123,7 +23159,7 @@
       </c>
       <c r="C7" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!U$6:U$21,"Fraqueza")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!U$6:U$21,"Neutro")</f>
@@ -23131,11 +23167,11 @@
       </c>
       <c r="E7" s="36" t="n">
         <f aca="false">COUNTBLANK('Indicadores (F-W)'!T$6:T$21)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">B7-C7</f>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="G7" s="36" t="n">
         <f aca="false">COUNTIFS('Fatores Externos (O-A)'!$B$6:$B$16,"Oportunidade",'Fatores Externos (O-A)'!I$6:I$16,"&gt;="&amp;Parâmetros!$B$5)</f>
@@ -23160,7 +23196,7 @@
       </c>
       <c r="C8" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!W$6:W$21,"Fraqueza")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!W$6:W$21,"Neutro")</f>
@@ -23168,11 +23204,11 @@
       </c>
       <c r="E8" s="36" t="n">
         <f aca="false">COUNTBLANK('Indicadores (F-W)'!V$6:V$21)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" s="36" t="n">
         <f aca="false">B8-C8</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="36" t="n">
         <f aca="false">COUNTIFS('Fatores Externos (O-A)'!$B$6:$B$16,"Oportunidade",'Fatores Externos (O-A)'!J$6:J$16,"&gt;="&amp;Parâmetros!$B$5)</f>
@@ -23197,7 +23233,7 @@
       </c>
       <c r="C9" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!Y$6:Y$21,"Fraqueza")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!Y$6:Y$21,"Neutro")</f>
@@ -23205,11 +23241,11 @@
       </c>
       <c r="E9" s="36" t="n">
         <f aca="false">COUNTBLANK('Indicadores (F-W)'!X$6:X$21)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9" s="36" t="n">
         <f aca="false">B9-C9</f>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G9" s="36" t="n">
         <f aca="false">COUNTIFS('Fatores Externos (O-A)'!$B$6:$B$16,"Oportunidade",'Fatores Externos (O-A)'!K$6:K$16,"&gt;="&amp;Parâmetros!$B$5)</f>
@@ -23234,7 +23270,7 @@
       </c>
       <c r="C10" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AA$6:AA$21,"Fraqueza")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AA$6:AA$21,"Neutro")</f>
@@ -23242,11 +23278,11 @@
       </c>
       <c r="E10" s="36" t="n">
         <f aca="false">COUNTBLANK('Indicadores (F-W)'!Z$6:Z$21)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" s="36" t="n">
         <f aca="false">B10-C10</f>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="G10" s="36" t="n">
         <f aca="false">COUNTIFS('Fatores Externos (O-A)'!$B$6:$B$16,"Oportunidade",'Fatores Externos (O-A)'!L$6:L$16,"&gt;="&amp;Parâmetros!$B$5)</f>
@@ -23271,7 +23307,7 @@
       </c>
       <c r="C11" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AC$6:AC$21,"Fraqueza")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AC$6:AC$21,"Neutro")</f>
@@ -23279,11 +23315,11 @@
       </c>
       <c r="E11" s="36" t="n">
         <f aca="false">COUNTBLANK('Indicadores (F-W)'!AB$6:AB$21)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11" s="36" t="n">
         <f aca="false">B11-C11</f>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="G11" s="36" t="n">
         <f aca="false">COUNTIFS('Fatores Externos (O-A)'!$B$6:$B$16,"Oportunidade",'Fatores Externos (O-A)'!M$6:M$16,"&gt;="&amp;Parâmetros!$B$5)</f>
@@ -23308,7 +23344,7 @@
       </c>
       <c r="C12" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AE$6:AE$21,"Fraqueza")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AE$6:AE$21,"Neutro")</f>
@@ -23316,11 +23352,11 @@
       </c>
       <c r="E12" s="36" t="n">
         <f aca="false">COUNTBLANK('Indicadores (F-W)'!AD$6:AD$21)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" s="36" t="n">
         <f aca="false">B12-C12</f>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G12" s="36" t="n">
         <f aca="false">COUNTIFS('Fatores Externos (O-A)'!$B$6:$B$16,"Oportunidade",'Fatores Externos (O-A)'!N$6:N$16,"&gt;="&amp;Parâmetros!$B$5)</f>
@@ -23345,7 +23381,7 @@
       </c>
       <c r="C13" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AG$6:AG$21,"Fraqueza")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AG$6:AG$21,"Neutro")</f>
@@ -23353,11 +23389,11 @@
       </c>
       <c r="E13" s="36" t="n">
         <f aca="false">COUNTBLANK('Indicadores (F-W)'!AF$6:AF$21)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" s="36" t="n">
         <f aca="false">B13-C13</f>
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G13" s="36" t="n">
         <f aca="false">COUNTIFS('Fatores Externos (O-A)'!$B$6:$B$16,"Oportunidade",'Fatores Externos (O-A)'!O$6:O$16,"&gt;="&amp;Parâmetros!$B$5)</f>
@@ -23382,7 +23418,7 @@
       </c>
       <c r="C14" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AI$6:AI$21,"Fraqueza")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AI$6:AI$21,"Neutro")</f>
@@ -23390,11 +23426,11 @@
       </c>
       <c r="E14" s="36" t="n">
         <f aca="false">COUNTBLANK('Indicadores (F-W)'!AH$6:AH$21)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14" s="36" t="n">
         <f aca="false">B14-C14</f>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="G14" s="36" t="n">
         <f aca="false">COUNTIFS('Fatores Externos (O-A)'!$B$6:$B$16,"Oportunidade",'Fatores Externos (O-A)'!P$6:P$16,"&gt;="&amp;Parâmetros!$B$5)</f>
@@ -23415,7 +23451,7 @@
       </c>
       <c r="B15" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AK$6:AK$21,"Força")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AK$6:AK$21,"Fraqueza")</f>
@@ -23427,11 +23463,11 @@
       </c>
       <c r="E15" s="36" t="n">
         <f aca="false">COUNTBLANK('Indicadores (F-W)'!AJ$6:AJ$21)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" s="36" t="n">
         <f aca="false">B15-C15</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="36" t="n">
         <f aca="false">COUNTIFS('Fatores Externos (O-A)'!$B$6:$B$16,"Oportunidade",'Fatores Externos (O-A)'!Q$6:Q$16,"&gt;="&amp;Parâmetros!$B$5)</f>
@@ -23456,7 +23492,7 @@
       </c>
       <c r="C16" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AM$6:AM$21,"Fraqueza")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!AM$6:AM$21,"Neutro")</f>
@@ -23464,11 +23500,11 @@
       </c>
       <c r="E16" s="36" t="n">
         <f aca="false">COUNTBLANK('Indicadores (F-W)'!AL$6:AL$21)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16" s="36" t="n">
         <f aca="false">B16-C16</f>
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G16" s="36" t="n">
         <f aca="false">COUNTIFS('Fatores Externos (O-A)'!$B$6:$B$16,"Oportunidade",'Fatores Externos (O-A)'!R$6:R$16,"&gt;="&amp;Parâmetros!$B$5)</f>
@@ -23972,23 +24008,23 @@
       </c>
       <c r="C36" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!$N21:$AM21,"Força")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!$N21:$AM21,"Neutro")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" s="36" t="n">
         <f aca="false">COUNTIF('Indicadores (F-W)'!$N21:$AM21,"Fraqueza")</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F36" s="36" t="n">
         <f aca="false">13-C36-D36-E36</f>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G36" s="36" t="str">
         <f aca="false">IF(C36+D36+E36=0,"sem dados",IF(C36&gt;=13/2,"Força regional",IF(E36&gt;=13/2,"Fraqueza regional","Heterogêneo")))</f>
-        <v>sem dados</v>
+        <v>Fraqueza regional</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27123,19 +27159,19 @@
       </c>
       <c r="C5" s="53" t="n">
         <f aca="false">Painel!C4</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="53" t="n">
         <f aca="false">16-Painel!E4</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" s="54" t="n">
         <f aca="false">D5/16</f>
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="F5" s="55" t="n">
         <f aca="false">IF(D5=0,"",(B5-C5)/D5)</f>
-        <v>-0.461538461538462</v>
+        <v>-0.5</v>
       </c>
       <c r="G5" s="53" t="n">
         <f aca="false">Painel!G4</f>
@@ -27159,7 +27195,7 @@
       </c>
       <c r="L5" s="56" t="n">
         <f aca="false">IF(F5="","",IF(K5="",F5,(F5+K5)/2))</f>
-        <v>-0.276223776223776</v>
+        <v>-0.295454545454545</v>
       </c>
       <c r="M5" s="46" t="n">
         <f aca="false">IF(L5="","",RANK(L5,$L$5:$L$17,0))</f>
@@ -27171,7 +27207,7 @@
       </c>
       <c r="T5" s="1" t="n">
         <f aca="false">IF(L5="",-9,L5)-ROW()*0.000000001</f>
-        <v>-0.276223781223776</v>
+        <v>-0.295454550454546</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27188,15 +27224,15 @@
       </c>
       <c r="D6" s="53" t="n">
         <f aca="false">16-Painel!E5</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" s="54" t="n">
         <f aca="false">D6/16</f>
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="F6" s="55" t="n">
         <f aca="false">IF(D6=0,"",(B6-C6)/D6)</f>
-        <v>-0.384615384615385</v>
+        <v>-0.357142857142857</v>
       </c>
       <c r="G6" s="53" t="n">
         <f aca="false">Painel!G5</f>
@@ -27220,11 +27256,11 @@
       </c>
       <c r="L6" s="56" t="n">
         <f aca="false">IF(F6="","",IF(K6="",F6,(F6+K6)/2))</f>
-        <v>-0.101398601398601</v>
+        <v>-0.0876623376623377</v>
       </c>
       <c r="M6" s="46" t="n">
         <f aca="false">IF(L6="","",RANK(L6,$L$5:$L$17,0))</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N6" s="49" t="str">
         <f aca="false">IF(AND(E6&gt;=0.75,J6&gt;=0.75),"Consolidado","PROVISÓRIO")</f>
@@ -27232,7 +27268,7 @@
       </c>
       <c r="T6" s="1" t="n">
         <f aca="false">IF(L6="",-9,L6)-ROW()*0.000000001</f>
-        <v>-0.101398607398601</v>
+        <v>-0.0876623436623377</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27245,19 +27281,19 @@
       </c>
       <c r="C7" s="53" t="n">
         <f aca="false">Painel!C6</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="53" t="n">
         <f aca="false">16-Painel!E6</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" s="54" t="n">
         <f aca="false">D7/16</f>
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="F7" s="55" t="n">
         <f aca="false">IF(D7=0,"",(B7-C7)/D7)</f>
-        <v>-0.461538461538462</v>
+        <v>-0.5</v>
       </c>
       <c r="G7" s="53" t="n">
         <f aca="false">Painel!G6</f>
@@ -27281,7 +27317,7 @@
       </c>
       <c r="L7" s="56" t="n">
         <f aca="false">IF(F7="","",IF(K7="",F7,(F7+K7)/2))</f>
-        <v>-0.276223776223776</v>
+        <v>-0.295454545454545</v>
       </c>
       <c r="M7" s="46" t="n">
         <f aca="false">IF(L7="","",RANK(L7,$L$5:$L$17,0))</f>
@@ -27293,7 +27329,7 @@
       </c>
       <c r="T7" s="1" t="n">
         <f aca="false">IF(L7="",-9,L7)-ROW()*0.000000001</f>
-        <v>-0.276223783223776</v>
+        <v>-0.295454552454546</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27306,19 +27342,19 @@
       </c>
       <c r="C8" s="53" t="n">
         <f aca="false">Painel!C7</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="53" t="n">
         <f aca="false">16-Painel!E7</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" s="54" t="n">
         <f aca="false">D8/16</f>
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="F8" s="55" t="n">
         <f aca="false">IF(D8=0,"",(B8-C8)/D8)</f>
-        <v>-0.461538461538462</v>
+        <v>-0.5</v>
       </c>
       <c r="G8" s="53" t="n">
         <f aca="false">Painel!G7</f>
@@ -27342,7 +27378,7 @@
       </c>
       <c r="L8" s="56" t="n">
         <f aca="false">IF(F8="","",IF(K8="",F8,(F8+K8)/2))</f>
-        <v>-0.276223776223776</v>
+        <v>-0.295454545454545</v>
       </c>
       <c r="M8" s="46" t="n">
         <f aca="false">IF(L8="","",RANK(L8,$L$5:$L$17,0))</f>
@@ -27354,7 +27390,7 @@
       </c>
       <c r="T8" s="1" t="n">
         <f aca="false">IF(L8="",-9,L8)-ROW()*0.000000001</f>
-        <v>-0.276223784223776</v>
+        <v>-0.295454553454545</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27367,19 +27403,19 @@
       </c>
       <c r="C9" s="53" t="n">
         <f aca="false">Painel!C8</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" s="53" t="n">
         <f aca="false">16-Painel!E8</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9" s="54" t="n">
         <f aca="false">D9/16</f>
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="F9" s="55" t="n">
         <f aca="false">IF(D9=0,"",(B9-C9)/D9)</f>
-        <v>0.153846153846154</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="G9" s="53" t="n">
         <f aca="false">Painel!G8</f>
@@ -27403,7 +27439,7 @@
       </c>
       <c r="L9" s="56" t="n">
         <f aca="false">IF(F9="","",IF(K9="",F9,(F9+K9)/2))</f>
-        <v>0.0769230769230769</v>
+        <v>0.0357142857142857</v>
       </c>
       <c r="M9" s="46" t="n">
         <f aca="false">IF(L9="","",RANK(L9,$L$5:$L$17,0))</f>
@@ -27415,7 +27451,7 @@
       </c>
       <c r="T9" s="1" t="n">
         <f aca="false">IF(L9="",-9,L9)-ROW()*0.000000001</f>
-        <v>0.0769230679230769</v>
+        <v>0.0357142767142857</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27428,19 +27464,19 @@
       </c>
       <c r="C10" s="53" t="n">
         <f aca="false">Painel!C9</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="53" t="n">
         <f aca="false">16-Painel!E9</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E10" s="54" t="n">
         <f aca="false">D10/16</f>
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="F10" s="55" t="n">
         <f aca="false">IF(D10=0,"",(B10-C10)/D10)</f>
-        <v>-0.230769230769231</v>
+        <v>-0.285714285714286</v>
       </c>
       <c r="G10" s="53" t="n">
         <f aca="false">Painel!G9</f>
@@ -27464,11 +27500,11 @@
       </c>
       <c r="L10" s="56" t="n">
         <f aca="false">IF(F10="","",IF(K10="",F10,(F10+K10)/2))</f>
-        <v>-0.0699300699300699</v>
+        <v>-0.0974025974025974</v>
       </c>
       <c r="M10" s="46" t="n">
         <f aca="false">IF(L10="","",RANK(L10,$L$5:$L$17,0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N10" s="49" t="str">
         <f aca="false">IF(AND(E10&gt;=0.75,J10&gt;=0.75),"Consolidado","PROVISÓRIO")</f>
@@ -27476,7 +27512,7 @@
       </c>
       <c r="T10" s="1" t="n">
         <f aca="false">IF(L10="",-9,L10)-ROW()*0.000000001</f>
-        <v>-0.0699300799300699</v>
+        <v>-0.0974026074025974</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27489,19 +27525,19 @@
       </c>
       <c r="C11" s="53" t="n">
         <f aca="false">Painel!C10</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="53" t="n">
         <f aca="false">16-Painel!E10</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" s="54" t="n">
         <f aca="false">D11/16</f>
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="F11" s="55" t="n">
         <f aca="false">IF(D11=0,"",(B11-C11)/D11)</f>
-        <v>-0.461538461538462</v>
+        <v>-0.5</v>
       </c>
       <c r="G11" s="53" t="n">
         <f aca="false">Painel!G10</f>
@@ -27525,7 +27561,7 @@
       </c>
       <c r="L11" s="56" t="n">
         <f aca="false">IF(F11="","",IF(K11="",F11,(F11+K11)/2))</f>
-        <v>-0.276223776223776</v>
+        <v>-0.295454545454545</v>
       </c>
       <c r="M11" s="46" t="n">
         <f aca="false">IF(L11="","",RANK(L11,$L$5:$L$17,0))</f>
@@ -27537,7 +27573,7 @@
       </c>
       <c r="T11" s="1" t="n">
         <f aca="false">IF(L11="",-9,L11)-ROW()*0.000000001</f>
-        <v>-0.276223787223776</v>
+        <v>-0.295454556454546</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27550,19 +27586,19 @@
       </c>
       <c r="C12" s="53" t="n">
         <f aca="false">Painel!C11</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" s="53" t="n">
         <f aca="false">16-Painel!E11</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E12" s="54" t="n">
         <f aca="false">D12/16</f>
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="F12" s="55" t="n">
         <f aca="false">IF(D12=0,"",(B12-C12)/D12)</f>
-        <v>-0.384615384615385</v>
+        <v>-0.428571428571429</v>
       </c>
       <c r="G12" s="53" t="n">
         <f aca="false">Painel!G11</f>
@@ -27586,7 +27622,7 @@
       </c>
       <c r="L12" s="56" t="n">
         <f aca="false">IF(F12="","",IF(K12="",F12,(F12+K12)/2))</f>
-        <v>-0.055944055944056</v>
+        <v>-0.0779220779220779</v>
       </c>
       <c r="M12" s="46" t="n">
         <f aca="false">IF(L12="","",RANK(L12,$L$5:$L$17,0))</f>
@@ -27598,7 +27634,7 @@
       </c>
       <c r="T12" s="1" t="n">
         <f aca="false">IF(L12="",-9,L12)-ROW()*0.000000001</f>
-        <v>-0.055944067944056</v>
+        <v>-0.0779220899220779</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27611,19 +27647,19 @@
       </c>
       <c r="C13" s="53" t="n">
         <f aca="false">Painel!C12</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" s="53" t="n">
         <f aca="false">16-Painel!E12</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E13" s="54" t="n">
         <f aca="false">D13/16</f>
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="F13" s="55" t="n">
         <f aca="false">IF(D13=0,"",(B13-C13)/D13)</f>
-        <v>-0.230769230769231</v>
+        <v>-0.285714285714286</v>
       </c>
       <c r="G13" s="53" t="n">
         <f aca="false">Painel!G12</f>
@@ -27647,11 +27683,11 @@
       </c>
       <c r="L13" s="56" t="n">
         <f aca="false">IF(F13="","",IF(K13="",F13,(F13+K13)/2))</f>
-        <v>-0.0699300699300699</v>
+        <v>-0.0974025974025974</v>
       </c>
       <c r="M13" s="46" t="n">
         <f aca="false">IF(L13="","",RANK(L13,$L$5:$L$17,0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N13" s="49" t="str">
         <f aca="false">IF(AND(E13&gt;=0.75,J13&gt;=0.75),"Consolidado","PROVISÓRIO")</f>
@@ -27659,7 +27695,7 @@
       </c>
       <c r="T13" s="1" t="n">
         <f aca="false">IF(L13="",-9,L13)-ROW()*0.000000001</f>
-        <v>-0.0699300829300699</v>
+        <v>-0.0974026104025974</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27672,19 +27708,19 @@
       </c>
       <c r="C14" s="53" t="n">
         <f aca="false">Painel!C13</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" s="53" t="n">
         <f aca="false">16-Painel!E13</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E14" s="54" t="n">
         <f aca="false">D14/16</f>
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="F14" s="55" t="n">
         <f aca="false">IF(D14=0,"",(B14-C14)/D14)</f>
-        <v>-0.692307692307692</v>
+        <v>-0.714285714285714</v>
       </c>
       <c r="G14" s="53" t="n">
         <f aca="false">Painel!G13</f>
@@ -27708,7 +27744,7 @@
       </c>
       <c r="L14" s="56" t="n">
         <f aca="false">IF(F14="","",IF(K14="",F14,(F14+K14)/2))</f>
-        <v>-0.346153846153846</v>
+        <v>-0.357142857142857</v>
       </c>
       <c r="M14" s="46" t="n">
         <f aca="false">IF(L14="","",RANK(L14,$L$5:$L$17,0))</f>
@@ -27720,7 +27756,7 @@
       </c>
       <c r="T14" s="1" t="n">
         <f aca="false">IF(L14="",-9,L14)-ROW()*0.000000001</f>
-        <v>-0.346153860153846</v>
+        <v>-0.357142871142857</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27733,19 +27769,19 @@
       </c>
       <c r="C15" s="53" t="n">
         <f aca="false">Painel!C14</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="53" t="n">
         <f aca="false">16-Painel!E14</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E15" s="54" t="n">
         <f aca="false">D15/16</f>
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="F15" s="55" t="n">
         <f aca="false">IF(D15=0,"",(B15-C15)/D15)</f>
-        <v>-0.384615384615385</v>
+        <v>-0.428571428571429</v>
       </c>
       <c r="G15" s="53" t="n">
         <f aca="false">Painel!G14</f>
@@ -27769,7 +27805,7 @@
       </c>
       <c r="L15" s="56" t="n">
         <f aca="false">IF(F15="","",IF(K15="",F15,(F15+K15)/2))</f>
-        <v>-0.237762237762238</v>
+        <v>-0.25974025974026</v>
       </c>
       <c r="M15" s="46" t="n">
         <f aca="false">IF(L15="","",RANK(L15,$L$5:$L$17,0))</f>
@@ -27781,7 +27817,7 @@
       </c>
       <c r="T15" s="1" t="n">
         <f aca="false">IF(L15="",-9,L15)-ROW()*0.000000001</f>
-        <v>-0.237762252762238</v>
+        <v>-0.25974027474026</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27790,7 +27826,7 @@
       </c>
       <c r="B16" s="53" t="n">
         <f aca="false">Painel!B15</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" s="53" t="n">
         <f aca="false">Painel!C15</f>
@@ -27798,15 +27834,15 @@
       </c>
       <c r="D16" s="53" t="n">
         <f aca="false">16-Painel!E15</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E16" s="54" t="n">
         <f aca="false">D16/16</f>
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="F16" s="55" t="n">
         <f aca="false">IF(D16=0,"",(B16-C16)/D16)</f>
-        <v>0</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="G16" s="53" t="n">
         <f aca="false">Painel!G15</f>
@@ -27830,7 +27866,7 @@
       </c>
       <c r="L16" s="56" t="n">
         <f aca="false">IF(F16="","",IF(K16="",F16,(F16+K16)/2))</f>
-        <v>0.0909090909090909</v>
+        <v>0.126623376623377</v>
       </c>
       <c r="M16" s="46" t="n">
         <f aca="false">IF(L16="","",RANK(L16,$L$5:$L$17,0))</f>
@@ -27842,7 +27878,7 @@
       </c>
       <c r="T16" s="1" t="n">
         <f aca="false">IF(L16="",-9,L16)-ROW()*0.000000001</f>
-        <v>0.0909090749090909</v>
+        <v>0.126623360623377</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27855,19 +27891,19 @@
       </c>
       <c r="C17" s="53" t="n">
         <f aca="false">Painel!C16</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" s="53" t="n">
         <f aca="false">16-Painel!E16</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E17" s="54" t="n">
         <f aca="false">D17/16</f>
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="F17" s="55" t="n">
         <f aca="false">IF(D17=0,"",(B17-C17)/D17)</f>
-        <v>-0.615384615384615</v>
+        <v>-0.642857142857143</v>
       </c>
       <c r="G17" s="53" t="n">
         <f aca="false">Painel!G16</f>
@@ -27891,7 +27927,7 @@
       </c>
       <c r="L17" s="56" t="n">
         <f aca="false">IF(F17="","",IF(K17="",F17,(F17+K17)/2))</f>
-        <v>-0.307692307692308</v>
+        <v>-0.321428571428571</v>
       </c>
       <c r="M17" s="46" t="n">
         <f aca="false">IF(L17="","",RANK(L17,$L$5:$L$17,0))</f>
@@ -27903,7 +27939,7 @@
       </c>
       <c r="T17" s="1" t="n">
         <f aca="false">IF(L17="",-9,L17)-ROW()*0.000000001</f>
-        <v>-0.307692324692308</v>
+        <v>-0.321428588428571</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27942,11 +27978,11 @@
       </c>
       <c r="C22" s="55" t="n">
         <f aca="false">INDEX($L$5:$L$17,MATCH(LARGE($T$5:$T$17,1),$T$5:$T$17,0))</f>
-        <v>0.0909090909090909</v>
+        <v>0.126623376623377</v>
       </c>
       <c r="D22" s="54" t="n">
         <f aca="false">INDEX($E$5:$E$17,MATCH(LARGE($T$5:$T$17,1),$T$5:$T$17,0))</f>
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="E22" s="54" t="n">
         <f aca="false">INDEX($J$5:$J$17,MATCH(LARGE($T$5:$T$17,1),$T$5:$T$17,0))</f>
@@ -27968,11 +28004,11 @@
       </c>
       <c r="C23" s="55" t="n">
         <f aca="false">INDEX($L$5:$L$17,MATCH(LARGE($T$5:$T$17,2),$T$5:$T$17,0))</f>
-        <v>0.0769230769230769</v>
+        <v>0.0357142857142857</v>
       </c>
       <c r="D23" s="54" t="n">
         <f aca="false">INDEX($E$5:$E$17,MATCH(LARGE($T$5:$T$17,2),$T$5:$T$17,0))</f>
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="E23" s="54" t="n">
         <f aca="false">INDEX($J$5:$J$17,MATCH(LARGE($T$5:$T$17,2),$T$5:$T$17,0))</f>
@@ -27994,11 +28030,11 @@
       </c>
       <c r="C24" s="55" t="n">
         <f aca="false">INDEX($L$5:$L$17,MATCH(LARGE($T$5:$T$17,3),$T$5:$T$17,0))</f>
-        <v>-0.055944055944056</v>
+        <v>-0.0779220779220779</v>
       </c>
       <c r="D24" s="54" t="n">
         <f aca="false">INDEX($E$5:$E$17,MATCH(LARGE($T$5:$T$17,3),$T$5:$T$17,0))</f>
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="E24" s="54" t="n">
         <f aca="false">INDEX($J$5:$J$17,MATCH(LARGE($T$5:$T$17,3),$T$5:$T$17,0))</f>
@@ -28016,15 +28052,15 @@
       </c>
       <c r="B25" s="38" t="str">
         <f aca="false">INDEX($A$5:$A$17,MATCH(LARGE($T$5:$T$17,4),$T$5:$T$17,0))</f>
-        <v>Juscimeira</v>
+        <v>Cáceres</v>
       </c>
       <c r="C25" s="55" t="n">
         <f aca="false">INDEX($L$5:$L$17,MATCH(LARGE($T$5:$T$17,4),$T$5:$T$17,0))</f>
-        <v>-0.0699300699300699</v>
+        <v>-0.0876623376623377</v>
       </c>
       <c r="D25" s="54" t="n">
         <f aca="false">INDEX($E$5:$E$17,MATCH(LARGE($T$5:$T$17,4),$T$5:$T$17,0))</f>
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="E25" s="54" t="n">
         <f aca="false">INDEX($J$5:$J$17,MATCH(LARGE($T$5:$T$17,4),$T$5:$T$17,0))</f>
@@ -28038,19 +28074,19 @@
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="46" t="n">
         <f aca="false">INDEX($M$5:$M$17,MATCH(LARGE($T$5:$T$17,5),$T$5:$T$17,0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B26" s="38" t="str">
         <f aca="false">INDEX($A$5:$A$17,MATCH(LARGE($T$5:$T$17,5),$T$5:$T$17,0))</f>
-        <v>Nossa Senhora do Livramento</v>
+        <v>Juscimeira</v>
       </c>
       <c r="C26" s="55" t="n">
         <f aca="false">INDEX($L$5:$L$17,MATCH(LARGE($T$5:$T$17,5),$T$5:$T$17,0))</f>
-        <v>-0.0699300699300699</v>
+        <v>-0.0974025974025974</v>
       </c>
       <c r="D26" s="54" t="n">
         <f aca="false">INDEX($E$5:$E$17,MATCH(LARGE($T$5:$T$17,5),$T$5:$T$17,0))</f>
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="E26" s="54" t="n">
         <f aca="false">INDEX($J$5:$J$17,MATCH(LARGE($T$5:$T$17,5),$T$5:$T$17,0))</f>
@@ -28064,19 +28100,19 @@
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="46" t="n">
         <f aca="false">INDEX($M$5:$M$17,MATCH(LARGE($T$5:$T$17,6),$T$5:$T$17,0))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B27" s="38" t="str">
         <f aca="false">INDEX($A$5:$A$17,MATCH(LARGE($T$5:$T$17,6),$T$5:$T$17,0))</f>
-        <v>Cáceres</v>
+        <v>Nossa Senhora do Livramento</v>
       </c>
       <c r="C27" s="55" t="n">
         <f aca="false">INDEX($L$5:$L$17,MATCH(LARGE($T$5:$T$17,6),$T$5:$T$17,0))</f>
-        <v>-0.101398601398601</v>
+        <v>-0.0974025974025974</v>
       </c>
       <c r="D27" s="54" t="n">
         <f aca="false">INDEX($E$5:$E$17,MATCH(LARGE($T$5:$T$17,6),$T$5:$T$17,0))</f>
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="E27" s="54" t="n">
         <f aca="false">INDEX($J$5:$J$17,MATCH(LARGE($T$5:$T$17,6),$T$5:$T$17,0))</f>
@@ -28098,11 +28134,11 @@
       </c>
       <c r="C28" s="55" t="n">
         <f aca="false">INDEX($L$5:$L$17,MATCH(LARGE($T$5:$T$17,7),$T$5:$T$17,0))</f>
-        <v>-0.237762237762238</v>
+        <v>-0.25974025974026</v>
       </c>
       <c r="D28" s="54" t="n">
         <f aca="false">INDEX($E$5:$E$17,MATCH(LARGE($T$5:$T$17,7),$T$5:$T$17,0))</f>
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="E28" s="54" t="n">
         <f aca="false">INDEX($J$5:$J$17,MATCH(LARGE($T$5:$T$17,7),$T$5:$T$17,0))</f>
@@ -28124,11 +28160,11 @@
       </c>
       <c r="C29" s="55" t="n">
         <f aca="false">INDEX($L$5:$L$17,MATCH(LARGE($T$5:$T$17,8),$T$5:$T$17,0))</f>
-        <v>-0.276223776223776</v>
+        <v>-0.295454545454545</v>
       </c>
       <c r="D29" s="54" t="n">
         <f aca="false">INDEX($E$5:$E$17,MATCH(LARGE($T$5:$T$17,8),$T$5:$T$17,0))</f>
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="E29" s="54" t="n">
         <f aca="false">INDEX($J$5:$J$17,MATCH(LARGE($T$5:$T$17,8),$T$5:$T$17,0))</f>
@@ -28150,11 +28186,11 @@
       </c>
       <c r="C30" s="55" t="n">
         <f aca="false">INDEX($L$5:$L$17,MATCH(LARGE($T$5:$T$17,9),$T$5:$T$17,0))</f>
-        <v>-0.276223776223776</v>
+        <v>-0.295454545454545</v>
       </c>
       <c r="D30" s="54" t="n">
         <f aca="false">INDEX($E$5:$E$17,MATCH(LARGE($T$5:$T$17,9),$T$5:$T$17,0))</f>
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="E30" s="54" t="n">
         <f aca="false">INDEX($J$5:$J$17,MATCH(LARGE($T$5:$T$17,9),$T$5:$T$17,0))</f>
@@ -28176,11 +28212,11 @@
       </c>
       <c r="C31" s="55" t="n">
         <f aca="false">INDEX($L$5:$L$17,MATCH(LARGE($T$5:$T$17,10),$T$5:$T$17,0))</f>
-        <v>-0.276223776223776</v>
+        <v>-0.295454545454545</v>
       </c>
       <c r="D31" s="54" t="n">
         <f aca="false">INDEX($E$5:$E$17,MATCH(LARGE($T$5:$T$17,10),$T$5:$T$17,0))</f>
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="E31" s="54" t="n">
         <f aca="false">INDEX($J$5:$J$17,MATCH(LARGE($T$5:$T$17,10),$T$5:$T$17,0))</f>
@@ -28202,11 +28238,11 @@
       </c>
       <c r="C32" s="55" t="n">
         <f aca="false">INDEX($L$5:$L$17,MATCH(LARGE($T$5:$T$17,11),$T$5:$T$17,0))</f>
-        <v>-0.276223776223776</v>
+        <v>-0.295454545454545</v>
       </c>
       <c r="D32" s="54" t="n">
         <f aca="false">INDEX($E$5:$E$17,MATCH(LARGE($T$5:$T$17,11),$T$5:$T$17,0))</f>
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="E32" s="54" t="n">
         <f aca="false">INDEX($J$5:$J$17,MATCH(LARGE($T$5:$T$17,11),$T$5:$T$17,0))</f>
@@ -28228,11 +28264,11 @@
       </c>
       <c r="C33" s="55" t="n">
         <f aca="false">INDEX($L$5:$L$17,MATCH(LARGE($T$5:$T$17,12),$T$5:$T$17,0))</f>
-        <v>-0.307692307692308</v>
+        <v>-0.321428571428571</v>
       </c>
       <c r="D33" s="54" t="n">
         <f aca="false">INDEX($E$5:$E$17,MATCH(LARGE($T$5:$T$17,12),$T$5:$T$17,0))</f>
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="E33" s="54" t="n">
         <f aca="false">INDEX($J$5:$J$17,MATCH(LARGE($T$5:$T$17,12),$T$5:$T$17,0))</f>
@@ -28254,11 +28290,11 @@
       </c>
       <c r="C34" s="55" t="n">
         <f aca="false">INDEX($L$5:$L$17,MATCH(LARGE($T$5:$T$17,13),$T$5:$T$17,0))</f>
-        <v>-0.346153846153846</v>
+        <v>-0.357142857142857</v>
       </c>
       <c r="D34" s="54" t="n">
         <f aca="false">INDEX($E$5:$E$17,MATCH(LARGE($T$5:$T$17,13),$T$5:$T$17,0))</f>
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="E34" s="54" t="n">
         <f aca="false">INDEX($J$5:$J$17,MATCH(LARGE($T$5:$T$17,13),$T$5:$T$17,0))</f>
@@ -28368,7 +28404,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
@@ -28756,6 +28792,23 @@
       </c>
       <c r="E35" s="58" t="s">
         <v>209</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="58" t="s">
+        <v>160</v>
+      </c>
+      <c r="B36" s="58" t="s">
+        <v>210</v>
+      </c>
+      <c r="C36" s="58" t="s">
+        <v>211</v>
+      </c>
+      <c r="D36" s="58" t="s">
+        <v>212</v>
+      </c>
+      <c r="E36" s="58" t="s">
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -28790,23 +28843,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="47" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="40" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B3" s="63" t="n">
         <v>0.1</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="40" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B4" s="64" t="n">
         <v>2</v>
@@ -28814,18 +28867,18 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="40" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B5" s="65" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28952,12 +29005,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28965,40 +29018,40 @@
         <v>59</v>
       </c>
       <c r="B4" s="66" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C4" s="66" t="s">
         <v>60</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E4" s="66" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F4" s="66" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="G4" s="66" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H4" s="66" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I4" s="66" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="J4" s="66" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="K4" s="66" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="L4" s="66" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="M4" s="66" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="N4" s="66" t="s">
         <v>46</v>
@@ -29068,79 +29121,79 @@
       <c r="L5" s="66"/>
       <c r="M5" s="66"/>
       <c r="N5" s="67" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="O5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="P5" s="67" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="R5" s="67" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="S5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="T5" s="67" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="U5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="V5" s="67" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="W5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="X5" s="67" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Y5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="Z5" s="67" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AA5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AB5" s="67" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AC5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AD5" s="67" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AE5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AF5" s="67" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AG5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AH5" s="67" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AI5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AJ5" s="67" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AK5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AL5" s="67" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AM5" s="67" t="s">
         <v>102</v>
@@ -29148,28 +29201,28 @@
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="68" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B6" s="69" t="s">
         <v>74</v>
       </c>
       <c r="C6" s="69" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D6" s="68" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E6" s="70" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F6" s="69" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="G6" s="70" t="n">
         <v>2021</v>
       </c>
       <c r="H6" s="70" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="I6" s="71" t="n">
         <v>1</v>
@@ -29288,22 +29341,22 @@
         <v>74</v>
       </c>
       <c r="C7" s="69" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D7" s="68" t="s">
+        <v>242</v>
+      </c>
+      <c r="E7" s="70" t="s">
         <v>238</v>
       </c>
-      <c r="E7" s="70" t="s">
-        <v>234</v>
-      </c>
       <c r="F7" s="69" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="G7" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H7" s="70" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="I7" s="71" t="n">
         <v>5602.9</v>
@@ -29418,22 +29471,22 @@
         <v>74</v>
       </c>
       <c r="C8" s="69" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D8" s="68" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E8" s="70" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F8" s="69" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="G8" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H8" s="70" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I8" s="71" t="n">
         <v>3.79</v>
@@ -29548,20 +29601,20 @@
         <v>74</v>
       </c>
       <c r="C9" s="69" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D9" s="68" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E9" s="70" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F9" s="69" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="G9" s="70"/>
       <c r="H9" s="70" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I9" s="71"/>
       <c r="J9" s="71"/>
@@ -29648,20 +29701,20 @@
         <v>74</v>
       </c>
       <c r="C10" s="69" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="D10" s="68" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E10" s="70" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F10" s="69" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="G10" s="70"/>
       <c r="H10" s="70" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="I10" s="71"/>
       <c r="J10" s="71"/>
@@ -29742,28 +29795,28 @@
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="75" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B11" s="76" t="s">
         <v>76</v>
       </c>
       <c r="C11" s="76" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D11" s="75" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E11" s="70" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F11" s="76" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="G11" s="70" t="n">
         <v>2021</v>
       </c>
       <c r="H11" s="70" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="I11" s="71" t="n">
         <v>1</v>
@@ -29882,22 +29935,22 @@
         <v>76</v>
       </c>
       <c r="C12" s="76" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D12" s="75" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E12" s="70" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F12" s="76" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="G12" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H12" s="70" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I12" s="71" t="n">
         <v>36.92</v>
@@ -30012,22 +30065,22 @@
         <v>76</v>
       </c>
       <c r="C13" s="76" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D13" s="75" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E13" s="70" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F13" s="76" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="G13" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H13" s="70" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="I13" s="71" t="n">
         <v>2956.72</v>
@@ -30136,28 +30189,28 @@
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="77" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B14" s="78" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C14" s="78" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D14" s="77" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E14" s="70" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F14" s="78" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="G14" s="70" t="n">
         <v>2021</v>
       </c>
       <c r="H14" s="70" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="I14" s="71" t="n">
         <v>1</v>
@@ -30273,25 +30326,25 @@
         <v>194</v>
       </c>
       <c r="B15" s="78" t="s">
+        <v>261</v>
+      </c>
+      <c r="C15" s="78" t="s">
+        <v>263</v>
+      </c>
+      <c r="D15" s="77" t="s">
+        <v>246</v>
+      </c>
+      <c r="E15" s="70" t="s">
+        <v>238</v>
+      </c>
+      <c r="F15" s="78" t="s">
         <v>257</v>
-      </c>
-      <c r="C15" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="D15" s="77" t="s">
-        <v>242</v>
-      </c>
-      <c r="E15" s="70" t="s">
-        <v>234</v>
-      </c>
-      <c r="F15" s="78" t="s">
-        <v>253</v>
       </c>
       <c r="G15" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H15" s="70" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I15" s="71" t="n">
         <v>38.11</v>
@@ -30403,25 +30456,25 @@
         <v>158</v>
       </c>
       <c r="B16" s="78" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C16" s="78" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D16" s="77" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E16" s="70" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F16" s="78" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="G16" s="70" t="n">
         <v>2021</v>
       </c>
       <c r="H16" s="70" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="I16" s="71" t="n">
         <v>33.22</v>
@@ -30533,25 +30586,25 @@
         <v>142</v>
       </c>
       <c r="B17" s="80" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C17" s="80" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D17" s="79" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E17" s="70" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F17" s="80" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="G17" s="70" t="n">
         <v>2023</v>
       </c>
       <c r="H17" s="70" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="I17" s="71" t="n">
         <v>74620.05</v>
@@ -30663,25 +30716,25 @@
         <v>138</v>
       </c>
       <c r="B18" s="80" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C18" s="80" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D18" s="79" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E18" s="70" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="F18" s="80" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="G18" s="70" t="n">
         <v>2021</v>
       </c>
       <c r="H18" s="70" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I18" s="71" t="n">
         <v>11.89</v>
@@ -30793,25 +30846,25 @@
         <v>199</v>
       </c>
       <c r="B19" s="80" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C19" s="80" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D19" s="79" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="E19" s="70" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F19" s="80" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="G19" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H19" s="70" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="I19" s="71" t="n">
         <v>31.51</v>
@@ -30923,25 +30976,25 @@
         <v>202</v>
       </c>
       <c r="B20" s="80" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C20" s="80" t="s">
+        <v>274</v>
+      </c>
+      <c r="D20" s="79" t="s">
+        <v>252</v>
+      </c>
+      <c r="E20" s="70" t="s">
         <v>270</v>
       </c>
-      <c r="D20" s="79" t="s">
-        <v>248</v>
-      </c>
-      <c r="E20" s="70" t="s">
-        <v>266</v>
-      </c>
       <c r="F20" s="80" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="G20" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H20" s="70" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="I20" s="83" t="n">
         <v>0.1254</v>
@@ -31053,104 +31106,134 @@
         <v>160</v>
       </c>
       <c r="B21" s="80" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C21" s="80" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D21" s="79" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E21" s="70" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F21" s="80" t="s">
-        <v>272</v>
-      </c>
-      <c r="G21" s="70"/>
+        <v>276</v>
+      </c>
+      <c r="G21" s="70" t="n">
+        <v>2022</v>
+      </c>
       <c r="H21" s="70" t="s">
-        <v>244</v>
-      </c>
-      <c r="I21" s="71"/>
+        <v>248</v>
+      </c>
+      <c r="I21" s="71" t="n">
+        <v>18.24</v>
+      </c>
       <c r="J21" s="71"/>
       <c r="K21" s="71"/>
-      <c r="L21" s="72" t="str">
+      <c r="L21" s="72" t="n">
         <f aca="false">IF($H21="Absoluto",IF($J21="","",$J21),IF($I21="","",IF($H21="Razão MT",MIN($I21*(1-Parâmetros!$B$3),$I21*(1+Parâmetros!$B$3)),$I21-Parâmetros!$B$4)))</f>
-        <v/>
-      </c>
-      <c r="M21" s="72" t="str">
+        <v>16.24</v>
+      </c>
+      <c r="M21" s="72" t="n">
         <f aca="false">IF($H21="Absoluto",IF($K21="","",$K21),IF($I21="","",IF($H21="Razão MT",MAX($I21*(1-Parâmetros!$B$3),$I21*(1+Parâmetros!$B$3)),$I21+Parâmetros!$B$4)))</f>
-        <v/>
-      </c>
-      <c r="N21" s="71"/>
+        <v>20.24</v>
+      </c>
+      <c r="N21" s="71" t="n">
+        <v>6.34</v>
+      </c>
       <c r="O21" s="74" t="str">
         <f aca="false">IF(OR(N21="",$L21="",$M21=""),"",IF($E21="+",IF(N21&gt;$M21,"Força",IF(N21&lt;$L21,"Fraqueza","Neutro")),IF(N21&lt;$L21,"Força",IF(N21&gt;$M21,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="P21" s="71"/>
+        <v>Fraqueza</v>
+      </c>
+      <c r="P21" s="71" t="n">
+        <v>17.68</v>
+      </c>
       <c r="Q21" s="74" t="str">
         <f aca="false">IF(OR(P21="",$L21="",$M21=""),"",IF($E21="+",IF(P21&gt;$M21,"Força",IF(P21&lt;$L21,"Fraqueza","Neutro")),IF(P21&lt;$L21,"Força",IF(P21&gt;$M21,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="R21" s="71"/>
+        <v>Neutro</v>
+      </c>
+      <c r="R21" s="71" t="n">
+        <v>5.5</v>
+      </c>
       <c r="S21" s="74" t="str">
         <f aca="false">IF(OR(R21="",$L21="",$M21=""),"",IF($E21="+",IF(R21&gt;$M21,"Força",IF(R21&lt;$L21,"Fraqueza","Neutro")),IF(R21&lt;$L21,"Força",IF(R21&gt;$M21,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="T21" s="71"/>
+        <v>Fraqueza</v>
+      </c>
+      <c r="T21" s="71" t="n">
+        <v>5.76</v>
+      </c>
       <c r="U21" s="74" t="str">
         <f aca="false">IF(OR(T21="",$L21="",$M21=""),"",IF($E21="+",IF(T21&gt;$M21,"Força",IF(T21&lt;$L21,"Fraqueza","Neutro")),IF(T21&lt;$L21,"Força",IF(T21&gt;$M21,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="V21" s="71"/>
+        <v>Fraqueza</v>
+      </c>
+      <c r="V21" s="71" t="n">
+        <v>11.87</v>
+      </c>
       <c r="W21" s="74" t="str">
         <f aca="false">IF(OR(V21="",$L21="",$M21=""),"",IF($E21="+",IF(V21&gt;$M21,"Força",IF(V21&lt;$L21,"Fraqueza","Neutro")),IF(V21&lt;$L21,"Força",IF(V21&gt;$M21,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="X21" s="71"/>
+        <v>Fraqueza</v>
+      </c>
+      <c r="X21" s="71" t="n">
+        <v>11.71</v>
+      </c>
       <c r="Y21" s="74" t="str">
         <f aca="false">IF(OR(X21="",$L21="",$M21=""),"",IF($E21="+",IF(X21&gt;$M21,"Força",IF(X21&lt;$L21,"Fraqueza","Neutro")),IF(X21&lt;$L21,"Força",IF(X21&gt;$M21,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="Z21" s="71"/>
+        <v>Fraqueza</v>
+      </c>
+      <c r="Z21" s="71" t="n">
+        <v>7.14</v>
+      </c>
       <c r="AA21" s="74" t="str">
         <f aca="false">IF(OR(Z21="",$L21="",$M21=""),"",IF($E21="+",IF(Z21&gt;$M21,"Força",IF(Z21&lt;$L21,"Fraqueza","Neutro")),IF(Z21&lt;$L21,"Força",IF(Z21&gt;$M21,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AB21" s="71"/>
+        <v>Fraqueza</v>
+      </c>
+      <c r="AB21" s="71" t="n">
+        <v>14.35</v>
+      </c>
       <c r="AC21" s="74" t="str">
         <f aca="false">IF(OR(AB21="",$L21="",$M21=""),"",IF($E21="+",IF(AB21&gt;$M21,"Força",IF(AB21&lt;$L21,"Fraqueza","Neutro")),IF(AB21&lt;$L21,"Força",IF(AB21&gt;$M21,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AD21" s="71"/>
+        <v>Fraqueza</v>
+      </c>
+      <c r="AD21" s="71" t="n">
+        <v>5.15</v>
+      </c>
       <c r="AE21" s="74" t="str">
         <f aca="false">IF(OR(AD21="",$L21="",$M21=""),"",IF($E21="+",IF(AD21&gt;$M21,"Força",IF(AD21&lt;$L21,"Fraqueza","Neutro")),IF(AD21&lt;$L21,"Força",IF(AD21&gt;$M21,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AF21" s="71"/>
+        <v>Fraqueza</v>
+      </c>
+      <c r="AF21" s="71" t="n">
+        <v>9.51</v>
+      </c>
       <c r="AG21" s="74" t="str">
         <f aca="false">IF(OR(AF21="",$L21="",$M21=""),"",IF($E21="+",IF(AF21&gt;$M21,"Força",IF(AF21&lt;$L21,"Fraqueza","Neutro")),IF(AF21&lt;$L21,"Força",IF(AF21&gt;$M21,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AH21" s="71"/>
+        <v>Fraqueza</v>
+      </c>
+      <c r="AH21" s="71" t="n">
+        <v>6.54</v>
+      </c>
       <c r="AI21" s="74" t="str">
         <f aca="false">IF(OR(AH21="",$L21="",$M21=""),"",IF($E21="+",IF(AH21&gt;$M21,"Força",IF(AH21&lt;$L21,"Fraqueza","Neutro")),IF(AH21&lt;$L21,"Força",IF(AH21&gt;$M21,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AJ21" s="71"/>
+        <v>Fraqueza</v>
+      </c>
+      <c r="AJ21" s="71" t="n">
+        <v>21.61</v>
+      </c>
       <c r="AK21" s="74" t="str">
         <f aca="false">IF(OR(AJ21="",$L21="",$M21=""),"",IF($E21="+",IF(AJ21&gt;$M21,"Força",IF(AJ21&lt;$L21,"Fraqueza","Neutro")),IF(AJ21&lt;$L21,"Força",IF(AJ21&gt;$M21,"Fraqueza","Neutro"))))</f>
-        <v/>
-      </c>
-      <c r="AL21" s="71"/>
+        <v>Força</v>
+      </c>
+      <c r="AL21" s="71" t="n">
+        <v>9.96</v>
+      </c>
       <c r="AM21" s="74" t="str">
         <f aca="false">IF(OR(AL21="",$L21="",$M21=""),"",IF($E21="+",IF(AL21&gt;$M21,"Força",IF(AL21&lt;$L21,"Fraqueza","Neutro")),IF(AL21&lt;$L21,"Força",IF(AL21&gt;$M21,"Fraqueza","Neutro"))))</f>
-        <v/>
+        <v>Fraqueza</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="33" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -31232,12 +31315,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31248,13 +31331,13 @@
         <v>67</v>
       </c>
       <c r="C4" s="84" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D4" s="84" t="s">
         <v>66</v>
       </c>
       <c r="E4" s="84" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="F4" s="84" t="s">
         <v>46</v>
@@ -31298,24 +31381,24 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C6" s="28" t="s">
         <v>74</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F6" s="70" t="n">
         <v>1</v>
@@ -31359,19 +31442,19 @@
     </row>
     <row r="7" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C7" s="28" t="s">
         <v>74</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="F7" s="70" t="n">
         <v>3</v>
@@ -31415,19 +31498,19 @@
     </row>
     <row r="8" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="F8" s="70" t="n">
         <v>3</v>
@@ -31471,19 +31554,19 @@
     </row>
     <row r="9" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C9" s="28" t="s">
         <v>76</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F9" s="70" t="n">
         <v>0</v>
@@ -31527,19 +31610,19 @@
     </row>
     <row r="10" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="F10" s="70" t="n">
         <v>1</v>
@@ -31583,19 +31666,19 @@
     </row>
     <row r="11" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="F11" s="70" t="n">
         <v>2</v>
@@ -31639,19 +31722,19 @@
     </row>
     <row r="12" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="85" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B12" s="85" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C12" s="86" t="s">
         <v>74</v>
       </c>
       <c r="D12" s="86" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="E12" s="86" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="F12" s="70" t="n">
         <v>3</v>
@@ -31695,19 +31778,19 @@
     </row>
     <row r="13" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="85" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B13" s="85" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C13" s="86" t="s">
         <v>74</v>
       </c>
       <c r="D13" s="86" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="E13" s="86" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="F13" s="70" t="n">
         <v>2</v>
@@ -31751,19 +31834,19 @@
     </row>
     <row r="14" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="85" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B14" s="85" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C14" s="86" t="s">
         <v>74</v>
       </c>
       <c r="D14" s="86" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E14" s="86" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="F14" s="70" t="n">
         <v>2</v>
@@ -31807,19 +31890,19 @@
     </row>
     <row r="15" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="85" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B15" s="85" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C15" s="86" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D15" s="86" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="E15" s="86" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F15" s="70" t="n">
         <v>1</v>
@@ -31863,19 +31946,19 @@
     </row>
     <row r="16" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="85" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B16" s="85" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C16" s="86" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D16" s="86" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="E16" s="86" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="F16" s="70" t="n">
         <v>3</v>
@@ -31919,7 +32002,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="33" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>

--- a/pesm-pantanal-norte/dados/Matriz_SWOT_PESM_Pantanal_Norte.xlsx
+++ b/pesm-pantanal-norte/dados/Matriz_SWOT_PESM_Pantanal_Norte.xlsx
@@ -318,8 +318,54 @@
 </comments>
 </file>
 
+<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="F14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nota revista de 2 para 3 em 25/09/2026: 188 km² desmatados em 2019–2023 (d4_desmatamento.csv); 1.0% dos imóveis do CAR em conformidade (d4_car.csv).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nota revista de 1 para 2 em 25/09/2026: 117 km² desmatados em 2019–2023 (d4_desmatamento.csv); 0.6% dos imóveis do CAR em conformidade (d4_car.csv).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nota revista de 2 para 3 em 25/09/2026: 185 km² desmatados em 2019–2023 (d4_desmatamento.csv); 1.2% dos imóveis do CAR em conformidade (d4_car.csv).</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="347">
   <si>
     <t xml:space="preserve">MATRIZ SWOT DO PERFIL ECONÔMICO-PRODUTIVO SETORIAL MUNICIPAL (PESM) — PANTANAL NORTE</t>
   </si>
@@ -963,6 +1009,21 @@
     <t xml:space="preserve">O cálculo com receita_propria_real ÷ receita_total_real reproduz a coluna (diferença &lt; 0,01 p.p.). Denominador diferente do previsto (receita total em vez de corrente): tratar como aproximação.</t>
   </si>
   <si>
+    <t xml:space="preserve">AM-03 (revisão)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019–2023 / 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d4_desmatamento.csv (PRODES/MapBiomas) e d4_car.csv (SICAR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notas revistas com dados: Barão de Melgaço 2→3, Poconé 2→3, N. Sra. do Livramento 1→2. Os demais mantidos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barão (188 km²), Poconé (185 km²), Cáceres (181), Sto. Antônio do Leverger (170) e Livramento (117) concentram o desmatamento recente da região; a conformidade do CAR é baixa em todos (0,6%–3,7%).</t>
+  </si>
+  <si>
     <t xml:space="preserve">PARÂMETROS</t>
   </si>
   <si>
@@ -1251,7 +1312,7 @@
     <t xml:space="preserve">Exigências ambientais de mercados importadores e barreiras ligadas a desmatamento (ex.: EUDR)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pesquisa web-based; Comex Stat. Evidências: Regulamento UE 2023/1115 (EUDR) exige rastreabilidade livre de desmatamento para carne e soja; maior exposição em municípios exportadores de grãos/carne (Itiquira, Rondonópolis, Cáceres, Sto. Antônio do Leverger).</t>
+    <t xml:space="preserve">Pesquisa web-based; Comex Stat. Evidências: Regulamento UE 2023/1115 (EUDR) exige rastreabilidade livre de desmatamento para carne e soja; maior exposição em municípios exportadores de grãos/carne (Itiquira, Rondonópolis, Cáceres, Sto. Antônio do Leverger). | Dados (d4_desmatamento.csv, d4_car.csv): desmatamento 2019–2023 — Barão de Melgaço 188 km²; Poconé 185 km²; Cáceres 181 km²; Santo Antônio do Leverger 170 km²; Nossa Senhora do Livramento 117 km²; Itiquira 56 km²; Porto Esperidião 35 km²; demais abaixo de 10 km². Só 0,6% a 3,7% dos imóveis do CAR estão em conformidade nos 13 municípios (2024).</t>
   </si>
   <si>
     <t xml:space="preserve">AM-04</t>
@@ -2554,7 +2615,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B2" s="1" t="n">
         <f aca="false">IFERROR(MATCH($B$1,'Indicadores (F-W)'!$A$4:$AM$4,0),"")</f>
@@ -2563,7 +2624,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B3" s="1" t="n">
         <f aca="false">IFERROR(MATCH($B$1,'Fatores Externos (O-A)'!$A$4:$R$4,0),"")</f>
@@ -2575,7 +2636,7 @@
         <v>59</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>102</v>
@@ -2584,16 +2645,16 @@
         <v>31</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>59</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>67</v>
@@ -2602,16 +2663,16 @@
         <v>33</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3415,12 +3476,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4079,7 +4140,7 @@
       </c>
       <c r="S14" s="1" t="n">
         <f aca="false">IF('Fatores Externos (O-A)'!F14="","",'Fatores Externos (O-A)'!F14)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T14" s="1" t="n">
         <f aca="false">IF(AND(R14="Oportunidade",ISNUMBER(S14)),IF(S14&gt;=Parâmetros!$B$5,1,0),0)</f>
@@ -4555,7 +4616,7 @@
       </c>
       <c r="H26" s="32" t="n">
         <f aca="false">IFERROR(INDEX($S$6:$S$16,MATCH(3,$W$6:$W$16,0)),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4813,7 +4874,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -4859,12 +4920,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6257,7 +6318,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -6303,12 +6364,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7701,7 +7762,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -7747,12 +7808,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9145,7 +9206,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -9191,12 +9252,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10589,7 +10650,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -10635,12 +10696,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12033,7 +12094,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -12079,12 +12140,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13477,7 +13538,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -13523,12 +13584,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14921,7 +14982,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -14967,12 +15028,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15631,7 +15692,7 @@
       </c>
       <c r="S14" s="1" t="n">
         <f aca="false">IF('Fatores Externos (O-A)'!N14="","",'Fatores Externos (O-A)'!N14)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T14" s="1" t="n">
         <f aca="false">IF(AND(R14="Oportunidade",ISNUMBER(S14)),IF(S14&gt;=Parâmetros!$B$5,1,0),0)</f>
@@ -15643,11 +15704,11 @@
       </c>
       <c r="V14" s="1" t="n">
         <f aca="false">IF(AND(R14="Ameaça",ISNUMBER(S14)),IF(S14&gt;=Parâmetros!$B$5,1,0),0)</f>
-        <v>0</v>
-      </c>
-      <c r="W14" s="1" t="str">
+        <v>1</v>
+      </c>
+      <c r="W14" s="1" t="n">
         <f aca="false">IF(V14=1,SUM(V$6:V14),"")</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15797,7 +15858,7 @@
       </c>
       <c r="W16" s="1" t="n">
         <f aca="false">IF(V16=1,SUM(V$6:V16),"")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16002,7 +16063,7 @@
       <c r="D22" s="23"/>
       <c r="F22" s="24" t="str">
         <f aca="false">"AMEAÇAS (T) — "&amp;SUM($V$6:$V$16)&amp;" item(ns)"</f>
-        <v>AMEAÇAS (T) — 3 item(ns)</v>
+        <v>AMEAÇAS (T) — 4 item(ns)</v>
       </c>
       <c r="G22" s="24"/>
       <c r="H22" s="24"/>
@@ -16103,11 +16164,11 @@
       </c>
       <c r="G26" s="31" t="str">
         <f aca="false">IFERROR(INDEX($Q$6:$Q$16,MATCH(3,$W$6:$W$16,0)),"")</f>
-        <v>[Comércio e Serviços] AM-05 – Polarização regional por centros maiores (evasão de consumo, serviços e mão de obra)</v>
+        <v>[Agropecuária] AM-03 – Exigências ambientais de mercados importadores e barreiras ligadas a desmatamento (ex.: EUDR)</v>
       </c>
       <c r="H26" s="32" t="n">
         <f aca="false">IFERROR(INDEX($S$6:$S$16,MATCH(3,$W$6:$W$16,0)),"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16124,17 +16185,17 @@
         <f aca="false">IFERROR(INDEX($S$6:$S$16,MATCH(4,$U$6:$U$16,0)),"")</f>
         <v>2</v>
       </c>
-      <c r="F27" s="30" t="str">
+      <c r="F27" s="30" t="n">
         <f aca="false">IF(G27="","",4)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="G27" s="31" t="str">
         <f aca="false">IFERROR(INDEX($Q$6:$Q$16,MATCH(4,$W$6:$W$16,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="32" t="str">
+        <v>[Comércio e Serviços] AM-05 – Polarização regional por centros maiores (evasão de consumo, serviços e mão de obra)</v>
+      </c>
+      <c r="H27" s="32" t="n">
         <f aca="false">IFERROR(INDEX($S$6:$S$16,MATCH(4,$W$6:$W$16,0)),"")</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16365,7 +16426,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -17232,12 +17293,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17896,7 +17957,7 @@
       </c>
       <c r="S14" s="1" t="n">
         <f aca="false">IF('Fatores Externos (O-A)'!O14="","",'Fatores Externos (O-A)'!O14)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T14" s="1" t="n">
         <f aca="false">IF(AND(R14="Oportunidade",ISNUMBER(S14)),IF(S14&gt;=Parâmetros!$B$5,1,0),0)</f>
@@ -18372,7 +18433,7 @@
       </c>
       <c r="H26" s="32" t="n">
         <f aca="false">IFERROR(INDEX($S$6:$S$16,MATCH(3,$W$6:$W$16,0)),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18630,7 +18691,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -18676,12 +18737,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20074,7 +20135,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -20120,12 +20181,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21518,7 +21579,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -21564,12 +21625,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22962,7 +23023,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -23364,11 +23425,11 @@
       </c>
       <c r="H12" s="36" t="n">
         <f aca="false">COUNTIFS('Fatores Externos (O-A)'!$B$6:$B$16,"Ameaça",'Fatores Externos (O-A)'!N$6:N$16,"&gt;="&amp;Parâmetros!$B$5)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I12" s="36" t="n">
         <f aca="false">G12-H12</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24240,11 +24301,11 @@
       </c>
       <c r="D48" s="36" t="n">
         <f aca="false">COUNTIF('Fatores Externos (O-A)'!$F14:$R14,"&gt;="&amp;Parâmetros!$B$5)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E48" s="39" t="n">
         <f aca="false">IF(COUNT('Fatores Externos (O-A)'!$F14:$R14)=0,"",AVERAGE('Fatores Externos (O-A)'!$F14:$R14))</f>
-        <v>2.15384615384615</v>
+        <v>2.38461538461538</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27667,7 +27728,7 @@
       </c>
       <c r="H13" s="53" t="n">
         <f aca="false">Painel!H12</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I13" s="53" t="n">
         <f aca="false">COUNT('Fatores Externos (O-A)'!N$6:N$16)</f>
@@ -27679,15 +27740,15 @@
       </c>
       <c r="K13" s="55" t="n">
         <f aca="false">IF(I13=0,"",(G13-H13)/I13)</f>
-        <v>0.0909090909090909</v>
+        <v>0</v>
       </c>
       <c r="L13" s="56" t="n">
         <f aca="false">IF(F13="","",IF(K13="",F13,(F13+K13)/2))</f>
-        <v>-0.0974025974025974</v>
+        <v>-0.142857142857143</v>
       </c>
       <c r="M13" s="46" t="n">
         <f aca="false">IF(L13="","",RANK(L13,$L$5:$L$17,0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N13" s="49" t="str">
         <f aca="false">IF(AND(E13&gt;=0.75,J13&gt;=0.75),"Consolidado","PROVISÓRIO")</f>
@@ -27695,7 +27756,7 @@
       </c>
       <c r="T13" s="1" t="n">
         <f aca="false">IF(L13="",-9,L13)-ROW()*0.000000001</f>
-        <v>-0.0974026104025974</v>
+        <v>-0.142857155857143</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28100,7 +28161,7 @@
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="46" t="n">
         <f aca="false">INDEX($M$5:$M$17,MATCH(LARGE($T$5:$T$17,6),$T$5:$T$17,0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B27" s="38" t="str">
         <f aca="false">INDEX($A$5:$A$17,MATCH(LARGE($T$5:$T$17,6),$T$5:$T$17,0))</f>
@@ -28108,7 +28169,7 @@
       </c>
       <c r="C27" s="55" t="n">
         <f aca="false">INDEX($L$5:$L$17,MATCH(LARGE($T$5:$T$17,6),$T$5:$T$17,0))</f>
-        <v>-0.0974025974025974</v>
+        <v>-0.142857142857143</v>
       </c>
       <c r="D27" s="54" t="n">
         <f aca="false">INDEX($E$5:$E$17,MATCH(LARGE($T$5:$T$17,6),$T$5:$T$17,0))</f>
@@ -28404,7 +28465,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
@@ -28809,6 +28870,23 @@
       </c>
       <c r="E36" s="58" t="s">
         <v>213</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="58" t="s">
+        <v>214</v>
+      </c>
+      <c r="B37" s="58" t="s">
+        <v>215</v>
+      </c>
+      <c r="C37" s="58" t="s">
+        <v>216</v>
+      </c>
+      <c r="D37" s="58" t="s">
+        <v>217</v>
+      </c>
+      <c r="E37" s="58" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -28843,23 +28921,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="47" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="40" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B3" s="63" t="n">
         <v>0.1</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="40" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B4" s="64" t="n">
         <v>2</v>
@@ -28867,18 +28945,18 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="40" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B5" s="65" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29005,12 +29083,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29018,40 +29096,40 @@
         <v>59</v>
       </c>
       <c r="B4" s="66" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C4" s="66" t="s">
         <v>60</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E4" s="66" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F4" s="66" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="G4" s="66" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="H4" s="66" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="I4" s="66" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="J4" s="66" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="K4" s="66" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="L4" s="66" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="M4" s="66" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="N4" s="66" t="s">
         <v>46</v>
@@ -29121,79 +29199,79 @@
       <c r="L5" s="66"/>
       <c r="M5" s="66"/>
       <c r="N5" s="67" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="O5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="P5" s="67" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="Q5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="R5" s="67" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="S5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="T5" s="67" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="U5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="V5" s="67" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="W5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="X5" s="67" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="Y5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="Z5" s="67" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="AA5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AB5" s="67" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="AC5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AD5" s="67" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="AE5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AF5" s="67" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="AG5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AH5" s="67" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="AI5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AJ5" s="67" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="AK5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AL5" s="67" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="AM5" s="67" t="s">
         <v>102</v>
@@ -29201,28 +29279,28 @@
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="68" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B6" s="69" t="s">
         <v>74</v>
       </c>
       <c r="C6" s="69" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D6" s="68" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E6" s="70" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="F6" s="69" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="G6" s="70" t="n">
         <v>2021</v>
       </c>
       <c r="H6" s="70" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="I6" s="71" t="n">
         <v>1</v>
@@ -29341,22 +29419,22 @@
         <v>74</v>
       </c>
       <c r="C7" s="69" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D7" s="68" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E7" s="70" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="F7" s="69" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="G7" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H7" s="70" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="I7" s="71" t="n">
         <v>5602.9</v>
@@ -29471,22 +29549,22 @@
         <v>74</v>
       </c>
       <c r="C8" s="69" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="D8" s="68" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E8" s="70" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="F8" s="69" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="G8" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H8" s="70" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="I8" s="71" t="n">
         <v>3.79</v>
@@ -29601,20 +29679,20 @@
         <v>74</v>
       </c>
       <c r="C9" s="69" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D9" s="68" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E9" s="70" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="F9" s="69" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="G9" s="70"/>
       <c r="H9" s="70" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="I9" s="71"/>
       <c r="J9" s="71"/>
@@ -29701,20 +29779,20 @@
         <v>74</v>
       </c>
       <c r="C10" s="69" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="D10" s="68" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="E10" s="70" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="F10" s="69" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="G10" s="70"/>
       <c r="H10" s="70" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="I10" s="71"/>
       <c r="J10" s="71"/>
@@ -29795,28 +29873,28 @@
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="75" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B11" s="76" t="s">
         <v>76</v>
       </c>
       <c r="C11" s="76" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="D11" s="75" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E11" s="70" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="F11" s="76" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="G11" s="70" t="n">
         <v>2021</v>
       </c>
       <c r="H11" s="70" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="I11" s="71" t="n">
         <v>1</v>
@@ -29935,22 +30013,22 @@
         <v>76</v>
       </c>
       <c r="C12" s="76" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="D12" s="75" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E12" s="70" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="F12" s="76" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="G12" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H12" s="70" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="I12" s="71" t="n">
         <v>36.92</v>
@@ -30065,22 +30143,22 @@
         <v>76</v>
       </c>
       <c r="C13" s="76" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="D13" s="75" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="E13" s="70" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="F13" s="76" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="G13" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H13" s="70" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="I13" s="71" t="n">
         <v>2956.72</v>
@@ -30189,28 +30267,28 @@
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="77" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B14" s="78" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C14" s="78" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D14" s="77" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E14" s="70" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="F14" s="78" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="G14" s="70" t="n">
         <v>2021</v>
       </c>
       <c r="H14" s="70" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="I14" s="71" t="n">
         <v>1</v>
@@ -30326,25 +30404,25 @@
         <v>194</v>
       </c>
       <c r="B15" s="78" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C15" s="78" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="D15" s="77" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E15" s="70" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="F15" s="78" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="G15" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H15" s="70" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="I15" s="71" t="n">
         <v>38.11</v>
@@ -30456,25 +30534,25 @@
         <v>158</v>
       </c>
       <c r="B16" s="78" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C16" s="78" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="D16" s="77" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E16" s="70" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="F16" s="78" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="G16" s="70" t="n">
         <v>2021</v>
       </c>
       <c r="H16" s="70" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="I16" s="71" t="n">
         <v>33.22</v>
@@ -30586,25 +30664,25 @@
         <v>142</v>
       </c>
       <c r="B17" s="80" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C17" s="80" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="D17" s="79" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="E17" s="70" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="F17" s="80" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="G17" s="70" t="n">
         <v>2023</v>
       </c>
       <c r="H17" s="70" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="I17" s="71" t="n">
         <v>74620.05</v>
@@ -30716,25 +30794,25 @@
         <v>138</v>
       </c>
       <c r="B18" s="80" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C18" s="80" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="D18" s="79" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E18" s="70" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="F18" s="80" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="G18" s="70" t="n">
         <v>2021</v>
       </c>
       <c r="H18" s="70" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="I18" s="71" t="n">
         <v>11.89</v>
@@ -30846,25 +30924,25 @@
         <v>199</v>
       </c>
       <c r="B19" s="80" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C19" s="80" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="D19" s="79" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E19" s="70" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="F19" s="80" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="G19" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H19" s="70" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="I19" s="71" t="n">
         <v>31.51</v>
@@ -30976,25 +31054,25 @@
         <v>202</v>
       </c>
       <c r="B20" s="80" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C20" s="80" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D20" s="79" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="E20" s="70" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="F20" s="80" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="G20" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H20" s="70" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="I20" s="83" t="n">
         <v>0.1254</v>
@@ -31106,25 +31184,25 @@
         <v>160</v>
       </c>
       <c r="B21" s="80" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C21" s="80" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="D21" s="79" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E21" s="70" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="F21" s="80" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="G21" s="70" t="n">
         <v>2022</v>
       </c>
       <c r="H21" s="70" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="I21" s="71" t="n">
         <v>18.24</v>
@@ -31233,7 +31311,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="33" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -31315,12 +31393,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31331,13 +31409,13 @@
         <v>67</v>
       </c>
       <c r="C4" s="84" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D4" s="84" t="s">
         <v>66</v>
       </c>
       <c r="E4" s="84" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="F4" s="84" t="s">
         <v>46</v>
@@ -31381,24 +31459,24 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C6" s="28" t="s">
         <v>74</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="F6" s="70" t="n">
         <v>1</v>
@@ -31442,19 +31520,19 @@
     </row>
     <row r="7" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C7" s="28" t="s">
         <v>74</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="F7" s="70" t="n">
         <v>3</v>
@@ -31498,19 +31576,19 @@
     </row>
     <row r="8" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="F8" s="70" t="n">
         <v>3</v>
@@ -31554,19 +31632,19 @@
     </row>
     <row r="9" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C9" s="28" t="s">
         <v>76</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="F9" s="70" t="n">
         <v>0</v>
@@ -31610,19 +31688,19 @@
     </row>
     <row r="10" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="F10" s="70" t="n">
         <v>1</v>
@@ -31666,19 +31744,19 @@
     </row>
     <row r="11" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="F11" s="70" t="n">
         <v>2</v>
@@ -31722,19 +31800,19 @@
     </row>
     <row r="12" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="85" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B12" s="85" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C12" s="86" t="s">
         <v>74</v>
       </c>
       <c r="D12" s="86" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="E12" s="86" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="F12" s="70" t="n">
         <v>3</v>
@@ -31778,19 +31856,19 @@
     </row>
     <row r="13" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="85" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B13" s="85" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C13" s="86" t="s">
         <v>74</v>
       </c>
       <c r="D13" s="86" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="E13" s="86" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F13" s="70" t="n">
         <v>2</v>
@@ -31834,22 +31912,22 @@
     </row>
     <row r="14" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="85" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B14" s="85" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C14" s="86" t="s">
         <v>74</v>
       </c>
       <c r="D14" s="86" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="E14" s="86" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="F14" s="70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" s="70" t="n">
         <v>3</v>
@@ -31873,10 +31951,10 @@
         <v>1</v>
       </c>
       <c r="N14" s="70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O14" s="70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P14" s="70" t="n">
         <v>2</v>
@@ -31890,19 +31968,19 @@
     </row>
     <row r="15" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="85" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B15" s="85" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C15" s="86" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D15" s="86" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="E15" s="86" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="F15" s="70" t="n">
         <v>1</v>
@@ -31946,19 +32024,19 @@
     </row>
     <row r="16" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="85" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B16" s="85" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C16" s="86" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D16" s="86" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="E16" s="86" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="F16" s="70" t="n">
         <v>3</v>
@@ -32002,7 +32080,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="33" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -32024,5 +32102,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/pesm-pantanal-norte/dados/Matriz_SWOT_PESM_Pantanal_Norte.xlsx
+++ b/pesm-pantanal-norte/dados/Matriz_SWOT_PESM_Pantanal_Norte.xlsx
@@ -336,6 +336,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="J12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nota revista de 2 para 1 em 25/09/2026. Focos de calor 2013–2022: 11,5 por mil km²/ano, abaixo da média de MT (30,9) (d4_queimadas.csv).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nota revista de 2 para 3 em 25/09/2026. Carne bovina congelada (SH4 0202) é o principal produto exportado: 65%–78% de US$ 108–184 milhões/ano em 2022–2024 (d2_comercio_exterior.csv).</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="N14" authorId="0">
       <text>
         <r>
@@ -360,12 +384,36 @@
         </r>
       </text>
     </comment>
+    <comment ref="P12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nota revista de 2 para 1 em 25/09/2026. Focos de calor 2013–2022: 16,1 por mil km²/ano, abaixo da média de MT (30,9) (d4_queimadas.csv).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nota revista de 2 para 3 em 25/09/2026. 133 km de rodovia duplicada (BR-163/364) e 98% da malha pavimentada (d5_rodovias.csv).</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="352">
   <si>
     <t xml:space="preserve">MATRIZ SWOT DO PERFIL ECONÔMICO-PRODUTIVO SETORIAL MUNICIPAL (PESM) — PANTANAL NORTE</t>
   </si>
@@ -1024,6 +1072,21 @@
     <t xml:space="preserve">Barão (188 km²), Poconé (185 km²), Cáceres (181), Sto. Antônio do Leverger (170) e Livramento (117) concentram o desmatamento recente da região; a conformidade do CAR é baixa em todos (0,6%–3,7%).</t>
   </si>
   <si>
+    <t xml:space="preserve">AM-01, OP-01, OP-05 (revisão)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013–2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d4_queimadas.csv, d2_comercio_exterior.csv, d5_rodovias.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notas revistas com dados: AM-01 Itiquira 2→1; AM-01 Porto Esperidião 2→1; OP-01 Mirassol D'Oeste 2→3; OP-05 Santo Antônio do Leverger 2→3.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Série de focos de 2023–2024 com quebra de escala (total de MT passa de ~30 mil para 0,7–1,7 milhão/ano): usar só para comparar municípios dentro do mesmo ano. d5_energia.csv mostra consumo industrial alto em Poconé (46%) e N. Sra. do Livramento (43%), ligado à mineração de ouro, não à agroindústria.</t>
+  </si>
+  <si>
     <t xml:space="preserve">PARÂMETROS</t>
   </si>
   <si>
@@ -1237,7 +1300,7 @@
     <t xml:space="preserve">Demanda externa por carne bovina e proteína animal</t>
   </si>
   <si>
-    <t xml:space="preserve">Comex Stat; IMEA; Cepea. Evidências: MT tem o maior rebanho do país (≈34 mi cab., 14,2% do BR – IBGE/PPM 2023); Cáceres é o maior rebanho de MT (≈1,4 mi cab., 4º do Brasil). Nota maior onde o QL agro e o rebanho são altos (Cáceres, Porto Esperidião, Sto. Antônio do Leverger).</t>
+    <t xml:space="preserve">Comex Stat; IMEA; Cepea. Evidências: MT tem o maior rebanho do país (≈34 mi cab., 14,2% do BR – IBGE/PPM 2023); Cáceres é o maior rebanho de MT (≈1,4 mi cab., 4º do Brasil). Nota maior onde o QL agro e o rebanho são altos (Cáceres, Porto Esperidião, Sto. Antônio do Leverger). | Dados (d2_comercio_exterior.csv): Mirassol D'Oeste exporta sobretudo carne bovina congelada (SH4 0202); Cáceres, madeira serrada (4407); Itiquira, soja (1201); Rondonópolis, farelo de soja (2304); Poconé e N. Sra. do Livramento, ouro (7108).</t>
   </si>
   <si>
     <t xml:space="preserve">OP-02</t>
@@ -1273,7 +1336,7 @@
     <t xml:space="preserve">Corredores logísticos (rodovias federais, ferrovia, hidrovia do Paraguai)</t>
   </si>
   <si>
-    <t xml:space="preserve">DNIT; ANTT; ANTAQ; pesquisa web-based. Evidências: Ferrovia Estadual Rondonópolis–Lucas do Rio Verde (Rumo; R$ 2 bi em 2025, trecho até Campo Verde previsto p/ 2026 – Rumo/BNDES); Porto de Cáceres reformado e terminal Paratudal em licenciamento (hidrovia Paraguai–Paraná); BR-163/364 (Rondonópolis, Itiquira, Juscimeira) e BR-070/174 (Cáceres, Livramento, Mirassol, Porto Esperidião).</t>
+    <t xml:space="preserve">DNIT; ANTT; ANTAQ; pesquisa web-based. Evidências: Ferrovia Estadual Rondonópolis–Lucas do Rio Verde (Rumo; R$ 2 bi em 2025, trecho até Campo Verde previsto p/ 2026 – Rumo/BNDES); Porto de Cáceres reformado e terminal Paratudal em licenciamento (hidrovia Paraguai–Paraná); BR-163/364 (Rondonópolis, Itiquira, Juscimeira) e BR-070/174 (Cáceres, Livramento, Mirassol, Porto Esperidião). | Dados (d5_rodovias.csv): rodovia duplicada em Rondonópolis (291 km), Itiquira (134), Sto. Antônio do Leverger (133) e Juscimeira (69); malha pavimentada abaixo de 40% em Lambari D'Oeste e Porto Esperidião.</t>
   </si>
   <si>
     <t xml:space="preserve">OP-06</t>
@@ -1294,7 +1357,7 @@
     <t xml:space="preserve">Eventos climáticos extremos: secas prolongadas e incêndios no Pantanal</t>
   </si>
   <si>
-    <t xml:space="preserve">INPE – BDQueimadas; MapBiomas; Cemaden. Evidências: incêndios de 2024 – Cáceres ≈87 mil ha, Poconé ≈61,5 mil ha, Barão de Melgaço ≈2,6 mil ha (Bombeiros-MT/INPE); 2020 foi o pior ano da série no Pantanal; ≈95% dos focos de 2024 começaram em propriedades privadas. Planície pantaneira = exposição alta.</t>
+    <t xml:space="preserve">INPE – BDQueimadas; MapBiomas; Cemaden. Evidências: incêndios de 2024 – Cáceres ≈87 mil ha, Poconé ≈61,5 mil ha, Barão de Melgaço ≈2,6 mil ha (Bombeiros-MT/INPE); 2020 foi o pior ano da série no Pantanal; ≈95% dos focos de 2024 começaram em propriedades privadas. Planície pantaneira = exposição alta. | Dados (d4_queimadas.csv, 2013–2022; a série de 2023–2024 muda de escala e não foi usada): focos por mil km²/ano — Barão de Melgaço 64,5; Poconé 51,4; Sto. Antônio do Leverger 34,1; N. Sra. do Livramento 30,7; Cáceres 25,4; MT 30,9; demais abaixo de 17.</t>
   </si>
   <si>
     <t xml:space="preserve">AM-02</t>
@@ -2615,7 +2678,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B2" s="1" t="n">
         <f aca="false">IFERROR(MATCH($B$1,'Indicadores (F-W)'!$A$4:$AM$4,0),"")</f>
@@ -2624,7 +2687,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B3" s="1" t="n">
         <f aca="false">IFERROR(MATCH($B$1,'Fatores Externos (O-A)'!$A$4:$R$4,0),"")</f>
@@ -2636,7 +2699,7 @@
         <v>59</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>102</v>
@@ -2645,16 +2708,16 @@
         <v>31</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>59</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>67</v>
@@ -2663,16 +2726,16 @@
         <v>33</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3476,12 +3539,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4874,7 +4937,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -4920,12 +4983,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6318,7 +6381,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -6364,12 +6427,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7762,7 +7825,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -7808,12 +7871,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9206,7 +9269,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -9252,12 +9315,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9766,7 +9829,7 @@
       </c>
       <c r="S12" s="1" t="n">
         <f aca="false">IF('Fatores Externos (O-A)'!J12="","",'Fatores Externos (O-A)'!J12)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T12" s="1" t="n">
         <f aca="false">IF(AND(R12="Oportunidade",ISNUMBER(S12)),IF(S12&gt;=Parâmetros!$B$5,1,0),0)</f>
@@ -9778,11 +9841,11 @@
       </c>
       <c r="V12" s="1" t="n">
         <f aca="false">IF(AND(R12="Ameaça",ISNUMBER(S12)),IF(S12&gt;=Parâmetros!$B$5,1,0),0)</f>
-        <v>1</v>
-      </c>
-      <c r="W12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="1" t="str">
         <f aca="false">IF(V12=1,SUM(V$6:V12),"")</f>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9857,7 +9920,7 @@
       </c>
       <c r="W13" s="1" t="n">
         <f aca="false">IF(V13=1,SUM(V$6:V13),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9932,7 +9995,7 @@
       </c>
       <c r="W14" s="1" t="n">
         <f aca="false">IF(V14=1,SUM(V$6:V14),"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10007,7 +10070,7 @@
       </c>
       <c r="W15" s="1" t="n">
         <f aca="false">IF(V15=1,SUM(V$6:V15),"")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10082,7 +10145,7 @@
       </c>
       <c r="W16" s="1" t="n">
         <f aca="false">IF(V16=1,SUM(V$6:V16),"")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10287,7 +10350,7 @@
       <c r="D22" s="23"/>
       <c r="F22" s="24" t="str">
         <f aca="false">"AMEAÇAS (T) — "&amp;SUM($V$6:$V$16)&amp;" item(ns)"</f>
-        <v>AMEAÇAS (T) — 5 item(ns)</v>
+        <v>AMEAÇAS (T) — 4 item(ns)</v>
       </c>
       <c r="G22" s="24"/>
       <c r="H22" s="24"/>
@@ -10334,11 +10397,11 @@
       </c>
       <c r="G24" s="31" t="str">
         <f aca="false">IFERROR(INDEX($Q$6:$Q$16,MATCH(1,$W$6:$W$16,0)),"")</f>
-        <v>[Agropecuária] AM-01 – Eventos climáticos extremos: secas prolongadas e incêndios no Pantanal</v>
+        <v>[Agropecuária] AM-02 – Volatilidade de preços de commodities (boi gordo, soja, milho)</v>
       </c>
       <c r="H24" s="32" t="n">
         <f aca="false">IFERROR(INDEX($S$6:$S$16,MATCH(1,$W$6:$W$16,0)),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10361,7 +10424,7 @@
       </c>
       <c r="G25" s="31" t="str">
         <f aca="false">IFERROR(INDEX($Q$6:$Q$16,MATCH(2,$W$6:$W$16,0)),"")</f>
-        <v>[Agropecuária] AM-02 – Volatilidade de preços de commodities (boi gordo, soja, milho)</v>
+        <v>[Agropecuária] AM-03 – Exigências ambientais de mercados importadores e barreiras ligadas a desmatamento (ex.: EUDR)</v>
       </c>
       <c r="H25" s="32" t="n">
         <f aca="false">IFERROR(INDEX($S$6:$S$16,MATCH(2,$W$6:$W$16,0)),"")</f>
@@ -10388,7 +10451,7 @@
       </c>
       <c r="G26" s="31" t="str">
         <f aca="false">IFERROR(INDEX($Q$6:$Q$16,MATCH(3,$W$6:$W$16,0)),"")</f>
-        <v>[Agropecuária] AM-03 – Exigências ambientais de mercados importadores e barreiras ligadas a desmatamento (ex.: EUDR)</v>
+        <v>[Estrutura Econômica e Fiscal] AM-04 – Transição da Reforma Tributária (IBS/CBS) e efeitos sobre a repartição de receitas municipais</v>
       </c>
       <c r="H26" s="32" t="n">
         <f aca="false">IFERROR(INDEX($S$6:$S$16,MATCH(3,$W$6:$W$16,0)),"")</f>
@@ -10415,11 +10478,11 @@
       </c>
       <c r="G27" s="31" t="str">
         <f aca="false">IFERROR(INDEX($Q$6:$Q$16,MATCH(4,$W$6:$W$16,0)),"")</f>
-        <v>[Estrutura Econômica e Fiscal] AM-04 – Transição da Reforma Tributária (IBS/CBS) e efeitos sobre a repartição de receitas municipais</v>
+        <v>[Comércio e Serviços] AM-05 – Polarização regional por centros maiores (evasão de consumo, serviços e mão de obra)</v>
       </c>
       <c r="H27" s="32" t="n">
         <f aca="false">IFERROR(INDEX($S$6:$S$16,MATCH(4,$W$6:$W$16,0)),"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10436,17 +10499,17 @@
         <f aca="false">IFERROR(INDEX($S$6:$S$16,MATCH(5,$U$6:$U$16,0)),"")</f>
         <v>3</v>
       </c>
-      <c r="F28" s="30" t="n">
+      <c r="F28" s="30" t="str">
         <f aca="false">IF(G28="","",5)</f>
-        <v>5</v>
+        <v/>
       </c>
       <c r="G28" s="31" t="str">
         <f aca="false">IFERROR(INDEX($Q$6:$Q$16,MATCH(5,$W$6:$W$16,0)),"")</f>
-        <v>[Comércio e Serviços] AM-05 – Polarização regional por centros maiores (evasão de consumo, serviços e mão de obra)</v>
-      </c>
-      <c r="H28" s="32" t="n">
+        <v/>
+      </c>
+      <c r="H28" s="32" t="str">
         <f aca="false">IFERROR(INDEX($S$6:$S$16,MATCH(5,$W$6:$W$16,0)),"")</f>
-        <v>2</v>
+        <v/>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10650,7 +10713,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -10696,12 +10759,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12094,7 +12157,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -12140,12 +12203,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13538,7 +13601,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -13584,12 +13647,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13653,7 +13716,7 @@
       </c>
       <c r="S6" s="1" t="n">
         <f aca="false">IF('Fatores Externos (O-A)'!M6="","",'Fatores Externos (O-A)'!M6)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T6" s="1" t="n">
         <f aca="false">IF(AND(R6="Oportunidade",ISNUMBER(S6)),IF(S6&gt;=Parâmetros!$B$5,1,0),0)</f>
@@ -14658,7 +14721,7 @@
       </c>
       <c r="D24" s="29" t="n">
         <f aca="false">IFERROR(INDEX($S$6:$S$16,MATCH(1,$U$6:$U$16,0)),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24" s="30" t="n">
         <f aca="false">IF(G24="","",1)</f>
@@ -14982,7 +15045,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -15028,12 +15091,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16426,7 +16489,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -17293,12 +17356,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18691,7 +18754,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -18737,12 +18800,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19251,7 +19314,7 @@
       </c>
       <c r="S12" s="1" t="n">
         <f aca="false">IF('Fatores Externos (O-A)'!P12="","",'Fatores Externos (O-A)'!P12)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T12" s="1" t="n">
         <f aca="false">IF(AND(R12="Oportunidade",ISNUMBER(S12)),IF(S12&gt;=Parâmetros!$B$5,1,0),0)</f>
@@ -19263,11 +19326,11 @@
       </c>
       <c r="V12" s="1" t="n">
         <f aca="false">IF(AND(R12="Ameaça",ISNUMBER(S12)),IF(S12&gt;=Parâmetros!$B$5,1,0),0)</f>
-        <v>1</v>
-      </c>
-      <c r="W12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="1" t="str">
         <f aca="false">IF(V12=1,SUM(V$6:V12),"")</f>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19342,7 +19405,7 @@
       </c>
       <c r="W13" s="1" t="n">
         <f aca="false">IF(V13=1,SUM(V$6:V13),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19417,7 +19480,7 @@
       </c>
       <c r="W14" s="1" t="n">
         <f aca="false">IF(V14=1,SUM(V$6:V14),"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19567,7 +19630,7 @@
       </c>
       <c r="W16" s="1" t="n">
         <f aca="false">IF(V16=1,SUM(V$6:V16),"")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19772,7 +19835,7 @@
       <c r="D22" s="23"/>
       <c r="F22" s="24" t="str">
         <f aca="false">"AMEAÇAS (T) — "&amp;SUM($V$6:$V$16)&amp;" item(ns)"</f>
-        <v>AMEAÇAS (T) — 4 item(ns)</v>
+        <v>AMEAÇAS (T) — 3 item(ns)</v>
       </c>
       <c r="G22" s="24"/>
       <c r="H22" s="24"/>
@@ -19819,11 +19882,11 @@
       </c>
       <c r="G24" s="31" t="str">
         <f aca="false">IFERROR(INDEX($Q$6:$Q$16,MATCH(1,$W$6:$W$16,0)),"")</f>
-        <v>[Agropecuária] AM-01 – Eventos climáticos extremos: secas prolongadas e incêndios no Pantanal</v>
+        <v>[Agropecuária] AM-02 – Volatilidade de preços de commodities (boi gordo, soja, milho)</v>
       </c>
       <c r="H24" s="32" t="n">
         <f aca="false">IFERROR(INDEX($S$6:$S$16,MATCH(1,$W$6:$W$16,0)),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19846,11 +19909,11 @@
       </c>
       <c r="G25" s="31" t="str">
         <f aca="false">IFERROR(INDEX($Q$6:$Q$16,MATCH(2,$W$6:$W$16,0)),"")</f>
-        <v>[Agropecuária] AM-02 – Volatilidade de preços de commodities (boi gordo, soja, milho)</v>
+        <v>[Agropecuária] AM-03 – Exigências ambientais de mercados importadores e barreiras ligadas a desmatamento (ex.: EUDR)</v>
       </c>
       <c r="H25" s="32" t="n">
         <f aca="false">IFERROR(INDEX($S$6:$S$16,MATCH(2,$W$6:$W$16,0)),"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19873,7 +19936,7 @@
       </c>
       <c r="G26" s="31" t="str">
         <f aca="false">IFERROR(INDEX($Q$6:$Q$16,MATCH(3,$W$6:$W$16,0)),"")</f>
-        <v>[Agropecuária] AM-03 – Exigências ambientais de mercados importadores e barreiras ligadas a desmatamento (ex.: EUDR)</v>
+        <v>[Comércio e Serviços] AM-05 – Polarização regional por centros maiores (evasão de consumo, serviços e mão de obra)</v>
       </c>
       <c r="H26" s="32" t="n">
         <f aca="false">IFERROR(INDEX($S$6:$S$16,MATCH(3,$W$6:$W$16,0)),"")</f>
@@ -19894,17 +19957,17 @@
         <f aca="false">IFERROR(INDEX($S$6:$S$16,MATCH(4,$U$6:$U$16,0)),"")</f>
         <v/>
       </c>
-      <c r="F27" s="30" t="n">
+      <c r="F27" s="30" t="str">
         <f aca="false">IF(G27="","",4)</f>
-        <v>4</v>
+        <v/>
       </c>
       <c r="G27" s="31" t="str">
         <f aca="false">IFERROR(INDEX($Q$6:$Q$16,MATCH(4,$W$6:$W$16,0)),"")</f>
-        <v>[Comércio e Serviços] AM-05 – Polarização regional por centros maiores (evasão de consumo, serviços e mão de obra)</v>
-      </c>
-      <c r="H27" s="32" t="n">
+        <v/>
+      </c>
+      <c r="H27" s="32" t="str">
         <f aca="false">IFERROR(INDEX($S$6:$S$16,MATCH(4,$W$6:$W$16,0)),"")</f>
-        <v>2</v>
+        <v/>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20135,7 +20198,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -20181,12 +20244,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21579,7 +21642,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -21625,12 +21688,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21989,7 +22052,7 @@
       </c>
       <c r="S10" s="1" t="n">
         <f aca="false">IF('Fatores Externos (O-A)'!R10="","",'Fatores Externos (O-A)'!R10)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T10" s="1" t="n">
         <f aca="false">IF(AND(R10="Oportunidade",ISNUMBER(S10)),IF(S10&gt;=Parâmetros!$B$5,1,0),0)</f>
@@ -22780,7 +22843,7 @@
       </c>
       <c r="D27" s="29" t="n">
         <f aca="false">IFERROR(INDEX($S$6:$S$16,MATCH(4,$U$6:$U$16,0)),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" s="30" t="n">
         <f aca="false">IF(G27="","",4)</f>
@@ -23023,7 +23086,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -23277,11 +23340,11 @@
       </c>
       <c r="H8" s="36" t="n">
         <f aca="false">COUNTIFS('Fatores Externos (O-A)'!$B$6:$B$16,"Ameaça",'Fatores Externos (O-A)'!J$6:J$16,"&gt;="&amp;Parâmetros!$B$5)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I8" s="36" t="n">
         <f aca="false">G8-H8</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23499,11 +23562,11 @@
       </c>
       <c r="H14" s="36" t="n">
         <f aca="false">COUNTIFS('Fatores Externos (O-A)'!$B$6:$B$16,"Ameaça",'Fatores Externos (O-A)'!P$6:P$16,"&gt;="&amp;Parâmetros!$B$5)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I14" s="36" t="n">
         <f aca="false">G14-H14</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24129,7 +24192,7 @@
       </c>
       <c r="E40" s="39" t="n">
         <f aca="false">IF(COUNT('Fatores Externos (O-A)'!$F6:$R6)=0,"",AVERAGE('Fatores Externos (O-A)'!$F6:$R6))</f>
-        <v>2.15384615384615</v>
+        <v>2.23076923076923</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24217,7 +24280,7 @@
       </c>
       <c r="E44" s="39" t="n">
         <f aca="false">IF(COUNT('Fatores Externos (O-A)'!$F10:$R10)=0,"",AVERAGE('Fatores Externos (O-A)'!$F10:$R10))</f>
-        <v>1.76923076923077</v>
+        <v>1.84615384615385</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24257,11 +24320,11 @@
       </c>
       <c r="D46" s="36" t="n">
         <f aca="false">COUNTIF('Fatores Externos (O-A)'!$F12:$R12,"&gt;="&amp;Parâmetros!$B$5)</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E46" s="39" t="n">
         <f aca="false">IF(COUNT('Fatores Externos (O-A)'!$F12:$R12)=0,"",AVERAGE('Fatores Externos (O-A)'!$F12:$R12))</f>
-        <v>1.84615384615385</v>
+        <v>1.69230769230769</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27484,7 +27547,7 @@
       </c>
       <c r="H9" s="53" t="n">
         <f aca="false">Painel!H8</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I9" s="53" t="n">
         <f aca="false">COUNT('Fatores Externos (O-A)'!J$6:J$16)</f>
@@ -27496,11 +27559,11 @@
       </c>
       <c r="K9" s="55" t="n">
         <f aca="false">IF(I9=0,"",(G9-H9)/I9)</f>
-        <v>0</v>
+        <v>0.0909090909090909</v>
       </c>
       <c r="L9" s="56" t="n">
         <f aca="false">IF(F9="","",IF(K9="",F9,(F9+K9)/2))</f>
-        <v>0.0357142857142857</v>
+        <v>0.0811688311688312</v>
       </c>
       <c r="M9" s="46" t="n">
         <f aca="false">IF(L9="","",RANK(L9,$L$5:$L$17,0))</f>
@@ -27512,7 +27575,7 @@
       </c>
       <c r="T9" s="1" t="n">
         <f aca="false">IF(L9="",-9,L9)-ROW()*0.000000001</f>
-        <v>0.0357142767142857</v>
+        <v>0.0811688221688312</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27850,7 +27913,7 @@
       </c>
       <c r="H15" s="53" t="n">
         <f aca="false">Painel!H14</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I15" s="53" t="n">
         <f aca="false">COUNT('Fatores Externos (O-A)'!P$6:P$16)</f>
@@ -27862,11 +27925,11 @@
       </c>
       <c r="K15" s="55" t="n">
         <f aca="false">IF(I15=0,"",(G15-H15)/I15)</f>
-        <v>-0.0909090909090909</v>
+        <v>0</v>
       </c>
       <c r="L15" s="56" t="n">
         <f aca="false">IF(F15="","",IF(K15="",F15,(F15+K15)/2))</f>
-        <v>-0.25974025974026</v>
+        <v>-0.214285714285714</v>
       </c>
       <c r="M15" s="46" t="n">
         <f aca="false">IF(L15="","",RANK(L15,$L$5:$L$17,0))</f>
@@ -27878,7 +27941,7 @@
       </c>
       <c r="T15" s="1" t="n">
         <f aca="false">IF(L15="",-9,L15)-ROW()*0.000000001</f>
-        <v>-0.25974027474026</v>
+        <v>-0.214285729285714</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28065,7 +28128,7 @@
       </c>
       <c r="C23" s="55" t="n">
         <f aca="false">INDEX($L$5:$L$17,MATCH(LARGE($T$5:$T$17,2),$T$5:$T$17,0))</f>
-        <v>0.0357142857142857</v>
+        <v>0.0811688311688312</v>
       </c>
       <c r="D23" s="54" t="n">
         <f aca="false">INDEX($E$5:$E$17,MATCH(LARGE($T$5:$T$17,2),$T$5:$T$17,0))</f>
@@ -28195,7 +28258,7 @@
       </c>
       <c r="C28" s="55" t="n">
         <f aca="false">INDEX($L$5:$L$17,MATCH(LARGE($T$5:$T$17,7),$T$5:$T$17,0))</f>
-        <v>-0.25974025974026</v>
+        <v>-0.214285714285714</v>
       </c>
       <c r="D28" s="54" t="n">
         <f aca="false">INDEX($E$5:$E$17,MATCH(LARGE($T$5:$T$17,7),$T$5:$T$17,0))</f>
@@ -28465,7 +28528,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
@@ -28887,6 +28950,23 @@
       </c>
       <c r="E37" s="58" t="s">
         <v>218</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="58" t="s">
+        <v>219</v>
+      </c>
+      <c r="B38" s="58" t="s">
+        <v>220</v>
+      </c>
+      <c r="C38" s="58" t="s">
+        <v>221</v>
+      </c>
+      <c r="D38" s="58" t="s">
+        <v>222</v>
+      </c>
+      <c r="E38" s="58" t="s">
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -28921,23 +29001,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="47" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="40" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B3" s="63" t="n">
         <v>0.1</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="40" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B4" s="64" t="n">
         <v>2</v>
@@ -28945,18 +29025,18 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="40" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B5" s="65" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29083,12 +29163,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29096,40 +29176,40 @@
         <v>59</v>
       </c>
       <c r="B4" s="66" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C4" s="66" t="s">
         <v>60</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E4" s="66" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="F4" s="66" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="G4" s="66" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="H4" s="66" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="I4" s="66" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="J4" s="66" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="K4" s="66" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="L4" s="66" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="M4" s="66" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="N4" s="66" t="s">
         <v>46</v>
@@ -29199,79 +29279,79 @@
       <c r="L5" s="66"/>
       <c r="M5" s="66"/>
       <c r="N5" s="67" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="O5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="P5" s="67" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="Q5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="R5" s="67" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="S5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="T5" s="67" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="U5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="V5" s="67" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="W5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="X5" s="67" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="Y5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="Z5" s="67" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="AA5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AB5" s="67" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="AC5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AD5" s="67" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="AE5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AF5" s="67" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="AG5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AH5" s="67" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="AI5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AJ5" s="67" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="AK5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AL5" s="67" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="AM5" s="67" t="s">
         <v>102</v>
@@ -29279,28 +29359,28 @@
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="68" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B6" s="69" t="s">
         <v>74</v>
       </c>
       <c r="C6" s="69" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D6" s="68" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E6" s="70" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F6" s="69" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="G6" s="70" t="n">
         <v>2021</v>
       </c>
       <c r="H6" s="70" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="I6" s="71" t="n">
         <v>1</v>
@@ -29419,22 +29499,22 @@
         <v>74</v>
       </c>
       <c r="C7" s="69" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="D7" s="68" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="E7" s="70" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F7" s="69" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="G7" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H7" s="70" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="I7" s="71" t="n">
         <v>5602.9</v>
@@ -29549,22 +29629,22 @@
         <v>74</v>
       </c>
       <c r="C8" s="69" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="D8" s="68" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E8" s="70" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F8" s="69" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="G8" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H8" s="70" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="I8" s="71" t="n">
         <v>3.79</v>
@@ -29679,20 +29759,20 @@
         <v>74</v>
       </c>
       <c r="C9" s="69" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="D9" s="68" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E9" s="70" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F9" s="69" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="G9" s="70"/>
       <c r="H9" s="70" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="I9" s="71"/>
       <c r="J9" s="71"/>
@@ -29779,20 +29859,20 @@
         <v>74</v>
       </c>
       <c r="C10" s="69" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="D10" s="68" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="E10" s="70" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F10" s="69" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="G10" s="70"/>
       <c r="H10" s="70" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="I10" s="71"/>
       <c r="J10" s="71"/>
@@ -29873,28 +29953,28 @@
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="75" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B11" s="76" t="s">
         <v>76</v>
       </c>
       <c r="C11" s="76" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D11" s="75" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E11" s="70" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F11" s="76" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="G11" s="70" t="n">
         <v>2021</v>
       </c>
       <c r="H11" s="70" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="I11" s="71" t="n">
         <v>1</v>
@@ -30013,22 +30093,22 @@
         <v>76</v>
       </c>
       <c r="C12" s="76" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D12" s="75" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E12" s="70" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F12" s="76" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="G12" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H12" s="70" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="I12" s="71" t="n">
         <v>36.92</v>
@@ -30143,22 +30223,22 @@
         <v>76</v>
       </c>
       <c r="C13" s="76" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="D13" s="75" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="E13" s="70" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F13" s="76" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="G13" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H13" s="70" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="I13" s="71" t="n">
         <v>2956.72</v>
@@ -30267,28 +30347,28 @@
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="77" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B14" s="78" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C14" s="78" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D14" s="77" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E14" s="70" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F14" s="78" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="G14" s="70" t="n">
         <v>2021</v>
       </c>
       <c r="H14" s="70" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="I14" s="71" t="n">
         <v>1</v>
@@ -30404,25 +30484,25 @@
         <v>194</v>
       </c>
       <c r="B15" s="78" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C15" s="78" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="D15" s="77" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E15" s="70" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F15" s="78" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="G15" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H15" s="70" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="I15" s="71" t="n">
         <v>38.11</v>
@@ -30534,25 +30614,25 @@
         <v>158</v>
       </c>
       <c r="B16" s="78" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C16" s="78" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="D16" s="77" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E16" s="70" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F16" s="78" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="G16" s="70" t="n">
         <v>2021</v>
       </c>
       <c r="H16" s="70" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="I16" s="71" t="n">
         <v>33.22</v>
@@ -30664,25 +30744,25 @@
         <v>142</v>
       </c>
       <c r="B17" s="80" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C17" s="80" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="D17" s="79" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="E17" s="70" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F17" s="80" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="G17" s="70" t="n">
         <v>2023</v>
       </c>
       <c r="H17" s="70" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="I17" s="71" t="n">
         <v>74620.05</v>
@@ -30794,25 +30874,25 @@
         <v>138</v>
       </c>
       <c r="B18" s="80" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C18" s="80" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D18" s="79" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E18" s="70" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="F18" s="80" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="G18" s="70" t="n">
         <v>2021</v>
       </c>
       <c r="H18" s="70" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="I18" s="71" t="n">
         <v>11.89</v>
@@ -30924,25 +31004,25 @@
         <v>199</v>
       </c>
       <c r="B19" s="80" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C19" s="80" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="D19" s="79" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E19" s="70" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F19" s="80" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="G19" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H19" s="70" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="I19" s="71" t="n">
         <v>31.51</v>
@@ -31054,25 +31134,25 @@
         <v>202</v>
       </c>
       <c r="B20" s="80" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C20" s="80" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D20" s="79" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="E20" s="70" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="F20" s="80" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="G20" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H20" s="70" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="I20" s="83" t="n">
         <v>0.1254</v>
@@ -31184,25 +31264,25 @@
         <v>160</v>
       </c>
       <c r="B21" s="80" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C21" s="80" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="D21" s="79" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E21" s="70" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F21" s="80" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="G21" s="70" t="n">
         <v>2022</v>
       </c>
       <c r="H21" s="70" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="I21" s="71" t="n">
         <v>18.24</v>
@@ -31311,7 +31391,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="33" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -31393,12 +31473,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31409,13 +31489,13 @@
         <v>67</v>
       </c>
       <c r="C4" s="84" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="D4" s="84" t="s">
         <v>66</v>
       </c>
       <c r="E4" s="84" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="F4" s="84" t="s">
         <v>46</v>
@@ -31459,24 +31539,24 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C6" s="28" t="s">
         <v>74</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="F6" s="70" t="n">
         <v>1</v>
@@ -31500,7 +31580,7 @@
         <v>2</v>
       </c>
       <c r="M6" s="70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N6" s="70" t="n">
         <v>2</v>
@@ -31520,19 +31600,19 @@
     </row>
     <row r="7" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C7" s="28" t="s">
         <v>74</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F7" s="70" t="n">
         <v>3</v>
@@ -31576,19 +31656,19 @@
     </row>
     <row r="8" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="F8" s="70" t="n">
         <v>3</v>
@@ -31632,19 +31712,19 @@
     </row>
     <row r="9" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C9" s="28" t="s">
         <v>76</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="F9" s="70" t="n">
         <v>0</v>
@@ -31688,19 +31768,19 @@
     </row>
     <row r="10" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F10" s="70" t="n">
         <v>1</v>
@@ -31739,24 +31819,24 @@
         <v>3</v>
       </c>
       <c r="R10" s="70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="F11" s="70" t="n">
         <v>2</v>
@@ -31800,19 +31880,19 @@
     </row>
     <row r="12" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="85" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B12" s="85" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C12" s="86" t="s">
         <v>74</v>
       </c>
       <c r="D12" s="86" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="E12" s="86" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="F12" s="70" t="n">
         <v>3</v>
@@ -31827,7 +31907,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K12" s="70" t="n">
         <v>1</v>
@@ -31845,7 +31925,7 @@
         <v>3</v>
       </c>
       <c r="P12" s="70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="70" t="n">
         <v>1</v>
@@ -31856,19 +31936,19 @@
     </row>
     <row r="13" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="85" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B13" s="85" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C13" s="86" t="s">
         <v>74</v>
       </c>
       <c r="D13" s="86" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="E13" s="86" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="F13" s="70" t="n">
         <v>2</v>
@@ -31912,19 +31992,19 @@
     </row>
     <row r="14" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="85" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B14" s="85" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C14" s="86" t="s">
         <v>74</v>
       </c>
       <c r="D14" s="86" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="E14" s="86" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="F14" s="70" t="n">
         <v>3</v>
@@ -31968,19 +32048,19 @@
     </row>
     <row r="15" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="85" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B15" s="85" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C15" s="86" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="D15" s="86" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="E15" s="86" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F15" s="70" t="n">
         <v>1</v>
@@ -32024,19 +32104,19 @@
     </row>
     <row r="16" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="85" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B16" s="85" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C16" s="86" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D16" s="86" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E16" s="86" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="F16" s="70" t="n">
         <v>3</v>
@@ -32080,7 +32160,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="33" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>

--- a/pesm-pantanal-norte/dados/Matriz_SWOT_PESM_Pantanal_Norte.xlsx
+++ b/pesm-pantanal-norte/dados/Matriz_SWOT_PESM_Pantanal_Norte.xlsx
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="357">
   <si>
     <t xml:space="preserve">MATRIZ SWOT DO PERFIL ECONÔMICO-PRODUTIVO SETORIAL MUNICIPAL (PESM) — PANTANAL NORTE</t>
   </si>
@@ -1087,6 +1087,21 @@
     <t xml:space="preserve">Série de focos de 2023–2024 com quebra de escala (total de MT passa de ~30 mil para 0,7–1,7 milhão/ano): usar só para comparar municípios dentro do mesmo ano. d5_energia.csv mostra consumo industrial alto em Poconé (46%) e N. Sra. do Livramento (43%), ligado à mineração de ouro, não à agroindústria.</t>
   </si>
   <si>
+    <t xml:space="preserve">OP-03 (conferência)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d2_ig_ativos.csv (UCs e TIs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Área de unidades de conservação e terras indígenas por município, usada como evidência do OP-03. Notas mantidas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A coluna flag_cobertura_ig_pantanal é verdadeira para os 13 municípios e falsa para os demais: só repete o recorte do grupo e não foi usada.</t>
+  </si>
+  <si>
     <t xml:space="preserve">PARÂMETROS</t>
   </si>
   <si>
@@ -1318,7 +1333,7 @@
     <t xml:space="preserve">Expansão do turismo de natureza, pesca esportiva e ecoturismo</t>
   </si>
   <si>
-    <t xml:space="preserve">SEDEC-MT; Cadastur; pesquisa de campo. Evidências: Transpantaneira (Poconé), Festival Internacional de Pesca e hidrovia (Cáceres), pesca esportiva e pousadas no rio Cuiabá (Barão de Melgaço, Sto. Antônio do Leverger); águas termais (Juscimeira); turismo de negócios e Cidade de Pedra (Rondonópolis).</t>
+    <t xml:space="preserve">SEDEC-MT; Cadastur; pesquisa de campo. Evidências: Transpantaneira (Poconé), Festival Internacional de Pesca e hidrovia (Cáceres), pesca esportiva e pousadas no rio Cuiabá (Barão de Melgaço, Sto. Antônio do Leverger); águas termais (Juscimeira); turismo de negócios e Cidade de Pedra (Rondonópolis). | Dados (d2_ig_ativos.csv, 2019): unidades de conservação em Poconé (3 UCs, 196,7 mil ha), Cáceres (4 UCs, 117,2 mil ha), Barão de Melgaço (2 UCs, 47,4 mil ha), Porto Esperidião (32,9 mil ha) e Rondonópolis (6,4 mil ha); sem UCs em Curvelândia, Glória D'Oeste, Itiquira, Juscimeira, Lambari D'Oeste, Mirassol D'Oeste e Livramento. Confirma as notas atuais.</t>
   </si>
   <si>
     <t xml:space="preserve">OP-04</t>
@@ -2678,7 +2693,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B2" s="1" t="n">
         <f aca="false">IFERROR(MATCH($B$1,'Indicadores (F-W)'!$A$4:$AM$4,0),"")</f>
@@ -2687,7 +2702,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B3" s="1" t="n">
         <f aca="false">IFERROR(MATCH($B$1,'Fatores Externos (O-A)'!$A$4:$R$4,0),"")</f>
@@ -2699,7 +2714,7 @@
         <v>59</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>102</v>
@@ -2708,16 +2723,16 @@
         <v>31</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>59</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>67</v>
@@ -2726,16 +2741,16 @@
         <v>33</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3539,12 +3554,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4937,7 +4952,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -4983,12 +4998,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6381,7 +6396,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -6427,12 +6442,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7825,7 +7840,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -7871,12 +7886,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9269,7 +9284,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -9315,12 +9330,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10713,7 +10728,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -10759,12 +10774,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12157,7 +12172,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -12203,12 +12218,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13601,7 +13616,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -13647,12 +13662,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15045,7 +15060,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -15091,12 +15106,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16489,7 +16504,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -17356,12 +17371,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18754,7 +18769,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -18800,12 +18815,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20198,7 +20213,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -20244,12 +20259,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21642,7 +21657,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -21688,12 +21703,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23086,7 +23101,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -28528,7 +28543,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
@@ -28967,6 +28982,23 @@
       </c>
       <c r="E38" s="58" t="s">
         <v>223</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="58" t="s">
+        <v>224</v>
+      </c>
+      <c r="B39" s="58" t="s">
+        <v>225</v>
+      </c>
+      <c r="C39" s="58" t="s">
+        <v>226</v>
+      </c>
+      <c r="D39" s="58" t="s">
+        <v>227</v>
+      </c>
+      <c r="E39" s="58" t="s">
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -29001,23 +29033,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="47" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="40" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B3" s="63" t="n">
         <v>0.1</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="40" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B4" s="64" t="n">
         <v>2</v>
@@ -29025,18 +29057,18 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="40" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B5" s="65" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29163,12 +29195,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29176,40 +29208,40 @@
         <v>59</v>
       </c>
       <c r="B4" s="66" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C4" s="66" t="s">
         <v>60</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E4" s="66" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="F4" s="66" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="G4" s="66" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="H4" s="66" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="I4" s="66" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="J4" s="66" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="K4" s="66" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="L4" s="66" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="M4" s="66" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="N4" s="66" t="s">
         <v>46</v>
@@ -29279,79 +29311,79 @@
       <c r="L5" s="66"/>
       <c r="M5" s="66"/>
       <c r="N5" s="67" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="O5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="P5" s="67" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="Q5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="R5" s="67" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="S5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="T5" s="67" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="U5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="V5" s="67" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="W5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="X5" s="67" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="Y5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="Z5" s="67" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="AA5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AB5" s="67" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="AC5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AD5" s="67" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="AE5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AF5" s="67" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="AG5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AH5" s="67" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="AI5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AJ5" s="67" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="AK5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AL5" s="67" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="AM5" s="67" t="s">
         <v>102</v>
@@ -29359,28 +29391,28 @@
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="68" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B6" s="69" t="s">
         <v>74</v>
       </c>
       <c r="C6" s="69" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="D6" s="68" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="E6" s="70" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F6" s="69" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="G6" s="70" t="n">
         <v>2021</v>
       </c>
       <c r="H6" s="70" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I6" s="71" t="n">
         <v>1</v>
@@ -29499,22 +29531,22 @@
         <v>74</v>
       </c>
       <c r="C7" s="69" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="D7" s="68" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="E7" s="70" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F7" s="69" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="G7" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H7" s="70" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="I7" s="71" t="n">
         <v>5602.9</v>
@@ -29629,22 +29661,22 @@
         <v>74</v>
       </c>
       <c r="C8" s="69" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="D8" s="68" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E8" s="70" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F8" s="69" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="G8" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H8" s="70" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="I8" s="71" t="n">
         <v>3.79</v>
@@ -29759,20 +29791,20 @@
         <v>74</v>
       </c>
       <c r="C9" s="69" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D9" s="68" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E9" s="70" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F9" s="69" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="G9" s="70"/>
       <c r="H9" s="70" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="I9" s="71"/>
       <c r="J9" s="71"/>
@@ -29859,20 +29891,20 @@
         <v>74</v>
       </c>
       <c r="C10" s="69" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D10" s="68" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E10" s="70" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F10" s="69" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="G10" s="70"/>
       <c r="H10" s="70" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="I10" s="71"/>
       <c r="J10" s="71"/>
@@ -29953,28 +29985,28 @@
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="75" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="B11" s="76" t="s">
         <v>76</v>
       </c>
       <c r="C11" s="76" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D11" s="75" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="E11" s="70" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F11" s="76" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="G11" s="70" t="n">
         <v>2021</v>
       </c>
       <c r="H11" s="70" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I11" s="71" t="n">
         <v>1</v>
@@ -30093,22 +30125,22 @@
         <v>76</v>
       </c>
       <c r="C12" s="76" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D12" s="75" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E12" s="70" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F12" s="76" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="G12" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H12" s="70" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="I12" s="71" t="n">
         <v>36.92</v>
@@ -30223,22 +30255,22 @@
         <v>76</v>
       </c>
       <c r="C13" s="76" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="D13" s="75" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="E13" s="70" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F13" s="76" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="G13" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H13" s="70" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="I13" s="71" t="n">
         <v>2956.72</v>
@@ -30347,28 +30379,28 @@
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="77" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B14" s="78" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C14" s="78" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="D14" s="77" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="E14" s="70" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F14" s="78" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="G14" s="70" t="n">
         <v>2021</v>
       </c>
       <c r="H14" s="70" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I14" s="71" t="n">
         <v>1</v>
@@ -30484,25 +30516,25 @@
         <v>194</v>
       </c>
       <c r="B15" s="78" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C15" s="78" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="D15" s="77" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E15" s="70" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F15" s="78" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="G15" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H15" s="70" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="I15" s="71" t="n">
         <v>38.11</v>
@@ -30614,25 +30646,25 @@
         <v>158</v>
       </c>
       <c r="B16" s="78" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C16" s="78" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D16" s="77" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="E16" s="70" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F16" s="78" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="G16" s="70" t="n">
         <v>2021</v>
       </c>
       <c r="H16" s="70" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="I16" s="71" t="n">
         <v>33.22</v>
@@ -30744,25 +30776,25 @@
         <v>142</v>
       </c>
       <c r="B17" s="80" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C17" s="80" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="D17" s="79" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="E17" s="70" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F17" s="80" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="G17" s="70" t="n">
         <v>2023</v>
       </c>
       <c r="H17" s="70" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="I17" s="71" t="n">
         <v>74620.05</v>
@@ -30874,25 +30906,25 @@
         <v>138</v>
       </c>
       <c r="B18" s="80" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C18" s="80" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D18" s="79" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E18" s="70" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="F18" s="80" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="G18" s="70" t="n">
         <v>2021</v>
       </c>
       <c r="H18" s="70" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="I18" s="71" t="n">
         <v>11.89</v>
@@ -31004,25 +31036,25 @@
         <v>199</v>
       </c>
       <c r="B19" s="80" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C19" s="80" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="D19" s="79" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E19" s="70" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F19" s="80" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G19" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H19" s="70" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="I19" s="71" t="n">
         <v>31.51</v>
@@ -31134,25 +31166,25 @@
         <v>202</v>
       </c>
       <c r="B20" s="80" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C20" s="80" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="D20" s="79" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E20" s="70" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="F20" s="80" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="G20" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H20" s="70" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="I20" s="83" t="n">
         <v>0.1254</v>
@@ -31264,25 +31296,25 @@
         <v>160</v>
       </c>
       <c r="B21" s="80" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C21" s="80" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="D21" s="79" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E21" s="70" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F21" s="80" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="G21" s="70" t="n">
         <v>2022</v>
       </c>
       <c r="H21" s="70" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="I21" s="71" t="n">
         <v>18.24</v>
@@ -31391,7 +31423,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="33" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -31473,12 +31505,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31489,13 +31521,13 @@
         <v>67</v>
       </c>
       <c r="C4" s="84" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="D4" s="84" t="s">
         <v>66</v>
       </c>
       <c r="E4" s="84" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="F4" s="84" t="s">
         <v>46</v>
@@ -31539,24 +31571,24 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C6" s="28" t="s">
         <v>74</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="F6" s="70" t="n">
         <v>1</v>
@@ -31600,19 +31632,19 @@
     </row>
     <row r="7" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C7" s="28" t="s">
         <v>74</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="F7" s="70" t="n">
         <v>3</v>
@@ -31656,19 +31688,19 @@
     </row>
     <row r="8" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="F8" s="70" t="n">
         <v>3</v>
@@ -31712,19 +31744,19 @@
     </row>
     <row r="9" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C9" s="28" t="s">
         <v>76</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="F9" s="70" t="n">
         <v>0</v>
@@ -31768,19 +31800,19 @@
     </row>
     <row r="10" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F10" s="70" t="n">
         <v>1</v>
@@ -31824,19 +31856,19 @@
     </row>
     <row r="11" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="F11" s="70" t="n">
         <v>2</v>
@@ -31880,19 +31912,19 @@
     </row>
     <row r="12" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="85" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B12" s="85" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C12" s="86" t="s">
         <v>74</v>
       </c>
       <c r="D12" s="86" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="E12" s="86" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="F12" s="70" t="n">
         <v>3</v>
@@ -31936,19 +31968,19 @@
     </row>
     <row r="13" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="85" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B13" s="85" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C13" s="86" t="s">
         <v>74</v>
       </c>
       <c r="D13" s="86" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E13" s="86" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F13" s="70" t="n">
         <v>2</v>
@@ -31992,19 +32024,19 @@
     </row>
     <row r="14" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="85" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B14" s="85" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C14" s="86" t="s">
         <v>74</v>
       </c>
       <c r="D14" s="86" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E14" s="86" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="F14" s="70" t="n">
         <v>3</v>
@@ -32048,19 +32080,19 @@
     </row>
     <row r="15" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="85" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B15" s="85" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C15" s="86" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="D15" s="86" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E15" s="86" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="F15" s="70" t="n">
         <v>1</v>
@@ -32104,19 +32136,19 @@
     </row>
     <row r="16" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="85" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B16" s="85" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C16" s="86" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="D16" s="86" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="E16" s="86" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="F16" s="70" t="n">
         <v>3</v>
@@ -32160,7 +32192,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="33" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>

--- a/pesm-pantanal-norte/dados/Matriz_SWOT_PESM_Pantanal_Norte.xlsx
+++ b/pesm-pantanal-norte/dados/Matriz_SWOT_PESM_Pantanal_Norte.xlsx
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="362">
   <si>
     <t xml:space="preserve">MATRIZ SWOT DO PERFIL ECONÔMICO-PRODUTIVO SETORIAL MUNICIPAL (PESM) — PANTANAL NORTE</t>
   </si>
@@ -1102,6 +1102,21 @@
     <t xml:space="preserve">A coluna flag_cobertura_ig_pantanal é verdadeira para os 13 municípios e falsa para os demais: só repete o recorte do grupo e não foi usada.</t>
   </si>
   <si>
+    <t xml:space="preserve">AM-01 (conferência)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2000–2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d4_uso_terra.csv (MapBiomas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variação da superfície de água por município, usada como evidência de seca prolongada. Notas mantidas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recebidos também d4_painel_pam.csv (mesmos dados de desmatamento e focos, inclusive a quebra de 2023) e novas cópias idênticas de d1_painel_pesm, d3_painel_psdm e d5_painel_pim.</t>
+  </si>
+  <si>
     <t xml:space="preserve">PARÂMETROS</t>
   </si>
   <si>
@@ -1372,7 +1387,7 @@
     <t xml:space="preserve">Eventos climáticos extremos: secas prolongadas e incêndios no Pantanal</t>
   </si>
   <si>
-    <t xml:space="preserve">INPE – BDQueimadas; MapBiomas; Cemaden. Evidências: incêndios de 2024 – Cáceres ≈87 mil ha, Poconé ≈61,5 mil ha, Barão de Melgaço ≈2,6 mil ha (Bombeiros-MT/INPE); 2020 foi o pior ano da série no Pantanal; ≈95% dos focos de 2024 começaram em propriedades privadas. Planície pantaneira = exposição alta. | Dados (d4_queimadas.csv, 2013–2022; a série de 2023–2024 muda de escala e não foi usada): focos por mil km²/ano — Barão de Melgaço 64,5; Poconé 51,4; Sto. Antônio do Leverger 34,1; N. Sra. do Livramento 30,7; Cáceres 25,4; MT 30,9; demais abaixo de 17.</t>
+    <t xml:space="preserve">INPE – BDQueimadas; MapBiomas; Cemaden. Evidências: incêndios de 2024 – Cáceres ≈87 mil ha, Poconé ≈61,5 mil ha, Barão de Melgaço ≈2,6 mil ha (Bombeiros-MT/INPE); 2020 foi o pior ano da série no Pantanal; ≈95% dos focos de 2024 começaram em propriedades privadas. Planície pantaneira = exposição alta. | Dados (d4_queimadas.csv, 2013–2022; a série de 2023–2024 muda de escala e não foi usada): focos por mil km²/ano — Barão de Melgaço 64,5; Poconé 51,4; Sto. Antônio do Leverger 34,1; N. Sra. do Livramento 30,7; Cáceres 25,4; MT 30,9; demais abaixo de 17. | Dados (d4_uso_terra.csv, MapBiomas 2000–2021): superfície de água caiu 63% em Cáceres (3.335 → 1.245 km²), 46% em Sto. Antônio do Leverger, 40% em Poconé e 13% em Barão de Melgaço; MT −29%. Confirma as notas atuais.</t>
   </si>
   <si>
     <t xml:space="preserve">AM-02</t>
@@ -2693,7 +2708,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B2" s="1" t="n">
         <f aca="false">IFERROR(MATCH($B$1,'Indicadores (F-W)'!$A$4:$AM$4,0),"")</f>
@@ -2702,7 +2717,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B3" s="1" t="n">
         <f aca="false">IFERROR(MATCH($B$1,'Fatores Externos (O-A)'!$A$4:$R$4,0),"")</f>
@@ -2714,7 +2729,7 @@
         <v>59</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>102</v>
@@ -2723,16 +2738,16 @@
         <v>31</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>59</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>67</v>
@@ -2741,16 +2756,16 @@
         <v>33</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3554,12 +3569,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4952,7 +4967,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -4998,12 +5013,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6396,7 +6411,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -6442,12 +6457,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7840,7 +7855,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -7886,12 +7901,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9284,7 +9299,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -9330,12 +9345,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10728,7 +10743,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -10774,12 +10789,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12172,7 +12187,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -12218,12 +12233,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13616,7 +13631,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -13662,12 +13677,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15060,7 +15075,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -15106,12 +15121,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16504,7 +16519,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -17371,12 +17386,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18769,7 +18784,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -18815,12 +18830,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20213,7 +20228,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -20259,12 +20274,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21657,7 +21672,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -21703,12 +21718,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="91" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23101,7 +23116,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="33" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -28543,7 +28558,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
@@ -28999,6 +29014,23 @@
       </c>
       <c r="E39" s="58" t="s">
         <v>228</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="58" t="s">
+        <v>229</v>
+      </c>
+      <c r="B40" s="58" t="s">
+        <v>230</v>
+      </c>
+      <c r="C40" s="58" t="s">
+        <v>231</v>
+      </c>
+      <c r="D40" s="58" t="s">
+        <v>232</v>
+      </c>
+      <c r="E40" s="58" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -29033,23 +29065,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="47" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="40" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B3" s="63" t="n">
         <v>0.1</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="40" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B4" s="64" t="n">
         <v>2</v>
@@ -29057,18 +29089,18 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="40" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B5" s="65" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29195,12 +29227,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29208,40 +29240,40 @@
         <v>59</v>
       </c>
       <c r="B4" s="66" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C4" s="66" t="s">
         <v>60</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E4" s="66" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="F4" s="66" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="G4" s="66" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="H4" s="66" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="I4" s="66" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="J4" s="66" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="K4" s="66" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="L4" s="66" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="M4" s="66" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="N4" s="66" t="s">
         <v>46</v>
@@ -29311,79 +29343,79 @@
       <c r="L5" s="66"/>
       <c r="M5" s="66"/>
       <c r="N5" s="67" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="O5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="P5" s="67" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="Q5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="R5" s="67" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="S5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="T5" s="67" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="U5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="V5" s="67" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="W5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="X5" s="67" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="Y5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="Z5" s="67" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="AA5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AB5" s="67" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="AC5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AD5" s="67" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="AE5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AF5" s="67" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="AG5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AH5" s="67" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="AI5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AJ5" s="67" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="AK5" s="67" t="s">
         <v>102</v>
       </c>
       <c r="AL5" s="67" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="AM5" s="67" t="s">
         <v>102</v>
@@ -29391,28 +29423,28 @@
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="68" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B6" s="69" t="s">
         <v>74</v>
       </c>
       <c r="C6" s="69" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="D6" s="68" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="E6" s="70" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F6" s="69" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="G6" s="70" t="n">
         <v>2021</v>
       </c>
       <c r="H6" s="70" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="I6" s="71" t="n">
         <v>1</v>
@@ -29531,22 +29563,22 @@
         <v>74</v>
       </c>
       <c r="C7" s="69" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="D7" s="68" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="E7" s="70" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F7" s="69" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="G7" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H7" s="70" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I7" s="71" t="n">
         <v>5602.9</v>
@@ -29661,22 +29693,22 @@
         <v>74</v>
       </c>
       <c r="C8" s="69" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D8" s="68" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E8" s="70" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F8" s="69" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="G8" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H8" s="70" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="I8" s="71" t="n">
         <v>3.79</v>
@@ -29791,20 +29823,20 @@
         <v>74</v>
       </c>
       <c r="C9" s="69" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="D9" s="68" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E9" s="70" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F9" s="69" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="G9" s="70"/>
       <c r="H9" s="70" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="I9" s="71"/>
       <c r="J9" s="71"/>
@@ -29891,20 +29923,20 @@
         <v>74</v>
       </c>
       <c r="C10" s="69" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D10" s="68" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="E10" s="70" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F10" s="69" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="G10" s="70"/>
       <c r="H10" s="70" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I10" s="71"/>
       <c r="J10" s="71"/>
@@ -29985,28 +30017,28 @@
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="75" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B11" s="76" t="s">
         <v>76</v>
       </c>
       <c r="C11" s="76" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="D11" s="75" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="E11" s="70" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F11" s="76" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="G11" s="70" t="n">
         <v>2021</v>
       </c>
       <c r="H11" s="70" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="I11" s="71" t="n">
         <v>1</v>
@@ -30125,22 +30157,22 @@
         <v>76</v>
       </c>
       <c r="C12" s="76" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="D12" s="75" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E12" s="70" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F12" s="76" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="G12" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H12" s="70" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="I12" s="71" t="n">
         <v>36.92</v>
@@ -30255,22 +30287,22 @@
         <v>76</v>
       </c>
       <c r="C13" s="76" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="D13" s="75" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="E13" s="70" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F13" s="76" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="G13" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H13" s="70" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I13" s="71" t="n">
         <v>2956.72</v>
@@ -30379,28 +30411,28 @@
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="77" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B14" s="78" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C14" s="78" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="D14" s="77" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="E14" s="70" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F14" s="78" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="G14" s="70" t="n">
         <v>2021</v>
       </c>
       <c r="H14" s="70" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="I14" s="71" t="n">
         <v>1</v>
@@ -30516,25 +30548,25 @@
         <v>194</v>
       </c>
       <c r="B15" s="78" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C15" s="78" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="D15" s="77" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E15" s="70" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F15" s="78" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="G15" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H15" s="70" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="I15" s="71" t="n">
         <v>38.11</v>
@@ -30646,25 +30678,25 @@
         <v>158</v>
       </c>
       <c r="B16" s="78" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C16" s="78" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D16" s="77" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="E16" s="70" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F16" s="78" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="G16" s="70" t="n">
         <v>2021</v>
       </c>
       <c r="H16" s="70" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I16" s="71" t="n">
         <v>33.22</v>
@@ -30776,25 +30808,25 @@
         <v>142</v>
       </c>
       <c r="B17" s="80" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C17" s="80" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="D17" s="79" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="E17" s="70" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F17" s="80" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="G17" s="70" t="n">
         <v>2023</v>
       </c>
       <c r="H17" s="70" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I17" s="71" t="n">
         <v>74620.05</v>
@@ -30906,25 +30938,25 @@
         <v>138</v>
       </c>
       <c r="B18" s="80" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C18" s="80" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="D18" s="79" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E18" s="70" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="F18" s="80" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="G18" s="70" t="n">
         <v>2021</v>
       </c>
       <c r="H18" s="70" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="I18" s="71" t="n">
         <v>11.89</v>
@@ -31036,25 +31068,25 @@
         <v>199</v>
       </c>
       <c r="B19" s="80" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C19" s="80" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="D19" s="79" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="E19" s="70" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F19" s="80" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="G19" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H19" s="70" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I19" s="71" t="n">
         <v>31.51</v>
@@ -31166,25 +31198,25 @@
         <v>202</v>
       </c>
       <c r="B20" s="80" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C20" s="80" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="D20" s="79" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="E20" s="70" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="F20" s="80" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="G20" s="70" t="n">
         <v>2024</v>
       </c>
       <c r="H20" s="70" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I20" s="83" t="n">
         <v>0.1254</v>
@@ -31296,25 +31328,25 @@
         <v>160</v>
       </c>
       <c r="B21" s="80" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C21" s="80" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="D21" s="79" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E21" s="70" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F21" s="80" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="G21" s="70" t="n">
         <v>2022</v>
       </c>
       <c r="H21" s="70" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="I21" s="71" t="n">
         <v>18.24</v>
@@ -31423,7 +31455,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="33" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -31505,12 +31537,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31521,13 +31553,13 @@
         <v>67</v>
       </c>
       <c r="C4" s="84" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="D4" s="84" t="s">
         <v>66</v>
       </c>
       <c r="E4" s="84" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="F4" s="84" t="s">
         <v>46</v>
@@ -31571,24 +31603,24 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C6" s="28" t="s">
         <v>74</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="F6" s="70" t="n">
         <v>1</v>
@@ -31632,19 +31664,19 @@
     </row>
     <row r="7" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C7" s="28" t="s">
         <v>74</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="F7" s="70" t="n">
         <v>3</v>
@@ -31688,19 +31720,19 @@
     </row>
     <row r="8" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F8" s="70" t="n">
         <v>3</v>
@@ -31744,19 +31776,19 @@
     </row>
     <row r="9" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C9" s="28" t="s">
         <v>76</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="F9" s="70" t="n">
         <v>0</v>
@@ -31800,19 +31832,19 @@
     </row>
     <row r="10" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="F10" s="70" t="n">
         <v>1</v>
@@ -31856,19 +31888,19 @@
     </row>
     <row r="11" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="F11" s="70" t="n">
         <v>2</v>
@@ -31912,19 +31944,19 @@
     </row>
     <row r="12" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="85" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B12" s="85" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C12" s="86" t="s">
         <v>74</v>
       </c>
       <c r="D12" s="86" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E12" s="86" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="F12" s="70" t="n">
         <v>3</v>
@@ -31968,19 +32000,19 @@
     </row>
     <row r="13" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="85" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B13" s="85" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C13" s="86" t="s">
         <v>74</v>
       </c>
       <c r="D13" s="86" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="E13" s="86" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="F13" s="70" t="n">
         <v>2</v>
@@ -32024,19 +32056,19 @@
     </row>
     <row r="14" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="85" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B14" s="85" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C14" s="86" t="s">
         <v>74</v>
       </c>
       <c r="D14" s="86" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="E14" s="86" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="F14" s="70" t="n">
         <v>3</v>
@@ -32080,19 +32112,19 @@
     </row>
     <row r="15" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="85" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B15" s="85" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C15" s="86" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="D15" s="86" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="E15" s="86" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="F15" s="70" t="n">
         <v>1</v>
@@ -32136,19 +32168,19 @@
     </row>
     <row r="16" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="85" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B16" s="85" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C16" s="86" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="D16" s="86" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="E16" s="86" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="F16" s="70" t="n">
         <v>3</v>
@@ -32192,7 +32224,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="33" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>
